--- a/input/ES/reg_wages.xlsx
+++ b/input/ES/reg_wages.xlsx
@@ -384,73 +384,73 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>0.031507016670039072</v>
+        <v>0.025696420185059358</v>
       </c>
       <c r="C2">
-        <v>5.4896633202278477e-06</v>
+        <v>3.2975039681769835e-06</v>
       </c>
       <c r="D2">
-        <v>-6.105905765363309e-08</v>
+        <v>-3.6529812395758479e-08</v>
       </c>
       <c r="E2">
-        <v>6.5287046549768611e-06</v>
+        <v>3.8134397798468078e-06</v>
       </c>
       <c r="F2">
-        <v>1.044325109017544e-06</v>
+        <v>1.1283716607503379e-07</v>
       </c>
       <c r="G2">
-        <v>-1.3632767535443971e-07</v>
+        <v>-8.024408023972643e-08</v>
       </c>
       <c r="H2">
-        <v>-2.3844959197648904e-08</v>
+        <v>-6.8250074294380194e-09</v>
       </c>
       <c r="I2">
-        <v>2.9648179256257129e-07</v>
+        <v>3.5764024527174491e-07</v>
       </c>
       <c r="J2">
-        <v>1.1966682617632075e-06</v>
+        <v>9.0310592838376997e-07</v>
       </c>
       <c r="K2">
-        <v>1.3833037118556151e-06</v>
+        <v>1.0197007572277122e-06</v>
       </c>
       <c r="L2">
-        <v>2.6238626936790982e-06</v>
+        <v>1.752819666886691e-06</v>
       </c>
       <c r="M2">
-        <v>5.0154540726717311e-08</v>
+        <v>1.3864298727483544e-07</v>
       </c>
       <c r="N2">
-        <v>2.0373711396292427e-07</v>
+        <v>3.2017440313383282e-07</v>
       </c>
       <c r="O2">
-        <v>1.9008843174109408e-09</v>
+        <v>1.142212658762969e-07</v>
       </c>
       <c r="P2">
-        <v>3.3938553949578643e-07</v>
+        <v>3.341249343141725e-07</v>
       </c>
       <c r="Q2">
-        <v>-2.0522002587249941e-07</v>
+        <v>1.0958239262944224e-08</v>
       </c>
       <c r="R2">
-        <v>-1.9407467033212193e-07</v>
+        <v>-3.8139965223970614e-08</v>
       </c>
       <c r="S2">
-        <v>4.1054035937742777e-07</v>
+        <v>-3.7161572841632485e-08</v>
       </c>
       <c r="T2">
-        <v>1.5746586652108136e-08</v>
+        <v>8.9567784602453331e-08</v>
       </c>
       <c r="U2">
-        <v>-2.16106664356873e-07</v>
+        <v>-4.3050807129335377e-07</v>
       </c>
       <c r="V2">
-        <v>-3.8845637762585339e-07</v>
+        <v>-4.3886414477833709e-07</v>
       </c>
       <c r="W2">
-        <v>-0.00012232323612427145</v>
+        <v>-8.1948005135246106e-05</v>
       </c>
       <c r="X2">
-        <v>6.4506150478479551e-06</v>
+        <v>4.0370232315436746e-06</v>
       </c>
     </row>
     <row r="3">
@@ -458,73 +458,73 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>-0.0001435707537429895</v>
+        <v>-8.8913982016396769e-05</v>
       </c>
       <c r="C3">
-        <v>-6.105905765363309e-08</v>
+        <v>-3.6529812395758479e-08</v>
       </c>
       <c r="D3">
-        <v>7.059133906768941e-10</v>
+        <v>4.1973120484063419e-10</v>
       </c>
       <c r="E3">
-        <v>2.3742682595459607e-08</v>
+        <v>1.3039625982074321e-08</v>
       </c>
       <c r="F3">
-        <v>8.7853345024573637e-08</v>
+        <v>5.5741750235237881e-08</v>
       </c>
       <c r="G3">
-        <v>-7.2287876392558779e-10</v>
+        <v>-3.8173297851703347e-10</v>
       </c>
       <c r="H3">
-        <v>-2.0475693390157772e-09</v>
+        <v>-1.2333690609531079e-09</v>
       </c>
       <c r="I3">
-        <v>-2.8105408664196555e-09</v>
+        <v>-4.0520286944204514e-09</v>
       </c>
       <c r="J3">
-        <v>-1.198387575505797e-08</v>
+        <v>-9.6805696241493437e-09</v>
       </c>
       <c r="K3">
-        <v>-1.0902780960255308e-08</v>
+        <v>-9.0386324349088642e-09</v>
       </c>
       <c r="L3">
-        <v>-1.9581115567673754e-08</v>
+        <v>-1.4122102515186193e-08</v>
       </c>
       <c r="M3">
-        <v>-9.0779187231684427e-10</v>
+        <v>-1.7582652920199261e-09</v>
       </c>
       <c r="N3">
-        <v>-2.4103943182396168e-09</v>
+        <v>-3.6751477929240483e-09</v>
       </c>
       <c r="O3">
-        <v>-3.8203519670049382e-10</v>
+        <v>-1.5255190061157289e-09</v>
       </c>
       <c r="P3">
-        <v>-3.6631833765851676e-09</v>
+        <v>-3.6367402927319189e-09</v>
       </c>
       <c r="Q3">
-        <v>2.6454199638090761e-09</v>
+        <v>5.4656640424326504e-11</v>
       </c>
       <c r="R3">
-        <v>2.8249235613673977e-09</v>
+        <v>7.5094641308874071e-10</v>
       </c>
       <c r="S3">
-        <v>-1.4278994513455447e-09</v>
+        <v>9.9371006257775301e-10</v>
       </c>
       <c r="T3">
-        <v>-3.0187921915712677e-10</v>
+        <v>-1.5064205468023872e-09</v>
       </c>
       <c r="U3">
-        <v>2.7461497853514081e-09</v>
+        <v>6.1127464348943115e-09</v>
       </c>
       <c r="V3">
-        <v>5.0476800561438572e-09</v>
+        <v>6.2173691225822712e-09</v>
       </c>
       <c r="W3">
-        <v>1.3167085971505099e-06</v>
+        <v>9.2675456231938234e-07</v>
       </c>
       <c r="X3">
-        <v>-7.2908006248319516e-08</v>
+        <v>-4.4930703899308752e-08</v>
       </c>
     </row>
     <row r="4">
@@ -532,73 +532,73 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>-0.098776577314864222</v>
+        <v>-0.11343046949276511</v>
       </c>
       <c r="C4">
-        <v>6.5287046549768611e-06</v>
+        <v>3.8134397798468078e-06</v>
       </c>
       <c r="D4">
-        <v>2.3742682595459607e-08</v>
+        <v>1.3039625982074321e-08</v>
       </c>
       <c r="E4">
-        <v>0.0011942376687430654</v>
+        <v>0.00070919912071874716</v>
       </c>
       <c r="F4">
-        <v>0.00040124040240732944</v>
+        <v>0.00023356271206436403</v>
       </c>
       <c r="G4">
-        <v>-2.5366411673344198e-05</v>
+        <v>-1.4948598237245384e-05</v>
       </c>
       <c r="H4">
-        <v>-8.6669314453410481e-06</v>
+        <v>-5.0013452777215388e-06</v>
       </c>
       <c r="I4">
-        <v>-1.5782409906760757e-06</v>
+        <v>8.4080989935792137e-07</v>
       </c>
       <c r="J4">
-        <v>-5.7451542378527661e-06</v>
+        <v>-2.7413066161234023e-06</v>
       </c>
       <c r="K4">
-        <v>-7.2450187027687709e-06</v>
+        <v>-3.5284807172009454e-06</v>
       </c>
       <c r="L4">
-        <v>-1.2310131253398271e-06</v>
+        <v>1.045490110851464e-08</v>
       </c>
       <c r="M4">
-        <v>3.9382679235925511e-06</v>
+        <v>2.3005580802923954e-06</v>
       </c>
       <c r="N4">
-        <v>5.0714192180235123e-06</v>
+        <v>2.3265125389912814e-06</v>
       </c>
       <c r="O4">
-        <v>2.7208827461459721e-06</v>
+        <v>1.278156403751324e-06</v>
       </c>
       <c r="P4">
-        <v>8.2904898571586624e-07</v>
+        <v>7.0587358472521583e-07</v>
       </c>
       <c r="Q4">
-        <v>-1.5316022443702719e-06</v>
+        <v>-7.6302690183408902e-07</v>
       </c>
       <c r="R4">
-        <v>1.8151767928325719e-06</v>
+        <v>1.0067700657887708e-06</v>
       </c>
       <c r="S4">
-        <v>-2.7765345965708148e-06</v>
+        <v>-2.0678765079626196e-06</v>
       </c>
       <c r="T4">
-        <v>7.6610834004403728e-08</v>
+        <v>3.0613904650882423e-07</v>
       </c>
       <c r="U4">
-        <v>1.9349580566708759e-06</v>
+        <v>6.5105715053470193e-07</v>
       </c>
       <c r="V4">
-        <v>-1.7128513730655725e-06</v>
+        <v>-1.2759035791928479e-06</v>
       </c>
       <c r="W4">
-        <v>-0.00034859511753136316</v>
+        <v>-0.00023009096026126906</v>
       </c>
       <c r="X4">
-        <v>-1.9563296528301664e-05</v>
+        <v>-1.1341283837345014e-05</v>
       </c>
     </row>
     <row r="5">
@@ -606,73 +606,73 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>0.0064899718545356078</v>
+        <v>0.046824045938554777</v>
       </c>
       <c r="C5">
-        <v>1.044325109017544e-06</v>
+        <v>1.1283716607503379e-07</v>
       </c>
       <c r="D5">
-        <v>8.7853345024573637e-08</v>
+        <v>5.5741750235237881e-08</v>
       </c>
       <c r="E5">
-        <v>0.00040124040240732944</v>
+        <v>0.00023356271206436403</v>
       </c>
       <c r="F5">
-        <v>0.0011856574417009526</v>
+        <v>0.00073661597848024261</v>
       </c>
       <c r="G5">
-        <v>-8.7935244214656616e-06</v>
+        <v>-5.0643292157262754e-06</v>
       </c>
       <c r="H5">
-        <v>-2.4451866801306279e-05</v>
+        <v>-1.5061695869096753e-05</v>
       </c>
       <c r="I5">
-        <v>-4.045439192660458e-06</v>
+        <v>-2.5688894739788384e-06</v>
       </c>
       <c r="J5">
-        <v>-1.6276720661828083e-05</v>
+        <v>-1.1196877800254609e-05</v>
       </c>
       <c r="K5">
-        <v>-1.9117871524796006e-05</v>
+        <v>-1.2843871475047249e-05</v>
       </c>
       <c r="L5">
-        <v>-8.1361946546195966e-06</v>
+        <v>-6.7142440201013043e-06</v>
       </c>
       <c r="M5">
-        <v>3.2609891648901684e-06</v>
+        <v>1.7232189954144349e-06</v>
       </c>
       <c r="N5">
-        <v>-1.6755810882882886e-06</v>
+        <v>-1.686686436667657e-06</v>
       </c>
       <c r="O5">
-        <v>-1.1587993757515621e-05</v>
+        <v>-6.6342444036298734e-06</v>
       </c>
       <c r="P5">
-        <v>-7.4977079012983521e-06</v>
+        <v>-4.2414349194628831e-06</v>
       </c>
       <c r="Q5">
-        <v>-1.9835188945481103e-05</v>
+        <v>-1.1369617532126823e-05</v>
       </c>
       <c r="R5">
-        <v>-8.6710233763946045e-06</v>
+        <v>-5.1746972412528082e-06</v>
       </c>
       <c r="S5">
-        <v>5.5532823288434747e-06</v>
+        <v>1.3786576642619549e-06</v>
       </c>
       <c r="T5">
-        <v>7.2480082789537109e-08</v>
+        <v>4.0984884995767465e-07</v>
       </c>
       <c r="U5">
-        <v>5.1649917180508045e-06</v>
+        <v>2.3364861998721039e-06</v>
       </c>
       <c r="V5">
-        <v>3.3251995052445521e-06</v>
+        <v>1.1289433398846271e-06</v>
       </c>
       <c r="W5">
-        <v>-0.00022069726037048088</v>
+        <v>-0.0001524006388416583</v>
       </c>
       <c r="X5">
-        <v>-1.9536670068393804e-05</v>
+        <v>-1.381490843236969e-05</v>
       </c>
     </row>
     <row r="6">
@@ -680,73 +680,73 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>-0.00625985748722573</v>
+        <v>-0.0059623937203997068</v>
       </c>
       <c r="C6">
-        <v>-1.3632767535443971e-07</v>
+        <v>-8.024408023972643e-08</v>
       </c>
       <c r="D6">
-        <v>-7.2287876392558779e-10</v>
+        <v>-3.8173297851703347e-10</v>
       </c>
       <c r="E6">
-        <v>-2.5366411673344198e-05</v>
+        <v>-1.4948598237245384e-05</v>
       </c>
       <c r="F6">
-        <v>-8.7935244214656616e-06</v>
+        <v>-5.0643292157262754e-06</v>
       </c>
       <c r="G6">
-        <v>5.7055389613202801e-07</v>
+        <v>3.3347564511095149e-07</v>
       </c>
       <c r="H6">
-        <v>2.0179330328936236e-07</v>
+        <v>1.151587337617194e-07</v>
       </c>
       <c r="I6">
-        <v>4.8143373997851835e-08</v>
+        <v>-2.4255309777454766e-08</v>
       </c>
       <c r="J6">
-        <v>1.3090948736561025e-07</v>
+        <v>4.9636289838053165e-08</v>
       </c>
       <c r="K6">
-        <v>2.5184720167662144e-07</v>
+        <v>1.1711422476994188e-07</v>
       </c>
       <c r="L6">
-        <v>1.6058284815307813e-07</v>
+        <v>6.5081523902758838e-08</v>
       </c>
       <c r="M6">
-        <v>-3.2077563384540644e-08</v>
+        <v>-1.9961831057816129e-08</v>
       </c>
       <c r="N6">
-        <v>-7.3182641781367508e-08</v>
+        <v>-3.5275887801187731e-08</v>
       </c>
       <c r="O6">
-        <v>-3.5842036846047712e-08</v>
+        <v>-1.671182211494701e-08</v>
       </c>
       <c r="P6">
-        <v>-3.9663546462319547e-08</v>
+        <v>-2.8219795948845958e-08</v>
       </c>
       <c r="Q6">
-        <v>4.0214415019689442e-08</v>
+        <v>2.1816823366073077e-08</v>
       </c>
       <c r="R6">
-        <v>-5.2992865808523326e-08</v>
+        <v>-2.9309071900597909e-08</v>
       </c>
       <c r="S6">
-        <v>-3.2074693537283943e-08</v>
+        <v>3.1503821667351492e-08</v>
       </c>
       <c r="T6">
-        <v>5.9577368540288884e-10</v>
+        <v>2.2128527109311206e-09</v>
       </c>
       <c r="U6">
-        <v>-3.8727040987091896e-08</v>
+        <v>-2.994253271236064e-08</v>
       </c>
       <c r="V6">
-        <v>4.1899282425971626e-08</v>
+        <v>1.5776979302878209e-08</v>
       </c>
       <c r="W6">
-        <v>6.9901930513384065e-06</v>
+        <v>3.9178240106067675e-06</v>
       </c>
       <c r="X6">
-        <v>3.096886481001305e-07</v>
+        <v>1.5280981299700067e-07</v>
       </c>
     </row>
     <row r="7">
@@ -754,73 +754,73 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>-0.012381235819995794</v>
+        <v>-0.012919196063505355</v>
       </c>
       <c r="C7">
-        <v>-2.3844959197648904e-08</v>
+        <v>-6.8250074294380194e-09</v>
       </c>
       <c r="D7">
-        <v>-2.0475693390157772e-09</v>
+        <v>-1.2333690609531079e-09</v>
       </c>
       <c r="E7">
-        <v>-8.6669314453410481e-06</v>
+        <v>-5.0013452777215388e-06</v>
       </c>
       <c r="F7">
-        <v>-2.4451866801306279e-05</v>
+        <v>-1.5061695869096753e-05</v>
       </c>
       <c r="G7">
-        <v>2.0179330328936236e-07</v>
+        <v>1.151587337617194e-07</v>
       </c>
       <c r="H7">
-        <v>5.3627404663149253e-07</v>
+        <v>3.2689343983341527e-07</v>
       </c>
       <c r="I7">
-        <v>8.5867726686836978e-08</v>
+        <v>4.2490607035674828e-08</v>
       </c>
       <c r="J7">
-        <v>3.4829841937176265e-07</v>
+        <v>2.2308907829895926e-07</v>
       </c>
       <c r="K7">
-        <v>5.5277168887868459e-07</v>
+        <v>3.3631007008296663e-07</v>
       </c>
       <c r="L7">
-        <v>4.0225259294134257e-07</v>
+        <v>2.4995037235956296e-07</v>
       </c>
       <c r="M7">
-        <v>-6.4646286497321161e-09</v>
+        <v>-5.4543774580176689e-09</v>
       </c>
       <c r="N7">
-        <v>1.1952665614494823e-07</v>
+        <v>7.7145377521158658e-08</v>
       </c>
       <c r="O7">
-        <v>1.966468429359607e-07</v>
+        <v>1.0811413766204395e-07</v>
       </c>
       <c r="P7">
-        <v>1.3763746948061823e-07</v>
+        <v>7.5041780804141119e-08</v>
       </c>
       <c r="Q7">
-        <v>3.4693030276664045e-07</v>
+        <v>1.9414465994645628e-07</v>
       </c>
       <c r="R7">
-        <v>1.3787040305771474e-07</v>
+        <v>8.1597653882209219e-08</v>
       </c>
       <c r="S7">
-        <v>-2.7313920362362323e-07</v>
+        <v>-5.3488352977584973e-08</v>
       </c>
       <c r="T7">
-        <v>3.9526641189592505e-09</v>
+        <v>1.366702920055904e-08</v>
       </c>
       <c r="U7">
-        <v>-1.1536486073428865e-07</v>
+        <v>-9.8542793182894399e-08</v>
       </c>
       <c r="V7">
-        <v>-7.0346949501994965e-08</v>
+        <v>-6.3493159269762477e-08</v>
       </c>
       <c r="W7">
-        <v>4.0303100617942011e-06</v>
+        <v>1.0277331053915232e-06</v>
       </c>
       <c r="X7">
-        <v>8.8439868856179938e-08</v>
+        <v>6.4128100646700016e-08</v>
       </c>
     </row>
     <row r="8">
@@ -828,73 +828,73 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>0.025935331540945208</v>
+        <v>-0.05695035937833752</v>
       </c>
       <c r="C8">
-        <v>2.9648179256257129e-07</v>
+        <v>3.5764024527174491e-07</v>
       </c>
       <c r="D8">
-        <v>-2.8105408664196555e-09</v>
+        <v>-4.0520286944204514e-09</v>
       </c>
       <c r="E8">
-        <v>-1.5782409906760757e-06</v>
+        <v>8.4080989935792137e-07</v>
       </c>
       <c r="F8">
-        <v>-4.045439192660458e-06</v>
+        <v>-2.5688894739788384e-06</v>
       </c>
       <c r="G8">
-        <v>4.8143373997851835e-08</v>
+        <v>-2.4255309777454766e-08</v>
       </c>
       <c r="H8">
-        <v>8.5867726686836978e-08</v>
+        <v>4.2490607035674828e-08</v>
       </c>
       <c r="I8">
-        <v>0.0035711347105383262</v>
+        <v>0.0019978313649363045</v>
       </c>
       <c r="J8">
-        <v>0.0030601844654566737</v>
+        <v>0.0016980916101362862</v>
       </c>
       <c r="K8">
-        <v>0.0030617232420029243</v>
+        <v>0.0016986117127408354</v>
       </c>
       <c r="L8">
-        <v>0.0030619441131953</v>
+        <v>0.0016985883913872351</v>
       </c>
       <c r="M8">
-        <v>2.1223542818968062e-06</v>
+        <v>8.1722791458565194e-07</v>
       </c>
       <c r="N8">
-        <v>3.6964110860048218e-06</v>
+        <v>1.8991381061682696e-06</v>
       </c>
       <c r="O8">
-        <v>-1.6527084950269715e-06</v>
+        <v>-4.3603241183414831e-08</v>
       </c>
       <c r="P8">
-        <v>1.8307333810478285e-06</v>
+        <v>1.599250973033335e-06</v>
       </c>
       <c r="Q8">
-        <v>6.706927565306245e-07</v>
+        <v>1.3154260810286157e-07</v>
       </c>
       <c r="R8">
-        <v>-5.2147827901099469e-07</v>
+        <v>-1.3519296256240985e-06</v>
       </c>
       <c r="S8">
-        <v>-6.4464332297358556e-07</v>
+        <v>-2.6690265932160374e-07</v>
       </c>
       <c r="T8">
-        <v>9.639634082922723e-08</v>
+        <v>3.0884058561387618e-07</v>
       </c>
       <c r="U8">
-        <v>-3.3721254358371121e-07</v>
+        <v>-8.8144932168151532e-07</v>
       </c>
       <c r="V8">
-        <v>-1.627237528716606e-06</v>
+        <v>-1.5700449837232645e-06</v>
       </c>
       <c r="W8">
-        <v>-0.0030843405126328031</v>
+        <v>-0.0017395412902696035</v>
       </c>
       <c r="X8">
-        <v>1.0442638059328664e-05</v>
+        <v>6.0638198289440282e-06</v>
       </c>
     </row>
     <row r="9">
@@ -902,73 +902,73 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>0.089620832362745248</v>
+        <v>0.0082652908405317031</v>
       </c>
       <c r="C9">
-        <v>1.1966682617632075e-06</v>
+        <v>9.0310592838376997e-07</v>
       </c>
       <c r="D9">
-        <v>-1.198387575505797e-08</v>
+        <v>-9.6805696241493437e-09</v>
       </c>
       <c r="E9">
-        <v>-5.7451542378527661e-06</v>
+        <v>-2.7413066161234023e-06</v>
       </c>
       <c r="F9">
-        <v>-1.6276720661828083e-05</v>
+        <v>-1.1196877800254609e-05</v>
       </c>
       <c r="G9">
-        <v>1.3090948736561025e-07</v>
+        <v>4.9636289838053165e-08</v>
       </c>
       <c r="H9">
-        <v>3.4829841937176265e-07</v>
+        <v>2.2308907829895926e-07</v>
       </c>
       <c r="I9">
-        <v>0.0030601844654566737</v>
+        <v>0.0016980916101362862</v>
       </c>
       <c r="J9">
-        <v>0.0031356919957945192</v>
+        <v>0.0017416834966166501</v>
       </c>
       <c r="K9">
-        <v>0.0030674696692131998</v>
+        <v>0.0017019684157258859</v>
       </c>
       <c r="L9">
-        <v>0.0030685090149568869</v>
+        <v>0.0017024816565692404</v>
       </c>
       <c r="M9">
-        <v>-8.420413834718031e-07</v>
+        <v>-5.0488061109787032e-07</v>
       </c>
       <c r="N9">
-        <v>8.3852647013177015e-07</v>
+        <v>7.1123634158072459e-07</v>
       </c>
       <c r="O9">
-        <v>-4.6935756049272769e-06</v>
+        <v>-9.3138013792192457e-07</v>
       </c>
       <c r="P9">
-        <v>6.5712132851097135e-07</v>
+        <v>1.4286494242565412e-06</v>
       </c>
       <c r="Q9">
-        <v>-2.2412570050669663e-06</v>
+        <v>-1.1932871211495151e-06</v>
       </c>
       <c r="R9">
-        <v>-5.6389378559209714e-06</v>
+        <v>-2.6379844205111986e-06</v>
       </c>
       <c r="S9">
-        <v>1.4905460164627341e-06</v>
+        <v>6.1314794196074334e-08</v>
       </c>
       <c r="T9">
-        <v>6.7459608592932464e-08</v>
+        <v>2.429677446205117e-07</v>
       </c>
       <c r="U9">
-        <v>-1.2513837287070051e-06</v>
+        <v>-1.4188388735541499e-06</v>
       </c>
       <c r="V9">
-        <v>-1.0986320445764306e-06</v>
+        <v>-1.2015932200612024e-06</v>
       </c>
       <c r="W9">
-        <v>-0.003109144489822491</v>
+        <v>-0.0017500342722169364</v>
       </c>
       <c r="X9">
-        <v>2.0170217187356443e-05</v>
+        <v>1.2343919075922591e-05</v>
       </c>
     </row>
     <row r="10">
@@ -976,73 +976,73 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>0.14589139744336904</v>
+        <v>0.063584343197898338</v>
       </c>
       <c r="C10">
-        <v>1.3833037118556151e-06</v>
+        <v>1.0197007572277122e-06</v>
       </c>
       <c r="D10">
-        <v>-1.0902780960255308e-08</v>
+        <v>-9.0386324349088642e-09</v>
       </c>
       <c r="E10">
-        <v>-7.2450187027687709e-06</v>
+        <v>-3.5284807172009454e-06</v>
       </c>
       <c r="F10">
-        <v>-1.9117871524796006e-05</v>
+        <v>-1.2843871475047249e-05</v>
       </c>
       <c r="G10">
-        <v>2.5184720167662144e-07</v>
+        <v>1.1711422476994188e-07</v>
       </c>
       <c r="H10">
-        <v>5.5277168887868459e-07</v>
+        <v>3.3631007008296663e-07</v>
       </c>
       <c r="I10">
-        <v>0.0030617232420029243</v>
+        <v>0.0016986117127408354</v>
       </c>
       <c r="J10">
-        <v>0.0030674696692131998</v>
+        <v>0.0017019684157258859</v>
       </c>
       <c r="K10">
-        <v>0.0030902751242545519</v>
+        <v>0.0017149497043046642</v>
       </c>
       <c r="L10">
-        <v>0.003077711813172194</v>
+        <v>0.0017073043766120031</v>
       </c>
       <c r="M10">
-        <v>-4.1931998172444245e-06</v>
+        <v>-2.1777239171497569e-06</v>
       </c>
       <c r="N10">
-        <v>-1.0713197446022852e-06</v>
+        <v>-2.0145431667135718e-07</v>
       </c>
       <c r="O10">
-        <v>-7.7274839065648659e-06</v>
+        <v>-2.5340321938349034e-06</v>
       </c>
       <c r="P10">
-        <v>-2.2392974454361761e-06</v>
+        <v>1.2279031633990134e-07</v>
       </c>
       <c r="Q10">
-        <v>-5.3052648239048114e-06</v>
+        <v>-2.8172173738938189e-06</v>
       </c>
       <c r="R10">
-        <v>-4.4991623048257738e-06</v>
+        <v>-2.2278579874561082e-06</v>
       </c>
       <c r="S10">
-        <v>2.6626231966069288e-06</v>
+        <v>5.1178886280251581e-07</v>
       </c>
       <c r="T10">
-        <v>1.7584738074174212e-07</v>
+        <v>4.67606941863126e-07</v>
       </c>
       <c r="U10">
-        <v>-3.227378830204865e-06</v>
+        <v>-2.9274803892434655e-06</v>
       </c>
       <c r="V10">
-        <v>-1.5085943709764373e-06</v>
+        <v>-1.5440782323262466e-06</v>
       </c>
       <c r="W10">
-        <v>-0.0031406125785030659</v>
+        <v>-0.0017840923352891898</v>
       </c>
       <c r="X10">
-        <v>2.4828011126237738e-05</v>
+        <v>1.5322817894831174e-05</v>
       </c>
     </row>
     <row r="11">
@@ -1050,73 +1050,73 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>0.18817389190582479</v>
+        <v>0.1182612509606307</v>
       </c>
       <c r="C11">
-        <v>2.6238626936790982e-06</v>
+        <v>1.752819666886691e-06</v>
       </c>
       <c r="D11">
-        <v>-1.9581115567673754e-08</v>
+        <v>-1.4122102515186193e-08</v>
       </c>
       <c r="E11">
-        <v>-1.2310131253398271e-06</v>
+        <v>1.045490110851464e-08</v>
       </c>
       <c r="F11">
-        <v>-8.1361946546195966e-06</v>
+        <v>-6.7142440201013043e-06</v>
       </c>
       <c r="G11">
-        <v>1.6058284815307813e-07</v>
+        <v>6.5081523902758838e-08</v>
       </c>
       <c r="H11">
-        <v>4.0225259294134257e-07</v>
+        <v>2.4995037235956296e-07</v>
       </c>
       <c r="I11">
-        <v>0.0030619441131953</v>
+        <v>0.0016985883913872351</v>
       </c>
       <c r="J11">
-        <v>0.0030685090149568869</v>
+        <v>0.0017024816565692404</v>
       </c>
       <c r="K11">
-        <v>0.003077711813172194</v>
+        <v>0.0017073043766120031</v>
       </c>
       <c r="L11">
-        <v>0.003137343335135631</v>
+        <v>0.0017426241417320097</v>
       </c>
       <c r="M11">
-        <v>-6.8746925429044887e-06</v>
+        <v>-3.8399491159399608e-06</v>
       </c>
       <c r="N11">
-        <v>-5.1714225467313075e-06</v>
+        <v>-2.5026110336148554e-06</v>
       </c>
       <c r="O11">
-        <v>-9.4801131389931632e-06</v>
+        <v>-3.5458195820445875e-06</v>
       </c>
       <c r="P11">
-        <v>-7.8232471624905351e-06</v>
+        <v>-2.9509892789255098e-06</v>
       </c>
       <c r="Q11">
-        <v>-1.014205209371782e-05</v>
+        <v>-5.5544649050715438e-06</v>
       </c>
       <c r="R11">
-        <v>-9.2617708755501254e-06</v>
+        <v>-5.1279441452728048e-06</v>
       </c>
       <c r="S11">
-        <v>3.3158550759522841e-06</v>
+        <v>6.6774458364615741e-07</v>
       </c>
       <c r="T11">
-        <v>2.4081338194827068e-07</v>
+        <v>7.3714996207856789e-07</v>
       </c>
       <c r="U11">
-        <v>-5.4623418845365463e-06</v>
+        <v>-4.7864809205145175e-06</v>
       </c>
       <c r="V11">
-        <v>-3.1846639572041999e-06</v>
+        <v>-2.9978739010551306e-06</v>
       </c>
       <c r="W11">
-        <v>-0.0031861956375807375</v>
+        <v>-0.0018341099051755057</v>
       </c>
       <c r="X11">
-        <v>2.4447933852421165e-05</v>
+        <v>1.5635364415151906e-05</v>
       </c>
     </row>
     <row r="12">
@@ -1124,73 +1124,73 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>0.21688112269294418</v>
+        <v>0.18659512521437158</v>
       </c>
       <c r="C12">
-        <v>5.0154540726717311e-08</v>
+        <v>1.3864298727483544e-07</v>
       </c>
       <c r="D12">
-        <v>-9.0779187231684427e-10</v>
+        <v>-1.7582652920199261e-09</v>
       </c>
       <c r="E12">
-        <v>3.9382679235925511e-06</v>
+        <v>2.3005580802923954e-06</v>
       </c>
       <c r="F12">
-        <v>3.2609891648901684e-06</v>
+        <v>1.7232189954144349e-06</v>
       </c>
       <c r="G12">
-        <v>-3.2077563384540644e-08</v>
+        <v>-1.9961831057816129e-08</v>
       </c>
       <c r="H12">
-        <v>-6.4646286497321161e-09</v>
+        <v>-5.4543774580176689e-09</v>
       </c>
       <c r="I12">
-        <v>2.1223542818968062e-06</v>
+        <v>8.1722791458565194e-07</v>
       </c>
       <c r="J12">
-        <v>-8.420413834718031e-07</v>
+        <v>-5.0488061109787032e-07</v>
       </c>
       <c r="K12">
-        <v>-4.1931998172444245e-06</v>
+        <v>-2.1777239171497569e-06</v>
       </c>
       <c r="L12">
-        <v>-6.8746925429044887e-06</v>
+        <v>-3.8399491159399608e-06</v>
       </c>
       <c r="M12">
-        <v>0.00013631511596295606</v>
+        <v>8.2950737687791044e-05</v>
       </c>
       <c r="N12">
-        <v>7.5936161934870515e-05</v>
+        <v>4.6476418929663224e-05</v>
       </c>
       <c r="O12">
-        <v>7.5469254815214548e-05</v>
+        <v>4.627524944485173e-05</v>
       </c>
       <c r="P12">
-        <v>7.5763039872914784e-05</v>
+        <v>4.6360175714605128e-05</v>
       </c>
       <c r="Q12">
-        <v>7.5353972749737051e-05</v>
+        <v>4.6193477845693241e-05</v>
       </c>
       <c r="R12">
-        <v>7.5190263958299395e-05</v>
+        <v>4.6050325393295446e-05</v>
       </c>
       <c r="S12">
-        <v>-2.8053048904823427e-06</v>
+        <v>-2.0482910300169638e-06</v>
       </c>
       <c r="T12">
-        <v>1.5163634048838138e-08</v>
+        <v>1.361144320115421e-07</v>
       </c>
       <c r="U12">
-        <v>6.8390193930773593e-07</v>
+        <v>3.1697784725870662e-08</v>
       </c>
       <c r="V12">
-        <v>-4.9000679270879933e-07</v>
+        <v>-5.1941576254680557e-07</v>
       </c>
       <c r="W12">
-        <v>-7.5054480476953922e-05</v>
+        <v>-6.0857961979947391e-05</v>
       </c>
       <c r="X12">
-        <v>1.6970627076604442e-06</v>
+        <v>1.5048789706230805e-06</v>
       </c>
     </row>
     <row r="13">
@@ -1198,73 +1198,73 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>0.19817619457361982</v>
+        <v>0.17517892841517541</v>
       </c>
       <c r="C13">
-        <v>2.0373711396292427e-07</v>
+        <v>3.2017440313383282e-07</v>
       </c>
       <c r="D13">
-        <v>-2.4103943182396168e-09</v>
+        <v>-3.6751477929240483e-09</v>
       </c>
       <c r="E13">
-        <v>5.0714192180235123e-06</v>
+        <v>2.3265125389912814e-06</v>
       </c>
       <c r="F13">
-        <v>-1.6755810882882886e-06</v>
+        <v>-1.686686436667657e-06</v>
       </c>
       <c r="G13">
-        <v>-7.3182641781367508e-08</v>
+        <v>-3.5275887801187731e-08</v>
       </c>
       <c r="H13">
-        <v>1.1952665614494823e-07</v>
+        <v>7.7145377521158658e-08</v>
       </c>
       <c r="I13">
-        <v>3.6964110860048218e-06</v>
+        <v>1.8991381061682696e-06</v>
       </c>
       <c r="J13">
-        <v>8.3852647013177015e-07</v>
+        <v>7.1123634158072459e-07</v>
       </c>
       <c r="K13">
-        <v>-1.0713197446022852e-06</v>
+        <v>-2.0145431667135718e-07</v>
       </c>
       <c r="L13">
-        <v>-5.1714225467313075e-06</v>
+        <v>-2.5026110336148554e-06</v>
       </c>
       <c r="M13">
-        <v>7.5936161934870515e-05</v>
+        <v>4.6476418929663224e-05</v>
       </c>
       <c r="N13">
-        <v>0.00016355722623054173</v>
+        <v>9.7782619499126334e-05</v>
       </c>
       <c r="O13">
-        <v>7.5439237691639436e-05</v>
+        <v>4.6152205248872275e-05</v>
       </c>
       <c r="P13">
-        <v>7.6099664166654038e-05</v>
+        <v>4.6559022675460846e-05</v>
       </c>
       <c r="Q13">
-        <v>7.5562228235200805e-05</v>
+        <v>4.6181317642674313e-05</v>
       </c>
       <c r="R13">
-        <v>7.539015736768401e-05</v>
+        <v>4.61636667145194e-05</v>
       </c>
       <c r="S13">
-        <v>1.0061095425401073e-06</v>
+        <v>3.0267839694968292e-07</v>
       </c>
       <c r="T13">
-        <v>-6.3995589873500957e-08</v>
+        <v>-2.7636266740667387e-07</v>
       </c>
       <c r="U13">
-        <v>1.2881314676265214e-06</v>
+        <v>1.3730319702048104e-06</v>
       </c>
       <c r="V13">
-        <v>-8.0183293281916124e-07</v>
+        <v>-8.7062776029841975e-09</v>
       </c>
       <c r="W13">
-        <v>-7.310120119067949e-05</v>
+        <v>-2.5835974256953269e-05</v>
       </c>
       <c r="X13">
-        <v>9.0397607574883004e-07</v>
+        <v>1.4721279851961132e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1272,73 +1272,73 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>0.092434091493971665</v>
+        <v>0.063304241408129167</v>
       </c>
       <c r="C14">
-        <v>1.9008843174109408e-09</v>
+        <v>1.142212658762969e-07</v>
       </c>
       <c r="D14">
-        <v>-3.8203519670049382e-10</v>
+        <v>-1.5255190061157289e-09</v>
       </c>
       <c r="E14">
-        <v>2.7208827461459721e-06</v>
+        <v>1.278156403751324e-06</v>
       </c>
       <c r="F14">
-        <v>-1.1587993757515621e-05</v>
+        <v>-6.6342444036298734e-06</v>
       </c>
       <c r="G14">
-        <v>-3.5842036846047712e-08</v>
+        <v>-1.671182211494701e-08</v>
       </c>
       <c r="H14">
-        <v>1.966468429359607e-07</v>
+        <v>1.0811413766204395e-07</v>
       </c>
       <c r="I14">
-        <v>-1.6527084950269715e-06</v>
+        <v>-4.3603241183414831e-08</v>
       </c>
       <c r="J14">
-        <v>-4.6935756049272769e-06</v>
+        <v>-9.3138013792192457e-07</v>
       </c>
       <c r="K14">
-        <v>-7.7274839065648659e-06</v>
+        <v>-2.5340321938349034e-06</v>
       </c>
       <c r="L14">
-        <v>-9.4801131389931632e-06</v>
+        <v>-3.5458195820445875e-06</v>
       </c>
       <c r="M14">
-        <v>7.5469254815214548e-05</v>
+        <v>4.627524944485173e-05</v>
       </c>
       <c r="N14">
-        <v>7.5439237691639436e-05</v>
+        <v>4.6152205248872275e-05</v>
       </c>
       <c r="O14">
-        <v>0.0001468746275125304</v>
+        <v>8.9501910032662477e-05</v>
       </c>
       <c r="P14">
-        <v>7.567730215083361e-05</v>
+        <v>4.6261948584373075e-05</v>
       </c>
       <c r="Q14">
-        <v>7.6392232500543879e-05</v>
+        <v>4.6713631465493459e-05</v>
       </c>
       <c r="R14">
-        <v>7.5822695838679313e-05</v>
+        <v>4.6368721523783043e-05</v>
       </c>
       <c r="S14">
-        <v>-1.6395103440666945e-06</v>
+        <v>-1.4453915249546863e-06</v>
       </c>
       <c r="T14">
-        <v>-4.4294540224541419e-08</v>
+        <v>-1.119435648061316e-07</v>
       </c>
       <c r="U14">
-        <v>-3.9928567077213876e-07</v>
+        <v>-4.1910620422897877e-08</v>
       </c>
       <c r="V14">
-        <v>-1.030671257836528e-06</v>
+        <v>-4.1795223417274571e-07</v>
       </c>
       <c r="W14">
-        <v>-6.0951183897472289e-05</v>
+        <v>-3.3366815790390487e-05</v>
       </c>
       <c r="X14">
-        <v>-2.5122592160735948e-06</v>
+        <v>-9.7760128243339665e-07</v>
       </c>
     </row>
     <row r="15">
@@ -1346,73 +1346,73 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>0.17445510601219122</v>
+        <v>0.1480753680648923</v>
       </c>
       <c r="C15">
-        <v>3.3938553949578643e-07</v>
+        <v>3.341249343141725e-07</v>
       </c>
       <c r="D15">
-        <v>-3.6631833765851676e-09</v>
+        <v>-3.6367402927319189e-09</v>
       </c>
       <c r="E15">
-        <v>8.2904898571586624e-07</v>
+        <v>7.0587358472521583e-07</v>
       </c>
       <c r="F15">
-        <v>-7.4977079012983521e-06</v>
+        <v>-4.2414349194628831e-06</v>
       </c>
       <c r="G15">
-        <v>-3.9663546462319547e-08</v>
+        <v>-2.8219795948845958e-08</v>
       </c>
       <c r="H15">
-        <v>1.3763746948061823e-07</v>
+        <v>7.5041780804141119e-08</v>
       </c>
       <c r="I15">
-        <v>1.8307333810478285e-06</v>
+        <v>1.599250973033335e-06</v>
       </c>
       <c r="J15">
-        <v>6.5712132851097135e-07</v>
+        <v>1.4286494242565412e-06</v>
       </c>
       <c r="K15">
-        <v>-2.2392974454361761e-06</v>
+        <v>1.2279031633990134e-07</v>
       </c>
       <c r="L15">
-        <v>-7.8232471624905351e-06</v>
+        <v>-2.9509892789255098e-06</v>
       </c>
       <c r="M15">
-        <v>7.5763039872914784e-05</v>
+        <v>4.6360175714605128e-05</v>
       </c>
       <c r="N15">
-        <v>7.6099664166654038e-05</v>
+        <v>4.6559022675460846e-05</v>
       </c>
       <c r="O15">
-        <v>7.567730215083361e-05</v>
+        <v>4.6261948584373075e-05</v>
       </c>
       <c r="P15">
-        <v>0.00011797057339719886</v>
+        <v>7.0238266712816343e-05</v>
       </c>
       <c r="Q15">
-        <v>7.6088344816235834e-05</v>
+        <v>4.6459496914630588e-05</v>
       </c>
       <c r="R15">
-        <v>7.5703189116296343e-05</v>
+        <v>4.638431579853753e-05</v>
       </c>
       <c r="S15">
-        <v>4.6685057774757678e-07</v>
+        <v>4.245805439207837e-07</v>
       </c>
       <c r="T15">
-        <v>-1.5487963817818511e-07</v>
+        <v>-5.6624270643329493e-07</v>
       </c>
       <c r="U15">
-        <v>4.9462167151012102e-06</v>
+        <v>4.1658103635407505e-06</v>
       </c>
       <c r="V15">
-        <v>4.2308909990961421e-06</v>
+        <v>3.586554724291756e-06</v>
       </c>
       <c r="W15">
-        <v>-6.4095506451924115e-05</v>
+        <v>2.9775632100304642e-06</v>
       </c>
       <c r="X15">
-        <v>1.7358493738469468e-06</v>
+        <v>1.561261445704054e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1420,73 +1420,73 @@
         <v>37</v>
       </c>
       <c r="B16">
-        <v>0.12155142706556252</v>
+        <v>0.089064392742123008</v>
       </c>
       <c r="C16">
-        <v>-2.0522002587249941e-07</v>
+        <v>1.0958239262944224e-08</v>
       </c>
       <c r="D16">
-        <v>2.6454199638090761e-09</v>
+        <v>5.4656640424326504e-11</v>
       </c>
       <c r="E16">
-        <v>-1.5316022443702719e-06</v>
+        <v>-7.6302690183408902e-07</v>
       </c>
       <c r="F16">
-        <v>-1.9835188945481103e-05</v>
+        <v>-1.1369617532126823e-05</v>
       </c>
       <c r="G16">
-        <v>4.0214415019689442e-08</v>
+        <v>2.1816823366073077e-08</v>
       </c>
       <c r="H16">
-        <v>3.4693030276664045e-07</v>
+        <v>1.9414465994645628e-07</v>
       </c>
       <c r="I16">
-        <v>6.706927565306245e-07</v>
+        <v>1.3154260810286157e-07</v>
       </c>
       <c r="J16">
-        <v>-2.2412570050669663e-06</v>
+        <v>-1.1932871211495151e-06</v>
       </c>
       <c r="K16">
-        <v>-5.3052648239048114e-06</v>
+        <v>-2.8172173738938189e-06</v>
       </c>
       <c r="L16">
-        <v>-1.014205209371782e-05</v>
+        <v>-5.5544649050715438e-06</v>
       </c>
       <c r="M16">
-        <v>7.5353972749737051e-05</v>
+        <v>4.6193477845693241e-05</v>
       </c>
       <c r="N16">
-        <v>7.5562228235200805e-05</v>
+        <v>4.6181317642674313e-05</v>
       </c>
       <c r="O16">
-        <v>7.6392232500543879e-05</v>
+        <v>4.6713631465493459e-05</v>
       </c>
       <c r="P16">
-        <v>7.6088344816235834e-05</v>
+        <v>4.6459496914630588e-05</v>
       </c>
       <c r="Q16">
-        <v>0.0001446603880318806</v>
+        <v>8.7439698158099015e-05</v>
       </c>
       <c r="R16">
-        <v>7.6655549871800102e-05</v>
+        <v>4.6804717924462996e-05</v>
       </c>
       <c r="S16">
-        <v>-4.4337749866826735e-07</v>
+        <v>-1.0988373658608962e-06</v>
       </c>
       <c r="T16">
-        <v>-8.976514740235861e-08</v>
+        <v>-3.7273091293591381e-07</v>
       </c>
       <c r="U16">
-        <v>1.6023813401698244e-06</v>
+        <v>1.9358410586813311e-06</v>
       </c>
       <c r="V16">
-        <v>2.4562696864142287e-07</v>
+        <v>9.145010668859207e-07</v>
       </c>
       <c r="W16">
-        <v>-5.3542702653487149e-05</v>
+        <v>-4.5585630841097833e-06</v>
       </c>
       <c r="X16">
-        <v>-6.8612543588132606e-06</v>
+        <v>-3.3911771963062025e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1494,73 +1494,73 @@
         <v>38</v>
       </c>
       <c r="B17">
-        <v>0.085053806599784745</v>
+        <v>0.071112566938278388</v>
       </c>
       <c r="C17">
-        <v>-1.9407467033212193e-07</v>
+        <v>-3.8139965223970614e-08</v>
       </c>
       <c r="D17">
-        <v>2.8249235613673977e-09</v>
+        <v>7.5094641308874071e-10</v>
       </c>
       <c r="E17">
-        <v>1.8151767928325719e-06</v>
+        <v>1.0067700657887708e-06</v>
       </c>
       <c r="F17">
-        <v>-8.6710233763946045e-06</v>
+        <v>-5.1746972412528082e-06</v>
       </c>
       <c r="G17">
-        <v>-5.2992865808523326e-08</v>
+        <v>-2.9309071900597909e-08</v>
       </c>
       <c r="H17">
-        <v>1.3787040305771474e-07</v>
+        <v>8.1597653882209219e-08</v>
       </c>
       <c r="I17">
-        <v>-5.2147827901099469e-07</v>
+        <v>-1.3519296256240985e-06</v>
       </c>
       <c r="J17">
-        <v>-5.6389378559209714e-06</v>
+        <v>-2.6379844205111986e-06</v>
       </c>
       <c r="K17">
-        <v>-4.4991623048257738e-06</v>
+        <v>-2.2278579874561082e-06</v>
       </c>
       <c r="L17">
-        <v>-9.2617708755501254e-06</v>
+        <v>-5.1279441452728048e-06</v>
       </c>
       <c r="M17">
-        <v>7.5190263958299395e-05</v>
+        <v>4.6050325393295446e-05</v>
       </c>
       <c r="N17">
-        <v>7.539015736768401e-05</v>
+        <v>4.61636667145194e-05</v>
       </c>
       <c r="O17">
-        <v>7.5822695838679313e-05</v>
+        <v>4.6368721523783043e-05</v>
       </c>
       <c r="P17">
-        <v>7.5703189116296343e-05</v>
+        <v>4.638431579853753e-05</v>
       </c>
       <c r="Q17">
-        <v>7.6655549871800102e-05</v>
+        <v>4.6804717924462996e-05</v>
       </c>
       <c r="R17">
-        <v>0.00038074377023987336</v>
+        <v>0.00022833070433600559</v>
       </c>
       <c r="S17">
-        <v>1.7065200985709853e-06</v>
+        <v>6.7887909396852992e-07</v>
       </c>
       <c r="T17">
-        <v>6.6653844318774602e-09</v>
+        <v>-7.262438765752836e-08</v>
       </c>
       <c r="U17">
-        <v>1.4573697275145067e-06</v>
+        <v>1.316131146748266e-06</v>
       </c>
       <c r="V17">
-        <v>1.690215704347055e-06</v>
+        <v>1.437114023221423e-06</v>
       </c>
       <c r="W17">
-        <v>-6.6213998844377568e-05</v>
+        <v>-3.5239166088930301e-05</v>
       </c>
       <c r="X17">
-        <v>-5.2253162663161077e-06</v>
+        <v>-2.4678787547563495e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1568,73 +1568,73 @@
         <v>39</v>
       </c>
       <c r="B18">
-        <v>0.0029589561571574043</v>
+        <v>0.051372291646209538</v>
       </c>
       <c r="C18">
-        <v>4.1054035937742777e-07</v>
+        <v>-3.7161572841632485e-08</v>
       </c>
       <c r="D18">
-        <v>-1.4278994513455447e-09</v>
+        <v>9.9371006257775301e-10</v>
       </c>
       <c r="E18">
-        <v>-2.7765345965708148e-06</v>
+        <v>-2.0678765079626196e-06</v>
       </c>
       <c r="F18">
-        <v>5.5532823288434747e-06</v>
+        <v>1.3786576642619549e-06</v>
       </c>
       <c r="G18">
-        <v>-3.2074693537283943e-08</v>
+        <v>3.1503821667351492e-08</v>
       </c>
       <c r="H18">
-        <v>-2.7313920362362323e-07</v>
+        <v>-5.3488352977584973e-08</v>
       </c>
       <c r="I18">
-        <v>-6.4464332297358556e-07</v>
+        <v>-2.6690265932160374e-07</v>
       </c>
       <c r="J18">
-        <v>1.4905460164627341e-06</v>
+        <v>6.1314794196074334e-08</v>
       </c>
       <c r="K18">
-        <v>2.6626231966069288e-06</v>
+        <v>5.1178886280251581e-07</v>
       </c>
       <c r="L18">
-        <v>3.3158550759522841e-06</v>
+        <v>6.6774458364615741e-07</v>
       </c>
       <c r="M18">
-        <v>-2.8053048904823427e-06</v>
+        <v>-2.0482910300169638e-06</v>
       </c>
       <c r="N18">
-        <v>1.0061095425401073e-06</v>
+        <v>3.0267839694968292e-07</v>
       </c>
       <c r="O18">
-        <v>-1.6395103440666945e-06</v>
+        <v>-1.4453915249546863e-06</v>
       </c>
       <c r="P18">
-        <v>4.6685057774757678e-07</v>
+        <v>4.245805439207837e-07</v>
       </c>
       <c r="Q18">
-        <v>-4.4337749866826735e-07</v>
+        <v>-1.0988373658608962e-06</v>
       </c>
       <c r="R18">
-        <v>1.7065200985709853e-06</v>
+        <v>6.7887909396852992e-07</v>
       </c>
       <c r="S18">
-        <v>7.2471838193783917e-05</v>
+        <v>2.6575064765735505e-05</v>
       </c>
       <c r="T18">
-        <v>1.2893929272766698e-08</v>
+        <v>1.7060194870029367e-08</v>
       </c>
       <c r="U18">
-        <v>-5.3358661944042356e-08</v>
+        <v>-4.5716282686620832e-07</v>
       </c>
       <c r="V18">
-        <v>-5.6982952156923586e-07</v>
+        <v>-8.71959017555618e-07</v>
       </c>
       <c r="W18">
-        <v>-2.5638565341969786e-05</v>
+        <v>-9.7947343193200566e-06</v>
       </c>
       <c r="X18">
-        <v>-7.6078599484291573e-06</v>
+        <v>-3.0446323904264108e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1642,73 +1642,73 @@
         <v>40</v>
       </c>
       <c r="B19">
-        <v>-5.4482132061426625e-05</v>
+        <v>0.0055558810710798603</v>
       </c>
       <c r="C19">
-        <v>1.5746586652108136e-08</v>
+        <v>8.9567784602453331e-08</v>
       </c>
       <c r="D19">
-        <v>-3.0187921915712677e-10</v>
+        <v>-1.5064205468023872e-09</v>
       </c>
       <c r="E19">
-        <v>7.6610834004403728e-08</v>
+        <v>3.0613904650882423e-07</v>
       </c>
       <c r="F19">
-        <v>7.2480082789537109e-08</v>
+        <v>4.0984884995767465e-07</v>
       </c>
       <c r="G19">
-        <v>5.9577368540288884e-10</v>
+        <v>2.2128527109311206e-09</v>
       </c>
       <c r="H19">
-        <v>3.9526641189592505e-09</v>
+        <v>1.366702920055904e-08</v>
       </c>
       <c r="I19">
-        <v>9.639634082922723e-08</v>
+        <v>3.0884058561387618e-07</v>
       </c>
       <c r="J19">
-        <v>6.7459608592932464e-08</v>
+        <v>2.429677446205117e-07</v>
       </c>
       <c r="K19">
-        <v>1.7584738074174212e-07</v>
+        <v>4.67606941863126e-07</v>
       </c>
       <c r="L19">
-        <v>2.4081338194827068e-07</v>
+        <v>7.3714996207856789e-07</v>
       </c>
       <c r="M19">
-        <v>1.5163634048838138e-08</v>
+        <v>1.361144320115421e-07</v>
       </c>
       <c r="N19">
-        <v>-6.3995589873500957e-08</v>
+        <v>-2.7636266740667387e-07</v>
       </c>
       <c r="O19">
-        <v>-4.4294540224541419e-08</v>
+        <v>-1.119435648061316e-07</v>
       </c>
       <c r="P19">
-        <v>-1.5487963817818511e-07</v>
+        <v>-5.6624270643329493e-07</v>
       </c>
       <c r="Q19">
-        <v>-8.976514740235861e-08</v>
+        <v>-3.7273091293591381e-07</v>
       </c>
       <c r="R19">
-        <v>6.6653844318774602e-09</v>
+        <v>-7.262438765752836e-08</v>
       </c>
       <c r="S19">
-        <v>1.2893929272766698e-08</v>
+        <v>1.7060194870029367e-08</v>
       </c>
       <c r="T19">
-        <v>6.4569436930293315e-08</v>
+        <v>2.9752906647221398e-06</v>
       </c>
       <c r="U19">
-        <v>-8.1614979803417367e-07</v>
+        <v>-1.0748474512769788e-05</v>
       </c>
       <c r="V19">
-        <v>-1.0146153011855014e-06</v>
+        <v>-1.0939979412821618e-05</v>
       </c>
       <c r="W19">
-        <v>-7.3855825146450985e-06</v>
+        <v>-0.00030118844128276481</v>
       </c>
       <c r="X19">
-        <v>2.4832870954042782e-08</v>
+        <v>1.7966849015138045e-07</v>
       </c>
     </row>
     <row r="20">
@@ -1716,73 +1716,73 @@
         <v>41</v>
       </c>
       <c r="B20">
-        <v>-0.068404279275775276</v>
+        <v>-0.097440885266903823</v>
       </c>
       <c r="C20">
-        <v>-2.16106664356873e-07</v>
+        <v>-4.3050807129335377e-07</v>
       </c>
       <c r="D20">
-        <v>2.7461497853514081e-09</v>
+        <v>6.1127464348943115e-09</v>
       </c>
       <c r="E20">
-        <v>1.9349580566708759e-06</v>
+        <v>6.5105715053470193e-07</v>
       </c>
       <c r="F20">
-        <v>5.1649917180508045e-06</v>
+        <v>2.3364861998721039e-06</v>
       </c>
       <c r="G20">
-        <v>-3.8727040987091896e-08</v>
+        <v>-2.994253271236064e-08</v>
       </c>
       <c r="H20">
-        <v>-1.1536486073428865e-07</v>
+        <v>-9.8542793182894399e-08</v>
       </c>
       <c r="I20">
-        <v>-3.3721254358371121e-07</v>
+        <v>-8.8144932168151532e-07</v>
       </c>
       <c r="J20">
-        <v>-1.2513837287070051e-06</v>
+        <v>-1.4188388735541499e-06</v>
       </c>
       <c r="K20">
-        <v>-3.227378830204865e-06</v>
+        <v>-2.9274803892434655e-06</v>
       </c>
       <c r="L20">
-        <v>-5.4623418845365463e-06</v>
+        <v>-4.7864809205145175e-06</v>
       </c>
       <c r="M20">
-        <v>6.8390193930773593e-07</v>
+        <v>3.1697784725870662e-08</v>
       </c>
       <c r="N20">
-        <v>1.2881314676265214e-06</v>
+        <v>1.3730319702048104e-06</v>
       </c>
       <c r="O20">
-        <v>-3.9928567077213876e-07</v>
+        <v>-4.1910620422897877e-08</v>
       </c>
       <c r="P20">
-        <v>4.9462167151012102e-06</v>
+        <v>4.1658103635407505e-06</v>
       </c>
       <c r="Q20">
-        <v>1.6023813401698244e-06</v>
+        <v>1.9358410586813311e-06</v>
       </c>
       <c r="R20">
-        <v>1.4573697275145067e-06</v>
+        <v>1.316131146748266e-06</v>
       </c>
       <c r="S20">
-        <v>-5.3358661944042356e-08</v>
+        <v>-4.5716282686620832e-07</v>
       </c>
       <c r="T20">
-        <v>-8.1614979803417367e-07</v>
+        <v>-1.0748474512769788e-05</v>
       </c>
       <c r="U20">
-        <v>0.00017972705489561577</v>
+        <v>0.00015653595057605512</v>
       </c>
       <c r="V20">
-        <v>2.5044307719980732e-05</v>
+        <v>4.6553405918093734e-05</v>
       </c>
       <c r="W20">
-        <v>8.3881066926500534e-05</v>
+        <v>0.0010850978160424894</v>
       </c>
       <c r="X20">
-        <v>-1.0343889102198269e-06</v>
+        <v>-1.7354828856531645e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1790,73 +1790,73 @@
         <v>42</v>
       </c>
       <c r="B21">
-        <v>-0.030678298770933931</v>
+        <v>-0.048147200828972406</v>
       </c>
       <c r="C21">
-        <v>-3.8845637762585339e-07</v>
+        <v>-4.3886414477833709e-07</v>
       </c>
       <c r="D21">
-        <v>5.0476800561438572e-09</v>
+        <v>6.2173691225822712e-09</v>
       </c>
       <c r="E21">
-        <v>-1.7128513730655725e-06</v>
+        <v>-1.2759035791928479e-06</v>
       </c>
       <c r="F21">
-        <v>3.3251995052445521e-06</v>
+        <v>1.1289433398846271e-06</v>
       </c>
       <c r="G21">
-        <v>4.1899282425971626e-08</v>
+        <v>1.5776979302878209e-08</v>
       </c>
       <c r="H21">
-        <v>-7.0346949501994965e-08</v>
+        <v>-6.3493159269762477e-08</v>
       </c>
       <c r="I21">
-        <v>-1.627237528716606e-06</v>
+        <v>-1.5700449837232645e-06</v>
       </c>
       <c r="J21">
-        <v>-1.0986320445764306e-06</v>
+        <v>-1.2015932200612024e-06</v>
       </c>
       <c r="K21">
-        <v>-1.5085943709764373e-06</v>
+        <v>-1.5440782323262466e-06</v>
       </c>
       <c r="L21">
-        <v>-3.1846639572041999e-06</v>
+        <v>-2.9978739010551306e-06</v>
       </c>
       <c r="M21">
-        <v>-4.9000679270879933e-07</v>
+        <v>-5.1941576254680557e-07</v>
       </c>
       <c r="N21">
-        <v>-8.0183293281916124e-07</v>
+        <v>-8.7062776029841975e-09</v>
       </c>
       <c r="O21">
-        <v>-1.030671257836528e-06</v>
+        <v>-4.1795223417274571e-07</v>
       </c>
       <c r="P21">
-        <v>4.2308909990961421e-06</v>
+        <v>3.586554724291756e-06</v>
       </c>
       <c r="Q21">
-        <v>2.4562696864142287e-07</v>
+        <v>9.145010668859207e-07</v>
       </c>
       <c r="R21">
-        <v>1.690215704347055e-06</v>
+        <v>1.437114023221423e-06</v>
       </c>
       <c r="S21">
-        <v>-5.6982952156923586e-07</v>
+        <v>-8.71959017555618e-07</v>
       </c>
       <c r="T21">
-        <v>-1.0146153011855014e-06</v>
+        <v>-1.0939979412821618e-05</v>
       </c>
       <c r="U21">
-        <v>2.5044307719980732e-05</v>
+        <v>4.6553405918093734e-05</v>
       </c>
       <c r="V21">
-        <v>0.0001814843511555582</v>
+        <v>0.00015369901290262949</v>
       </c>
       <c r="W21">
-        <v>0.00010647908336758758</v>
+        <v>0.0011028502601045632</v>
       </c>
       <c r="X21">
-        <v>3.039277734559388e-06</v>
+        <v>1.3479960049563198e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1864,73 +1864,73 @@
         <v>43</v>
       </c>
       <c r="B22">
-        <v>1.1086808806252773</v>
+        <v>0.79636229069833875</v>
       </c>
       <c r="C22">
-        <v>-0.00012232323612427145</v>
+        <v>-8.1948005135246106e-05</v>
       </c>
       <c r="D22">
-        <v>1.3167085971505099e-06</v>
+        <v>9.2675456231938234e-07</v>
       </c>
       <c r="E22">
-        <v>-0.00034859511753136316</v>
+        <v>-0.00023009096026126906</v>
       </c>
       <c r="F22">
-        <v>-0.00022069726037048088</v>
+        <v>-0.0001524006388416583</v>
       </c>
       <c r="G22">
-        <v>6.9901930513384065e-06</v>
+        <v>3.9178240106067675e-06</v>
       </c>
       <c r="H22">
-        <v>4.0303100617942011e-06</v>
+        <v>1.0277331053915232e-06</v>
       </c>
       <c r="I22">
-        <v>-0.0030843405126328031</v>
+        <v>-0.0017395412902696035</v>
       </c>
       <c r="J22">
-        <v>-0.003109144489822491</v>
+        <v>-0.0017500342722169364</v>
       </c>
       <c r="K22">
-        <v>-0.0031406125785030659</v>
+        <v>-0.0017840923352891898</v>
       </c>
       <c r="L22">
-        <v>-0.0031861956375807375</v>
+        <v>-0.0018341099051755057</v>
       </c>
       <c r="M22">
-        <v>-7.5054480476953922e-05</v>
+        <v>-6.0857961979947391e-05</v>
       </c>
       <c r="N22">
-        <v>-7.310120119067949e-05</v>
+        <v>-2.5835974256953269e-05</v>
       </c>
       <c r="O22">
-        <v>-6.0951183897472289e-05</v>
+        <v>-3.3366815790390487e-05</v>
       </c>
       <c r="P22">
-        <v>-6.4095506451924115e-05</v>
+        <v>2.9775632100304642e-06</v>
       </c>
       <c r="Q22">
-        <v>-5.3542702653487149e-05</v>
+        <v>-4.5585630841097833e-06</v>
       </c>
       <c r="R22">
-        <v>-6.6213998844377568e-05</v>
+        <v>-3.5239166088930301e-05</v>
       </c>
       <c r="S22">
-        <v>-2.5638565341969786e-05</v>
+        <v>-9.7947343193200566e-06</v>
       </c>
       <c r="T22">
-        <v>-7.3855825146450985e-06</v>
+        <v>-0.00030118844128276481</v>
       </c>
       <c r="U22">
-        <v>8.3881066926500534e-05</v>
+        <v>0.0010850978160424894</v>
       </c>
       <c r="V22">
-        <v>0.00010647908336758758</v>
+        <v>0.0011028502601045632</v>
       </c>
       <c r="W22">
-        <v>0.0067869286018103761</v>
+        <v>0.033937293545460844</v>
       </c>
       <c r="X22">
-        <v>-0.00017912294450595312</v>
+        <v>-0.00012866173175828395</v>
       </c>
     </row>
     <row r="23">
@@ -1938,73 +1938,73 @@
         <v>44</v>
       </c>
       <c r="B23">
-        <v>-0.3219107829834465</v>
+        <v>-0.23686682811636584</v>
       </c>
       <c r="C23">
-        <v>6.4506150478479551e-06</v>
+        <v>4.0370232315436746e-06</v>
       </c>
       <c r="D23">
-        <v>-7.2908006248319516e-08</v>
+        <v>-4.4930703899308752e-08</v>
       </c>
       <c r="E23">
-        <v>-1.9563296528301664e-05</v>
+        <v>-1.1341283837345014e-05</v>
       </c>
       <c r="F23">
-        <v>-1.9536670068393804e-05</v>
+        <v>-1.381490843236969e-05</v>
       </c>
       <c r="G23">
-        <v>3.096886481001305e-07</v>
+        <v>1.5280981299700067e-07</v>
       </c>
       <c r="H23">
-        <v>8.8439868856179938e-08</v>
+        <v>6.4128100646700016e-08</v>
       </c>
       <c r="I23">
-        <v>1.0442638059328664e-05</v>
+        <v>6.0638198289440282e-06</v>
       </c>
       <c r="J23">
-        <v>2.0170217187356443e-05</v>
+        <v>1.2343919075922591e-05</v>
       </c>
       <c r="K23">
-        <v>2.4828011126237738e-05</v>
+        <v>1.5322817894831174e-05</v>
       </c>
       <c r="L23">
-        <v>2.4447933852421165e-05</v>
+        <v>1.5635364415151906e-05</v>
       </c>
       <c r="M23">
-        <v>1.6970627076604442e-06</v>
+        <v>1.5048789706230805e-06</v>
       </c>
       <c r="N23">
-        <v>9.0397607574883004e-07</v>
+        <v>1.4721279851961132e-06</v>
       </c>
       <c r="O23">
-        <v>-2.5122592160735948e-06</v>
+        <v>-9.7760128243339665e-07</v>
       </c>
       <c r="P23">
-        <v>1.7358493738469468e-06</v>
+        <v>1.561261445704054e-06</v>
       </c>
       <c r="Q23">
-        <v>-6.8612543588132606e-06</v>
+        <v>-3.3911771963062025e-06</v>
       </c>
       <c r="R23">
-        <v>-5.2253162663161077e-06</v>
+        <v>-2.4678787547563495e-06</v>
       </c>
       <c r="S23">
-        <v>-7.6078599484291573e-06</v>
+        <v>-3.0446323904264108e-06</v>
       </c>
       <c r="T23">
-        <v>2.4832870954042782e-08</v>
+        <v>1.7966849015138045e-07</v>
       </c>
       <c r="U23">
-        <v>-1.0343889102198269e-06</v>
+        <v>-1.7354828856531645e-06</v>
       </c>
       <c r="V23">
-        <v>3.039277734559388e-06</v>
+        <v>1.3479960049563198e-06</v>
       </c>
       <c r="W23">
-        <v>-0.00017912294450595312</v>
+        <v>-0.00012866173175828395</v>
       </c>
       <c r="X23">
-        <v>7.033108552484975e-05</v>
+        <v>4.3554566343627936e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2095,73 +2095,73 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>0.02642139144019149</v>
+        <v>0.029375659118469555</v>
       </c>
       <c r="C2">
-        <v>5.3703723892881309e-06</v>
+        <v>3.3279902099848618e-06</v>
       </c>
       <c r="D2">
-        <v>-5.8767793041916528e-08</v>
+        <v>-3.6262271155531198e-08</v>
       </c>
       <c r="E2">
-        <v>1.2928284659325363e-05</v>
+        <v>7.8876387254454837e-06</v>
       </c>
       <c r="F2">
-        <v>8.2941316052888299e-06</v>
+        <v>4.8225913342166112e-06</v>
       </c>
       <c r="G2">
-        <v>-2.7694154010929676e-07</v>
+        <v>-1.721906801668218e-07</v>
       </c>
       <c r="H2">
-        <v>-1.8471559829967692e-07</v>
+        <v>-1.1251897676673943e-07</v>
       </c>
       <c r="I2">
-        <v>2.1161563114723858e-06</v>
+        <v>1.2333236412625038e-06</v>
       </c>
       <c r="J2">
-        <v>3.685560298877946e-06</v>
+        <v>2.2665815362355675e-06</v>
       </c>
       <c r="K2">
-        <v>4.445034068823162e-06</v>
+        <v>2.7258112901682537e-06</v>
       </c>
       <c r="L2">
-        <v>6.1181306184804479e-06</v>
+        <v>3.7322547528325326e-06</v>
       </c>
       <c r="M2">
-        <v>8.2914862551926378e-08</v>
+        <v>1.4041082979469972e-07</v>
       </c>
       <c r="N2">
-        <v>-1.2429554423605797e-07</v>
+        <v>4.380868490048439e-08</v>
       </c>
       <c r="O2">
-        <v>7.7709607190259538e-08</v>
+        <v>4.4122284688709487e-08</v>
       </c>
       <c r="P2">
-        <v>1.4610405126855955e-07</v>
+        <v>2.3827625833281059e-07</v>
       </c>
       <c r="Q2">
-        <v>-5.8622239572058345e-07</v>
+        <v>-2.99062881405449e-07</v>
       </c>
       <c r="R2">
-        <v>-1.7005921930215995e-07</v>
+        <v>-1.7545300850464649e-07</v>
       </c>
       <c r="S2">
-        <v>2.2109437456303696e-06</v>
+        <v>6.3831462097915736e-07</v>
       </c>
       <c r="T2">
-        <v>1.5736596529589868e-08</v>
+        <v>9.2347866611862261e-08</v>
       </c>
       <c r="U2">
-        <v>-2.0270337464454527e-07</v>
+        <v>-4.4559128900166206e-07</v>
       </c>
       <c r="V2">
-        <v>-1.4458300968294122e-07</v>
+        <v>-3.4696848245923081e-07</v>
       </c>
       <c r="W2">
-        <v>-0.00012546612458146881</v>
+        <v>-8.6135704860567633e-05</v>
       </c>
       <c r="X2">
-        <v>1.0455581032611639e-05</v>
+        <v>6.7069195917287852e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2169,73 +2169,73 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>-9.4763911353772668e-05</v>
+        <v>-0.00012672132021444428</v>
       </c>
       <c r="C3">
-        <v>-5.8767793041916528e-08</v>
+        <v>-3.6262271155531198e-08</v>
       </c>
       <c r="D3">
-        <v>6.7244171151890138e-10</v>
+        <v>4.1204813477196182e-10</v>
       </c>
       <c r="E3">
-        <v>-3.3512286346208618e-08</v>
+        <v>-2.2517946028243797e-08</v>
       </c>
       <c r="F3">
-        <v>2.0256530784661044e-08</v>
+        <v>1.2678412889262683e-08</v>
       </c>
       <c r="G3">
-        <v>5.9033251459893973e-10</v>
+        <v>4.5724150215993446e-10</v>
       </c>
       <c r="H3">
-        <v>-4.7092270205185077e-10</v>
+        <v>-2.2399023302630454e-10</v>
       </c>
       <c r="I3">
-        <v>-2.6257509815267539e-08</v>
+        <v>-1.4721713719761832e-08</v>
       </c>
       <c r="J3">
-        <v>-4.3639031261424481e-08</v>
+        <v>-2.5881535583296474e-08</v>
       </c>
       <c r="K3">
-        <v>-4.8868900124228963e-08</v>
+        <v>-2.898552477092516e-08</v>
       </c>
       <c r="L3">
-        <v>-6.1842351470927272e-08</v>
+        <v>-3.6752763542972027e-08</v>
       </c>
       <c r="M3">
-        <v>-7.8341543573045777e-10</v>
+        <v>-1.4335994195424684e-09</v>
       </c>
       <c r="N3">
-        <v>1.9823002188435579e-09</v>
+        <v>-1.8337673303141687e-10</v>
       </c>
       <c r="O3">
-        <v>-4.2475825882080202e-10</v>
+        <v>-2.9514634650504945e-10</v>
       </c>
       <c r="P3">
-        <v>-1.5467672006439117e-09</v>
+        <v>-2.5128847962562099e-09</v>
       </c>
       <c r="Q3">
-        <v>6.542959569119153e-09</v>
+        <v>3.3443603061827796e-09</v>
       </c>
       <c r="R3">
-        <v>1.5411730349516057e-09</v>
+        <v>1.7804072977194792e-09</v>
       </c>
       <c r="S3">
-        <v>-1.8798484543004069e-08</v>
+        <v>-6.5396647830094919e-09</v>
       </c>
       <c r="T3">
-        <v>-2.4883764556573461e-10</v>
+        <v>-1.318850483344708e-09</v>
       </c>
       <c r="U3">
-        <v>2.1449056192622969e-09</v>
+        <v>5.5683694421109859e-09</v>
       </c>
       <c r="V3">
-        <v>1.5389260456839868e-09</v>
+        <v>4.4451197735316568e-09</v>
       </c>
       <c r="W3">
-        <v>1.3215511423378105e-06</v>
+        <v>9.337960431079408e-07</v>
       </c>
       <c r="X3">
-        <v>-1.2125604381215531e-07</v>
+        <v>-7.6213490241779506e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2243,73 +2243,73 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>0.02670440406788319</v>
+        <v>0.038448889080366908</v>
       </c>
       <c r="C4">
-        <v>1.2928284659325363e-05</v>
+        <v>7.8876387254454837e-06</v>
       </c>
       <c r="D4">
-        <v>-3.3512286346208618e-08</v>
+        <v>-2.2517946028243797e-08</v>
       </c>
       <c r="E4">
-        <v>0.0011256000603266155</v>
+        <v>0.00068956939451041556</v>
       </c>
       <c r="F4">
-        <v>0.0004746411695942766</v>
+        <v>0.00028330989048693097</v>
       </c>
       <c r="G4">
-        <v>-2.3913609375688506e-05</v>
+        <v>-1.4536450294102679e-05</v>
       </c>
       <c r="H4">
-        <v>-1.006712286754183e-05</v>
+        <v>-5.9623228648482768e-06</v>
       </c>
       <c r="I4">
-        <v>-6.8775457989607489e-06</v>
+        <v>2.41022682042803e-06</v>
       </c>
       <c r="J4">
-        <v>-1.2952227766507095e-05</v>
+        <v>-7.6065349548365968e-07</v>
       </c>
       <c r="K4">
-        <v>-1.6005171934637243e-05</v>
+        <v>-3.218915130107781e-06</v>
       </c>
       <c r="L4">
-        <v>-1.2758937026873732e-05</v>
+        <v>-1.5005007366577838e-06</v>
       </c>
       <c r="M4">
-        <v>2.6213039324548115e-06</v>
+        <v>1.7127143869271695e-06</v>
       </c>
       <c r="N4">
-        <v>4.5087434092918401e-06</v>
+        <v>2.4120803576117145e-06</v>
       </c>
       <c r="O4">
-        <v>1.6398229552421353e-06</v>
+        <v>7.6900538884351821e-07</v>
       </c>
       <c r="P4">
-        <v>1.6777172942240577e-06</v>
+        <v>1.3072263182490793e-06</v>
       </c>
       <c r="Q4">
-        <v>-2.1487808375777844e-06</v>
+        <v>-1.0766089063389579e-06</v>
       </c>
       <c r="R4">
-        <v>-5.9019995185752376e-06</v>
+        <v>-3.8249167689963524e-06</v>
       </c>
       <c r="S4">
-        <v>7.1369334377269769e-07</v>
+        <v>-6.1745447681902818e-07</v>
       </c>
       <c r="T4">
-        <v>1.2278271127015002e-07</v>
+        <v>5.8779696145160811e-07</v>
       </c>
       <c r="U4">
-        <v>-9.7762331634457306e-07</v>
+        <v>-2.0959982591894199e-06</v>
       </c>
       <c r="V4">
-        <v>2.625870444742593e-07</v>
+        <v>-1.1654882370044985e-06</v>
       </c>
       <c r="W4">
-        <v>-0.00052351916991724744</v>
+        <v>-0.00037464939001333083</v>
       </c>
       <c r="X4">
-        <v>-1.7951586308822488e-05</v>
+        <v>-1.035688868389197e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2317,73 +2317,73 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>-0.03236256168848025</v>
+        <v>0.03356211294832457</v>
       </c>
       <c r="C5">
-        <v>8.2941316052888299e-06</v>
+        <v>4.8225913342166112e-06</v>
       </c>
       <c r="D5">
-        <v>2.0256530784661044e-08</v>
+        <v>1.2678412889262683e-08</v>
       </c>
       <c r="E5">
-        <v>0.0004746411695942766</v>
+        <v>0.00028330989048693097</v>
       </c>
       <c r="F5">
-        <v>0.00093649514471520485</v>
+        <v>0.00058536503964136757</v>
       </c>
       <c r="G5">
-        <v>-1.0135905155095957e-05</v>
+        <v>-5.9905700585669627e-06</v>
       </c>
       <c r="H5">
-        <v>-1.9525092049632524e-05</v>
+        <v>-1.2110876026805744e-05</v>
       </c>
       <c r="I5">
-        <v>5.1374239311945125e-06</v>
+        <v>5.0664366784036076e-06</v>
       </c>
       <c r="J5">
-        <v>-9.6121948616692356e-06</v>
+        <v>-4.0939540307735126e-06</v>
       </c>
       <c r="K5">
-        <v>-1.537990964837132e-05</v>
+        <v>-8.2093599110819967e-06</v>
       </c>
       <c r="L5">
-        <v>-5.6385945804816186e-06</v>
+        <v>-2.4377180695303889e-06</v>
       </c>
       <c r="M5">
-        <v>3.9466442992367816e-06</v>
+        <v>2.5128821941412691e-06</v>
       </c>
       <c r="N5">
-        <v>5.7975966129483781e-06</v>
+        <v>3.0301203591299258e-06</v>
       </c>
       <c r="O5">
-        <v>-4.7376194903435959e-06</v>
+        <v>-2.6209433696631801e-06</v>
       </c>
       <c r="P5">
-        <v>-4.5306049353335566e-06</v>
+        <v>-1.9724439576049307e-06</v>
       </c>
       <c r="Q5">
-        <v>-1.3161790907493813e-05</v>
+        <v>-7.5058704414926041e-06</v>
       </c>
       <c r="R5">
-        <v>-8.3586095746351317e-06</v>
+        <v>-4.7843497757450738e-06</v>
       </c>
       <c r="S5">
-        <v>9.0889919330291049e-06</v>
+        <v>2.6551264185437377e-06</v>
       </c>
       <c r="T5">
-        <v>1.7180943560402525e-07</v>
+        <v>8.5086434858341272e-07</v>
       </c>
       <c r="U5">
-        <v>-2.2057779769789285e-07</v>
+        <v>-1.8732273009389505e-06</v>
       </c>
       <c r="V5">
-        <v>-1.0903998764887966e-06</v>
+        <v>-2.3220229144512334e-06</v>
       </c>
       <c r="W5">
-        <v>-0.00043242440922887089</v>
+        <v>-0.00033166157308438439</v>
       </c>
       <c r="X5">
-        <v>-2.5682604106283385e-05</v>
+        <v>-1.6851567021776492e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2391,73 +2391,73 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>-0.0071971849907123868</v>
+        <v>-0.0072963258095088803</v>
       </c>
       <c r="C6">
-        <v>-2.7694154010929676e-07</v>
+        <v>-1.721906801668218e-07</v>
       </c>
       <c r="D6">
-        <v>5.9033251459893973e-10</v>
+        <v>4.5724150215993446e-10</v>
       </c>
       <c r="E6">
-        <v>-2.3913609375688506e-05</v>
+        <v>-1.4536450294102679e-05</v>
       </c>
       <c r="F6">
-        <v>-1.0135905155095957e-05</v>
+        <v>-5.9905700585669627e-06</v>
       </c>
       <c r="G6">
-        <v>5.3834477500734261e-07</v>
+        <v>3.2464608052607189e-07</v>
       </c>
       <c r="H6">
-        <v>2.2726093049792789e-07</v>
+        <v>1.333951378970521e-07</v>
       </c>
       <c r="I6">
-        <v>1.4157568371813914e-07</v>
+        <v>-7.3161196917114321e-08</v>
       </c>
       <c r="J6">
-        <v>2.7708624727927888e-07</v>
+        <v>-1.851156588879776e-08</v>
       </c>
       <c r="K6">
-        <v>4.0481975997965387e-07</v>
+        <v>6.8822861719614051e-08</v>
       </c>
       <c r="L6">
-        <v>3.5552426044910941e-07</v>
+        <v>4.6440395198811167e-08</v>
       </c>
       <c r="M6">
-        <v>-4.5292655070975729e-08</v>
+        <v>-2.8353879337663724e-08</v>
       </c>
       <c r="N6">
-        <v>-4.904756381215579e-08</v>
+        <v>-2.1417050174670084e-08</v>
       </c>
       <c r="O6">
-        <v>-5.5546074287435023e-08</v>
+        <v>-2.8757219342061482e-08</v>
       </c>
       <c r="P6">
-        <v>-4.4243220338563667e-08</v>
+        <v>-3.2425692134887075e-08</v>
       </c>
       <c r="Q6">
-        <v>2.8424868198247749e-08</v>
+        <v>1.2513510070548327e-08</v>
       </c>
       <c r="R6">
-        <v>1.1306879042275067e-07</v>
+        <v>7.8209858965876035e-08</v>
       </c>
       <c r="S6">
-        <v>-3.8447159166000082e-08</v>
+        <v>4.9620404200772498e-08</v>
       </c>
       <c r="T6">
-        <v>-1.2913184765141024e-09</v>
+        <v>-6.9565804294949885e-09</v>
       </c>
       <c r="U6">
-        <v>-3.6107723187413001e-10</v>
+        <v>1.9010334441766715e-08</v>
       </c>
       <c r="V6">
-        <v>1.4467321154248042e-09</v>
+        <v>1.6026538654936847e-08</v>
       </c>
       <c r="W6">
-        <v>1.0733386389793854e-05</v>
+        <v>7.3433440236952521e-06</v>
       </c>
       <c r="X6">
-        <v>4.081895060385785e-07</v>
+        <v>1.8119699709677232e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2465,73 +2465,73 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>-0.0095271175616012931</v>
+        <v>-0.010961756273961525</v>
       </c>
       <c r="C7">
-        <v>-1.8471559829967692e-07</v>
+        <v>-1.1251897676673943e-07</v>
       </c>
       <c r="D7">
-        <v>-4.7092270205185077e-10</v>
+        <v>-2.2399023302630454e-10</v>
       </c>
       <c r="E7">
-        <v>-1.006712286754183e-05</v>
+        <v>-5.9623228648482768e-06</v>
       </c>
       <c r="F7">
-        <v>-1.9525092049632524e-05</v>
+        <v>-1.2110876026805744e-05</v>
       </c>
       <c r="G7">
-        <v>2.2726093049792789e-07</v>
+        <v>1.333951378970521e-07</v>
       </c>
       <c r="H7">
-        <v>4.3204146916140512e-07</v>
+        <v>2.659461947314574e-07</v>
       </c>
       <c r="I7">
-        <v>-1.291283437427928e-07</v>
+        <v>-1.3328553427478961e-07</v>
       </c>
       <c r="J7">
-        <v>2.0723426776142587e-07</v>
+        <v>6.1434589131513894e-08</v>
       </c>
       <c r="K7">
-        <v>4.2675322889178206e-07</v>
+        <v>2.0385180899495021e-07</v>
       </c>
       <c r="L7">
-        <v>2.8405752913263239e-07</v>
+        <v>1.2010355033783214e-07</v>
       </c>
       <c r="M7">
-        <v>-3.2634314426085393e-08</v>
+        <v>-2.2046817601907856e-08</v>
       </c>
       <c r="N7">
-        <v>-1.6956543593306618e-08</v>
+        <v>-5.9895431393608689e-10</v>
       </c>
       <c r="O7">
-        <v>-5.7309398588232916e-10</v>
+        <v>-7.0701380993573055e-09</v>
       </c>
       <c r="P7">
-        <v>8.6993322627702071e-08</v>
+        <v>3.8395609796791128e-08</v>
       </c>
       <c r="Q7">
-        <v>1.9031464901169752e-07</v>
+        <v>1.0202727998399963e-07</v>
       </c>
       <c r="R7">
-        <v>1.6034629992247997e-07</v>
+        <v>9.5432132150408785e-08</v>
       </c>
       <c r="S7">
-        <v>-1.6633381307028806e-07</v>
+        <v>2.166237268980406e-08</v>
       </c>
       <c r="T7">
-        <v>-2.7092590079700373e-11</v>
+        <v>-3.0193255652640209e-09</v>
       </c>
       <c r="U7">
-        <v>-1.8127540823070135e-08</v>
+        <v>-7.4089991632828871e-09</v>
       </c>
       <c r="V7">
-        <v>2.4466884577962495e-08</v>
+        <v>1.8777698169445832e-08</v>
       </c>
       <c r="W7">
-        <v>8.6572351378183877e-06</v>
+        <v>5.5634150626270134e-06</v>
       </c>
       <c r="X7">
-        <v>3.8631899123312303e-07</v>
+        <v>2.0285732989710305e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2539,73 +2539,73 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>-0.037481310360076882</v>
+        <v>-0.10058549067353313</v>
       </c>
       <c r="C8">
-        <v>2.1161563114723858e-06</v>
+        <v>1.2333236412625038e-06</v>
       </c>
       <c r="D8">
-        <v>-2.6257509815267539e-08</v>
+        <v>-1.4721713719761832e-08</v>
       </c>
       <c r="E8">
-        <v>-6.8775457989607489e-06</v>
+        <v>2.41022682042803e-06</v>
       </c>
       <c r="F8">
-        <v>5.1374239311945125e-06</v>
+        <v>5.0664366784036076e-06</v>
       </c>
       <c r="G8">
-        <v>1.4157568371813914e-07</v>
+        <v>-7.3161196917114321e-08</v>
       </c>
       <c r="H8">
-        <v>-1.291283437427928e-07</v>
+        <v>-1.3328553427478961e-07</v>
       </c>
       <c r="I8">
-        <v>0.0042128970555513718</v>
+        <v>0.0023345892887651348</v>
       </c>
       <c r="J8">
-        <v>0.0035986051765683593</v>
+        <v>0.0019641737963285401</v>
       </c>
       <c r="K8">
-        <v>0.0035993946425954106</v>
+        <v>0.0019640688149028642</v>
       </c>
       <c r="L8">
-        <v>0.0035984848917515991</v>
+        <v>0.0019634706296957219</v>
       </c>
       <c r="M8">
-        <v>4.8121849271200402e-06</v>
+        <v>3.2825259747920316e-06</v>
       </c>
       <c r="N8">
-        <v>1.5455017151122618e-06</v>
+        <v>2.4874756927726963e-06</v>
       </c>
       <c r="O8">
-        <v>9.5856361227497586e-07</v>
+        <v>1.1930872587068983e-06</v>
       </c>
       <c r="P8">
-        <v>3.1054125130754121e-06</v>
+        <v>2.0021600693850307e-06</v>
       </c>
       <c r="Q8">
-        <v>4.8937629180182282e-06</v>
+        <v>2.0798043023296797e-06</v>
       </c>
       <c r="R8">
-        <v>2.9655036441781254e-06</v>
+        <v>2.2271271196166561e-06</v>
       </c>
       <c r="S8">
-        <v>3.7362791813685918e-06</v>
+        <v>1.1803478862580395e-06</v>
       </c>
       <c r="T8">
-        <v>9.5543821248701074e-08</v>
+        <v>2.6170602307804488e-07</v>
       </c>
       <c r="U8">
-        <v>-1.5501773062014169e-07</v>
+        <v>-9.7178305191811022e-07</v>
       </c>
       <c r="V8">
-        <v>1.0759202719307106e-06</v>
+        <v>-2.4068820777528743e-07</v>
       </c>
       <c r="W8">
-        <v>-0.0036563720781899256</v>
+        <v>-0.0020177277923954578</v>
       </c>
       <c r="X8">
-        <v>1.6181417415004284e-05</v>
+        <v>6.8887760842260003e-06</v>
       </c>
     </row>
     <row r="9">
@@ -2613,73 +2613,73 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>-0.016372377063636895</v>
+        <v>-0.080096063042714508</v>
       </c>
       <c r="C9">
-        <v>3.685560298877946e-06</v>
+        <v>2.2665815362355675e-06</v>
       </c>
       <c r="D9">
-        <v>-4.3639031261424481e-08</v>
+        <v>-2.5881535583296474e-08</v>
       </c>
       <c r="E9">
-        <v>-1.2952227766507095e-05</v>
+        <v>-7.6065349548365968e-07</v>
       </c>
       <c r="F9">
-        <v>-9.6121948616692356e-06</v>
+        <v>-4.0939540307735126e-06</v>
       </c>
       <c r="G9">
-        <v>2.7708624727927888e-07</v>
+        <v>-1.851156588879776e-08</v>
       </c>
       <c r="H9">
-        <v>2.0723426776142587e-07</v>
+        <v>6.1434589131513894e-08</v>
       </c>
       <c r="I9">
-        <v>0.0035986051765683593</v>
+        <v>0.0019641737963285401</v>
       </c>
       <c r="J9">
-        <v>0.0036823023635611809</v>
+        <v>0.0020138558553832804</v>
       </c>
       <c r="K9">
-        <v>0.003613869556685868</v>
+        <v>0.0019721317809909067</v>
       </c>
       <c r="L9">
-        <v>0.0036142122095667072</v>
+        <v>0.0019723314537297477</v>
       </c>
       <c r="M9">
-        <v>3.8895516873232724e-06</v>
+        <v>2.6860309871752469e-06</v>
       </c>
       <c r="N9">
-        <v>-1.4779176683123049e-06</v>
+        <v>8.2129124583263951e-07</v>
       </c>
       <c r="O9">
-        <v>-2.7374452220560306e-06</v>
+        <v>-9.6624730398145827e-07</v>
       </c>
       <c r="P9">
-        <v>8.1508862488486024e-07</v>
+        <v>6.8152339478594483e-07</v>
       </c>
       <c r="Q9">
-        <v>-8.2517039709554159e-08</v>
+        <v>-1.0839373045809267e-06</v>
       </c>
       <c r="R9">
-        <v>-1.4352033668420956e-06</v>
+        <v>-6.6015261868477459e-07</v>
       </c>
       <c r="S9">
-        <v>-9.8387610132932602e-07</v>
+        <v>2.1909178074049111e-07</v>
       </c>
       <c r="T9">
-        <v>8.0234823580471861e-08</v>
+        <v>2.2576538981983191e-07</v>
       </c>
       <c r="U9">
-        <v>1.0073893522078189e-06</v>
+        <v>-4.6147680511370409e-07</v>
       </c>
       <c r="V9">
-        <v>-8.0311933206678084e-08</v>
+        <v>-1.0352812569220545e-06</v>
       </c>
       <c r="W9">
-        <v>-0.0037072313160477605</v>
+        <v>-0.0020470076158963044</v>
       </c>
       <c r="X9">
-        <v>4.0437956469392843e-05</v>
+        <v>2.2186131349639733e-05</v>
       </c>
     </row>
     <row r="10">
@@ -2687,73 +2687,73 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>0.0455635576936761</v>
+        <v>-0.023875208229729203</v>
       </c>
       <c r="C10">
-        <v>4.445034068823162e-06</v>
+        <v>2.7258112901682537e-06</v>
       </c>
       <c r="D10">
-        <v>-4.8868900124228963e-08</v>
+        <v>-2.898552477092516e-08</v>
       </c>
       <c r="E10">
-        <v>-1.6005171934637243e-05</v>
+        <v>-3.218915130107781e-06</v>
       </c>
       <c r="F10">
-        <v>-1.537990964837132e-05</v>
+        <v>-8.2093599110819967e-06</v>
       </c>
       <c r="G10">
-        <v>4.0481975997965387e-07</v>
+        <v>6.8822861719614051e-08</v>
       </c>
       <c r="H10">
-        <v>4.2675322889178206e-07</v>
+        <v>2.0385180899495021e-07</v>
       </c>
       <c r="I10">
-        <v>0.0035993946425954106</v>
+        <v>0.0019640688149028642</v>
       </c>
       <c r="J10">
-        <v>0.003613869556685868</v>
+        <v>0.0019721317809909067</v>
       </c>
       <c r="K10">
-        <v>0.0036373979524125422</v>
+        <v>0.0019859684356466952</v>
       </c>
       <c r="L10">
-        <v>0.0036257404216317162</v>
+        <v>0.001978714297088075</v>
       </c>
       <c r="M10">
-        <v>3.2785379939738339e-06</v>
+        <v>2.2236406151331254e-06</v>
       </c>
       <c r="N10">
-        <v>-3.0040119527045583e-06</v>
+        <v>2.2814319343545029e-07</v>
       </c>
       <c r="O10">
-        <v>-4.4163774647249155e-06</v>
+        <v>-2.1056621502812261e-06</v>
       </c>
       <c r="P10">
-        <v>5.8294615533189446e-08</v>
+        <v>3.553171303792283e-07</v>
       </c>
       <c r="Q10">
-        <v>-1.6608126507197853e-06</v>
+        <v>-2.2292834289343421e-06</v>
       </c>
       <c r="R10">
-        <v>8.5926167486825056e-07</v>
+        <v>7.9549732674391419e-07</v>
       </c>
       <c r="S10">
-        <v>6.3989531030515949e-09</v>
+        <v>2.2873187431132911e-07</v>
       </c>
       <c r="T10">
-        <v>1.8104826321824563e-07</v>
+        <v>5.24114297731499e-07</v>
       </c>
       <c r="U10">
-        <v>-1.0977318535794971e-06</v>
+        <v>-2.3594303585497083e-06</v>
       </c>
       <c r="V10">
-        <v>-1.8309771369108177e-07</v>
+        <v>-1.4475734578342303e-06</v>
       </c>
       <c r="W10">
-        <v>-0.003754808394680227</v>
+        <v>-0.0020984949640080559</v>
       </c>
       <c r="X10">
-        <v>5.0837439620828661e-05</v>
+        <v>2.8872792830923177e-05</v>
       </c>
     </row>
     <row r="11">
@@ -2761,73 +2761,73 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>0.087195603906792443</v>
+        <v>0.018179892873423975</v>
       </c>
       <c r="C11">
-        <v>6.1181306184804479e-06</v>
+        <v>3.7322547528325326e-06</v>
       </c>
       <c r="D11">
-        <v>-6.1842351470927272e-08</v>
+        <v>-3.6752763542972027e-08</v>
       </c>
       <c r="E11">
-        <v>-1.2758937026873732e-05</v>
+        <v>-1.5005007366577838e-06</v>
       </c>
       <c r="F11">
-        <v>-5.6385945804816186e-06</v>
+        <v>-2.4377180695303889e-06</v>
       </c>
       <c r="G11">
-        <v>3.5552426044910941e-07</v>
+        <v>4.6440395198811167e-08</v>
       </c>
       <c r="H11">
-        <v>2.8405752913263239e-07</v>
+        <v>1.2010355033783214e-07</v>
       </c>
       <c r="I11">
-        <v>0.0035984848917515991</v>
+        <v>0.0019634706296957219</v>
       </c>
       <c r="J11">
-        <v>0.0036142122095667072</v>
+        <v>0.0019723314537297477</v>
       </c>
       <c r="K11">
-        <v>0.0036257404216317162</v>
+        <v>0.001978714297088075</v>
       </c>
       <c r="L11">
-        <v>0.0036792973410119585</v>
+        <v>0.0020118803083875492</v>
       </c>
       <c r="M11">
-        <v>1.4037002279495573e-06</v>
+        <v>1.0381286348901247e-06</v>
       </c>
       <c r="N11">
-        <v>-5.9560557073772939e-06</v>
+        <v>-1.4740194276012787e-06</v>
       </c>
       <c r="O11">
-        <v>-4.9112941044887004e-06</v>
+        <v>-2.4543342064783845e-06</v>
       </c>
       <c r="P11">
-        <v>-4.1235156255856757e-06</v>
+        <v>-2.0935206828177745e-06</v>
       </c>
       <c r="Q11">
-        <v>-5.2477150013399959e-06</v>
+        <v>-4.3514767903426905e-06</v>
       </c>
       <c r="R11">
-        <v>-4.3115264646801797e-06</v>
+        <v>-2.3173572496350908e-06</v>
       </c>
       <c r="S11">
-        <v>2.6199108956384544e-07</v>
+        <v>-3.4224784417662871e-07</v>
       </c>
       <c r="T11">
-        <v>2.2188270726498923e-07</v>
+        <v>6.9030153453445602e-07</v>
       </c>
       <c r="U11">
-        <v>-2.5750495194650927e-06</v>
+        <v>-3.5735310416959659e-06</v>
       </c>
       <c r="V11">
-        <v>-1.6327764701196598e-06</v>
+        <v>-2.5430432574825612e-06</v>
       </c>
       <c r="W11">
-        <v>-0.0038091760120159525</v>
+        <v>-0.0021453854904648724</v>
       </c>
       <c r="X11">
-        <v>5.2035651785058216e-05</v>
+        <v>2.9927801989330906e-05</v>
       </c>
     </row>
     <row r="12">
@@ -2835,73 +2835,73 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>0.17755583180947135</v>
+        <v>0.16365800758800902</v>
       </c>
       <c r="C12">
-        <v>8.2914862551926378e-08</v>
+        <v>1.4041082979469972e-07</v>
       </c>
       <c r="D12">
-        <v>-7.8341543573045777e-10</v>
+        <v>-1.4335994195424684e-09</v>
       </c>
       <c r="E12">
-        <v>2.6213039324548115e-06</v>
+        <v>1.7127143869271695e-06</v>
       </c>
       <c r="F12">
-        <v>3.9466442992367816e-06</v>
+        <v>2.5128821941412691e-06</v>
       </c>
       <c r="G12">
-        <v>-4.5292655070975729e-08</v>
+        <v>-2.8353879337663724e-08</v>
       </c>
       <c r="H12">
-        <v>-3.2634314426085393e-08</v>
+        <v>-2.2046817601907856e-08</v>
       </c>
       <c r="I12">
-        <v>4.8121849271200402e-06</v>
+        <v>3.2825259747920316e-06</v>
       </c>
       <c r="J12">
-        <v>3.8895516873232724e-06</v>
+        <v>2.6860309871752469e-06</v>
       </c>
       <c r="K12">
-        <v>3.2785379939738339e-06</v>
+        <v>2.2236406151331254e-06</v>
       </c>
       <c r="L12">
-        <v>1.4037002279495573e-06</v>
+        <v>1.0381286348901247e-06</v>
       </c>
       <c r="M12">
-        <v>0.00013222327096958534</v>
+        <v>8.3204938489662921e-05</v>
       </c>
       <c r="N12">
-        <v>7.4827224056829507e-05</v>
+        <v>4.7316968276197888e-05</v>
       </c>
       <c r="O12">
-        <v>7.4171703240471381e-05</v>
+        <v>4.6884944178442028e-05</v>
       </c>
       <c r="P12">
-        <v>7.4591154438736557e-05</v>
+        <v>4.7176437306905528e-05</v>
       </c>
       <c r="Q12">
-        <v>7.4132991558448428e-05</v>
+        <v>4.6846647944421673e-05</v>
       </c>
       <c r="R12">
-        <v>7.4244361150923568e-05</v>
+        <v>4.6922506101528113e-05</v>
       </c>
       <c r="S12">
-        <v>3.9837159036709628e-07</v>
+        <v>3.7665197011923627e-07</v>
       </c>
       <c r="T12">
-        <v>2.108940395087655e-08</v>
+        <v>1.7276710674373856e-07</v>
       </c>
       <c r="U12">
-        <v>9.0112460417230126e-07</v>
+        <v>3.139075213811659e-08</v>
       </c>
       <c r="V12">
-        <v>6.0701718043850161e-08</v>
+        <v>-3.7746945115730733e-07</v>
       </c>
       <c r="W12">
-        <v>-8.3863266022522363e-05</v>
+        <v>-7.1134568991818329e-05</v>
       </c>
       <c r="X12">
-        <v>2.6692290579696258e-06</v>
+        <v>2.0739626442682634e-06</v>
       </c>
     </row>
     <row r="13">
@@ -2909,73 +2909,73 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>0.15132460854612329</v>
+        <v>0.15557706192950091</v>
       </c>
       <c r="C13">
-        <v>-1.2429554423605797e-07</v>
+        <v>4.380868490048439e-08</v>
       </c>
       <c r="D13">
-        <v>1.9823002188435579e-09</v>
+        <v>-1.8337673303141687e-10</v>
       </c>
       <c r="E13">
-        <v>4.5087434092918401e-06</v>
+        <v>2.4120803576117145e-06</v>
       </c>
       <c r="F13">
-        <v>5.7975966129483781e-06</v>
+        <v>3.0301203591299258e-06</v>
       </c>
       <c r="G13">
-        <v>-4.904756381215579e-08</v>
+        <v>-2.1417050174670084e-08</v>
       </c>
       <c r="H13">
-        <v>-1.6956543593306618e-08</v>
+        <v>-5.9895431393608689e-10</v>
       </c>
       <c r="I13">
-        <v>1.5455017151122618e-06</v>
+        <v>2.4874756927726963e-06</v>
       </c>
       <c r="J13">
-        <v>-1.4779176683123049e-06</v>
+        <v>8.2129124583263951e-07</v>
       </c>
       <c r="K13">
-        <v>-3.0040119527045583e-06</v>
+        <v>2.2814319343545029e-07</v>
       </c>
       <c r="L13">
-        <v>-5.9560557073772939e-06</v>
+        <v>-1.4740194276012787e-06</v>
       </c>
       <c r="M13">
-        <v>7.4827224056829507e-05</v>
+        <v>4.7316968276197888e-05</v>
       </c>
       <c r="N13">
-        <v>0.00016323746615097792</v>
+        <v>0.00010108394079083829</v>
       </c>
       <c r="O13">
-        <v>7.4112952429227999e-05</v>
+        <v>4.6825807754023282e-05</v>
       </c>
       <c r="P13">
-        <v>7.483639957959104e-05</v>
+        <v>4.7266918584361561e-05</v>
       </c>
       <c r="Q13">
-        <v>7.4379342720015101e-05</v>
+        <v>4.6938619103807022e-05</v>
       </c>
       <c r="R13">
-        <v>7.455016886991753e-05</v>
+        <v>4.7084381253587998e-05</v>
       </c>
       <c r="S13">
-        <v>-3.5025303400271095e-08</v>
+        <v>4.3496486255882944e-07</v>
       </c>
       <c r="T13">
-        <v>-4.6074476685752659e-08</v>
+        <v>-1.7895408280841728e-07</v>
       </c>
       <c r="U13">
-        <v>9.4264166016684592e-07</v>
+        <v>9.9631696083391135e-07</v>
       </c>
       <c r="V13">
-        <v>-1.0940146485748192e-06</v>
+        <v>-3.6088785329453103e-07</v>
       </c>
       <c r="W13">
-        <v>-6.6817725967629674e-05</v>
+        <v>-3.2179817211009222e-05</v>
       </c>
       <c r="X13">
-        <v>-1.4098477318437173e-06</v>
+        <v>6.6739022485783718e-08</v>
       </c>
     </row>
     <row r="14">
@@ -2983,73 +2983,73 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>-0.043663116326313735</v>
+        <v>-0.040197828195555833</v>
       </c>
       <c r="C14">
-        <v>7.7709607190259538e-08</v>
+        <v>4.4122284688709487e-08</v>
       </c>
       <c r="D14">
-        <v>-4.2475825882080202e-10</v>
+        <v>-2.9514634650504945e-10</v>
       </c>
       <c r="E14">
-        <v>1.6398229552421353e-06</v>
+        <v>7.6900538884351821e-07</v>
       </c>
       <c r="F14">
-        <v>-4.7376194903435959e-06</v>
+        <v>-2.6209433696631801e-06</v>
       </c>
       <c r="G14">
-        <v>-5.5546074287435023e-08</v>
+        <v>-2.8757219342061482e-08</v>
       </c>
       <c r="H14">
-        <v>-5.7309398588232916e-10</v>
+        <v>-7.0701380993573055e-09</v>
       </c>
       <c r="I14">
-        <v>9.5856361227497586e-07</v>
+        <v>1.1930872587068983e-06</v>
       </c>
       <c r="J14">
-        <v>-2.7374452220560306e-06</v>
+        <v>-9.6624730398145827e-07</v>
       </c>
       <c r="K14">
-        <v>-4.4163774647249155e-06</v>
+        <v>-2.1056621502812261e-06</v>
       </c>
       <c r="L14">
-        <v>-4.9112941044887004e-06</v>
+        <v>-2.4543342064783845e-06</v>
       </c>
       <c r="M14">
-        <v>7.4171703240471381e-05</v>
+        <v>4.6884944178442028e-05</v>
       </c>
       <c r="N14">
-        <v>7.4112952429227999e-05</v>
+        <v>4.6825807754023282e-05</v>
       </c>
       <c r="O14">
-        <v>0.00013455134718316943</v>
+        <v>8.51416296336889e-05</v>
       </c>
       <c r="P14">
-        <v>7.4575163132703875e-05</v>
+        <v>4.7089110981367829e-05</v>
       </c>
       <c r="Q14">
-        <v>7.5061121072342221e-05</v>
+        <v>4.7437548052888804e-05</v>
       </c>
       <c r="R14">
-        <v>7.4640097104323392e-05</v>
+        <v>4.7162560233743226e-05</v>
       </c>
       <c r="S14">
-        <v>9.5616344297695552e-07</v>
+        <v>-3.8558696130886547e-07</v>
       </c>
       <c r="T14">
-        <v>-3.5560492381224271e-08</v>
+        <v>-9.078536228236172e-08</v>
       </c>
       <c r="U14">
-        <v>-2.2942199197662599e-07</v>
+        <v>-1.275282769523594e-07</v>
       </c>
       <c r="V14">
-        <v>-1.4639647522614751e-07</v>
+        <v>-2.3709729775831237e-08</v>
       </c>
       <c r="W14">
-        <v>-6.6806155722915937e-05</v>
+        <v>-3.5990810904028854e-05</v>
       </c>
       <c r="X14">
-        <v>-8.6319366535271177e-07</v>
+        <v>-4.511587874639927e-07</v>
       </c>
     </row>
     <row r="15">
@@ -3057,73 +3057,73 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>0.097711552856478465</v>
+        <v>0.1007388342949881</v>
       </c>
       <c r="C15">
-        <v>1.4610405126855955e-07</v>
+        <v>2.3827625833281059e-07</v>
       </c>
       <c r="D15">
-        <v>-1.5467672006439117e-09</v>
+        <v>-2.5128847962562099e-09</v>
       </c>
       <c r="E15">
-        <v>1.6777172942240577e-06</v>
+        <v>1.3072263182490793e-06</v>
       </c>
       <c r="F15">
-        <v>-4.5306049353335566e-06</v>
+        <v>-1.9724439576049307e-06</v>
       </c>
       <c r="G15">
-        <v>-4.4243220338563667e-08</v>
+        <v>-3.2425692134887075e-08</v>
       </c>
       <c r="H15">
-        <v>8.6993322627702071e-08</v>
+        <v>3.8395609796791128e-08</v>
       </c>
       <c r="I15">
-        <v>3.1054125130754121e-06</v>
+        <v>2.0021600693850307e-06</v>
       </c>
       <c r="J15">
-        <v>8.1508862488486024e-07</v>
+        <v>6.8152339478594483e-07</v>
       </c>
       <c r="K15">
-        <v>5.8294615533189446e-08</v>
+        <v>3.553171303792283e-07</v>
       </c>
       <c r="L15">
-        <v>-4.1235156255856757e-06</v>
+        <v>-2.0935206828177745e-06</v>
       </c>
       <c r="M15">
-        <v>7.4591154438736557e-05</v>
+        <v>4.7176437306905528e-05</v>
       </c>
       <c r="N15">
-        <v>7.483639957959104e-05</v>
+        <v>4.7266918584361561e-05</v>
       </c>
       <c r="O15">
-        <v>7.4575163132703875e-05</v>
+        <v>4.7089110981367829e-05</v>
       </c>
       <c r="P15">
-        <v>0.00011523102575247914</v>
+        <v>7.0976359353320517e-05</v>
       </c>
       <c r="Q15">
-        <v>7.4879205080853096e-05</v>
+        <v>4.7242990058070845e-05</v>
       </c>
       <c r="R15">
-        <v>7.4747049745887769e-05</v>
+        <v>4.7220256880313026e-05</v>
       </c>
       <c r="S15">
-        <v>-1.7815615428799294e-06</v>
+        <v>2.8194387418862452e-07</v>
       </c>
       <c r="T15">
-        <v>-1.2988473801113131e-07</v>
+        <v>-5.124505496224439e-07</v>
       </c>
       <c r="U15">
-        <v>4.3188658387198656e-06</v>
+        <v>3.7968176110638784e-06</v>
       </c>
       <c r="V15">
-        <v>3.7205872734100176e-06</v>
+        <v>3.309427656934714e-06</v>
       </c>
       <c r="W15">
-        <v>-6.3414927617280324e-05</v>
+        <v>-1.340213646973437e-06</v>
       </c>
       <c r="X15">
-        <v>9.0355096247470089e-07</v>
+        <v>1.0580653316468206e-06</v>
       </c>
     </row>
     <row r="16">
@@ -3131,73 +3131,73 @@
         <v>37</v>
       </c>
       <c r="B16">
-        <v>0.017081308255933125</v>
+        <v>0.0092736149766526437</v>
       </c>
       <c r="C16">
-        <v>-5.8622239572058345e-07</v>
+        <v>-2.99062881405449e-07</v>
       </c>
       <c r="D16">
-        <v>6.542959569119153e-09</v>
+        <v>3.3443603061827796e-09</v>
       </c>
       <c r="E16">
-        <v>-2.1487808375777844e-06</v>
+        <v>-1.0766089063389579e-06</v>
       </c>
       <c r="F16">
-        <v>-1.3161790907493813e-05</v>
+        <v>-7.5058704414926041e-06</v>
       </c>
       <c r="G16">
-        <v>2.8424868198247749e-08</v>
+        <v>1.2513510070548327e-08</v>
       </c>
       <c r="H16">
-        <v>1.9031464901169752e-07</v>
+        <v>1.0202727998399963e-07</v>
       </c>
       <c r="I16">
-        <v>4.8937629180182282e-06</v>
+        <v>2.0798043023296797e-06</v>
       </c>
       <c r="J16">
-        <v>-8.2517039709554159e-08</v>
+        <v>-1.0839373045809267e-06</v>
       </c>
       <c r="K16">
-        <v>-1.6608126507197853e-06</v>
+        <v>-2.2292834289343421e-06</v>
       </c>
       <c r="L16">
-        <v>-5.2477150013399959e-06</v>
+        <v>-4.3514767903426905e-06</v>
       </c>
       <c r="M16">
-        <v>7.4132991558448428e-05</v>
+        <v>4.6846647944421673e-05</v>
       </c>
       <c r="N16">
-        <v>7.4379342720015101e-05</v>
+        <v>4.6938619103807022e-05</v>
       </c>
       <c r="O16">
-        <v>7.5061121072342221e-05</v>
+        <v>4.7437548052888804e-05</v>
       </c>
       <c r="P16">
-        <v>7.4879205080853096e-05</v>
+        <v>4.7242990058070845e-05</v>
       </c>
       <c r="Q16">
-        <v>0.00013101690477241223</v>
+        <v>8.2301326942635627e-05</v>
       </c>
       <c r="R16">
-        <v>7.5348673286032678e-05</v>
+        <v>4.7564827657778204e-05</v>
       </c>
       <c r="S16">
-        <v>-4.016345663725339e-07</v>
+        <v>-9.2991343076317298e-07</v>
       </c>
       <c r="T16">
-        <v>-5.3347096457564854e-08</v>
+        <v>-2.4670300268298013e-07</v>
       </c>
       <c r="U16">
-        <v>6.193969332404872e-07</v>
+        <v>1.0448503742937948e-06</v>
       </c>
       <c r="V16">
-        <v>2.3220694810097234e-07</v>
+        <v>7.8771671293451827e-07</v>
       </c>
       <c r="W16">
-        <v>-5.0998528824526807e-05</v>
+        <v>-1.1638070097909952e-05</v>
       </c>
       <c r="X16">
-        <v>-5.1728085315299949e-06</v>
+        <v>-2.8664403560488243e-06</v>
       </c>
     </row>
     <row r="17">
@@ -3205,73 +3205,73 @@
         <v>38</v>
       </c>
       <c r="B17">
-        <v>-0.035664536914295247</v>
+        <v>-0.051315773389335059</v>
       </c>
       <c r="C17">
-        <v>-1.7005921930215995e-07</v>
+        <v>-1.7545300850464649e-07</v>
       </c>
       <c r="D17">
-        <v>1.5411730349516057e-09</v>
+        <v>1.7804072977194792e-09</v>
       </c>
       <c r="E17">
-        <v>-5.9019995185752376e-06</v>
+        <v>-3.8249167689963524e-06</v>
       </c>
       <c r="F17">
-        <v>-8.3586095746351317e-06</v>
+        <v>-4.7843497757450738e-06</v>
       </c>
       <c r="G17">
-        <v>1.1306879042275067e-07</v>
+        <v>7.8209858965876035e-08</v>
       </c>
       <c r="H17">
-        <v>1.6034629992247997e-07</v>
+        <v>9.5432132150408785e-08</v>
       </c>
       <c r="I17">
-        <v>2.9655036441781254e-06</v>
+        <v>2.2271271196166561e-06</v>
       </c>
       <c r="J17">
-        <v>-1.4352033668420956e-06</v>
+        <v>-6.6015261868477459e-07</v>
       </c>
       <c r="K17">
-        <v>8.5926167486825056e-07</v>
+        <v>7.9549732674391419e-07</v>
       </c>
       <c r="L17">
-        <v>-4.3115264646801797e-06</v>
+        <v>-2.3173572496350908e-06</v>
       </c>
       <c r="M17">
-        <v>7.4244361150923568e-05</v>
+        <v>4.6922506101528113e-05</v>
       </c>
       <c r="N17">
-        <v>7.455016886991753e-05</v>
+        <v>4.7084381253587998e-05</v>
       </c>
       <c r="O17">
-        <v>7.4640097104323392e-05</v>
+        <v>4.7162560233743226e-05</v>
       </c>
       <c r="P17">
-        <v>7.4747049745887769e-05</v>
+        <v>4.7220256880313026e-05</v>
       </c>
       <c r="Q17">
-        <v>7.5348673286032678e-05</v>
+        <v>4.7564827657778204e-05</v>
       </c>
       <c r="R17">
-        <v>0.00037037823000432856</v>
+        <v>0.00023219852991016572</v>
       </c>
       <c r="S17">
-        <v>-2.2768809449850723e-07</v>
+        <v>-6.0215449896334543e-07</v>
       </c>
       <c r="T17">
-        <v>3.4890119805456863e-08</v>
+        <v>8.6609719655588869e-08</v>
       </c>
       <c r="U17">
-        <v>1.7239860882597988e-06</v>
+        <v>1.1295128361037212e-06</v>
       </c>
       <c r="V17">
-        <v>1.0515436407688073e-06</v>
+        <v>8.3451214705338291e-07</v>
       </c>
       <c r="W17">
-        <v>-7.1304336271863362e-05</v>
+        <v>-5.0555335630387713e-05</v>
       </c>
       <c r="X17">
-        <v>-6.600903574208328e-06</v>
+        <v>-3.9298627327537028e-06</v>
       </c>
     </row>
     <row r="18">
@@ -3279,73 +3279,73 @@
         <v>39</v>
       </c>
       <c r="B18">
-        <v>0.011255856262466765</v>
+        <v>0.11249909852080556</v>
       </c>
       <c r="C18">
-        <v>2.2109437456303696e-06</v>
+        <v>6.3831462097915736e-07</v>
       </c>
       <c r="D18">
-        <v>-1.8798484543004069e-08</v>
+        <v>-6.5396647830094919e-09</v>
       </c>
       <c r="E18">
-        <v>7.1369334377269769e-07</v>
+        <v>-6.1745447681902818e-07</v>
       </c>
       <c r="F18">
-        <v>9.0889919330291049e-06</v>
+        <v>2.6551264185437377e-06</v>
       </c>
       <c r="G18">
-        <v>-3.8447159166000082e-08</v>
+        <v>4.9620404200772498e-08</v>
       </c>
       <c r="H18">
-        <v>-1.6633381307028806e-07</v>
+        <v>2.166237268980406e-08</v>
       </c>
       <c r="I18">
-        <v>3.7362791813685918e-06</v>
+        <v>1.1803478862580395e-06</v>
       </c>
       <c r="J18">
-        <v>-9.8387610132932602e-07</v>
+        <v>2.1909178074049111e-07</v>
       </c>
       <c r="K18">
-        <v>6.3989531030515949e-09</v>
+        <v>2.2873187431132911e-07</v>
       </c>
       <c r="L18">
-        <v>2.6199108956384544e-07</v>
+        <v>-3.4224784417662871e-07</v>
       </c>
       <c r="M18">
-        <v>3.9837159036709628e-07</v>
+        <v>3.7665197011923627e-07</v>
       </c>
       <c r="N18">
-        <v>-3.5025303400271095e-08</v>
+        <v>4.3496486255882944e-07</v>
       </c>
       <c r="O18">
-        <v>9.5616344297695552e-07</v>
+        <v>-3.8558696130886547e-07</v>
       </c>
       <c r="P18">
-        <v>-1.7815615428799294e-06</v>
+        <v>2.8194387418862452e-07</v>
       </c>
       <c r="Q18">
-        <v>-4.016345663725339e-07</v>
+        <v>-9.2991343076317298e-07</v>
       </c>
       <c r="R18">
-        <v>-2.2768809449850723e-07</v>
+        <v>-6.0215449896334543e-07</v>
       </c>
       <c r="S18">
-        <v>0.00022116991144535667</v>
+        <v>5.6055650708995507e-05</v>
       </c>
       <c r="T18">
-        <v>-5.9462736773577274e-08</v>
+        <v>-1.3392042174056749e-07</v>
       </c>
       <c r="U18">
-        <v>-6.1083995110803917e-07</v>
+        <v>1.1238324281131318e-07</v>
       </c>
       <c r="V18">
-        <v>-1.1254517846751124e-06</v>
+        <v>-7.3402692833243432e-07</v>
       </c>
       <c r="W18">
-        <v>-5.6342212932593192e-05</v>
+        <v>-7.5158473762935867e-06</v>
       </c>
       <c r="X18">
-        <v>-1.7589958552603652e-05</v>
+        <v>-6.1795548449070217e-06</v>
       </c>
     </row>
     <row r="19">
@@ -3353,73 +3353,73 @@
         <v>40</v>
       </c>
       <c r="B19">
-        <v>-0.0001708365504700716</v>
+        <v>0.0030025822199691017</v>
       </c>
       <c r="C19">
-        <v>1.5736596529589868e-08</v>
+        <v>9.2347866611862261e-08</v>
       </c>
       <c r="D19">
-        <v>-2.4883764556573461e-10</v>
+        <v>-1.318850483344708e-09</v>
       </c>
       <c r="E19">
-        <v>1.2278271127015002e-07</v>
+        <v>5.8779696145160811e-07</v>
       </c>
       <c r="F19">
-        <v>1.7180943560402525e-07</v>
+        <v>8.5086434858341272e-07</v>
       </c>
       <c r="G19">
-        <v>-1.2913184765141024e-09</v>
+        <v>-6.9565804294949885e-09</v>
       </c>
       <c r="H19">
-        <v>-2.7092590079700373e-11</v>
+        <v>-3.0193255652640209e-09</v>
       </c>
       <c r="I19">
-        <v>9.5543821248701074e-08</v>
+        <v>2.6170602307804488e-07</v>
       </c>
       <c r="J19">
-        <v>8.0234823580471861e-08</v>
+        <v>2.2576538981983191e-07</v>
       </c>
       <c r="K19">
-        <v>1.8104826321824563e-07</v>
+        <v>5.24114297731499e-07</v>
       </c>
       <c r="L19">
-        <v>2.2188270726498923e-07</v>
+        <v>6.9030153453445602e-07</v>
       </c>
       <c r="M19">
-        <v>2.108940395087655e-08</v>
+        <v>1.7276710674373856e-07</v>
       </c>
       <c r="N19">
-        <v>-4.6074476685752659e-08</v>
+        <v>-1.7895408280841728e-07</v>
       </c>
       <c r="O19">
-        <v>-3.5560492381224271e-08</v>
+        <v>-9.078536228236172e-08</v>
       </c>
       <c r="P19">
-        <v>-1.2988473801113131e-07</v>
+        <v>-5.124505496224439e-07</v>
       </c>
       <c r="Q19">
-        <v>-5.3347096457564854e-08</v>
+        <v>-2.4670300268298013e-07</v>
       </c>
       <c r="R19">
-        <v>3.4890119805456863e-08</v>
+        <v>8.6609719655588869e-08</v>
       </c>
       <c r="S19">
-        <v>-5.9462736773577274e-08</v>
+        <v>-1.3392042174056749e-07</v>
       </c>
       <c r="T19">
-        <v>5.6844512981593905e-08</v>
+        <v>2.6825903495362383e-06</v>
       </c>
       <c r="U19">
-        <v>-7.5538463255733704e-07</v>
+        <v>-9.8491095138724426e-06</v>
       </c>
       <c r="V19">
-        <v>-9.2778324490427186e-07</v>
+        <v>-1.0019804652105466e-05</v>
       </c>
       <c r="W19">
-        <v>-6.622784648321054e-06</v>
+        <v>-0.00027211715918463292</v>
       </c>
       <c r="X19">
-        <v>4.9944660398948163e-08</v>
+        <v>2.2624288011360063e-07</v>
       </c>
     </row>
     <row r="20">
@@ -3427,73 +3427,73 @@
         <v>41</v>
       </c>
       <c r="B20">
-        <v>-0.062314234559333756</v>
+        <v>-0.074508971438190949</v>
       </c>
       <c r="C20">
-        <v>-2.0270337464454527e-07</v>
+        <v>-4.4559128900166206e-07</v>
       </c>
       <c r="D20">
-        <v>2.1449056192622969e-09</v>
+        <v>5.5683694421109859e-09</v>
       </c>
       <c r="E20">
-        <v>-9.7762331634457306e-07</v>
+        <v>-2.0959982591894199e-06</v>
       </c>
       <c r="F20">
-        <v>-2.2057779769789285e-07</v>
+        <v>-1.8732273009389505e-06</v>
       </c>
       <c r="G20">
-        <v>-3.6107723187413001e-10</v>
+        <v>1.9010334441766715e-08</v>
       </c>
       <c r="H20">
-        <v>-1.8127540823070135e-08</v>
+        <v>-7.4089991632828871e-09</v>
       </c>
       <c r="I20">
-        <v>-1.5501773062014169e-07</v>
+        <v>-9.7178305191811022e-07</v>
       </c>
       <c r="J20">
-        <v>1.0073893522078189e-06</v>
+        <v>-4.6147680511370409e-07</v>
       </c>
       <c r="K20">
-        <v>-1.0977318535794971e-06</v>
+        <v>-2.3594303585497083e-06</v>
       </c>
       <c r="L20">
-        <v>-2.5750495194650927e-06</v>
+        <v>-3.5735310416959659e-06</v>
       </c>
       <c r="M20">
-        <v>9.0112460417230126e-07</v>
+        <v>3.139075213811659e-08</v>
       </c>
       <c r="N20">
-        <v>9.4264166016684592e-07</v>
+        <v>9.9631696083391135e-07</v>
       </c>
       <c r="O20">
-        <v>-2.2942199197662599e-07</v>
+        <v>-1.275282769523594e-07</v>
       </c>
       <c r="P20">
-        <v>4.3188658387198656e-06</v>
+        <v>3.7968176110638784e-06</v>
       </c>
       <c r="Q20">
-        <v>6.193969332404872e-07</v>
+        <v>1.0448503742937948e-06</v>
       </c>
       <c r="R20">
-        <v>1.7239860882597988e-06</v>
+        <v>1.1295128361037212e-06</v>
       </c>
       <c r="S20">
-        <v>-6.1083995110803917e-07</v>
+        <v>1.1238324281131318e-07</v>
       </c>
       <c r="T20">
-        <v>-7.5538463255733704e-07</v>
+        <v>-9.8491095138724426e-06</v>
       </c>
       <c r="U20">
-        <v>0.00016794719842589889</v>
+        <v>0.00014901235678002711</v>
       </c>
       <c r="V20">
-        <v>2.3568529027360461e-05</v>
+        <v>4.3522314412432709e-05</v>
       </c>
       <c r="W20">
-        <v>7.6629953069317166e-05</v>
+        <v>0.00099553256909250786</v>
       </c>
       <c r="X20">
-        <v>2.3284724900516203e-07</v>
+        <v>-8.8023992502645066e-07</v>
       </c>
     </row>
     <row r="21">
@@ -3501,73 +3501,73 @@
         <v>42</v>
       </c>
       <c r="B21">
-        <v>-0.018575825220133402</v>
+        <v>-0.030273208814415358</v>
       </c>
       <c r="C21">
-        <v>-1.4458300968294122e-07</v>
+        <v>-3.4696848245923081e-07</v>
       </c>
       <c r="D21">
-        <v>1.5389260456839868e-09</v>
+        <v>4.4451197735316568e-09</v>
       </c>
       <c r="E21">
-        <v>2.625870444742593e-07</v>
+        <v>-1.1654882370044985e-06</v>
       </c>
       <c r="F21">
-        <v>-1.0903998764887966e-06</v>
+        <v>-2.3220229144512334e-06</v>
       </c>
       <c r="G21">
-        <v>1.4467321154248042e-09</v>
+        <v>1.6026538654936847e-08</v>
       </c>
       <c r="H21">
-        <v>2.4466884577962495e-08</v>
+        <v>1.8777698169445832e-08</v>
       </c>
       <c r="I21">
-        <v>1.0759202719307106e-06</v>
+        <v>-2.4068820777528743e-07</v>
       </c>
       <c r="J21">
-        <v>-8.0311933206678084e-08</v>
+        <v>-1.0352812569220545e-06</v>
       </c>
       <c r="K21">
-        <v>-1.8309771369108177e-07</v>
+        <v>-1.4475734578342303e-06</v>
       </c>
       <c r="L21">
-        <v>-1.6327764701196598e-06</v>
+        <v>-2.5430432574825612e-06</v>
       </c>
       <c r="M21">
-        <v>6.0701718043850161e-08</v>
+        <v>-3.7746945115730733e-07</v>
       </c>
       <c r="N21">
-        <v>-1.0940146485748192e-06</v>
+        <v>-3.6088785329453103e-07</v>
       </c>
       <c r="O21">
-        <v>-1.4639647522614751e-07</v>
+        <v>-2.3709729775831237e-08</v>
       </c>
       <c r="P21">
-        <v>3.7205872734100176e-06</v>
+        <v>3.309427656934714e-06</v>
       </c>
       <c r="Q21">
-        <v>2.3220694810097234e-07</v>
+        <v>7.8771671293451827e-07</v>
       </c>
       <c r="R21">
-        <v>1.0515436407688073e-06</v>
+        <v>8.3451214705338291e-07</v>
       </c>
       <c r="S21">
-        <v>-1.1254517846751124e-06</v>
+        <v>-7.3402692833243432e-07</v>
       </c>
       <c r="T21">
-        <v>-9.2778324490427186e-07</v>
+        <v>-1.0019804652105466e-05</v>
       </c>
       <c r="U21">
-        <v>2.3568529027360461e-05</v>
+        <v>4.3522314412432709e-05</v>
       </c>
       <c r="V21">
-        <v>0.00017370943964181869</v>
+        <v>0.00014960385826336608</v>
       </c>
       <c r="W21">
-        <v>9.2174508320160394e-05</v>
+        <v>0.0010091054864431934</v>
       </c>
       <c r="X21">
-        <v>3.9543046276547882e-06</v>
+        <v>1.9602230418419477e-06</v>
       </c>
     </row>
     <row r="22">
@@ -3575,73 +3575,73 @@
         <v>43</v>
       </c>
       <c r="B22">
-        <v>1.5303832830444042</v>
+        <v>1.2202177544122985</v>
       </c>
       <c r="C22">
-        <v>-0.00012546612458146881</v>
+        <v>-8.6135704860567633e-05</v>
       </c>
       <c r="D22">
-        <v>1.3215511423378105e-06</v>
+        <v>9.337960431079408e-07</v>
       </c>
       <c r="E22">
-        <v>-0.00052351916991724744</v>
+        <v>-0.00037464939001333083</v>
       </c>
       <c r="F22">
-        <v>-0.00043242440922887089</v>
+        <v>-0.00033166157308438439</v>
       </c>
       <c r="G22">
-        <v>1.0733386389793854e-05</v>
+        <v>7.3433440236952521e-06</v>
       </c>
       <c r="H22">
-        <v>8.6572351378183877e-06</v>
+        <v>5.5634150626270134e-06</v>
       </c>
       <c r="I22">
-        <v>-0.0036563720781899256</v>
+        <v>-0.0020177277923954578</v>
       </c>
       <c r="J22">
-        <v>-0.0037072313160477605</v>
+        <v>-0.0020470076158963044</v>
       </c>
       <c r="K22">
-        <v>-0.003754808394680227</v>
+        <v>-0.0020984949640080559</v>
       </c>
       <c r="L22">
-        <v>-0.0038091760120159525</v>
+        <v>-0.0021453854904648724</v>
       </c>
       <c r="M22">
-        <v>-8.3863266022522363e-05</v>
+        <v>-7.1134568991818329e-05</v>
       </c>
       <c r="N22">
-        <v>-6.6817725967629674e-05</v>
+        <v>-3.2179817211009222e-05</v>
       </c>
       <c r="O22">
-        <v>-6.6806155722915937e-05</v>
+        <v>-3.5990810904028854e-05</v>
       </c>
       <c r="P22">
-        <v>-6.3414927617280324e-05</v>
+        <v>-1.340213646973437e-06</v>
       </c>
       <c r="Q22">
-        <v>-5.0998528824526807e-05</v>
+        <v>-1.1638070097909952e-05</v>
       </c>
       <c r="R22">
-        <v>-7.1304336271863362e-05</v>
+        <v>-5.0555335630387713e-05</v>
       </c>
       <c r="S22">
-        <v>-5.6342212932593192e-05</v>
+        <v>-7.5158473762935867e-06</v>
       </c>
       <c r="T22">
-        <v>-6.622784648321054e-06</v>
+        <v>-0.00027211715918463292</v>
       </c>
       <c r="U22">
-        <v>7.6629953069317166e-05</v>
+        <v>0.00099553256909250786</v>
       </c>
       <c r="V22">
-        <v>9.2174508320160394e-05</v>
+        <v>0.0010091054864431934</v>
       </c>
       <c r="W22">
-        <v>0.0074745520009505606</v>
+        <v>0.03149410169124052</v>
       </c>
       <c r="X22">
-        <v>-0.00029261682456252708</v>
+        <v>-0.00020369333500919038</v>
       </c>
     </row>
     <row r="23">
@@ -3649,73 +3649,73 @@
         <v>44</v>
       </c>
       <c r="B23">
-        <v>-0.46359966921410784</v>
+        <v>-0.35513461619989861</v>
       </c>
       <c r="C23">
-        <v>1.0455581032611639e-05</v>
+        <v>6.7069195917287852e-06</v>
       </c>
       <c r="D23">
-        <v>-1.2125604381215531e-07</v>
+        <v>-7.6213490241779506e-08</v>
       </c>
       <c r="E23">
-        <v>-1.7951586308822488e-05</v>
+        <v>-1.035688868389197e-05</v>
       </c>
       <c r="F23">
-        <v>-2.5682604106283385e-05</v>
+        <v>-1.6851567021776492e-05</v>
       </c>
       <c r="G23">
-        <v>4.081895060385785e-07</v>
+        <v>1.8119699709677232e-07</v>
       </c>
       <c r="H23">
-        <v>3.8631899123312303e-07</v>
+        <v>2.0285732989710305e-07</v>
       </c>
       <c r="I23">
-        <v>1.6181417415004284e-05</v>
+        <v>6.8887760842260003e-06</v>
       </c>
       <c r="J23">
-        <v>4.0437956469392843e-05</v>
+        <v>2.2186131349639733e-05</v>
       </c>
       <c r="K23">
-        <v>5.0837439620828661e-05</v>
+        <v>2.8872792830923177e-05</v>
       </c>
       <c r="L23">
-        <v>5.2035651785058216e-05</v>
+        <v>2.9927801989330906e-05</v>
       </c>
       <c r="M23">
-        <v>2.6692290579696258e-06</v>
+        <v>2.0739626442682634e-06</v>
       </c>
       <c r="N23">
-        <v>-1.4098477318437173e-06</v>
+        <v>6.6739022485783718e-08</v>
       </c>
       <c r="O23">
-        <v>-8.6319366535271177e-07</v>
+        <v>-4.511587874639927e-07</v>
       </c>
       <c r="P23">
-        <v>9.0355096247470089e-07</v>
+        <v>1.0580653316468206e-06</v>
       </c>
       <c r="Q23">
-        <v>-5.1728085315299949e-06</v>
+        <v>-2.8664403560488243e-06</v>
       </c>
       <c r="R23">
-        <v>-6.600903574208328e-06</v>
+        <v>-3.9298627327537028e-06</v>
       </c>
       <c r="S23">
-        <v>-1.7589958552603652e-05</v>
+        <v>-6.1795548449070217e-06</v>
       </c>
       <c r="T23">
-        <v>4.9944660398948163e-08</v>
+        <v>2.2624288011360063e-07</v>
       </c>
       <c r="U23">
-        <v>2.3284724900516203e-07</v>
+        <v>-8.8023992502645066e-07</v>
       </c>
       <c r="V23">
-        <v>3.9543046276547882e-06</v>
+        <v>1.9602230418419477e-06</v>
       </c>
       <c r="W23">
-        <v>-0.00029261682456252708</v>
+        <v>-0.00020369333500919038</v>
       </c>
       <c r="X23">
-        <v>9.8800029494914502e-05</v>
+        <v>6.3399253414147367e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3809,76 +3809,76 @@
         <v>46</v>
       </c>
       <c r="B2">
-        <v>0.78860836541144197</v>
+        <v>0.83490606256408417</v>
       </c>
       <c r="C2">
-        <v>8.5705127900287207e-06</v>
+        <v>5.4149444841903821e-06</v>
       </c>
       <c r="D2">
-        <v>-1.798538716780193e-07</v>
+        <v>-1.9170400435041665e-07</v>
       </c>
       <c r="E2">
-        <v>4.5337090293373758e-10</v>
+        <v>1.1102350662795997e-09</v>
       </c>
       <c r="F2">
-        <v>1.3731519445720949e-06</v>
+        <v>9.3179337954984099e-07</v>
       </c>
       <c r="G2">
-        <v>1.2278557895288793e-07</v>
+        <v>2.089789604934276e-07</v>
       </c>
       <c r="H2">
-        <v>4.2884938157551056e-08</v>
+        <v>2.7941512939287481e-08</v>
       </c>
       <c r="I2">
-        <v>1.0261761662782507e-07</v>
+        <v>6.4904040226913373e-08</v>
       </c>
       <c r="J2">
-        <v>-1.1499834255349719e-06</v>
+        <v>-6.9382535870024479e-08</v>
       </c>
       <c r="K2">
-        <v>-1.2957962179887819e-06</v>
+        <v>-4.389170197566782e-07</v>
       </c>
       <c r="L2">
-        <v>-1.7967812804220199e-06</v>
+        <v>-8.2474746917796295e-07</v>
       </c>
       <c r="M2">
-        <v>-2.2634741526766576e-06</v>
+        <v>-1.1548416059109898e-06</v>
       </c>
       <c r="N2">
-        <v>-1.8719351822892052e-06</v>
+        <v>-1.0802015969646813e-06</v>
       </c>
       <c r="O2">
-        <v>-1.6827737793938412e-06</v>
+        <v>-9.968017005840478e-07</v>
       </c>
       <c r="P2">
-        <v>-8.4839324090577684e-07</v>
+        <v>-4.1098103065741263e-07</v>
       </c>
       <c r="Q2">
-        <v>-1.4426751589838297e-06</v>
+        <v>-8.503463491871904e-07</v>
       </c>
       <c r="R2">
-        <v>-1.102521802711483e-06</v>
+        <v>-4.9303470864363799e-07</v>
       </c>
       <c r="S2">
-        <v>-8.0883417878357524e-07</v>
+        <v>-4.0457110883420921e-07</v>
       </c>
       <c r="T2">
-        <v>1.4876913557592861e-06</v>
+        <v>1.5961393929950517e-07</v>
       </c>
       <c r="U2">
-        <v>1.3669052619210692e-08</v>
+        <v>3.7565263323006585e-08</v>
       </c>
       <c r="V2">
-        <v>1.1089614151102615e-07</v>
+        <v>1.2109519962481994e-07</v>
       </c>
       <c r="W2">
-        <v>5.10240037640505e-07</v>
+        <v>3.0392419529036894e-07</v>
       </c>
       <c r="X2">
-        <v>-1.2993195352891279e-05</v>
+        <v>-9.5958740143851906e-06</v>
       </c>
       <c r="Y2">
-        <v>3.2475171196025608e-06</v>
+        <v>4.2058815475524122e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3886,76 +3886,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>0.011118117400467526</v>
+        <v>0.0090653067350520387</v>
       </c>
       <c r="C3">
-        <v>-1.798538716780193e-07</v>
+        <v>-1.9170400435041665e-07</v>
       </c>
       <c r="D3">
-        <v>2.9649461797543819e-05</v>
+        <v>1.1192572000669344e-05</v>
       </c>
       <c r="E3">
-        <v>-3.2458902172785458e-07</v>
+        <v>-1.2185083522255474e-07</v>
       </c>
       <c r="F3">
-        <v>-6.3412882352260221e-05</v>
+        <v>-2.0201999328672566e-05</v>
       </c>
       <c r="G3">
-        <v>-7.0012676377104817e-05</v>
+        <v>-2.5637694875882812e-05</v>
       </c>
       <c r="H3">
-        <v>9.7898650168773815e-07</v>
+        <v>2.5659718394078791e-07</v>
       </c>
       <c r="I3">
-        <v>2.7456479557319802e-07</v>
+        <v>5.0806724060246176e-08</v>
       </c>
       <c r="J3">
-        <v>4.9386379733936852e-05</v>
+        <v>1.4284797802598443e-05</v>
       </c>
       <c r="K3">
-        <v>8.9428678492758666e-05</v>
+        <v>2.9842502337778091e-05</v>
       </c>
       <c r="L3">
-        <v>0.00011259195833285064</v>
+        <v>3.8579333329106759e-05</v>
       </c>
       <c r="M3">
-        <v>0.00011306011910998863</v>
+        <v>3.9779566615345429e-05</v>
       </c>
       <c r="N3">
-        <v>4.9142059228956903e-06</v>
+        <v>2.1705180812626739e-06</v>
       </c>
       <c r="O3">
-        <v>5.1685659007837972e-06</v>
+        <v>3.2565846257639228e-06</v>
       </c>
       <c r="P3">
-        <v>-1.3435306870210824e-05</v>
+        <v>-3.9172667434620598e-06</v>
       </c>
       <c r="Q3">
-        <v>5.0824604874281112e-06</v>
+        <v>2.5616244434764704e-06</v>
       </c>
       <c r="R3">
-        <v>-2.6569250769062528e-05</v>
+        <v>-8.5413095471995388e-06</v>
       </c>
       <c r="S3">
-        <v>-2.3838304619432189e-05</v>
+        <v>-6.9175867121210128e-06</v>
       </c>
       <c r="T3">
-        <v>1.6746050310917497e-07</v>
+        <v>-2.3795956639701235e-07</v>
       </c>
       <c r="U3">
-        <v>-3.4616025827412038e-09</v>
+        <v>-2.0017585538444142e-08</v>
       </c>
       <c r="V3">
-        <v>-1.573056761131753e-05</v>
+        <v>-7.8215473990291999e-06</v>
       </c>
       <c r="W3">
-        <v>2.8932331615611547e-06</v>
+        <v>1.0355701785805711e-06</v>
       </c>
       <c r="X3">
-        <v>-0.00082229069051768344</v>
+        <v>-0.00030442236026177933</v>
       </c>
       <c r="Y3">
-        <v>0.00049182210711146222</v>
+        <v>0.00018589599351392399</v>
       </c>
     </row>
     <row r="4">
@@ -3963,76 +3963,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>-9.1930698637086275e-05</v>
+        <v>-7.8075964907221805e-05</v>
       </c>
       <c r="C4">
-        <v>4.5337090293373758e-10</v>
+        <v>1.1102350662795997e-09</v>
       </c>
       <c r="D4">
-        <v>-3.2458902172785458e-07</v>
+        <v>-1.2185083522255474e-07</v>
       </c>
       <c r="E4">
-        <v>3.5631432744558615e-09</v>
+        <v>1.3311051287264849e-09</v>
       </c>
       <c r="F4">
-        <v>7.2931844049348862e-07</v>
+        <v>2.3644388862352365e-07</v>
       </c>
       <c r="G4">
-        <v>8.0267866135309283e-07</v>
+        <v>2.9615059554108301e-07</v>
       </c>
       <c r="H4">
-        <v>-1.1533569065745204e-08</v>
+        <v>-3.1761372525692363e-09</v>
       </c>
       <c r="I4">
-        <v>-3.8562548571881963e-09</v>
+        <v>-9.524871316569343e-10</v>
       </c>
       <c r="J4">
-        <v>-5.4013890471938954e-07</v>
+        <v>-1.5547477286129524e-07</v>
       </c>
       <c r="K4">
-        <v>-9.7809330198501626e-07</v>
+        <v>-3.2464896080022149e-07</v>
       </c>
       <c r="L4">
-        <v>-1.2304375965035396e-06</v>
+        <v>-4.1911197519529342e-07</v>
       </c>
       <c r="M4">
-        <v>-1.2337530820365671e-06</v>
+        <v>-4.3126530003810835e-07</v>
       </c>
       <c r="N4">
-        <v>-5.3477692979978095e-08</v>
+        <v>-2.3470515219144589e-08</v>
       </c>
       <c r="O4">
-        <v>-5.6196333467049493e-08</v>
+        <v>-3.5262592434547071e-08</v>
       </c>
       <c r="P4">
-        <v>1.4705026850079929e-07</v>
+        <v>4.2617600863876326e-08</v>
       </c>
       <c r="Q4">
-        <v>-5.521307414705835e-08</v>
+        <v>-2.7675765860521686e-08</v>
       </c>
       <c r="R4">
-        <v>2.9104576124237777e-07</v>
+        <v>9.3064981657292449e-08</v>
       </c>
       <c r="S4">
-        <v>2.6122344549966236e-07</v>
+        <v>7.5431400360237955e-08</v>
       </c>
       <c r="T4">
-        <v>-1.1389543636260151e-09</v>
+        <v>2.6852729225980295e-09</v>
       </c>
       <c r="U4">
-        <v>-9.1784107546116283e-12</v>
+        <v>5.8951553396905426e-11</v>
       </c>
       <c r="V4">
-        <v>1.7226663104359276e-07</v>
+        <v>8.5508111950068873e-08</v>
       </c>
       <c r="W4">
-        <v>-3.1374269602771049e-08</v>
+        <v>-1.0859427514709191e-08</v>
       </c>
       <c r="X4">
-        <v>8.9886789644505795e-06</v>
+        <v>3.3220812413424139e-06</v>
       </c>
       <c r="Y4">
-        <v>-5.3840308178254267e-06</v>
+        <v>-2.0234058564472576e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4040,76 +4040,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.064545973123786391</v>
+        <v>-0.054485874728289946</v>
       </c>
       <c r="C5">
-        <v>1.3731519445720949e-06</v>
+        <v>9.3179337954984099e-07</v>
       </c>
       <c r="D5">
-        <v>-6.3412882352260221e-05</v>
+        <v>-2.0201999328672566e-05</v>
       </c>
       <c r="E5">
-        <v>7.2931844049348862e-07</v>
+        <v>2.3644388862352365e-07</v>
       </c>
       <c r="F5">
-        <v>0.00063301903078840228</v>
+        <v>0.00027779364057496528</v>
       </c>
       <c r="G5">
-        <v>0.00031599798848023803</v>
+        <v>0.00012487442748567899</v>
       </c>
       <c r="H5">
-        <v>-1.2439233122582172e-05</v>
+        <v>-5.4405572857225522e-06</v>
       </c>
       <c r="I5">
-        <v>-3.8658641022559972e-06</v>
+        <v>-1.6276468052586796e-06</v>
       </c>
       <c r="J5">
-        <v>-0.00011432122601866902</v>
+        <v>-2.7803838990665341e-05</v>
       </c>
       <c r="K5">
-        <v>-0.00020940517656767017</v>
+        <v>-6.0651932358632397e-05</v>
       </c>
       <c r="L5">
-        <v>-0.00026497184603160092</v>
+        <v>-7.9122141456063096e-05</v>
       </c>
       <c r="M5">
-        <v>-0.00026325916335528097</v>
+        <v>-8.0208772531911111e-05</v>
       </c>
       <c r="N5">
-        <v>-9.8415662335419772e-06</v>
+        <v>-3.631601993855779e-06</v>
       </c>
       <c r="O5">
-        <v>-9.4112032960609329e-06</v>
+        <v>-5.5695825012548857e-06</v>
       </c>
       <c r="P5">
-        <v>3.3017658686816881e-05</v>
+        <v>8.6809161868353704e-06</v>
       </c>
       <c r="Q5">
-        <v>-1.0426890052296108e-05</v>
+        <v>-4.4801773536565245e-06</v>
       </c>
       <c r="R5">
-        <v>6.2000765424114054e-05</v>
+        <v>1.7482499834264954e-05</v>
       </c>
       <c r="S5">
-        <v>5.7312749468146801e-05</v>
+        <v>1.4769458480835752e-05</v>
       </c>
       <c r="T5">
-        <v>-6.8509699303470422e-07</v>
+        <v>6.8208045815348623e-08</v>
       </c>
       <c r="U5">
-        <v>7.1772419304783736e-08</v>
+        <v>2.5991658397765661e-07</v>
       </c>
       <c r="V5">
-        <v>3.77674523185336e-05</v>
+        <v>1.6058854667617644e-05</v>
       </c>
       <c r="W5">
-        <v>-7.8764500127419655e-06</v>
+        <v>-2.9351116732279857e-06</v>
       </c>
       <c r="X5">
-        <v>0.0017084387849719582</v>
+        <v>0.00050325609427480053</v>
       </c>
       <c r="Y5">
-        <v>-0.0011652789686892396</v>
+        <v>-0.00038651503738428863</v>
       </c>
     </row>
     <row r="6">
@@ -4117,76 +4117,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.025811289448791387</v>
+        <v>-0.016203745025241273</v>
       </c>
       <c r="C6">
-        <v>1.2278557895288793e-07</v>
+        <v>2.089789604934276e-07</v>
       </c>
       <c r="D6">
-        <v>-7.0012676377104817e-05</v>
+        <v>-2.5637694875882812e-05</v>
       </c>
       <c r="E6">
-        <v>8.0267866135309283e-07</v>
+        <v>2.9615059554108301e-07</v>
       </c>
       <c r="F6">
-        <v>0.00031599798848023803</v>
+        <v>0.00012487442748567899</v>
       </c>
       <c r="G6">
-        <v>0.00065721146797676389</v>
+        <v>0.00030855178787808667</v>
       </c>
       <c r="H6">
-        <v>-5.8446561140815413e-06</v>
+        <v>-2.2365232511937591e-06</v>
       </c>
       <c r="I6">
-        <v>-1.047883752242374e-05</v>
+        <v>-5.0740932757516796e-06</v>
       </c>
       <c r="J6">
-        <v>-0.00012620295913079205</v>
+        <v>-3.6004482042494818e-05</v>
       </c>
       <c r="K6">
-        <v>-0.00023122563130940007</v>
+        <v>-7.7316075197451662e-05</v>
       </c>
       <c r="L6">
-        <v>-0.000291021569504138</v>
+        <v>-9.9778824410068552e-05</v>
       </c>
       <c r="M6">
-        <v>-0.00028769499989263745</v>
+        <v>-0.00010057819284417825</v>
       </c>
       <c r="N6">
-        <v>-1.0864554869618429e-05</v>
+        <v>-4.7367393060452349e-06</v>
       </c>
       <c r="O6">
-        <v>-1.3239796522878982e-05</v>
+        <v>-8.4143917276524361e-06</v>
       </c>
       <c r="P6">
-        <v>3.0221535514344041e-05</v>
+        <v>8.0561838559952498e-06</v>
       </c>
       <c r="Q6">
-        <v>-1.5006606608891666e-05</v>
+        <v>-7.4135845518161722e-06</v>
       </c>
       <c r="R6">
-        <v>6.0790773727989887e-05</v>
+        <v>1.8303644756337456e-05</v>
       </c>
       <c r="S6">
-        <v>5.6830883699233198e-05</v>
+        <v>1.5620405915373223e-05</v>
       </c>
       <c r="T6">
-        <v>1.3091994742353465e-06</v>
+        <v>7.9144542865582013e-07</v>
       </c>
       <c r="U6">
-        <v>6.0789541091559927e-08</v>
+        <v>2.8655030166801858e-07</v>
       </c>
       <c r="V6">
-        <v>4.0849007127186253e-05</v>
+        <v>1.9715418306668763e-05</v>
       </c>
       <c r="W6">
-        <v>-6.5771455963505682e-06</v>
+        <v>-2.7128615164868928e-06</v>
       </c>
       <c r="X6">
-        <v>0.0018941763073360117</v>
+        <v>0.00065246730075265011</v>
       </c>
       <c r="Y6">
-        <v>-0.0012544040432574204</v>
+        <v>-0.00047065749231569389</v>
       </c>
     </row>
     <row r="7">
@@ -4194,76 +4194,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.00055805582033835563</v>
+        <v>-0.00030273868509955477</v>
       </c>
       <c r="C7">
-        <v>4.2884938157551056e-08</v>
+        <v>2.7941512939287481e-08</v>
       </c>
       <c r="D7">
-        <v>9.7898650168773815e-07</v>
+        <v>2.5659718394078791e-07</v>
       </c>
       <c r="E7">
-        <v>-1.1533569065745204e-08</v>
+        <v>-3.1761372525692363e-09</v>
       </c>
       <c r="F7">
-        <v>-1.2439233122582172e-05</v>
+        <v>-5.4405572857225522e-06</v>
       </c>
       <c r="G7">
-        <v>-5.8446561140815413e-06</v>
+        <v>-2.2365232511937591e-06</v>
       </c>
       <c r="H7">
-        <v>2.5897914363559073e-07</v>
+        <v>1.1424902088387156e-07</v>
       </c>
       <c r="I7">
-        <v>8.4722205507317174e-08</v>
+        <v>3.6501694422914346e-08</v>
       </c>
       <c r="J7">
-        <v>1.7574098292805886e-06</v>
+        <v>3.4881645867390443e-07</v>
       </c>
       <c r="K7">
-        <v>3.2393786817222615e-06</v>
+        <v>7.801407385316338e-07</v>
       </c>
       <c r="L7">
-        <v>4.134702007571985e-06</v>
+        <v>1.0354016048426646e-06</v>
       </c>
       <c r="M7">
-        <v>4.1050138767937288e-06</v>
+        <v>1.0452873540547052e-06</v>
       </c>
       <c r="N7">
-        <v>1.4562386264334485e-07</v>
+        <v>4.0508315537168323e-08</v>
       </c>
       <c r="O7">
-        <v>1.3038346682492481e-07</v>
+        <v>6.1047307161279447e-08</v>
       </c>
       <c r="P7">
-        <v>-5.1725708835510129e-07</v>
+        <v>-1.1618928720924609e-07</v>
       </c>
       <c r="Q7">
-        <v>1.3832282922322063e-07</v>
+        <v>4.4025686323584624e-08</v>
       </c>
       <c r="R7">
-        <v>-9.6363087905559529e-07</v>
+        <v>-2.2671440292976046e-07</v>
       </c>
       <c r="S7">
-        <v>-9.0635544137996135e-07</v>
+        <v>-2.0094002984831379e-07</v>
       </c>
       <c r="T7">
-        <v>-7.9405996967787316e-09</v>
+        <v>1.5725185508595396e-10</v>
       </c>
       <c r="U7">
-        <v>-5.0492075387558062e-10</v>
+        <v>-1.8115508004098128e-09</v>
       </c>
       <c r="V7">
-        <v>-5.8811543804783727e-07</v>
+        <v>-2.1324803933218143e-07</v>
       </c>
       <c r="W7">
-        <v>1.3206321914855699e-07</v>
+        <v>4.1082399052457023e-08</v>
       </c>
       <c r="X7">
-        <v>-2.6194522684207799e-05</v>
+        <v>-6.3622847002115338e-06</v>
       </c>
       <c r="Y7">
-        <v>1.8143175942442899e-05</v>
+        <v>5.0368660252443435e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4271,76 +4271,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>-0.0025743322216109561</v>
+        <v>-0.0019611283378634164</v>
       </c>
       <c r="C8">
-        <v>1.0261761662782507e-07</v>
+        <v>6.4904040226913373e-08</v>
       </c>
       <c r="D8">
-        <v>2.7456479557319802e-07</v>
+        <v>5.0806724060246176e-08</v>
       </c>
       <c r="E8">
-        <v>-3.8562548571881963e-09</v>
+        <v>-9.524871316569343e-10</v>
       </c>
       <c r="F8">
-        <v>-3.8658641022559972e-06</v>
+        <v>-1.6276468052586796e-06</v>
       </c>
       <c r="G8">
-        <v>-1.047883752242374e-05</v>
+        <v>-5.0740932757516796e-06</v>
       </c>
       <c r="H8">
-        <v>8.4722205507317174e-08</v>
+        <v>3.6501694422914346e-08</v>
       </c>
       <c r="I8">
-        <v>2.1504015340330277e-07</v>
+        <v>1.0683910696755915e-07</v>
       </c>
       <c r="J8">
-        <v>4.7565973779275853e-07</v>
+        <v>6.7729220510425642e-08</v>
       </c>
       <c r="K8">
-        <v>9.4587072136822492e-07</v>
+        <v>1.8982351553323668e-07</v>
       </c>
       <c r="L8">
-        <v>1.2360216330556205e-06</v>
+        <v>2.6014435230324474e-07</v>
       </c>
       <c r="M8">
-        <v>1.18547068016262e-06</v>
+        <v>2.3725852053151399e-07</v>
       </c>
       <c r="N8">
-        <v>1.4360638998344341e-08</v>
+        <v>-6.2970214572685166e-09</v>
       </c>
       <c r="O8">
-        <v>6.5282810567690629e-08</v>
+        <v>2.5035108160045569e-08</v>
       </c>
       <c r="P8">
-        <v>-6.6512883777694546e-08</v>
+        <v>1.0618101419584612e-08</v>
       </c>
       <c r="Q8">
-        <v>7.9387478225791e-08</v>
+        <v>2.4915806087741695e-08</v>
       </c>
       <c r="R8">
-        <v>-1.4546698088385246e-07</v>
+        <v>1.3112688904982292e-08</v>
       </c>
       <c r="S8">
-        <v>-1.7005363637801167e-07</v>
+        <v>-4.8491981354917893e-09</v>
       </c>
       <c r="T8">
-        <v>-7.5870946147771853e-08</v>
+        <v>-1.2438801471828536e-08</v>
       </c>
       <c r="U8">
-        <v>1.13704376411175e-09</v>
+        <v>2.9433769826306958e-09</v>
       </c>
       <c r="V8">
-        <v>-1.7225537007922357e-07</v>
+        <v>-5.444744392702974e-08</v>
       </c>
       <c r="W8">
-        <v>1.015446245770106e-08</v>
+        <v>-7.255588097708684e-09</v>
       </c>
       <c r="X8">
-        <v>-6.5070901507099508e-06</v>
+        <v>-1.1209254959576135e-06</v>
       </c>
       <c r="Y8">
-        <v>4.8441814428071592e-06</v>
+        <v>9.087217792319713e-07</v>
       </c>
     </row>
     <row r="9">
@@ -4348,76 +4348,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>-0.00081989403969137415</v>
+        <v>-0.016262208043115935</v>
       </c>
       <c r="C9">
-        <v>-1.1499834255349719e-06</v>
+        <v>-6.9382535870024479e-08</v>
       </c>
       <c r="D9">
-        <v>4.9386379733936852e-05</v>
+        <v>1.4284797802598443e-05</v>
       </c>
       <c r="E9">
-        <v>-5.4013890471938954e-07</v>
+        <v>-1.5547477286129524e-07</v>
       </c>
       <c r="F9">
-        <v>-0.00011432122601866902</v>
+        <v>-2.7803838990665341e-05</v>
       </c>
       <c r="G9">
-        <v>-0.00012620295913079205</v>
+        <v>-3.6004482042494818e-05</v>
       </c>
       <c r="H9">
-        <v>1.7574098292805886e-06</v>
+        <v>3.4881645867390443e-07</v>
       </c>
       <c r="I9">
-        <v>4.7565973779275853e-07</v>
+        <v>6.7729220510425642e-08</v>
       </c>
       <c r="J9">
-        <v>0.0013730336603324368</v>
+        <v>0.00061487167017753946</v>
       </c>
       <c r="K9">
-        <v>0.0012629425622256126</v>
+        <v>0.00054852890550611676</v>
       </c>
       <c r="L9">
-        <v>0.0013050419023545952</v>
+        <v>0.00056091255366612163</v>
       </c>
       <c r="M9">
-        <v>0.0013051534379718733</v>
+        <v>0.00056226386330454972</v>
       </c>
       <c r="N9">
-        <v>9.8744484978302159e-06</v>
+        <v>3.0933796796486743e-06</v>
       </c>
       <c r="O9">
-        <v>1.0895823666592456e-05</v>
+        <v>5.1390006481087921e-06</v>
       </c>
       <c r="P9">
-        <v>-2.4455832152374442e-05</v>
+        <v>-5.4387840462035279e-06</v>
       </c>
       <c r="Q9">
-        <v>9.5587357772669832e-06</v>
+        <v>3.9659579421946913e-06</v>
       </c>
       <c r="R9">
-        <v>-4.6976222269989976e-05</v>
+        <v>-1.1777350205071405e-05</v>
       </c>
       <c r="S9">
-        <v>-4.314812141882721e-05</v>
+        <v>-1.014924195108342e-05</v>
       </c>
       <c r="T9">
-        <v>-1.1954101292813481e-07</v>
+        <v>-3.4204518793654737e-07</v>
       </c>
       <c r="U9">
-        <v>2.7311154412417875e-08</v>
+        <v>5.955013657228466e-08</v>
       </c>
       <c r="V9">
-        <v>-2.8954989545790399e-05</v>
+        <v>-1.1436448180573681e-05</v>
       </c>
       <c r="W9">
-        <v>4.736593716540253e-06</v>
+        <v>1.1452816325383639e-06</v>
       </c>
       <c r="X9">
-        <v>-0.002499076397709285</v>
+        <v>-0.00091262790470936434</v>
       </c>
       <c r="Y9">
-        <v>0.00088604782218495179</v>
+        <v>0.00026249820986849612</v>
       </c>
     </row>
     <row r="10">
@@ -4425,76 +4425,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>0.066868171141265614</v>
+        <v>0.020895713598523543</v>
       </c>
       <c r="C10">
-        <v>-1.2957962179887819e-06</v>
+        <v>-4.389170197566782e-07</v>
       </c>
       <c r="D10">
-        <v>8.9428678492758666e-05</v>
+        <v>2.9842502337778091e-05</v>
       </c>
       <c r="E10">
-        <v>-9.7809330198501626e-07</v>
+        <v>-3.2464896080022149e-07</v>
       </c>
       <c r="F10">
-        <v>-0.00020940517656767017</v>
+        <v>-6.0651932358632397e-05</v>
       </c>
       <c r="G10">
-        <v>-0.00023122563130940007</v>
+        <v>-7.7316075197451662e-05</v>
       </c>
       <c r="H10">
-        <v>3.2393786817222615e-06</v>
+        <v>7.801407385316338e-07</v>
       </c>
       <c r="I10">
-        <v>9.4587072136822492e-07</v>
+        <v>1.8982351553323668e-07</v>
       </c>
       <c r="J10">
-        <v>0.0012629425622256126</v>
+        <v>0.00054852890550611676</v>
       </c>
       <c r="K10">
-        <v>0.0014181708992336073</v>
+        <v>0.00060623479366765155</v>
       </c>
       <c r="L10">
-        <v>0.0014695146496847672</v>
+        <v>0.00062034672638229874</v>
       </c>
       <c r="M10">
-        <v>0.0014699463652398641</v>
+        <v>0.0006233552829110374</v>
       </c>
       <c r="N10">
-        <v>1.5723394890527811e-05</v>
+        <v>5.8690581764370234e-06</v>
       </c>
       <c r="O10">
-        <v>1.6985319433617874e-05</v>
+        <v>9.5366841757540435e-06</v>
       </c>
       <c r="P10">
-        <v>-4.5372070164631008e-05</v>
+        <v>-1.1859304983706229e-05</v>
       </c>
       <c r="Q10">
-        <v>1.6096696121644269e-05</v>
+        <v>7.6195116392870917e-06</v>
       </c>
       <c r="R10">
-        <v>-8.6921183349168452e-05</v>
+        <v>-2.5422248068628436e-05</v>
       </c>
       <c r="S10">
-        <v>-7.9455123780406583e-05</v>
+        <v>-2.1053711903401142e-05</v>
       </c>
       <c r="T10">
-        <v>1.1610901825532232e-06</v>
+        <v>-5.254650045859939e-07</v>
       </c>
       <c r="U10">
-        <v>8.0072461534031352e-09</v>
+        <v>-2.6138651677631299e-08</v>
       </c>
       <c r="V10">
-        <v>-5.1894958767801047e-05</v>
+        <v>-2.3315385097676407e-05</v>
       </c>
       <c r="W10">
-        <v>9.5727470190799382e-06</v>
+        <v>3.1463906391498534e-06</v>
       </c>
       <c r="X10">
-        <v>-0.0036271894745440038</v>
+        <v>-0.0013388504605177575</v>
       </c>
       <c r="Y10">
-        <v>0.0016002822276409384</v>
+        <v>0.00054686572298210767</v>
       </c>
     </row>
     <row r="11">
@@ -4502,76 +4502,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>0.091496105238957751</v>
+        <v>0.038042078126474789</v>
       </c>
       <c r="C11">
-        <v>-1.7967812804220199e-06</v>
+        <v>-8.2474746917796295e-07</v>
       </c>
       <c r="D11">
-        <v>0.00011259195833285064</v>
+        <v>3.8579333329106759e-05</v>
       </c>
       <c r="E11">
-        <v>-1.2304375965035396e-06</v>
+        <v>-4.1911197519529342e-07</v>
       </c>
       <c r="F11">
-        <v>-0.00026497184603160092</v>
+        <v>-7.9122141456063096e-05</v>
       </c>
       <c r="G11">
-        <v>-0.000291021569504138</v>
+        <v>-9.9778824410068552e-05</v>
       </c>
       <c r="H11">
-        <v>4.134702007571985e-06</v>
+        <v>1.0354016048426646e-06</v>
       </c>
       <c r="I11">
-        <v>1.2360216330556205e-06</v>
+        <v>2.6014435230324474e-07</v>
       </c>
       <c r="J11">
-        <v>0.0013050419023545952</v>
+        <v>0.00056091255366612163</v>
       </c>
       <c r="K11">
-        <v>0.0014695146496847672</v>
+        <v>0.00062034672638229874</v>
       </c>
       <c r="L11">
-        <v>0.0015718846352478601</v>
+        <v>0.00065710757180092191</v>
       </c>
       <c r="M11">
-        <v>0.0015676792266067952</v>
+        <v>0.00065865758530372204</v>
       </c>
       <c r="N11">
-        <v>1.8676954646868157e-05</v>
+        <v>7.2373262994493086e-06</v>
       </c>
       <c r="O11">
-        <v>2.0615494901539866e-05</v>
+        <v>1.2032443787187547e-05</v>
       </c>
       <c r="P11">
-        <v>-5.7803142437246739e-05</v>
+        <v>-1.5739382032367234e-05</v>
       </c>
       <c r="Q11">
-        <v>1.9142853405847167e-05</v>
+        <v>9.3367505924156006e-06</v>
       </c>
       <c r="R11">
-        <v>-0.00011038351332490892</v>
+        <v>-3.3271063146459877e-05</v>
       </c>
       <c r="S11">
-        <v>-9.9445783250567006e-05</v>
+        <v>-2.7009261030942069e-05</v>
       </c>
       <c r="T11">
-        <v>1.5106569597387023e-06</v>
+        <v>-5.8427042448626439e-07</v>
       </c>
       <c r="U11">
-        <v>3.8502827979042164e-08</v>
+        <v>2.4579581091591098e-09</v>
       </c>
       <c r="V11">
-        <v>-6.5835933481242021e-05</v>
+        <v>-3.0437422389276659e-05</v>
       </c>
       <c r="W11">
-        <v>1.1957232244727099e-05</v>
+        <v>4.0077784754383725e-06</v>
       </c>
       <c r="X11">
-        <v>-0.0042880176831162145</v>
+        <v>-0.0015876835256496032</v>
       </c>
       <c r="Y11">
-        <v>0.0020152437277199471</v>
+        <v>0.00070736538284481331</v>
       </c>
     </row>
     <row r="12">
@@ -4579,76 +4579,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.096690882997627181</v>
+        <v>0.047613654257599614</v>
       </c>
       <c r="C12">
-        <v>-2.2634741526766576e-06</v>
+        <v>-1.1548416059109898e-06</v>
       </c>
       <c r="D12">
-        <v>0.00011306011910998863</v>
+        <v>3.9779566615345429e-05</v>
       </c>
       <c r="E12">
-        <v>-1.2337530820365671e-06</v>
+        <v>-4.3126530003810835e-07</v>
       </c>
       <c r="F12">
-        <v>-0.00026325916335528097</v>
+        <v>-8.0208772531911111e-05</v>
       </c>
       <c r="G12">
-        <v>-0.00028769499989263745</v>
+        <v>-0.00010057819284417825</v>
       </c>
       <c r="H12">
-        <v>4.1050138767937288e-06</v>
+        <v>1.0452873540547052e-06</v>
       </c>
       <c r="I12">
-        <v>1.18547068016262e-06</v>
+        <v>2.3725852053151399e-07</v>
       </c>
       <c r="J12">
-        <v>0.0013051534379718733</v>
+        <v>0.00056226386330454972</v>
       </c>
       <c r="K12">
-        <v>0.0014699463652398641</v>
+        <v>0.0006233552829110374</v>
       </c>
       <c r="L12">
-        <v>0.0015676792266067952</v>
+        <v>0.00065865758530372204</v>
       </c>
       <c r="M12">
-        <v>0.0015886619058082076</v>
+        <v>0.00067266830267302268</v>
       </c>
       <c r="N12">
-        <v>1.795221893177796e-05</v>
+        <v>7.0810126765002326e-06</v>
       </c>
       <c r="O12">
-        <v>1.9335255710333218e-05</v>
+        <v>1.1762218290051498e-05</v>
       </c>
       <c r="P12">
-        <v>-5.8294316839143797e-05</v>
+        <v>-1.6343020623086341e-05</v>
       </c>
       <c r="Q12">
-        <v>1.7404428114878331e-05</v>
+        <v>8.8054843259354408e-06</v>
       </c>
       <c r="R12">
-        <v>-0.00011197419672236745</v>
+        <v>-3.4854538055549133e-05</v>
       </c>
       <c r="S12">
-        <v>-0.00010105375938242005</v>
+        <v>-2.8444940106264236e-05</v>
       </c>
       <c r="T12">
-        <v>1.6868288774258642e-06</v>
+        <v>-5.6805946546510858e-07</v>
       </c>
       <c r="U12">
-        <v>6.0129674102023668e-08</v>
+        <v>6.5456480167735415e-08</v>
       </c>
       <c r="V12">
-        <v>-6.6544712648786844e-05</v>
+        <v>-3.1663908300751647e-05</v>
       </c>
       <c r="W12">
-        <v>1.1225212060819412e-05</v>
+        <v>3.6688987721083748e-06</v>
       </c>
       <c r="X12">
-        <v>-0.004303963122336215</v>
+        <v>-0.0016276743318835922</v>
       </c>
       <c r="Y12">
-        <v>0.0020153521196437578</v>
+        <v>0.00072541972682367735</v>
       </c>
     </row>
     <row r="13">
@@ -4656,76 +4656,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.038797037748614149</v>
+        <v>0.023430647992605573</v>
       </c>
       <c r="C13">
-        <v>-1.8719351822892052e-06</v>
+        <v>-1.0802015969646813e-06</v>
       </c>
       <c r="D13">
-        <v>4.9142059228956903e-06</v>
+        <v>2.1705180812626739e-06</v>
       </c>
       <c r="E13">
-        <v>-5.3477692979978095e-08</v>
+        <v>-2.3470515219144589e-08</v>
       </c>
       <c r="F13">
-        <v>-9.8415662335419772e-06</v>
+        <v>-3.631601993855779e-06</v>
       </c>
       <c r="G13">
-        <v>-1.0864554869618429e-05</v>
+        <v>-4.7367393060452349e-06</v>
       </c>
       <c r="H13">
-        <v>1.4562386264334485e-07</v>
+        <v>4.0508315537168323e-08</v>
       </c>
       <c r="I13">
-        <v>1.4360638998344341e-08</v>
+        <v>-6.2970214572685166e-09</v>
       </c>
       <c r="J13">
-        <v>9.8744484978302159e-06</v>
+        <v>3.0933796796486743e-06</v>
       </c>
       <c r="K13">
-        <v>1.5723394890527811e-05</v>
+        <v>5.8690581764370234e-06</v>
       </c>
       <c r="L13">
-        <v>1.8676954646868157e-05</v>
+        <v>7.2373262994493086e-06</v>
       </c>
       <c r="M13">
-        <v>1.795221893177796e-05</v>
+        <v>7.0810126765002326e-06</v>
       </c>
       <c r="N13">
-        <v>4.7616850924958242e-05</v>
+        <v>2.4070780431922979e-05</v>
       </c>
       <c r="O13">
-        <v>2.7209431931384031e-05</v>
+        <v>1.4041960768521622e-05</v>
       </c>
       <c r="P13">
-        <v>2.3594022349248128e-05</v>
+        <v>1.2406018112468796e-05</v>
       </c>
       <c r="Q13">
-        <v>2.7078397826886384e-05</v>
+        <v>1.3836042222886755e-05</v>
       </c>
       <c r="R13">
-        <v>2.1292496426126869e-05</v>
+        <v>1.1447607551893188e-05</v>
       </c>
       <c r="S13">
-        <v>2.1655030864776665e-05</v>
+        <v>1.1719203612126038e-05</v>
       </c>
       <c r="T13">
-        <v>-1.3295014441671119e-06</v>
+        <v>-6.9071152178091714e-07</v>
       </c>
       <c r="U13">
-        <v>1.8132655318334872e-09</v>
+        <v>3.2238112507922701e-08</v>
       </c>
       <c r="V13">
-        <v>-2.585954803416979e-06</v>
+        <v>-1.6245071757062736e-06</v>
       </c>
       <c r="W13">
-        <v>2.8443847015067994e-07</v>
+        <v>2.4133608828007539e-08</v>
       </c>
       <c r="X13">
-        <v>-0.00015992546938117536</v>
+        <v>-7.3831641599804269e-05</v>
       </c>
       <c r="Y13">
-        <v>8.7025558840640445e-05</v>
+        <v>3.8876075961376768e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4733,76 +4733,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.038602022575032577</v>
+        <v>0.029087704644993957</v>
       </c>
       <c r="C14">
-        <v>-1.6827737793938412e-06</v>
+        <v>-9.968017005840478e-07</v>
       </c>
       <c r="D14">
-        <v>5.1685659007837972e-06</v>
+        <v>3.2565846257639228e-06</v>
       </c>
       <c r="E14">
-        <v>-5.6196333467049493e-08</v>
+        <v>-3.5262592434547071e-08</v>
       </c>
       <c r="F14">
-        <v>-9.4112032960609329e-06</v>
+        <v>-5.5695825012548857e-06</v>
       </c>
       <c r="G14">
-        <v>-1.3239796522878982e-05</v>
+        <v>-8.4143917276524361e-06</v>
       </c>
       <c r="H14">
-        <v>1.3038346682492481e-07</v>
+        <v>6.1047307161279447e-08</v>
       </c>
       <c r="I14">
-        <v>6.5282810567690629e-08</v>
+        <v>2.5035108160045569e-08</v>
       </c>
       <c r="J14">
-        <v>1.0895823666592456e-05</v>
+        <v>5.1390006481087921e-06</v>
       </c>
       <c r="K14">
-        <v>1.6985319433617874e-05</v>
+        <v>9.5366841757540435e-06</v>
       </c>
       <c r="L14">
-        <v>2.0615494901539866e-05</v>
+        <v>1.2032443787187547e-05</v>
       </c>
       <c r="M14">
-        <v>1.9335255710333218e-05</v>
+        <v>1.1762218290051498e-05</v>
       </c>
       <c r="N14">
-        <v>2.7209431931384031e-05</v>
+        <v>1.4041960768521622e-05</v>
       </c>
       <c r="O14">
-        <v>5.6492180174462332e-05</v>
+        <v>2.8591668680719527e-05</v>
       </c>
       <c r="P14">
-        <v>2.3496141471914248e-05</v>
+        <v>1.1959034007195313e-05</v>
       </c>
       <c r="Q14">
-        <v>2.7182931248914508e-05</v>
+        <v>1.4125136921928142e-05</v>
       </c>
       <c r="R14">
-        <v>2.1200584196350302e-05</v>
+        <v>1.0563432772918668e-05</v>
       </c>
       <c r="S14">
-        <v>2.1594423628122155e-05</v>
+        <v>1.1052612379658422e-05</v>
       </c>
       <c r="T14">
-        <v>-7.9787605770758569e-09</v>
+        <v>-8.6062159873588874e-09</v>
       </c>
       <c r="U14">
-        <v>-2.155434061842188e-08</v>
+        <v>-8.3219969458834459e-08</v>
       </c>
       <c r="V14">
-        <v>-2.4629385506773198e-06</v>
+        <v>-2.0270905054865779e-06</v>
       </c>
       <c r="W14">
-        <v>2.2889183035389677e-07</v>
+        <v>3.0901366540381607e-07</v>
       </c>
       <c r="X14">
-        <v>-0.00016570552223314227</v>
+        <v>-9.3483960018726379e-05</v>
       </c>
       <c r="Y14">
-        <v>8.9399256862211164e-05</v>
+        <v>5.7559167331081122e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4810,76 +4810,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.014153982431147965</v>
+        <v>0.0035294315085298328</v>
       </c>
       <c r="C15">
-        <v>-8.4839324090577684e-07</v>
+        <v>-4.1098103065741263e-07</v>
       </c>
       <c r="D15">
-        <v>-1.3435306870210824e-05</v>
+        <v>-3.9172667434620598e-06</v>
       </c>
       <c r="E15">
-        <v>1.4705026850079929e-07</v>
+        <v>4.2617600863876326e-08</v>
       </c>
       <c r="F15">
-        <v>3.3017658686816881e-05</v>
+        <v>8.6809161868353704e-06</v>
       </c>
       <c r="G15">
-        <v>3.0221535514344041e-05</v>
+        <v>8.0561838559952498e-06</v>
       </c>
       <c r="H15">
-        <v>-5.1725708835510129e-07</v>
+        <v>-1.1618928720924609e-07</v>
       </c>
       <c r="I15">
-        <v>-6.6512883777694546e-08</v>
+        <v>1.0618101419584612e-08</v>
       </c>
       <c r="J15">
-        <v>-2.4455832152374442e-05</v>
+        <v>-5.4387840462035279e-06</v>
       </c>
       <c r="K15">
-        <v>-4.5372070164631008e-05</v>
+        <v>-1.1859304983706229e-05</v>
       </c>
       <c r="L15">
-        <v>-5.7803142437246739e-05</v>
+        <v>-1.5739382032367234e-05</v>
       </c>
       <c r="M15">
-        <v>-5.8294316839143797e-05</v>
+        <v>-1.6343020623086341e-05</v>
       </c>
       <c r="N15">
-        <v>2.3594022349248128e-05</v>
+        <v>1.2406018112468796e-05</v>
       </c>
       <c r="O15">
-        <v>2.3496141471914248e-05</v>
+        <v>1.1959034007195313e-05</v>
       </c>
       <c r="P15">
-        <v>5.7655909632594532e-05</v>
+        <v>2.732104178588196e-05</v>
       </c>
       <c r="Q15">
-        <v>2.3617962831170144e-05</v>
+        <v>1.224946588347958e-05</v>
       </c>
       <c r="R15">
-        <v>3.9294115857908411e-05</v>
+        <v>1.6691385068045789e-05</v>
       </c>
       <c r="S15">
-        <v>3.7759615768348998e-05</v>
+        <v>1.5936372934331804e-05</v>
       </c>
       <c r="T15">
-        <v>-9.3824549647227915e-07</v>
+        <v>-4.0108086500794395e-07</v>
       </c>
       <c r="U15">
-        <v>-1.3389258908355836e-08</v>
+        <v>-1.8725193260008439e-08</v>
       </c>
       <c r="V15">
-        <v>7.7182165931296854e-06</v>
+        <v>3.1095308112344178e-06</v>
       </c>
       <c r="W15">
-        <v>-1.7983507466949319e-06</v>
+        <v>-5.2243891837971979e-07</v>
       </c>
       <c r="X15">
-        <v>0.00036007334920701631</v>
+        <v>0.00010058405661502449</v>
       </c>
       <c r="Y15">
-        <v>-0.00024282955444504954</v>
+        <v>-7.3381672070635059e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4887,76 +4887,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.040397211016300866</v>
+        <v>0.025603504673016118</v>
       </c>
       <c r="C16">
-        <v>-1.4426751589838297e-06</v>
+        <v>-8.503463491871904e-07</v>
       </c>
       <c r="D16">
-        <v>5.0824604874281112e-06</v>
+        <v>2.5616244434764704e-06</v>
       </c>
       <c r="E16">
-        <v>-5.521307414705835e-08</v>
+        <v>-2.7675765860521686e-08</v>
       </c>
       <c r="F16">
-        <v>-1.0426890052296108e-05</v>
+        <v>-4.4801773536565245e-06</v>
       </c>
       <c r="G16">
-        <v>-1.5006606608891666e-05</v>
+        <v>-7.4135845518161722e-06</v>
       </c>
       <c r="H16">
-        <v>1.3832282922322063e-07</v>
+        <v>4.4025686323584624e-08</v>
       </c>
       <c r="I16">
-        <v>7.9387478225791e-08</v>
+        <v>2.4915806087741695e-08</v>
       </c>
       <c r="J16">
-        <v>9.5587357772669832e-06</v>
+        <v>3.9659579421946913e-06</v>
       </c>
       <c r="K16">
-        <v>1.6096696121644269e-05</v>
+        <v>7.6195116392870917e-06</v>
       </c>
       <c r="L16">
-        <v>1.9142853405847167e-05</v>
+        <v>9.3367505924156006e-06</v>
       </c>
       <c r="M16">
-        <v>1.7404428114878331e-05</v>
+        <v>8.8054843259354408e-06</v>
       </c>
       <c r="N16">
-        <v>2.7078397826886384e-05</v>
+        <v>1.3836042222886755e-05</v>
       </c>
       <c r="O16">
-        <v>2.7182931248914508e-05</v>
+        <v>1.4125136921928142e-05</v>
       </c>
       <c r="P16">
-        <v>2.3617962831170144e-05</v>
+        <v>1.224946588347958e-05</v>
       </c>
       <c r="Q16">
-        <v>4.1376699216732621e-05</v>
+        <v>2.0615781575586699e-05</v>
       </c>
       <c r="R16">
-        <v>2.1470039271591434e-05</v>
+        <v>1.1212209065329734e-05</v>
       </c>
       <c r="S16">
-        <v>2.1783319764803975e-05</v>
+        <v>1.1576443897960304e-05</v>
       </c>
       <c r="T16">
-        <v>-1.7310931306616981e-07</v>
+        <v>4.7019590636019592e-08</v>
       </c>
       <c r="U16">
-        <v>-5.658415497476381e-08</v>
+        <v>-1.7360743829891166e-07</v>
       </c>
       <c r="V16">
-        <v>-1.0918649338698213e-06</v>
+        <v>-6.6573803187886861e-07</v>
       </c>
       <c r="W16">
-        <v>1.9477989678308597e-06</v>
+        <v>1.2746315986340119e-06</v>
       </c>
       <c r="X16">
-        <v>-0.00015845367151692835</v>
+        <v>-6.5125806844308051e-05</v>
       </c>
       <c r="Y16">
-        <v>8.7169740522222201e-05</v>
+        <v>4.479010644990466e-05</v>
       </c>
     </row>
     <row r="17">
@@ -4964,76 +4964,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>0.024046778764385907</v>
+        <v>0.01521001120519266</v>
       </c>
       <c r="C17">
-        <v>-1.102521802711483e-06</v>
+        <v>-4.9303470864363799e-07</v>
       </c>
       <c r="D17">
-        <v>-2.6569250769062528e-05</v>
+        <v>-8.5413095471995388e-06</v>
       </c>
       <c r="E17">
-        <v>2.9104576124237777e-07</v>
+        <v>9.3064981657292449e-08</v>
       </c>
       <c r="F17">
-        <v>6.2000765424114054e-05</v>
+        <v>1.7482499834264954e-05</v>
       </c>
       <c r="G17">
-        <v>6.0790773727989887e-05</v>
+        <v>1.8303644756337456e-05</v>
       </c>
       <c r="H17">
-        <v>-9.6363087905559529e-07</v>
+        <v>-2.2671440292976046e-07</v>
       </c>
       <c r="I17">
-        <v>-1.4546698088385246e-07</v>
+        <v>1.3112688904982292e-08</v>
       </c>
       <c r="J17">
-        <v>-4.6976222269989976e-05</v>
+        <v>-1.1777350205071405e-05</v>
       </c>
       <c r="K17">
-        <v>-8.6921183349168452e-05</v>
+        <v>-2.5422248068628436e-05</v>
       </c>
       <c r="L17">
-        <v>-0.00011038351332490892</v>
+        <v>-3.3271063146459877e-05</v>
       </c>
       <c r="M17">
-        <v>-0.00011197419672236745</v>
+        <v>-3.4854538055549133e-05</v>
       </c>
       <c r="N17">
-        <v>2.1292496426126869e-05</v>
+        <v>1.1447607551893188e-05</v>
       </c>
       <c r="O17">
-        <v>2.1200584196350302e-05</v>
+        <v>1.0563432772918668e-05</v>
       </c>
       <c r="P17">
-        <v>3.9294115857908411e-05</v>
+        <v>1.6691385068045789e-05</v>
       </c>
       <c r="Q17">
-        <v>2.1470039271591434e-05</v>
+        <v>1.1212209065329734e-05</v>
       </c>
       <c r="R17">
-        <v>7.6887512839998438e-05</v>
+        <v>3.2840825552024607e-05</v>
       </c>
       <c r="S17">
-        <v>4.947425580304851e-05</v>
+        <v>1.9237983852947061e-05</v>
       </c>
       <c r="T17">
-        <v>-5.8413448049414026e-07</v>
+        <v>-2.33898727898607e-07</v>
       </c>
       <c r="U17">
-        <v>-2.2979295662329864e-08</v>
+        <v>-5.9652446247993817e-08</v>
       </c>
       <c r="V17">
-        <v>1.5694149064509687e-05</v>
+        <v>7.0605225212848227e-06</v>
       </c>
       <c r="W17">
-        <v>-2.940648446642605e-06</v>
+        <v>-7.952644641934495e-07</v>
       </c>
       <c r="X17">
-        <v>0.00073114602378608184</v>
+        <v>0.00023419712648719068</v>
       </c>
       <c r="Y17">
-        <v>-0.00047909329732596158</v>
+        <v>-0.00015884221803105428</v>
       </c>
     </row>
     <row r="18">
@@ -5041,76 +5041,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>0.017302436983416297</v>
+        <v>0.0096526882218952188</v>
       </c>
       <c r="C18">
-        <v>-8.0883417878357524e-07</v>
+        <v>-4.0457110883420921e-07</v>
       </c>
       <c r="D18">
-        <v>-2.3838304619432189e-05</v>
+        <v>-6.9175867121210128e-06</v>
       </c>
       <c r="E18">
-        <v>2.6122344549966236e-07</v>
+        <v>7.5431400360237955e-08</v>
       </c>
       <c r="F18">
-        <v>5.7312749468146801e-05</v>
+        <v>1.4769458480835752e-05</v>
       </c>
       <c r="G18">
-        <v>5.6830883699233198e-05</v>
+        <v>1.5620405915373223e-05</v>
       </c>
       <c r="H18">
-        <v>-9.0635544137996135e-07</v>
+        <v>-2.0094002984831379e-07</v>
       </c>
       <c r="I18">
-        <v>-1.7005363637801167e-07</v>
+        <v>-4.8491981354917893e-09</v>
       </c>
       <c r="J18">
-        <v>-4.314812141882721e-05</v>
+        <v>-1.014924195108342e-05</v>
       </c>
       <c r="K18">
-        <v>-7.9455123780406583e-05</v>
+        <v>-2.1053711903401142e-05</v>
       </c>
       <c r="L18">
-        <v>-9.9445783250567006e-05</v>
+        <v>-2.7009261030942069e-05</v>
       </c>
       <c r="M18">
-        <v>-0.00010105375938242005</v>
+        <v>-2.8444940106264236e-05</v>
       </c>
       <c r="N18">
-        <v>2.1655030864776665e-05</v>
+        <v>1.1719203612126038e-05</v>
       </c>
       <c r="O18">
-        <v>2.1594423628122155e-05</v>
+        <v>1.1052612379658422e-05</v>
       </c>
       <c r="P18">
-        <v>3.7759615768348998e-05</v>
+        <v>1.5936372934331804e-05</v>
       </c>
       <c r="Q18">
-        <v>2.1783319764803975e-05</v>
+        <v>1.1576443897960304e-05</v>
       </c>
       <c r="R18">
-        <v>4.947425580304851e-05</v>
+        <v>1.9237983852947061e-05</v>
       </c>
       <c r="S18">
-        <v>0.0001578230745732516</v>
+        <v>7.2219381336933298e-05</v>
       </c>
       <c r="T18">
-        <v>2.904705798147347e-07</v>
+        <v>3.3710838328491461e-07</v>
       </c>
       <c r="U18">
-        <v>1.0784597107069667e-08</v>
+        <v>2.2121955252224153e-09</v>
       </c>
       <c r="V18">
-        <v>1.3950282741127898e-05</v>
+        <v>5.6480744361936988e-06</v>
       </c>
       <c r="W18">
-        <v>-2.2415272029695866e-06</v>
+        <v>-4.2287593562071534e-07</v>
       </c>
       <c r="X18">
-        <v>0.00064970346861565297</v>
+        <v>0.00018191453983690197</v>
       </c>
       <c r="Y18">
-        <v>-0.00042958153411353796</v>
+        <v>-0.00012818933719486122</v>
       </c>
     </row>
     <row r="19">
@@ -5118,76 +5118,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.078212538538672285</v>
+        <v>0.055160178004331983</v>
       </c>
       <c r="C19">
-        <v>1.4876913557592861e-06</v>
+        <v>1.5961393929950517e-07</v>
       </c>
       <c r="D19">
-        <v>1.6746050310917497e-07</v>
+        <v>-2.3795956639701235e-07</v>
       </c>
       <c r="E19">
-        <v>-1.1389543636260151e-09</v>
+        <v>2.6852729225980295e-09</v>
       </c>
       <c r="F19">
-        <v>-6.8509699303470422e-07</v>
+        <v>6.8208045815348623e-08</v>
       </c>
       <c r="G19">
-        <v>1.3091994742353465e-06</v>
+        <v>7.9144542865582013e-07</v>
       </c>
       <c r="H19">
-        <v>-7.9405996967787316e-09</v>
+        <v>1.5725185508595396e-10</v>
       </c>
       <c r="I19">
-        <v>-7.5870946147771853e-08</v>
+        <v>-1.2438801471828536e-08</v>
       </c>
       <c r="J19">
-        <v>-1.1954101292813481e-07</v>
+        <v>-3.4204518793654737e-07</v>
       </c>
       <c r="K19">
-        <v>1.1610901825532232e-06</v>
+        <v>-5.254650045859939e-07</v>
       </c>
       <c r="L19">
-        <v>1.5106569597387023e-06</v>
+        <v>-5.8427042448626439e-07</v>
       </c>
       <c r="M19">
-        <v>1.6868288774258642e-06</v>
+        <v>-5.6805946546510858e-07</v>
       </c>
       <c r="N19">
-        <v>-1.3295014441671119e-06</v>
+        <v>-6.9071152178091714e-07</v>
       </c>
       <c r="O19">
-        <v>-7.9787605770758569e-09</v>
+        <v>-8.6062159873588874e-09</v>
       </c>
       <c r="P19">
-        <v>-9.3824549647227915e-07</v>
+        <v>-4.0108086500794395e-07</v>
       </c>
       <c r="Q19">
-        <v>-1.7310931306616981e-07</v>
+        <v>4.7019590636019592e-08</v>
       </c>
       <c r="R19">
-        <v>-5.8413448049414026e-07</v>
+        <v>-2.33898727898607e-07</v>
       </c>
       <c r="S19">
-        <v>2.904705798147347e-07</v>
+        <v>3.3710838328491461e-07</v>
       </c>
       <c r="T19">
-        <v>2.8487333551355234e-05</v>
+        <v>7.8955631438471635e-06</v>
       </c>
       <c r="U19">
-        <v>7.4997071680824588e-09</v>
+        <v>1.435195099747199e-09</v>
       </c>
       <c r="V19">
-        <v>-1.616740842358521e-07</v>
+        <v>5.0927482704789162e-09</v>
       </c>
       <c r="W19">
-        <v>-6.3634513392295363e-08</v>
+        <v>-2.5912249614332344e-07</v>
       </c>
       <c r="X19">
-        <v>-1.3565854421655968e-05</v>
+        <v>3.4444129915008987e-06</v>
       </c>
       <c r="Y19">
-        <v>-7.3170170665981745e-07</v>
+        <v>-4.7239067074631937e-06</v>
       </c>
     </row>
     <row r="20">
@@ -5195,76 +5195,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>0.0007303405489464045</v>
+        <v>0.010206939491254789</v>
       </c>
       <c r="C20">
-        <v>1.3669052619210692e-08</v>
+        <v>3.7565263323006585e-08</v>
       </c>
       <c r="D20">
-        <v>-3.4616025827412038e-09</v>
+        <v>-2.0017585538444142e-08</v>
       </c>
       <c r="E20">
-        <v>-9.1784107546116283e-12</v>
+        <v>5.8951553396905426e-11</v>
       </c>
       <c r="F20">
-        <v>7.1772419304783736e-08</v>
+        <v>2.5991658397765661e-07</v>
       </c>
       <c r="G20">
-        <v>6.0789541091559927e-08</v>
+        <v>2.8655030166801858e-07</v>
       </c>
       <c r="H20">
-        <v>-5.0492075387558062e-10</v>
+        <v>-1.8115508004098128e-09</v>
       </c>
       <c r="I20">
-        <v>1.13704376411175e-09</v>
+        <v>2.9433769826306958e-09</v>
       </c>
       <c r="J20">
-        <v>2.7311154412417875e-08</v>
+        <v>5.955013657228466e-08</v>
       </c>
       <c r="K20">
-        <v>8.0072461534031352e-09</v>
+        <v>-2.6138651677631299e-08</v>
       </c>
       <c r="L20">
-        <v>3.8502827979042164e-08</v>
+        <v>2.4579581091591098e-09</v>
       </c>
       <c r="M20">
-        <v>6.0129674102023668e-08</v>
+        <v>6.5456480167735415e-08</v>
       </c>
       <c r="N20">
-        <v>1.8132655318334872e-09</v>
+        <v>3.2238112507922701e-08</v>
       </c>
       <c r="O20">
-        <v>-2.155434061842188e-08</v>
+        <v>-8.3219969458834459e-08</v>
       </c>
       <c r="P20">
-        <v>-1.3389258908355836e-08</v>
+        <v>-1.8725193260008439e-08</v>
       </c>
       <c r="Q20">
-        <v>-5.658415497476381e-08</v>
+        <v>-1.7360743829891166e-07</v>
       </c>
       <c r="R20">
-        <v>-2.2979295662329864e-08</v>
+        <v>-5.9652446247993817e-08</v>
       </c>
       <c r="S20">
-        <v>1.0784597107069667e-08</v>
+        <v>2.2121955252224153e-09</v>
       </c>
       <c r="T20">
-        <v>7.4997071680824588e-09</v>
+        <v>1.435195099747199e-09</v>
       </c>
       <c r="U20">
-        <v>2.3070120460444747e-08</v>
+        <v>8.8239399589656674e-07</v>
       </c>
       <c r="V20">
-        <v>-2.8303698618483381e-07</v>
+        <v>-3.1366985950991495e-06</v>
       </c>
       <c r="W20">
-        <v>-3.597858924730553e-07</v>
+        <v>-3.234970501477392e-06</v>
       </c>
       <c r="X20">
-        <v>-2.4310290782897873e-06</v>
+        <v>-8.8165096026272539e-05</v>
       </c>
       <c r="Y20">
-        <v>-1.2149613741402882e-07</v>
+        <v>-7.0768431516283677e-07</v>
       </c>
     </row>
     <row r="21">
@@ -5272,76 +5272,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.056389625250635171</v>
+        <v>-0.08438464923298282</v>
       </c>
       <c r="C21">
-        <v>1.1089614151102615e-07</v>
+        <v>1.2109519962481994e-07</v>
       </c>
       <c r="D21">
-        <v>-1.573056761131753e-05</v>
+        <v>-7.8215473990291999e-06</v>
       </c>
       <c r="E21">
-        <v>1.7226663104359276e-07</v>
+        <v>8.5508111950068873e-08</v>
       </c>
       <c r="F21">
-        <v>3.77674523185336e-05</v>
+        <v>1.6058854667617644e-05</v>
       </c>
       <c r="G21">
-        <v>4.0849007127186253e-05</v>
+        <v>1.9715418306668763e-05</v>
       </c>
       <c r="H21">
-        <v>-5.8811543804783727e-07</v>
+        <v>-2.1324803933218143e-07</v>
       </c>
       <c r="I21">
-        <v>-1.7225537007922357e-07</v>
+        <v>-5.444744392702974e-08</v>
       </c>
       <c r="J21">
-        <v>-2.8954989545790399e-05</v>
+        <v>-1.1436448180573681e-05</v>
       </c>
       <c r="K21">
-        <v>-5.1894958767801047e-05</v>
+        <v>-2.3315385097676407e-05</v>
       </c>
       <c r="L21">
-        <v>-6.5835933481242021e-05</v>
+        <v>-3.0437422389276659e-05</v>
       </c>
       <c r="M21">
-        <v>-6.6544712648786844e-05</v>
+        <v>-3.1663908300751647e-05</v>
       </c>
       <c r="N21">
-        <v>-2.585954803416979e-06</v>
+        <v>-1.6245071757062736e-06</v>
       </c>
       <c r="O21">
-        <v>-2.4629385506773198e-06</v>
+        <v>-2.0270905054865779e-06</v>
       </c>
       <c r="P21">
-        <v>7.7182165931296854e-06</v>
+        <v>3.1095308112344178e-06</v>
       </c>
       <c r="Q21">
-        <v>-1.0918649338698213e-06</v>
+        <v>-6.6573803187886861e-07</v>
       </c>
       <c r="R21">
-        <v>1.5694149064509687e-05</v>
+        <v>7.0605225212848227e-06</v>
       </c>
       <c r="S21">
-        <v>1.3950282741127898e-05</v>
+        <v>5.6480744361936988e-06</v>
       </c>
       <c r="T21">
-        <v>-1.616740842358521e-07</v>
+        <v>5.0927482704789162e-09</v>
       </c>
       <c r="U21">
-        <v>-2.8303698618483381e-07</v>
+        <v>-3.1366985950991495e-06</v>
       </c>
       <c r="V21">
-        <v>7.0316377151405019e-05</v>
+        <v>5.0678680019036081e-05</v>
       </c>
       <c r="W21">
-        <v>6.9314491175848699e-06</v>
+        <v>1.2716786352939688e-05</v>
       </c>
       <c r="X21">
-        <v>0.0004714475112771009</v>
+        <v>0.0005321876985731255</v>
       </c>
       <c r="Y21">
-        <v>-0.00028072052652222467</v>
+        <v>-0.00014192090778209941</v>
       </c>
     </row>
     <row r="22">
@@ -5349,76 +5349,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>0.026525630972308496</v>
+        <v>0.0059931099562607563</v>
       </c>
       <c r="C22">
-        <v>5.10240037640505e-07</v>
+        <v>3.0392419529036894e-07</v>
       </c>
       <c r="D22">
-        <v>2.8932331615611547e-06</v>
+        <v>1.0355701785805711e-06</v>
       </c>
       <c r="E22">
-        <v>-3.1374269602771049e-08</v>
+        <v>-1.0859427514709191e-08</v>
       </c>
       <c r="F22">
-        <v>-7.8764500127419655e-06</v>
+        <v>-2.9351116732279857e-06</v>
       </c>
       <c r="G22">
-        <v>-6.5771455963505682e-06</v>
+        <v>-2.7128615164868928e-06</v>
       </c>
       <c r="H22">
-        <v>1.3206321914855699e-07</v>
+        <v>4.1082399052457023e-08</v>
       </c>
       <c r="I22">
-        <v>1.015446245770106e-08</v>
+        <v>-7.255588097708684e-09</v>
       </c>
       <c r="J22">
-        <v>4.736593716540253e-06</v>
+        <v>1.1452816325383639e-06</v>
       </c>
       <c r="K22">
-        <v>9.5727470190799382e-06</v>
+        <v>3.1463906391498534e-06</v>
       </c>
       <c r="L22">
-        <v>1.1957232244727099e-05</v>
+        <v>4.0077784754383725e-06</v>
       </c>
       <c r="M22">
-        <v>1.1225212060819412e-05</v>
+        <v>3.6688987721083748e-06</v>
       </c>
       <c r="N22">
-        <v>2.8443847015067994e-07</v>
+        <v>2.4133608828007539e-08</v>
       </c>
       <c r="O22">
-        <v>2.2889183035389677e-07</v>
+        <v>3.0901366540381607e-07</v>
       </c>
       <c r="P22">
-        <v>-1.7983507466949319e-06</v>
+        <v>-5.2243891837971979e-07</v>
       </c>
       <c r="Q22">
-        <v>1.9477989678308597e-06</v>
+        <v>1.2746315986340119e-06</v>
       </c>
       <c r="R22">
-        <v>-2.940648446642605e-06</v>
+        <v>-7.952644641934495e-07</v>
       </c>
       <c r="S22">
-        <v>-2.2415272029695866e-06</v>
+        <v>-4.2287593562071534e-07</v>
       </c>
       <c r="T22">
-        <v>-6.3634513392295363e-08</v>
+        <v>-2.5912249614332344e-07</v>
       </c>
       <c r="U22">
-        <v>-3.597858924730553e-07</v>
+        <v>-3.234970501477392e-06</v>
       </c>
       <c r="V22">
-        <v>6.9314491175848699e-06</v>
+        <v>1.2716786352939688e-05</v>
       </c>
       <c r="W22">
-        <v>6.0551740851849327e-05</v>
+        <v>4.3228741629367646e-05</v>
       </c>
       <c r="X22">
-        <v>-4.8887505943657285e-05</v>
+        <v>0.00029288390551605078</v>
       </c>
       <c r="Y22">
-        <v>5.6231988371600645e-05</v>
+        <v>2.2161272781502884e-05</v>
       </c>
     </row>
     <row r="23">
@@ -5426,76 +5426,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.0073748138842720115</v>
+        <v>-0.92950523258235174</v>
       </c>
       <c r="C23">
-        <v>-1.2993195352891279e-05</v>
+        <v>-9.5958740143851906e-06</v>
       </c>
       <c r="D23">
-        <v>-0.00082229069051768344</v>
+        <v>-0.00030442236026177933</v>
       </c>
       <c r="E23">
-        <v>8.9886789644505795e-06</v>
+        <v>3.3220812413424139e-06</v>
       </c>
       <c r="F23">
-        <v>0.0017084387849719582</v>
+        <v>0.00050325609427480053</v>
       </c>
       <c r="G23">
-        <v>0.0018941763073360117</v>
+        <v>0.00065246730075265011</v>
       </c>
       <c r="H23">
-        <v>-2.6194522684207799e-05</v>
+        <v>-6.3622847002115338e-06</v>
       </c>
       <c r="I23">
-        <v>-6.5070901507099508e-06</v>
+        <v>-1.1209254959576135e-06</v>
       </c>
       <c r="J23">
-        <v>-0.002499076397709285</v>
+        <v>-0.00091262790470936434</v>
       </c>
       <c r="K23">
-        <v>-0.0036271894745440038</v>
+        <v>-0.0013388504605177575</v>
       </c>
       <c r="L23">
-        <v>-0.0042880176831162145</v>
+        <v>-0.0015876835256496032</v>
       </c>
       <c r="M23">
-        <v>-0.004303963122336215</v>
+        <v>-0.0016276743318835922</v>
       </c>
       <c r="N23">
-        <v>-0.00015992546938117536</v>
+        <v>-7.3831641599804269e-05</v>
       </c>
       <c r="O23">
-        <v>-0.00016570552223314227</v>
+        <v>-9.3483960018726379e-05</v>
       </c>
       <c r="P23">
-        <v>0.00036007334920701631</v>
+        <v>0.00010058405661502449</v>
       </c>
       <c r="Q23">
-        <v>-0.00015845367151692835</v>
+        <v>-6.5125806844308051e-05</v>
       </c>
       <c r="R23">
-        <v>0.00073114602378608184</v>
+        <v>0.00023419712648719068</v>
       </c>
       <c r="S23">
-        <v>0.00064970346861565297</v>
+        <v>0.00018191453983690197</v>
       </c>
       <c r="T23">
-        <v>-1.3565854421655968e-05</v>
+        <v>3.4444129915008987e-06</v>
       </c>
       <c r="U23">
-        <v>-2.4310290782897873e-06</v>
+        <v>-8.8165096026272539e-05</v>
       </c>
       <c r="V23">
-        <v>0.0004714475112771009</v>
+        <v>0.0005321876985731255</v>
       </c>
       <c r="W23">
-        <v>-4.8887505943657285e-05</v>
+        <v>0.00029288390551605078</v>
       </c>
       <c r="X23">
-        <v>0.024375175856896705</v>
+        <v>0.017800131515057632</v>
       </c>
       <c r="Y23">
-        <v>-0.013874256740457475</v>
+        <v>-0.0051312155197763493</v>
       </c>
     </row>
     <row r="24">
@@ -5503,76 +5503,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>0.051096702760304973</v>
+        <v>0.054908965052377357</v>
       </c>
       <c r="C24">
-        <v>3.2475171196025608e-06</v>
+        <v>4.2058815475524122e-07</v>
       </c>
       <c r="D24">
-        <v>0.00049182210711146222</v>
+        <v>0.00018589599351392399</v>
       </c>
       <c r="E24">
-        <v>-5.3840308178254267e-06</v>
+        <v>-2.0234058564472576e-06</v>
       </c>
       <c r="F24">
-        <v>-0.0011652789686892396</v>
+        <v>-0.00038651503738428863</v>
       </c>
       <c r="G24">
-        <v>-0.0012544040432574204</v>
+        <v>-0.00047065749231569389</v>
       </c>
       <c r="H24">
-        <v>1.8143175942442899e-05</v>
+        <v>5.0368660252443435e-06</v>
       </c>
       <c r="I24">
-        <v>4.8441814428071592e-06</v>
+        <v>9.087217792319713e-07</v>
       </c>
       <c r="J24">
-        <v>0.00088604782218495179</v>
+        <v>0.00026249820986849612</v>
       </c>
       <c r="K24">
-        <v>0.0016002822276409384</v>
+        <v>0.00054686572298210767</v>
       </c>
       <c r="L24">
-        <v>0.0020152437277199471</v>
+        <v>0.00070736538284481331</v>
       </c>
       <c r="M24">
-        <v>0.0020153521196437578</v>
+        <v>0.00072541972682367735</v>
       </c>
       <c r="N24">
-        <v>8.7025558840640445e-05</v>
+        <v>3.8876075961376768e-05</v>
       </c>
       <c r="O24">
-        <v>8.9399256862211164e-05</v>
+        <v>5.7559167331081122e-05</v>
       </c>
       <c r="P24">
-        <v>-0.00024282955444504954</v>
+        <v>-7.3381672070635059e-05</v>
       </c>
       <c r="Q24">
-        <v>8.7169740522222201e-05</v>
+        <v>4.479010644990466e-05</v>
       </c>
       <c r="R24">
-        <v>-0.00047909329732596158</v>
+        <v>-0.00015884221803105428</v>
       </c>
       <c r="S24">
-        <v>-0.00042958153411353796</v>
+        <v>-0.00012818933719486122</v>
       </c>
       <c r="T24">
-        <v>-7.3170170665981745e-07</v>
+        <v>-4.7239067074631937e-06</v>
       </c>
       <c r="U24">
-        <v>-1.2149613741402882e-07</v>
+        <v>-7.0768431516283677e-07</v>
       </c>
       <c r="V24">
-        <v>-0.00028072052652222467</v>
+        <v>-0.00014192090778209941</v>
       </c>
       <c r="W24">
-        <v>5.6231988371600645e-05</v>
+        <v>2.2161272781502884e-05</v>
       </c>
       <c r="X24">
-        <v>-0.013874256740457475</v>
+        <v>-0.0051312155197763493</v>
       </c>
       <c r="Y24">
-        <v>0.0087936723428397763</v>
+        <v>0.0034041640890603319</v>
       </c>
     </row>
   </sheetData>
@@ -5666,76 +5666,76 @@
         <v>46</v>
       </c>
       <c r="B2">
-        <v>0.83126590473728301</v>
+        <v>0.86975088072294982</v>
       </c>
       <c r="C2">
-        <v>5.9237837908117589e-06</v>
+        <v>3.7493092483746337e-06</v>
       </c>
       <c r="D2">
-        <v>4.5887247426779988e-08</v>
+        <v>-2.6020684252774799e-08</v>
       </c>
       <c r="E2">
-        <v>-1.4961941143428185e-09</v>
+        <v>-4.0356222855670436e-10</v>
       </c>
       <c r="F2">
-        <v>7.1732336728278648e-08</v>
+        <v>-5.6546087702198896e-08</v>
       </c>
       <c r="G2">
-        <v>-9.8367293940792031e-08</v>
+        <v>-1.5564906990507795e-07</v>
       </c>
       <c r="H2">
-        <v>3.2012109515060903e-08</v>
+        <v>2.3649609794356989e-08</v>
       </c>
       <c r="I2">
-        <v>5.3959519731611457e-08</v>
+        <v>3.8848045755767354e-08</v>
       </c>
       <c r="J2">
-        <v>2.7855784309168728e-07</v>
+        <v>4.7915313652132934e-07</v>
       </c>
       <c r="K2">
-        <v>1.0486267527294199e-06</v>
+        <v>8.3409089714013324e-07</v>
       </c>
       <c r="L2">
-        <v>8.8612922197393107e-07</v>
+        <v>6.8138721747397799e-07</v>
       </c>
       <c r="M2">
-        <v>6.4963505411069502e-07</v>
+        <v>5.4874956897907983e-07</v>
       </c>
       <c r="N2">
-        <v>-9.6066022111804419e-07</v>
+        <v>-5.8330687499419406e-07</v>
       </c>
       <c r="O2">
-        <v>-9.0146236335787515e-07</v>
+        <v>-5.9153659494403362e-07</v>
       </c>
       <c r="P2">
-        <v>6.6440271327904965e-08</v>
+        <v>6.1276383870881833e-08</v>
       </c>
       <c r="Q2">
-        <v>-5.9190702730673294e-07</v>
+        <v>-3.9080372082962989e-07</v>
       </c>
       <c r="R2">
-        <v>-2.8522656107090189e-07</v>
+        <v>-1.422498135683048e-07</v>
       </c>
       <c r="S2">
-        <v>-5.6547022472950161e-08</v>
+        <v>3.831574188680449e-08</v>
       </c>
       <c r="T2">
-        <v>1.3287275762302553e-06</v>
+        <v>-1.3980890365962598e-07</v>
       </c>
       <c r="U2">
-        <v>5.2377921735377083e-09</v>
+        <v>1.7995809731197625e-08</v>
       </c>
       <c r="V2">
-        <v>-5.5290649816510161e-08</v>
+        <v>3.4055850287699676e-09</v>
       </c>
       <c r="W2">
-        <v>4.3607407506954471e-07</v>
+        <v>2.873535427769429e-07</v>
       </c>
       <c r="X2">
-        <v>-1.5675557809395382e-05</v>
+        <v>-1.0213282233439339e-05</v>
       </c>
       <c r="Y2">
-        <v>6.6927244685118126e-06</v>
+        <v>3.305903920989959e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5743,76 +5743,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-0.0058343757216171551</v>
+        <v>-0.0049820258574171236</v>
       </c>
       <c r="C3">
-        <v>4.5887247426779988e-08</v>
+        <v>-2.6020684252774799e-08</v>
       </c>
       <c r="D3">
-        <v>1.3954839072145686e-05</v>
+        <v>6.4920014096326296e-06</v>
       </c>
       <c r="E3">
-        <v>-1.558149829118318e-07</v>
+        <v>-7.2217789537414341e-08</v>
       </c>
       <c r="F3">
-        <v>-8.7148949651765035e-06</v>
+        <v>-4.4837722738557759e-06</v>
       </c>
       <c r="G3">
-        <v>-1.7873099092108959e-05</v>
+        <v>-8.4319290491743917e-06</v>
       </c>
       <c r="H3">
-        <v>1.3313099506281436e-07</v>
+        <v>4.9617903803808591e-08</v>
       </c>
       <c r="I3">
-        <v>9.5954672707735298e-08</v>
+        <v>3.6304586080088117e-08</v>
       </c>
       <c r="J3">
-        <v>2.0013482185669336e-05</v>
+        <v>8.2975147555771073e-06</v>
       </c>
       <c r="K3">
-        <v>6.0129700557721514e-05</v>
+        <v>2.6866290794447383e-05</v>
       </c>
       <c r="L3">
-        <v>7.2362126840079628e-05</v>
+        <v>3.2519824450121845e-05</v>
       </c>
       <c r="M3">
-        <v>7.4154737287557201e-05</v>
+        <v>3.3966365713674791e-05</v>
       </c>
       <c r="N3">
-        <v>3.4782511213754523e-06</v>
+        <v>1.5008711439621603e-06</v>
       </c>
       <c r="O3">
-        <v>9.2328484205766048e-07</v>
+        <v>6.2949577764948125e-07</v>
       </c>
       <c r="P3">
-        <v>-3.4447999737633082e-06</v>
+        <v>-1.6847509287975427e-06</v>
       </c>
       <c r="Q3">
-        <v>1.5422586855312324e-06</v>
+        <v>6.4996117400315975e-07</v>
       </c>
       <c r="R3">
-        <v>-5.944987610232904e-06</v>
+        <v>-2.9823135974582155e-06</v>
       </c>
       <c r="S3">
-        <v>-7.4966643943244017e-06</v>
+        <v>-4.0738935503178311e-06</v>
       </c>
       <c r="T3">
-        <v>-1.66524894100824e-07</v>
+        <v>-1.4884043431229844e-07</v>
       </c>
       <c r="U3">
-        <v>-1.8663216877748614e-08</v>
+        <v>-5.9045169121804041e-08</v>
       </c>
       <c r="V3">
-        <v>-1.9811620688097642e-06</v>
+        <v>-1.452944066437684e-06</v>
       </c>
       <c r="W3">
-        <v>3.9872227176512081e-06</v>
+        <v>2.1899198775295396e-06</v>
       </c>
       <c r="X3">
-        <v>-0.00039376374772302232</v>
+        <v>-0.00017668152883912151</v>
       </c>
       <c r="Y3">
-        <v>0.0002077004979772021</v>
+        <v>9.8922400228267234e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5820,76 +5820,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>8.2392447887299128e-05</v>
+        <v>6.8657210371679092e-05</v>
       </c>
       <c r="C4">
-        <v>-1.4961941143428185e-09</v>
+        <v>-4.0356222855670436e-10</v>
       </c>
       <c r="D4">
-        <v>-1.558149829118318e-07</v>
+        <v>-7.2217789537414341e-08</v>
       </c>
       <c r="E4">
-        <v>1.7491709864580634e-09</v>
+        <v>8.0783068173369531e-10</v>
       </c>
       <c r="F4">
-        <v>1.3368689047586091e-07</v>
+        <v>6.7352991174450275e-08</v>
       </c>
       <c r="G4">
-        <v>2.3668663177665324e-07</v>
+        <v>1.115918906753979e-07</v>
       </c>
       <c r="H4">
-        <v>-2.2978073277342186e-09</v>
+        <v>-9.381530559641011e-10</v>
       </c>
       <c r="I4">
-        <v>-1.8859064866362593e-09</v>
+        <v>-7.9209737482479619e-10</v>
       </c>
       <c r="J4">
-        <v>-2.2531484894784967e-07</v>
+        <v>-9.3060084178158029e-08</v>
       </c>
       <c r="K4">
-        <v>-6.7533380903206184e-07</v>
+        <v>-3.006834914001377e-07</v>
       </c>
       <c r="L4">
-        <v>-8.1149596928046327e-07</v>
+        <v>-3.6338290619828779e-07</v>
       </c>
       <c r="M4">
-        <v>-8.2985245309986549e-07</v>
+        <v>-3.7868040509728426e-07</v>
       </c>
       <c r="N4">
-        <v>-3.8722402834084351e-08</v>
+        <v>-1.6599433517581187e-08</v>
       </c>
       <c r="O4">
-        <v>-9.9000472671791189e-09</v>
+        <v>-6.7970503252989376e-09</v>
       </c>
       <c r="P4">
-        <v>3.8802443247592751e-08</v>
+        <v>1.8897972135137436e-08</v>
       </c>
       <c r="Q4">
-        <v>-1.7077864676435316e-08</v>
+        <v>-7.118513568822003e-09</v>
       </c>
       <c r="R4">
-        <v>6.667319453899624e-08</v>
+        <v>3.3364712290748938e-08</v>
       </c>
       <c r="S4">
-        <v>8.3976364964385809e-08</v>
+        <v>4.5498903101837152e-08</v>
       </c>
       <c r="T4">
-        <v>3.3756688884194295e-09</v>
+        <v>1.7297438270260241e-09</v>
       </c>
       <c r="U4">
-        <v>1.8657707516982281e-10</v>
+        <v>5.8630657187560685e-10</v>
       </c>
       <c r="V4">
-        <v>2.225534337520319e-08</v>
+        <v>1.6429437300475129e-08</v>
       </c>
       <c r="W4">
-        <v>-4.4765961341869402e-08</v>
+        <v>-2.4375005538066314e-08</v>
       </c>
       <c r="X4">
-        <v>4.3864294117804359e-06</v>
+        <v>1.9668894929256238e-06</v>
       </c>
       <c r="Y4">
-        <v>-2.3324970550775778e-06</v>
+        <v>-1.1072361420490673e-06</v>
       </c>
     </row>
     <row r="5">
@@ -5897,76 +5897,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0019482819604356432</v>
+        <v>0.00057550558606304036</v>
       </c>
       <c r="C5">
-        <v>7.1732336728278648e-08</v>
+        <v>-5.6546087702198896e-08</v>
       </c>
       <c r="D5">
-        <v>-8.7148949651765035e-06</v>
+        <v>-4.4837722738557759e-06</v>
       </c>
       <c r="E5">
-        <v>1.3368689047586091e-07</v>
+        <v>6.7352991174450275e-08</v>
       </c>
       <c r="F5">
-        <v>0.00038806792322780272</v>
+        <v>0.00019444848296790355</v>
       </c>
       <c r="G5">
-        <v>0.00017325106484382399</v>
+        <v>8.4814638127603186e-05</v>
       </c>
       <c r="H5">
-        <v>-8.1197795818348011e-06</v>
+        <v>-4.0125967802973832e-06</v>
       </c>
       <c r="I5">
-        <v>-3.359976975652168e-06</v>
+        <v>-1.6139445221402664e-06</v>
       </c>
       <c r="J5">
-        <v>-2.2200230299043288e-05</v>
+        <v>-9.0649502230944772e-06</v>
       </c>
       <c r="K5">
-        <v>-6.5599528854290066e-05</v>
+        <v>-3.1167343615661486e-05</v>
       </c>
       <c r="L5">
-        <v>-7.8919802030794257e-05</v>
+        <v>-3.8148457151824427e-05</v>
       </c>
       <c r="M5">
-        <v>-7.9434554860319392e-05</v>
+        <v>-3.9089452174247567e-05</v>
       </c>
       <c r="N5">
-        <v>-2.6986659927696137e-06</v>
+        <v>-1.1531209037193306e-06</v>
       </c>
       <c r="O5">
-        <v>1.1657966600431001e-06</v>
+        <v>3.1617444695255206e-07</v>
       </c>
       <c r="P5">
-        <v>4.3737019801844475e-06</v>
+        <v>2.2974523175395136e-06</v>
       </c>
       <c r="Q5">
-        <v>-4.3504871186556587e-07</v>
+        <v>-9.3083412858741814e-09</v>
       </c>
       <c r="R5">
-        <v>5.2130673001730663e-06</v>
+        <v>3.1103810922205245e-06</v>
       </c>
       <c r="S5">
-        <v>6.1174234925863808e-06</v>
+        <v>3.7063988518787839e-06</v>
       </c>
       <c r="T5">
-        <v>3.2717994297094283e-06</v>
+        <v>4.0098069644085504e-07</v>
       </c>
       <c r="U5">
-        <v>6.7305737183686909e-08</v>
+        <v>2.4936636386985689e-07</v>
       </c>
       <c r="V5">
-        <v>1.6444367371135147e-06</v>
+        <v>1.0631059525672129e-06</v>
       </c>
       <c r="W5">
-        <v>-4.2140562749643492e-06</v>
+        <v>-2.8934685905956172e-06</v>
       </c>
       <c r="X5">
-        <v>0.00019959015422445545</v>
+        <v>8.0744572336243663e-05</v>
       </c>
       <c r="Y5">
-        <v>-0.00022037206003641167</v>
+        <v>-0.00011561373723827647</v>
       </c>
     </row>
     <row r="6">
@@ -5974,76 +5974,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.038104523133063541</v>
+        <v>-0.021546442268283984</v>
       </c>
       <c r="C6">
-        <v>-9.8367293940792031e-08</v>
+        <v>-1.5564906990507795e-07</v>
       </c>
       <c r="D6">
-        <v>-1.7873099092108959e-05</v>
+        <v>-8.4319290491743917e-06</v>
       </c>
       <c r="E6">
-        <v>2.3668663177665324e-07</v>
+        <v>1.115918906753979e-07</v>
       </c>
       <c r="F6">
-        <v>0.00017325106484382399</v>
+        <v>8.4814638127603186e-05</v>
       </c>
       <c r="G6">
-        <v>0.00034683178136187969</v>
+        <v>0.00017525938764336856</v>
       </c>
       <c r="H6">
-        <v>-3.5893245491464491e-06</v>
+        <v>-1.7071555804151653e-06</v>
       </c>
       <c r="I6">
-        <v>-6.7288241936962753e-06</v>
+        <v>-3.3705387204697344e-06</v>
       </c>
       <c r="J6">
-        <v>-3.0769526104212214e-05</v>
+        <v>-1.2704703787767528e-05</v>
       </c>
       <c r="K6">
-        <v>-0.00010248558534714489</v>
+        <v>-4.7004137331979826e-05</v>
       </c>
       <c r="L6">
-        <v>-0.00012433019303519094</v>
+        <v>-5.7622802465991116e-05</v>
       </c>
       <c r="M6">
-        <v>-0.000123866240163597</v>
+        <v>-5.8372642374019188e-05</v>
       </c>
       <c r="N6">
-        <v>-4.3975775627392715e-06</v>
+        <v>-1.7211455778821662e-06</v>
       </c>
       <c r="O6">
-        <v>6.4182520887894778e-07</v>
+        <v>-3.3538541482072645e-08</v>
       </c>
       <c r="P6">
-        <v>4.4203215265220427e-06</v>
+        <v>2.3179724315835008e-06</v>
       </c>
       <c r="Q6">
-        <v>-3.5934935990956382e-06</v>
+        <v>-1.330157009369033e-06</v>
       </c>
       <c r="R6">
-        <v>5.4572344863974676e-06</v>
+        <v>3.1106497498038197e-06</v>
       </c>
       <c r="S6">
-        <v>9.6576797139496394e-06</v>
+        <v>5.6190447616348639e-06</v>
       </c>
       <c r="T6">
-        <v>4.4549656765141915e-06</v>
+        <v>1.3148158607457092e-06</v>
       </c>
       <c r="U6">
-        <v>7.3647517009285963e-08</v>
+        <v>2.9566211107643744e-07</v>
       </c>
       <c r="V6">
-        <v>3.4080551761399092e-06</v>
+        <v>2.12955715060847e-06</v>
       </c>
       <c r="W6">
-        <v>-6.7529208042759716e-06</v>
+        <v>-4.1967795708656656e-06</v>
       </c>
       <c r="X6">
-        <v>0.00045523870911117316</v>
+        <v>0.00018616673067599869</v>
       </c>
       <c r="Y6">
-        <v>-0.00035111507104032297</v>
+        <v>-0.00017212153293463017</v>
       </c>
     </row>
     <row r="7">
@@ -6051,76 +6051,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.0010872750907351524</v>
+        <v>-0.00084380521135939493</v>
       </c>
       <c r="C7">
-        <v>3.2012109515060903e-08</v>
+        <v>2.3649609794356989e-08</v>
       </c>
       <c r="D7">
-        <v>1.3313099506281436e-07</v>
+        <v>4.9617903803808591e-08</v>
       </c>
       <c r="E7">
-        <v>-2.2978073277342186e-09</v>
+        <v>-9.381530559641011e-10</v>
       </c>
       <c r="F7">
-        <v>-8.1197795818348011e-06</v>
+        <v>-4.0125967802973832e-06</v>
       </c>
       <c r="G7">
-        <v>-3.5893245491464491e-06</v>
+        <v>-1.7071555804151653e-06</v>
       </c>
       <c r="H7">
-        <v>1.787481468362799e-07</v>
+        <v>8.7435946642852617e-08</v>
       </c>
       <c r="I7">
-        <v>7.4346594050843133e-08</v>
+        <v>3.5288465635049357e-08</v>
       </c>
       <c r="J7">
-        <v>3.8790514206460526e-07</v>
+        <v>1.2668275442650656e-07</v>
       </c>
       <c r="K7">
-        <v>1.1445017259723074e-06</v>
+        <v>4.4789464588845343e-07</v>
       </c>
       <c r="L7">
-        <v>1.3912482243445577e-06</v>
+        <v>5.5831176476437219e-07</v>
       </c>
       <c r="M7">
-        <v>1.4006845438746326e-06</v>
+        <v>5.7120364065679443e-07</v>
       </c>
       <c r="N7">
-        <v>3.9189937611493101e-08</v>
+        <v>1.0845928954749191e-08</v>
       </c>
       <c r="O7">
-        <v>-2.0587783921893348e-08</v>
+        <v>-7.8863308380046609e-09</v>
       </c>
       <c r="P7">
-        <v>-8.425802755565154e-08</v>
+        <v>-3.7810072888058567e-08</v>
       </c>
       <c r="Q7">
-        <v>-2.9749858540179763e-09</v>
+        <v>-7.5861303317833193e-09</v>
       </c>
       <c r="R7">
-        <v>-9.2039865286875139e-08</v>
+        <v>-4.5723386324652696e-08</v>
       </c>
       <c r="S7">
-        <v>-1.0031366292135383e-07</v>
+        <v>-4.6432332062957618e-08</v>
       </c>
       <c r="T7">
-        <v>-5.7006550310835056e-08</v>
+        <v>3.6740225890595579e-09</v>
       </c>
       <c r="U7">
-        <v>-9.1750634036044571e-10</v>
+        <v>-3.2473049249459306e-09</v>
       </c>
       <c r="V7">
-        <v>-3.3529024612047614e-08</v>
+        <v>-1.7905531805868269e-08</v>
       </c>
       <c r="W7">
-        <v>7.6257218101995673e-08</v>
+        <v>4.2667883946027046e-08</v>
       </c>
       <c r="X7">
-        <v>-2.950294593108907e-06</v>
+        <v>-7.0436012023153355e-07</v>
       </c>
       <c r="Y7">
-        <v>3.8565178576067315e-06</v>
+        <v>1.6868593373019716e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6128,76 +6128,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>-0.00074211044660848656</v>
+        <v>-0.00070010586150180882</v>
       </c>
       <c r="C8">
-        <v>5.3959519731611457e-08</v>
+        <v>3.8848045755767354e-08</v>
       </c>
       <c r="D8">
-        <v>9.5954672707735298e-08</v>
+        <v>3.6304586080088117e-08</v>
       </c>
       <c r="E8">
-        <v>-1.8859064866362593e-09</v>
+        <v>-7.9209737482479619e-10</v>
       </c>
       <c r="F8">
-        <v>-3.359976975652168e-06</v>
+        <v>-1.6139445221402664e-06</v>
       </c>
       <c r="G8">
-        <v>-6.7288241936962753e-06</v>
+        <v>-3.3705387204697344e-06</v>
       </c>
       <c r="H8">
-        <v>7.4346594050843133e-08</v>
+        <v>3.5288465635049357e-08</v>
       </c>
       <c r="I8">
-        <v>1.4360711784852036e-07</v>
+        <v>7.1668537277623062e-08</v>
       </c>
       <c r="J8">
-        <v>2.0132503619176631e-07</v>
+        <v>6.8052189089356633e-08</v>
       </c>
       <c r="K8">
-        <v>8.0891463998523087e-07</v>
+        <v>3.351880387446948e-07</v>
       </c>
       <c r="L8">
-        <v>1.0155820212859466e-06</v>
+        <v>4.3107311852507323e-07</v>
       </c>
       <c r="M8">
-        <v>9.9173452374288045e-07</v>
+        <v>4.2446323942422309e-07</v>
       </c>
       <c r="N8">
-        <v>1.8453898443766697e-08</v>
+        <v>1.3306708774711502e-09</v>
       </c>
       <c r="O8">
-        <v>-1.3791195539239086e-08</v>
+        <v>-5.4217143545375601e-09</v>
       </c>
       <c r="P8">
-        <v>-4.0413331647797797e-08</v>
+        <v>-2.010986336759991e-08</v>
       </c>
       <c r="Q8">
-        <v>3.4013435788667961e-08</v>
+        <v>9.1743366550895453e-09</v>
       </c>
       <c r="R8">
-        <v>-8.4933442535895586e-09</v>
+        <v>-6.8766190139455755e-09</v>
       </c>
       <c r="S8">
-        <v>-3.2842988188935253e-08</v>
+        <v>-1.7199568806099296e-08</v>
       </c>
       <c r="T8">
-        <v>-4.6466897732681156e-08</v>
+        <v>-1.0865355455699018e-09</v>
       </c>
       <c r="U8">
-        <v>-4.4966324398754097e-12</v>
+        <v>-8.8413202586812228e-10</v>
       </c>
       <c r="V8">
-        <v>-3.4329337945069541e-08</v>
+        <v>-2.1145732159066031e-08</v>
       </c>
       <c r="W8">
-        <v>5.2404092373262274e-08</v>
+        <v>2.7448085571362176e-08</v>
       </c>
       <c r="X8">
-        <v>-1.802194501066031e-06</v>
+        <v>-5.1289073447274079e-07</v>
       </c>
       <c r="Y8">
-        <v>2.7027134891823049e-06</v>
+        <v>1.192513436268208e-06</v>
       </c>
     </row>
     <row r="9">
@@ -6205,76 +6205,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>-0.029439923156171954</v>
+        <v>-0.018317645453312267</v>
       </c>
       <c r="C9">
-        <v>2.7855784309168728e-07</v>
+        <v>4.7915313652132934e-07</v>
       </c>
       <c r="D9">
-        <v>2.0013482185669336e-05</v>
+        <v>8.2975147555771073e-06</v>
       </c>
       <c r="E9">
-        <v>-2.2531484894784967e-07</v>
+        <v>-9.3060084178158029e-08</v>
       </c>
       <c r="F9">
-        <v>-2.2200230299043288e-05</v>
+        <v>-9.0649502230944772e-06</v>
       </c>
       <c r="G9">
-        <v>-3.0769526104212214e-05</v>
+        <v>-1.2704703787767528e-05</v>
       </c>
       <c r="H9">
-        <v>3.8790514206460526e-07</v>
+        <v>1.2668275442650656e-07</v>
       </c>
       <c r="I9">
-        <v>2.0132503619176631e-07</v>
+        <v>6.8052189089356633e-08</v>
       </c>
       <c r="J9">
-        <v>0.0013776840950269424</v>
+        <v>0.0006089531188407328</v>
       </c>
       <c r="K9">
-        <v>0.0012540197201127987</v>
+        <v>0.00054469028556392691</v>
       </c>
       <c r="L9">
-        <v>0.0012736512617439349</v>
+        <v>0.00055267386829419116</v>
       </c>
       <c r="M9">
-        <v>0.0012754644394875206</v>
+        <v>0.00055427776517151268</v>
       </c>
       <c r="N9">
-        <v>6.4621860430255533e-06</v>
+        <v>2.7449286249292225e-06</v>
       </c>
       <c r="O9">
-        <v>1.608137257407316e-06</v>
+        <v>1.5205527580832647e-06</v>
       </c>
       <c r="P9">
-        <v>-6.3237685478894463e-06</v>
+        <v>-2.4602292046622618e-06</v>
       </c>
       <c r="Q9">
-        <v>2.6958564570493996e-06</v>
+        <v>1.159232439146969e-06</v>
       </c>
       <c r="R9">
-        <v>-8.9335729862000204e-06</v>
+        <v>-3.9142690101402254e-06</v>
       </c>
       <c r="S9">
-        <v>-1.1107858342998105e-05</v>
+        <v>-4.9740430826625885e-06</v>
       </c>
       <c r="T9">
-        <v>-6.4264315426858742e-07</v>
+        <v>-5.4990974310952464e-07</v>
       </c>
       <c r="U9">
-        <v>-1.0293055073266041e-09</v>
+        <v>-8.7998620831458841e-09</v>
       </c>
       <c r="V9">
-        <v>-2.9234090131560762e-06</v>
+        <v>-2.1678559648716723e-06</v>
       </c>
       <c r="W9">
-        <v>6.4156100948280014e-06</v>
+        <v>3.010978595897957e-06</v>
       </c>
       <c r="X9">
-        <v>-0.0017387958361043373</v>
+        <v>-0.00074523114350746617</v>
       </c>
       <c r="Y9">
-        <v>0.00033458979698305317</v>
+        <v>0.000141595968505922</v>
       </c>
     </row>
     <row r="10">
@@ -6282,76 +6282,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>-0.036329812740739716</v>
+        <v>-0.026376237821834969</v>
       </c>
       <c r="C10">
-        <v>1.0486267527294199e-06</v>
+        <v>8.3409089714013324e-07</v>
       </c>
       <c r="D10">
-        <v>6.0129700557721514e-05</v>
+        <v>2.6866290794447383e-05</v>
       </c>
       <c r="E10">
-        <v>-6.7533380903206184e-07</v>
+        <v>-3.006834914001377e-07</v>
       </c>
       <c r="F10">
-        <v>-6.5599528854290066e-05</v>
+        <v>-3.1167343615661486e-05</v>
       </c>
       <c r="G10">
-        <v>-0.00010248558534714489</v>
+        <v>-4.7004137331979826e-05</v>
       </c>
       <c r="H10">
-        <v>1.1445017259723074e-06</v>
+        <v>4.4789464588845343e-07</v>
       </c>
       <c r="I10">
-        <v>8.0891463998523087e-07</v>
+        <v>3.351880387446948e-07</v>
       </c>
       <c r="J10">
-        <v>0.0012540197201127987</v>
+        <v>0.00054469028556392691</v>
       </c>
       <c r="K10">
-        <v>0.0014732772120472021</v>
+        <v>0.00064350435838150214</v>
       </c>
       <c r="L10">
-        <v>0.0015122180312632703</v>
+        <v>0.00065986188304341766</v>
       </c>
       <c r="M10">
-        <v>0.0015186314909092342</v>
+        <v>0.00066559637746996551</v>
       </c>
       <c r="N10">
-        <v>1.7546478430945737e-05</v>
+        <v>7.4164454368304886e-06</v>
       </c>
       <c r="O10">
-        <v>3.6378605974693558e-06</v>
+        <v>3.0157035244512283e-06</v>
       </c>
       <c r="P10">
-        <v>-1.8730956616534432e-05</v>
+        <v>-8.5038717859722384e-06</v>
       </c>
       <c r="Q10">
-        <v>6.9666982957134516e-06</v>
+        <v>2.8040376653474367e-06</v>
       </c>
       <c r="R10">
-        <v>-2.9293063091893173e-05</v>
+        <v>-1.4226247799795768e-05</v>
       </c>
       <c r="S10">
-        <v>-3.6883821031825323e-05</v>
+        <v>-1.8938739548977797e-05</v>
       </c>
       <c r="T10">
-        <v>-4.9523513682471413e-06</v>
+        <v>-1.7434364261560208e-06</v>
       </c>
       <c r="U10">
-        <v>-7.6420759748410273e-08</v>
+        <v>-2.584254374300843e-07</v>
       </c>
       <c r="V10">
-        <v>-8.9338675228979132e-06</v>
+        <v>-6.5833724288756769e-06</v>
       </c>
       <c r="W10">
-        <v>1.9550793963314952e-05</v>
+        <v>1.0329262700234433e-05</v>
       </c>
       <c r="X10">
-        <v>-0.0029054995981686949</v>
+        <v>-0.0012597000370176302</v>
       </c>
       <c r="Y10">
-        <v>0.0010135774353958857</v>
+        <v>0.00046583080152770096</v>
       </c>
     </row>
     <row r="11">
@@ -6359,76 +6359,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.021906606451623317</v>
+        <v>-0.022803440788909155</v>
       </c>
       <c r="C11">
-        <v>8.8612922197393107e-07</v>
+        <v>6.8138721747397799e-07</v>
       </c>
       <c r="D11">
-        <v>7.2362126840079628e-05</v>
+        <v>3.2519824450121845e-05</v>
       </c>
       <c r="E11">
-        <v>-8.1149596928046327e-07</v>
+        <v>-3.6338290619828779e-07</v>
       </c>
       <c r="F11">
-        <v>-7.8919802030794257e-05</v>
+        <v>-3.8148457151824427e-05</v>
       </c>
       <c r="G11">
-        <v>-0.00012433019303519094</v>
+        <v>-5.7622802465991116e-05</v>
       </c>
       <c r="H11">
-        <v>1.3912482243445577e-06</v>
+        <v>5.5831176476437219e-07</v>
       </c>
       <c r="I11">
-        <v>1.0155820212859466e-06</v>
+        <v>4.3107311852507323e-07</v>
       </c>
       <c r="J11">
-        <v>0.0012736512617439349</v>
+        <v>0.00055267386829419116</v>
       </c>
       <c r="K11">
-        <v>0.0015122180312632703</v>
+        <v>0.00065986188304341766</v>
       </c>
       <c r="L11">
-        <v>0.001589971224691609</v>
+        <v>0.00069500881340959911</v>
       </c>
       <c r="M11">
-        <v>0.001594174146135942</v>
+        <v>0.00070016236595029085</v>
       </c>
       <c r="N11">
-        <v>2.0856542594608544e-05</v>
+        <v>8.7874293070027796e-06</v>
       </c>
       <c r="O11">
-        <v>4.1721718910241178e-06</v>
+        <v>3.5077856709944612e-06</v>
       </c>
       <c r="P11">
-        <v>-2.2680428637966826e-05</v>
+        <v>-1.0484730405781603e-05</v>
       </c>
       <c r="Q11">
-        <v>8.2704746000603579e-06</v>
+        <v>3.3239401602094616e-06</v>
       </c>
       <c r="R11">
-        <v>-3.5499897491956005e-05</v>
+        <v>-1.7420948205828125e-05</v>
       </c>
       <c r="S11">
-        <v>-4.3542500584354036e-05</v>
+        <v>-2.2579347144171473e-05</v>
       </c>
       <c r="T11">
-        <v>-5.4349870505749709e-06</v>
+        <v>-2.031040103899715e-06</v>
       </c>
       <c r="U11">
-        <v>-6.8180339477921365e-08</v>
+        <v>-2.6388657331497087e-07</v>
       </c>
       <c r="V11">
-        <v>-1.1547170069487894e-05</v>
+        <v>-8.4177487108553692e-06</v>
       </c>
       <c r="W11">
-        <v>2.3517053811397191e-05</v>
+        <v>1.2496710816861038e-05</v>
       </c>
       <c r="X11">
-        <v>-0.0032673999284424538</v>
+        <v>-0.0014246005271922877</v>
       </c>
       <c r="Y11">
-        <v>0.0012202160104896633</v>
+        <v>0.00056448322647335619</v>
       </c>
     </row>
     <row r="12">
@@ -6436,76 +6436,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>-0.011214860264227565</v>
+        <v>-0.015940442378472451</v>
       </c>
       <c r="C12">
-        <v>6.4963505411069502e-07</v>
+        <v>5.4874956897907983e-07</v>
       </c>
       <c r="D12">
-        <v>7.4154737287557201e-05</v>
+        <v>3.3966365713674791e-05</v>
       </c>
       <c r="E12">
-        <v>-8.2985245309986549e-07</v>
+        <v>-3.7868040509728426e-07</v>
       </c>
       <c r="F12">
-        <v>-7.9434554860319392e-05</v>
+        <v>-3.9089452174247567e-05</v>
       </c>
       <c r="G12">
-        <v>-0.000123866240163597</v>
+        <v>-5.8372642374019188e-05</v>
       </c>
       <c r="H12">
-        <v>1.4006845438746326e-06</v>
+        <v>5.7120364065679443e-07</v>
       </c>
       <c r="I12">
-        <v>9.9173452374288045e-07</v>
+        <v>4.2446323942422309e-07</v>
       </c>
       <c r="J12">
-        <v>0.0012754644394875206</v>
+        <v>0.00055427776517151268</v>
       </c>
       <c r="K12">
-        <v>0.0015186314909092342</v>
+        <v>0.00066559637746996551</v>
       </c>
       <c r="L12">
-        <v>0.001594174146135942</v>
+        <v>0.00070016236595029085</v>
       </c>
       <c r="M12">
-        <v>0.0016177558311154003</v>
+        <v>0.00071533295645487824</v>
       </c>
       <c r="N12">
-        <v>2.0725671868562124e-05</v>
+        <v>8.8381051002626628e-06</v>
       </c>
       <c r="O12">
-        <v>3.4477614664454284e-06</v>
+        <v>3.2529216484541024e-06</v>
       </c>
       <c r="P12">
-        <v>-2.3212406682500637e-05</v>
+        <v>-1.0936252240624855e-05</v>
       </c>
       <c r="Q12">
-        <v>7.2353014885073951e-06</v>
+        <v>2.8834708102124759e-06</v>
       </c>
       <c r="R12">
-        <v>-3.7146714563001814e-05</v>
+        <v>-1.8552351795101257e-05</v>
       </c>
       <c r="S12">
-        <v>-4.586849288417331e-05</v>
+        <v>-2.4202830423442321e-05</v>
       </c>
       <c r="T12">
-        <v>-5.4896398646304776e-06</v>
+        <v>-2.236052886520916e-06</v>
       </c>
       <c r="U12">
-        <v>-5.7895774924919584e-08</v>
+        <v>-2.3967346192380434e-07</v>
       </c>
       <c r="V12">
-        <v>-1.2157872755243855e-05</v>
+        <v>-8.988114897224455e-06</v>
       </c>
       <c r="W12">
-        <v>2.3463697084120206e-05</v>
+        <v>1.2692324832023408e-05</v>
       </c>
       <c r="X12">
-        <v>-0.003320588776061729</v>
+        <v>-0.0014689048567187229</v>
       </c>
       <c r="Y12">
-        <v>0.0012421952749848717</v>
+        <v>0.00058550601628740693</v>
       </c>
     </row>
     <row r="13">
@@ -6513,76 +6513,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.030602787668427247</v>
+        <v>0.022874529471946091</v>
       </c>
       <c r="C13">
-        <v>-9.6066022111804419e-07</v>
+        <v>-5.8330687499419406e-07</v>
       </c>
       <c r="D13">
-        <v>3.4782511213754523e-06</v>
+        <v>1.5008711439621603e-06</v>
       </c>
       <c r="E13">
-        <v>-3.8722402834084351e-08</v>
+        <v>-1.6599433517581187e-08</v>
       </c>
       <c r="F13">
-        <v>-2.6986659927696137e-06</v>
+        <v>-1.1531209037193306e-06</v>
       </c>
       <c r="G13">
-        <v>-4.3975775627392715e-06</v>
+        <v>-1.7211455778821662e-06</v>
       </c>
       <c r="H13">
-        <v>3.9189937611493101e-08</v>
+        <v>1.0845928954749191e-08</v>
       </c>
       <c r="I13">
-        <v>1.8453898443766697e-08</v>
+        <v>1.3306708774711502e-09</v>
       </c>
       <c r="J13">
-        <v>6.4621860430255533e-06</v>
+        <v>2.7449286249292225e-06</v>
       </c>
       <c r="K13">
-        <v>1.7546478430945737e-05</v>
+        <v>7.4164454368304886e-06</v>
       </c>
       <c r="L13">
-        <v>2.0856542594608544e-05</v>
+        <v>8.7874293070027796e-06</v>
       </c>
       <c r="M13">
-        <v>2.0725671868562124e-05</v>
+        <v>8.8381051002626628e-06</v>
       </c>
       <c r="N13">
-        <v>3.9000936845275753e-05</v>
+        <v>2.0050047062684238e-05</v>
       </c>
       <c r="O13">
-        <v>2.2005081848938601e-05</v>
+        <v>1.1467319450577922e-05</v>
       </c>
       <c r="P13">
-        <v>2.0426728853892344e-05</v>
+        <v>1.0665525592105547e-05</v>
       </c>
       <c r="Q13">
-        <v>2.2052189764989284e-05</v>
+        <v>1.1400605672398986e-05</v>
       </c>
       <c r="R13">
-        <v>1.9822895359430533e-05</v>
+        <v>1.0374560138716969e-05</v>
       </c>
       <c r="S13">
-        <v>1.9333743471964781e-05</v>
+        <v>1.0071096869765839e-05</v>
       </c>
       <c r="T13">
-        <v>-1.8165162225673399e-07</v>
+        <v>5.1364467425380882e-08</v>
       </c>
       <c r="U13">
-        <v>4.62647773835559e-10</v>
+        <v>2.6668127355950781e-08</v>
       </c>
       <c r="V13">
-        <v>-3.6898645367662476e-07</v>
+        <v>-4.1325835706299723e-07</v>
       </c>
       <c r="W13">
-        <v>9.9736428415731605e-07</v>
+        <v>4.014699990072e-07</v>
       </c>
       <c r="X13">
-        <v>-0.00012187564194992336</v>
+        <v>-5.6539326209574275e-05</v>
       </c>
       <c r="Y13">
-        <v>5.7780069542840608e-05</v>
+        <v>2.5469938952961809e-05</v>
       </c>
     </row>
     <row r="14">
@@ -6590,76 +6590,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.027814902467189182</v>
+        <v>0.023668422532654585</v>
       </c>
       <c r="C14">
-        <v>-9.0146236335787515e-07</v>
+        <v>-5.9153659494403362e-07</v>
       </c>
       <c r="D14">
-        <v>9.2328484205766048e-07</v>
+        <v>6.2949577764948125e-07</v>
       </c>
       <c r="E14">
-        <v>-9.9000472671791189e-09</v>
+        <v>-6.7970503252989376e-09</v>
       </c>
       <c r="F14">
-        <v>1.1657966600431001e-06</v>
+        <v>3.1617444695255206e-07</v>
       </c>
       <c r="G14">
-        <v>6.4182520887894778e-07</v>
+        <v>-3.3538541482072645e-08</v>
       </c>
       <c r="H14">
-        <v>-2.0587783921893348e-08</v>
+        <v>-7.8863308380046609e-09</v>
       </c>
       <c r="I14">
-        <v>-1.3791195539239086e-08</v>
+        <v>-5.4217143545375601e-09</v>
       </c>
       <c r="J14">
-        <v>1.608137257407316e-06</v>
+        <v>1.5205527580832647e-06</v>
       </c>
       <c r="K14">
-        <v>3.6378605974693558e-06</v>
+        <v>3.0157035244512283e-06</v>
       </c>
       <c r="L14">
-        <v>4.1721718910241178e-06</v>
+        <v>3.5077856709944612e-06</v>
       </c>
       <c r="M14">
-        <v>3.4477614664454284e-06</v>
+        <v>3.2529216484541024e-06</v>
       </c>
       <c r="N14">
-        <v>2.2005081848938601e-05</v>
+        <v>1.1467319450577922e-05</v>
       </c>
       <c r="O14">
-        <v>4.7442089558016077e-05</v>
+        <v>2.4121605495951048e-05</v>
       </c>
       <c r="P14">
-        <v>2.1160971494982666e-05</v>
+        <v>1.0924164319234877e-05</v>
       </c>
       <c r="Q14">
-        <v>2.1812175078289327e-05</v>
+        <v>1.1334882696038892e-05</v>
       </c>
       <c r="R14">
-        <v>2.1095818264103157e-05</v>
+        <v>1.084945650129914e-05</v>
       </c>
       <c r="S14">
-        <v>2.0972760510677107e-05</v>
+        <v>1.0734141503816105e-05</v>
       </c>
       <c r="T14">
-        <v>4.0750697548289772e-08</v>
+        <v>1.3025283331446349e-07</v>
       </c>
       <c r="U14">
-        <v>-1.70851273018203e-08</v>
+        <v>-5.2716883873425985e-08</v>
       </c>
       <c r="V14">
-        <v>1.2574247640244044e-07</v>
+        <v>6.0541068925221891e-08</v>
       </c>
       <c r="W14">
-        <v>-1.7175559610046124e-07</v>
+        <v>7.7016920278972321e-08</v>
       </c>
       <c r="X14">
-        <v>-4.4404549660104301e-05</v>
+        <v>-2.3191385662431578e-05</v>
       </c>
       <c r="Y14">
-        <v>1.3621616760275154e-05</v>
+        <v>9.7566046105163711e-06</v>
       </c>
     </row>
     <row r="15">
@@ -6667,76 +6667,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>-0.0083338038845150869</v>
+        <v>-0.0048969764469375433</v>
       </c>
       <c r="C15">
-        <v>6.6440271327904965e-08</v>
+        <v>6.1276383870881833e-08</v>
       </c>
       <c r="D15">
-        <v>-3.4447999737633082e-06</v>
+        <v>-1.6847509287975427e-06</v>
       </c>
       <c r="E15">
-        <v>3.8802443247592751e-08</v>
+        <v>1.8897972135137436e-08</v>
       </c>
       <c r="F15">
-        <v>4.3737019801844475e-06</v>
+        <v>2.2974523175395136e-06</v>
       </c>
       <c r="G15">
-        <v>4.4203215265220427e-06</v>
+        <v>2.3179724315835008e-06</v>
       </c>
       <c r="H15">
-        <v>-8.425802755565154e-08</v>
+        <v>-3.7810072888058567e-08</v>
       </c>
       <c r="I15">
-        <v>-4.0413331647797797e-08</v>
+        <v>-2.010986336759991e-08</v>
       </c>
       <c r="J15">
-        <v>-6.3237685478894463e-06</v>
+        <v>-2.4602292046622618e-06</v>
       </c>
       <c r="K15">
-        <v>-1.8730956616534432e-05</v>
+        <v>-8.5038717859722384e-06</v>
       </c>
       <c r="L15">
-        <v>-2.2680428637966826e-05</v>
+        <v>-1.0484730405781603e-05</v>
       </c>
       <c r="M15">
-        <v>-2.3212406682500637e-05</v>
+        <v>-1.0936252240624855e-05</v>
       </c>
       <c r="N15">
-        <v>2.0426728853892344e-05</v>
+        <v>1.0665525592105547e-05</v>
       </c>
       <c r="O15">
-        <v>2.1160971494982666e-05</v>
+        <v>1.0924164319234877e-05</v>
       </c>
       <c r="P15">
-        <v>4.0040210772682656e-05</v>
+        <v>2.0772728256596493e-05</v>
       </c>
       <c r="Q15">
-        <v>2.111071868217562e-05</v>
+        <v>1.098415706448276e-05</v>
       </c>
       <c r="R15">
-        <v>2.3340048255148463e-05</v>
+        <v>1.2142068628927472e-05</v>
       </c>
       <c r="S15">
-        <v>2.3718886616615546e-05</v>
+        <v>1.2423515307059621e-05</v>
       </c>
       <c r="T15">
-        <v>7.4772584416469751e-07</v>
+        <v>-1.0546193135909428e-08</v>
       </c>
       <c r="U15">
-        <v>-4.4816246675164398e-09</v>
+        <v>-4.489354974277207e-10</v>
       </c>
       <c r="V15">
-        <v>5.0150529757137585e-07</v>
+        <v>3.9596818227467573e-07</v>
       </c>
       <c r="W15">
-        <v>-1.2909790809517062e-06</v>
+        <v>-7.2102564324556662e-07</v>
       </c>
       <c r="X15">
-        <v>8.1997706909487742e-05</v>
+        <v>3.8540245118071877e-05</v>
       </c>
       <c r="Y15">
-        <v>-5.8904373322382824e-05</v>
+        <v>-2.9713623869275202e-05</v>
       </c>
     </row>
     <row r="16">
@@ -6744,76 +6744,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.015564202521356799</v>
+        <v>0.014519476654106456</v>
       </c>
       <c r="C16">
-        <v>-5.9190702730673294e-07</v>
+        <v>-3.9080372082962989e-07</v>
       </c>
       <c r="D16">
-        <v>1.5422586855312324e-06</v>
+        <v>6.4996117400315975e-07</v>
       </c>
       <c r="E16">
-        <v>-1.7077864676435316e-08</v>
+        <v>-7.118513568822003e-09</v>
       </c>
       <c r="F16">
-        <v>-4.3504871186556587e-07</v>
+        <v>-9.3083412858741814e-09</v>
       </c>
       <c r="G16">
-        <v>-3.5934935990956382e-06</v>
+        <v>-1.330157009369033e-06</v>
       </c>
       <c r="H16">
-        <v>-2.9749858540179763e-09</v>
+        <v>-7.5861303317833193e-09</v>
       </c>
       <c r="I16">
-        <v>3.4013435788667961e-08</v>
+        <v>9.1743366550895453e-09</v>
       </c>
       <c r="J16">
-        <v>2.6958564570493996e-06</v>
+        <v>1.159232439146969e-06</v>
       </c>
       <c r="K16">
-        <v>6.9666982957134516e-06</v>
+        <v>2.8040376653474367e-06</v>
       </c>
       <c r="L16">
-        <v>8.2704746000603579e-06</v>
+        <v>3.3239401602094616e-06</v>
       </c>
       <c r="M16">
-        <v>7.2353014885073951e-06</v>
+        <v>2.8834708102124759e-06</v>
       </c>
       <c r="N16">
-        <v>2.2052189764989284e-05</v>
+        <v>1.1400605672398986e-05</v>
       </c>
       <c r="O16">
-        <v>2.1812175078289327e-05</v>
+        <v>1.1334882696038892e-05</v>
       </c>
       <c r="P16">
-        <v>2.111071868217562e-05</v>
+        <v>1.098415706448276e-05</v>
       </c>
       <c r="Q16">
-        <v>3.3579137508229255e-05</v>
+        <v>1.6951521861526585e-05</v>
       </c>
       <c r="R16">
-        <v>2.0945115852694453e-05</v>
+        <v>1.091219010831858e-05</v>
       </c>
       <c r="S16">
-        <v>2.067306873691721e-05</v>
+        <v>1.0770948807376037e-05</v>
       </c>
       <c r="T16">
-        <v>-5.6698154929729048e-07</v>
+        <v>1.1055444961409331e-07</v>
       </c>
       <c r="U16">
-        <v>-4.0639494026583278e-08</v>
+        <v>-1.2195734979326113e-07</v>
       </c>
       <c r="V16">
-        <v>9.422068795317852e-07</v>
+        <v>6.8186842487580836e-07</v>
       </c>
       <c r="W16">
-        <v>1.4431967342332227e-06</v>
+        <v>9.2344366717895829e-07</v>
       </c>
       <c r="X16">
-        <v>-5.996415585611756e-05</v>
+        <v>-1.6506508620669098e-05</v>
       </c>
       <c r="Y16">
-        <v>2.4404400748169735e-05</v>
+        <v>1.0072949624571831e-05</v>
       </c>
     </row>
     <row r="17">
@@ -6821,76 +6821,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>0.0094366800060803457</v>
+        <v>0.0077534181918946362</v>
       </c>
       <c r="C17">
-        <v>-2.8522656107090189e-07</v>
+        <v>-1.422498135683048e-07</v>
       </c>
       <c r="D17">
-        <v>-5.944987610232904e-06</v>
+        <v>-2.9823135974582155e-06</v>
       </c>
       <c r="E17">
-        <v>6.667319453899624e-08</v>
+        <v>3.3364712290748938e-08</v>
       </c>
       <c r="F17">
-        <v>5.2130673001730663e-06</v>
+        <v>3.1103810922205245e-06</v>
       </c>
       <c r="G17">
-        <v>5.4572344863974676e-06</v>
+        <v>3.1106497498038197e-06</v>
       </c>
       <c r="H17">
-        <v>-9.2039865286875139e-08</v>
+        <v>-4.5723386324652696e-08</v>
       </c>
       <c r="I17">
-        <v>-8.4933442535895586e-09</v>
+        <v>-6.8766190139455755e-09</v>
       </c>
       <c r="J17">
-        <v>-8.9335729862000204e-06</v>
+        <v>-3.9142690101402254e-06</v>
       </c>
       <c r="K17">
-        <v>-2.9293063091893173e-05</v>
+        <v>-1.4226247799795768e-05</v>
       </c>
       <c r="L17">
-        <v>-3.5499897491956005e-05</v>
+        <v>-1.7420948205828125e-05</v>
       </c>
       <c r="M17">
-        <v>-3.7146714563001814e-05</v>
+        <v>-1.8552351795101257e-05</v>
       </c>
       <c r="N17">
-        <v>1.9822895359430533e-05</v>
+        <v>1.0374560138716969e-05</v>
       </c>
       <c r="O17">
-        <v>2.1095818264103157e-05</v>
+        <v>1.084945650129914e-05</v>
       </c>
       <c r="P17">
-        <v>2.3340048255148463e-05</v>
+        <v>1.2142068628927472e-05</v>
       </c>
       <c r="Q17">
-        <v>2.0945115852694453e-05</v>
+        <v>1.091219010831858e-05</v>
       </c>
       <c r="R17">
-        <v>4.124381389196289e-05</v>
+        <v>2.131181826112905e-05</v>
       </c>
       <c r="S17">
-        <v>2.5329564282225202e-05</v>
+        <v>1.3398387265432405e-05</v>
       </c>
       <c r="T17">
-        <v>2.9904974194047999e-07</v>
+        <v>-9.4865716912762452e-08</v>
       </c>
       <c r="U17">
-        <v>-6.2774722432900562e-09</v>
+        <v>-1.6808675362616801e-08</v>
       </c>
       <c r="V17">
-        <v>1.0988760737497767e-06</v>
+        <v>9.4007228602262187e-07</v>
       </c>
       <c r="W17">
-        <v>-1.9753137015592781e-06</v>
+        <v>-1.0738758910207293e-06</v>
       </c>
       <c r="X17">
-        <v>0.00015446027939079818</v>
+        <v>7.7907037649363172e-05</v>
       </c>
       <c r="Y17">
-        <v>-9.9709154978586215e-05</v>
+        <v>-5.1863180440202406e-05</v>
       </c>
     </row>
     <row r="18">
@@ -6898,76 +6898,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.0057139989213501616</v>
+        <v>-0.0039516675357244412</v>
       </c>
       <c r="C18">
-        <v>-5.6547022472950161e-08</v>
+        <v>3.831574188680449e-08</v>
       </c>
       <c r="D18">
-        <v>-7.4966643943244017e-06</v>
+        <v>-4.0738935503178311e-06</v>
       </c>
       <c r="E18">
-        <v>8.3976364964385809e-08</v>
+        <v>4.5498903101837152e-08</v>
       </c>
       <c r="F18">
-        <v>6.1174234925863808e-06</v>
+        <v>3.7063988518787839e-06</v>
       </c>
       <c r="G18">
-        <v>9.6576797139496394e-06</v>
+        <v>5.6190447616348639e-06</v>
       </c>
       <c r="H18">
-        <v>-1.0031366292135383e-07</v>
+        <v>-4.6432332062957618e-08</v>
       </c>
       <c r="I18">
-        <v>-3.2842988188935253e-08</v>
+        <v>-1.7199568806099296e-08</v>
       </c>
       <c r="J18">
-        <v>-1.1107858342998105e-05</v>
+        <v>-4.9740430826625885e-06</v>
       </c>
       <c r="K18">
-        <v>-3.6883821031825323e-05</v>
+        <v>-1.8938739548977797e-05</v>
       </c>
       <c r="L18">
-        <v>-4.3542500584354036e-05</v>
+        <v>-2.2579347144171473e-05</v>
       </c>
       <c r="M18">
-        <v>-4.586849288417331e-05</v>
+        <v>-2.4202830423442321e-05</v>
       </c>
       <c r="N18">
-        <v>1.9333743471964781e-05</v>
+        <v>1.0071096869765839e-05</v>
       </c>
       <c r="O18">
-        <v>2.0972760510677107e-05</v>
+        <v>1.0734141503816105e-05</v>
       </c>
       <c r="P18">
-        <v>2.3718886616615546e-05</v>
+        <v>1.2423515307059621e-05</v>
       </c>
       <c r="Q18">
-        <v>2.067306873691721e-05</v>
+        <v>1.0770948807376037e-05</v>
       </c>
       <c r="R18">
-        <v>2.5329564282225202e-05</v>
+        <v>1.3398387265432405e-05</v>
       </c>
       <c r="S18">
-        <v>0.00011695012677762435</v>
+        <v>6.0292996480164563e-05</v>
       </c>
       <c r="T18">
-        <v>6.928291246900277e-07</v>
+        <v>6.3942500874135346e-08</v>
       </c>
       <c r="U18">
-        <v>2.4909890577111255e-08</v>
+        <v>8.1448764664496548e-08</v>
       </c>
       <c r="V18">
-        <v>1.6810656848438285e-06</v>
+        <v>1.2386295702407575e-06</v>
       </c>
       <c r="W18">
-        <v>-2.2240213219971352e-06</v>
+        <v>-1.4835219700372946e-06</v>
       </c>
       <c r="X18">
-        <v>0.00019516430507977018</v>
+        <v>9.8258050731745892e-05</v>
       </c>
       <c r="Y18">
-        <v>-0.00012913625397574022</v>
+        <v>-7.1671545818464792e-05</v>
       </c>
     </row>
     <row r="19">
@@ -6975,76 +6975,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.093858536995847688</v>
+        <v>0.069043616531642746</v>
       </c>
       <c r="C19">
-        <v>1.3287275762302553e-06</v>
+        <v>-1.3980890365962598e-07</v>
       </c>
       <c r="D19">
-        <v>-1.66524894100824e-07</v>
+        <v>-1.4884043431229844e-07</v>
       </c>
       <c r="E19">
-        <v>3.3756688884194295e-09</v>
+        <v>1.7297438270260241e-09</v>
       </c>
       <c r="F19">
-        <v>3.2717994297094283e-06</v>
+        <v>4.0098069644085504e-07</v>
       </c>
       <c r="G19">
-        <v>4.4549656765141915e-06</v>
+        <v>1.3148158607457092e-06</v>
       </c>
       <c r="H19">
-        <v>-5.7006550310835056e-08</v>
+        <v>3.6740225890595579e-09</v>
       </c>
       <c r="I19">
-        <v>-4.6466897732681156e-08</v>
+        <v>-1.0865355455699018e-09</v>
       </c>
       <c r="J19">
-        <v>-6.4264315426858742e-07</v>
+        <v>-5.4990974310952464e-07</v>
       </c>
       <c r="K19">
-        <v>-4.9523513682471413e-06</v>
+        <v>-1.7434364261560208e-06</v>
       </c>
       <c r="L19">
-        <v>-5.4349870505749709e-06</v>
+        <v>-2.031040103899715e-06</v>
       </c>
       <c r="M19">
-        <v>-5.4896398646304776e-06</v>
+        <v>-2.236052886520916e-06</v>
       </c>
       <c r="N19">
-        <v>-1.8165162225673399e-07</v>
+        <v>5.1364467425380882e-08</v>
       </c>
       <c r="O19">
-        <v>4.0750697548289772e-08</v>
+        <v>1.3025283331446349e-07</v>
       </c>
       <c r="P19">
-        <v>7.4772584416469751e-07</v>
+        <v>-1.0546193135909428e-08</v>
       </c>
       <c r="Q19">
-        <v>-5.6698154929729048e-07</v>
+        <v>1.1055444961409331e-07</v>
       </c>
       <c r="R19">
-        <v>2.9904974194047999e-07</v>
+        <v>-9.4865716912762452e-08</v>
       </c>
       <c r="S19">
-        <v>6.928291246900277e-07</v>
+        <v>6.3942500874135346e-08</v>
       </c>
       <c r="T19">
-        <v>8.75792800197913e-05</v>
+        <v>1.4483927529275792e-05</v>
       </c>
       <c r="U19">
-        <v>-1.3317338008624296e-08</v>
+        <v>-2.2549808028429151e-08</v>
       </c>
       <c r="V19">
-        <v>-1.631342861863448e-07</v>
+        <v>6.2763225757431089e-08</v>
       </c>
       <c r="W19">
-        <v>-7.4219987079449914e-07</v>
+        <v>-3.2253755552994855e-07</v>
       </c>
       <c r="X19">
-        <v>3.8204341745559217e-06</v>
+        <v>6.641151462444159e-06</v>
       </c>
       <c r="Y19">
-        <v>-2.0471867895267251e-05</v>
+        <v>-6.6510148861428491e-06</v>
       </c>
     </row>
     <row r="20">
@@ -7052,76 +7052,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>0.00053002171359693294</v>
+        <v>0.0070264445659336721</v>
       </c>
       <c r="C20">
-        <v>5.2377921735377083e-09</v>
+        <v>1.7995809731197625e-08</v>
       </c>
       <c r="D20">
-        <v>-1.8663216877748614e-08</v>
+        <v>-5.9045169121804041e-08</v>
       </c>
       <c r="E20">
-        <v>1.8657707516982281e-10</v>
+        <v>5.8630657187560685e-10</v>
       </c>
       <c r="F20">
-        <v>6.7305737183686909e-08</v>
+        <v>2.4936636386985689e-07</v>
       </c>
       <c r="G20">
-        <v>7.3647517009285963e-08</v>
+        <v>2.9566211107643744e-07</v>
       </c>
       <c r="H20">
-        <v>-9.1750634036044571e-10</v>
+        <v>-3.2473049249459306e-09</v>
       </c>
       <c r="I20">
-        <v>-4.4966324398754097e-12</v>
+        <v>-8.8413202586812228e-10</v>
       </c>
       <c r="J20">
-        <v>-1.0293055073266041e-09</v>
+        <v>-8.7998620831458841e-09</v>
       </c>
       <c r="K20">
-        <v>-7.6420759748410273e-08</v>
+        <v>-2.584254374300843e-07</v>
       </c>
       <c r="L20">
-        <v>-6.8180339477921365e-08</v>
+        <v>-2.6388657331497087e-07</v>
       </c>
       <c r="M20">
-        <v>-5.7895774924919584e-08</v>
+        <v>-2.3967346192380434e-07</v>
       </c>
       <c r="N20">
-        <v>4.62647773835559e-10</v>
+        <v>2.6668127355950781e-08</v>
       </c>
       <c r="O20">
-        <v>-1.70851273018203e-08</v>
+        <v>-5.2716883873425985e-08</v>
       </c>
       <c r="P20">
-        <v>-4.4816246675164398e-09</v>
+        <v>-4.489354974277207e-10</v>
       </c>
       <c r="Q20">
-        <v>-4.0639494026583278e-08</v>
+        <v>-1.2195734979326113e-07</v>
       </c>
       <c r="R20">
-        <v>-6.2774722432900562e-09</v>
+        <v>-1.6808675362616801e-08</v>
       </c>
       <c r="S20">
-        <v>2.4909890577111255e-08</v>
+        <v>8.1448764664496548e-08</v>
       </c>
       <c r="T20">
-        <v>-1.3317338008624296e-08</v>
+        <v>-2.2549808028429151e-08</v>
       </c>
       <c r="U20">
-        <v>1.6898658928917583e-08</v>
+        <v>6.3872727161321803e-07</v>
       </c>
       <c r="V20">
-        <v>-2.1822956553342149e-07</v>
+        <v>-2.3138535826157306e-06</v>
       </c>
       <c r="W20">
-        <v>-2.7982508861597894e-07</v>
+        <v>-2.4014350255821309e-06</v>
       </c>
       <c r="X20">
-        <v>-1.3177041239297825e-06</v>
+        <v>-6.2576360770925157e-05</v>
       </c>
       <c r="Y20">
-        <v>-3.4024540851450842e-07</v>
+        <v>-1.1909410549241248e-06</v>
       </c>
     </row>
     <row r="21">
@@ -7129,76 +7129,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.058894550947306112</v>
+        <v>-0.07499136753439678</v>
       </c>
       <c r="C21">
-        <v>-5.5290649816510161e-08</v>
+        <v>3.4055850287699676e-09</v>
       </c>
       <c r="D21">
-        <v>-1.9811620688097642e-06</v>
+        <v>-1.452944066437684e-06</v>
       </c>
       <c r="E21">
-        <v>2.225534337520319e-08</v>
+        <v>1.6429437300475129e-08</v>
       </c>
       <c r="F21">
-        <v>1.6444367371135147e-06</v>
+        <v>1.0631059525672129e-06</v>
       </c>
       <c r="G21">
-        <v>3.4080551761399092e-06</v>
+        <v>2.12955715060847e-06</v>
       </c>
       <c r="H21">
-        <v>-3.3529024612047614e-08</v>
+        <v>-1.7905531805868269e-08</v>
       </c>
       <c r="I21">
-        <v>-3.4329337945069541e-08</v>
+        <v>-2.1145732159066031e-08</v>
       </c>
       <c r="J21">
-        <v>-2.9234090131560762e-06</v>
+        <v>-2.1678559648716723e-06</v>
       </c>
       <c r="K21">
-        <v>-8.9338675228979132e-06</v>
+        <v>-6.5833724288756769e-06</v>
       </c>
       <c r="L21">
-        <v>-1.1547170069487894e-05</v>
+        <v>-8.4177487108553692e-06</v>
       </c>
       <c r="M21">
-        <v>-1.2157872755243855e-05</v>
+        <v>-8.988114897224455e-06</v>
       </c>
       <c r="N21">
-        <v>-3.6898645367662476e-07</v>
+        <v>-4.1325835706299723e-07</v>
       </c>
       <c r="O21">
-        <v>1.2574247640244044e-07</v>
+        <v>6.0541068925221891e-08</v>
       </c>
       <c r="P21">
-        <v>5.0150529757137585e-07</v>
+        <v>3.9596818227467573e-07</v>
       </c>
       <c r="Q21">
-        <v>9.422068795317852e-07</v>
+        <v>6.8186842487580836e-07</v>
       </c>
       <c r="R21">
-        <v>1.0988760737497767e-06</v>
+        <v>9.4007228602262187e-07</v>
       </c>
       <c r="S21">
-        <v>1.6810656848438285e-06</v>
+        <v>1.2386295702407575e-06</v>
       </c>
       <c r="T21">
-        <v>-1.631342861863448e-07</v>
+        <v>6.2763225757431089e-08</v>
       </c>
       <c r="U21">
-        <v>-2.1822956553342149e-07</v>
+        <v>-2.3138535826157306e-06</v>
       </c>
       <c r="V21">
-        <v>4.8215607723194493e-05</v>
+        <v>3.5185495089717083e-05</v>
       </c>
       <c r="W21">
-        <v>6.185375265563252e-06</v>
+        <v>9.7125149795642154e-06</v>
       </c>
       <c r="X21">
-        <v>7.8289439312666603e-05</v>
+        <v>0.00027308343086591443</v>
       </c>
       <c r="Y21">
-        <v>-3.2980499166593536e-05</v>
+        <v>-2.4332457282517719e-05</v>
       </c>
     </row>
     <row r="22">
@@ -7206,76 +7206,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>0.040163062851492459</v>
+        <v>0.02559804532032502</v>
       </c>
       <c r="C22">
-        <v>4.3607407506954471e-07</v>
+        <v>2.873535427769429e-07</v>
       </c>
       <c r="D22">
-        <v>3.9872227176512081e-06</v>
+        <v>2.1899198775295396e-06</v>
       </c>
       <c r="E22">
-        <v>-4.4765961341869402e-08</v>
+        <v>-2.4375005538066314e-08</v>
       </c>
       <c r="F22">
-        <v>-4.2140562749643492e-06</v>
+        <v>-2.8934685905956172e-06</v>
       </c>
       <c r="G22">
-        <v>-6.7529208042759716e-06</v>
+        <v>-4.1967795708656656e-06</v>
       </c>
       <c r="H22">
-        <v>7.6257218101995673e-08</v>
+        <v>4.2667883946027046e-08</v>
       </c>
       <c r="I22">
-        <v>5.2404092373262274e-08</v>
+        <v>2.7448085571362176e-08</v>
       </c>
       <c r="J22">
-        <v>6.4156100948280014e-06</v>
+        <v>3.010978595897957e-06</v>
       </c>
       <c r="K22">
-        <v>1.9550793963314952e-05</v>
+        <v>1.0329262700234433e-05</v>
       </c>
       <c r="L22">
-        <v>2.3517053811397191e-05</v>
+        <v>1.2496710816861038e-05</v>
       </c>
       <c r="M22">
-        <v>2.3463697084120206e-05</v>
+        <v>1.2692324832023408e-05</v>
       </c>
       <c r="N22">
-        <v>9.9736428415731605e-07</v>
+        <v>4.014699990072e-07</v>
       </c>
       <c r="O22">
-        <v>-1.7175559610046124e-07</v>
+        <v>7.7016920278972321e-08</v>
       </c>
       <c r="P22">
-        <v>-1.2909790809517062e-06</v>
+        <v>-7.2102564324556662e-07</v>
       </c>
       <c r="Q22">
-        <v>1.4431967342332227e-06</v>
+        <v>9.2344366717895829e-07</v>
       </c>
       <c r="R22">
-        <v>-1.9753137015592781e-06</v>
+        <v>-1.0738758910207293e-06</v>
       </c>
       <c r="S22">
-        <v>-2.2240213219971352e-06</v>
+        <v>-1.4835219700372946e-06</v>
       </c>
       <c r="T22">
-        <v>-7.4219987079449914e-07</v>
+        <v>-3.2253755552994855e-07</v>
       </c>
       <c r="U22">
-        <v>-2.7982508861597894e-07</v>
+        <v>-2.4014350255821309e-06</v>
       </c>
       <c r="V22">
-        <v>6.185375265563252e-06</v>
+        <v>9.7125149795642154e-06</v>
       </c>
       <c r="W22">
-        <v>5.0535605609105836e-05</v>
+        <v>3.59430484649174e-05</v>
       </c>
       <c r="X22">
-        <v>-9.0424781354253475e-05</v>
+        <v>0.00017561015272217327</v>
       </c>
       <c r="Y22">
-        <v>7.0202800001117492e-05</v>
+        <v>4.0335248818838959e-05</v>
       </c>
     </row>
     <row r="23">
@@ -7283,76 +7283,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.49798392718443835</v>
+        <v>-0.25715976351179865</v>
       </c>
       <c r="C23">
-        <v>-1.5675557809395382e-05</v>
+        <v>-1.0213282233439339e-05</v>
       </c>
       <c r="D23">
-        <v>-0.00039376374772302232</v>
+        <v>-0.00017668152883912151</v>
       </c>
       <c r="E23">
-        <v>4.3864294117804359e-06</v>
+        <v>1.9668894929256238e-06</v>
       </c>
       <c r="F23">
-        <v>0.00019959015422445545</v>
+        <v>8.0744572336243663e-05</v>
       </c>
       <c r="G23">
-        <v>0.00045523870911117316</v>
+        <v>0.00018616673067599869</v>
       </c>
       <c r="H23">
-        <v>-2.950294593108907e-06</v>
+        <v>-7.0436012023153355e-07</v>
       </c>
       <c r="I23">
-        <v>-1.802194501066031e-06</v>
+        <v>-5.1289073447274079e-07</v>
       </c>
       <c r="J23">
-        <v>-0.0017387958361043373</v>
+        <v>-0.00074523114350746617</v>
       </c>
       <c r="K23">
-        <v>-0.0029054995981686949</v>
+        <v>-0.0012597000370176302</v>
       </c>
       <c r="L23">
-        <v>-0.0032673999284424538</v>
+        <v>-0.0014246005271922877</v>
       </c>
       <c r="M23">
-        <v>-0.003320588776061729</v>
+        <v>-0.0014689048567187229</v>
       </c>
       <c r="N23">
-        <v>-0.00012187564194992336</v>
+        <v>-5.6539326209574275e-05</v>
       </c>
       <c r="O23">
-        <v>-4.4404549660104301e-05</v>
+        <v>-2.3191385662431578e-05</v>
       </c>
       <c r="P23">
-        <v>8.1997706909487742e-05</v>
+        <v>3.8540245118071877e-05</v>
       </c>
       <c r="Q23">
-        <v>-5.996415585611756e-05</v>
+        <v>-1.6506508620669098e-05</v>
       </c>
       <c r="R23">
-        <v>0.00015446027939079818</v>
+        <v>7.7907037649363172e-05</v>
       </c>
       <c r="S23">
-        <v>0.00019516430507977018</v>
+        <v>9.8258050731745892e-05</v>
       </c>
       <c r="T23">
-        <v>3.8204341745559217e-06</v>
+        <v>6.641151462444159e-06</v>
       </c>
       <c r="U23">
-        <v>-1.3177041239297825e-06</v>
+        <v>-6.2576360770925157e-05</v>
       </c>
       <c r="V23">
-        <v>7.8289439312666603e-05</v>
+        <v>0.00027308343086591443</v>
       </c>
       <c r="W23">
-        <v>-9.0424781354253475e-05</v>
+        <v>0.00017561015272217327</v>
       </c>
       <c r="X23">
-        <v>0.012640854428264339</v>
+        <v>0.011856810853525031</v>
       </c>
       <c r="Y23">
-        <v>-0.0060301699031437154</v>
+        <v>-0.0027485701253922314</v>
       </c>
     </row>
     <row r="24">
@@ -7360,76 +7360,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-0.19965046205802742</v>
+        <v>-0.17798602943342903</v>
       </c>
       <c r="C24">
-        <v>6.6927244685118126e-06</v>
+        <v>3.305903920989959e-06</v>
       </c>
       <c r="D24">
-        <v>0.0002077004979772021</v>
+        <v>9.8922400228267234e-05</v>
       </c>
       <c r="E24">
-        <v>-2.3324970550775778e-06</v>
+        <v>-1.1072361420490673e-06</v>
       </c>
       <c r="F24">
-        <v>-0.00022037206003641167</v>
+        <v>-0.00011561373723827647</v>
       </c>
       <c r="G24">
-        <v>-0.00035111507104032297</v>
+        <v>-0.00017212153293463017</v>
       </c>
       <c r="H24">
-        <v>3.8565178576067315e-06</v>
+        <v>1.6868593373019716e-06</v>
       </c>
       <c r="I24">
-        <v>2.7027134891823049e-06</v>
+        <v>1.192513436268208e-06</v>
       </c>
       <c r="J24">
-        <v>0.00033458979698305317</v>
+        <v>0.000141595968505922</v>
       </c>
       <c r="K24">
-        <v>0.0010135774353958857</v>
+        <v>0.00046583080152770096</v>
       </c>
       <c r="L24">
-        <v>0.0012202160104896633</v>
+        <v>0.00056448322647335619</v>
       </c>
       <c r="M24">
-        <v>0.0012421952749848717</v>
+        <v>0.00058550601628740693</v>
       </c>
       <c r="N24">
-        <v>5.7780069542840608e-05</v>
+        <v>2.5469938952961809e-05</v>
       </c>
       <c r="O24">
-        <v>1.3621616760275154e-05</v>
+        <v>9.7566046105163711e-06</v>
       </c>
       <c r="P24">
-        <v>-5.8904373322382824e-05</v>
+        <v>-2.9713623869275202e-05</v>
       </c>
       <c r="Q24">
-        <v>2.4404400748169735e-05</v>
+        <v>1.0072949624571831e-05</v>
       </c>
       <c r="R24">
-        <v>-9.9709154978586215e-05</v>
+        <v>-5.1863180440202406e-05</v>
       </c>
       <c r="S24">
-        <v>-0.00012913625397574022</v>
+        <v>-7.1671545818464792e-05</v>
       </c>
       <c r="T24">
-        <v>-2.0471867895267251e-05</v>
+        <v>-6.6510148861428491e-06</v>
       </c>
       <c r="U24">
-        <v>-3.4024540851450842e-07</v>
+        <v>-1.1909410549241248e-06</v>
       </c>
       <c r="V24">
-        <v>-3.2980499166593536e-05</v>
+        <v>-2.4332457282517719e-05</v>
       </c>
       <c r="W24">
-        <v>7.0202800001117492e-05</v>
+        <v>4.0335248818838959e-05</v>
       </c>
       <c r="X24">
-        <v>-0.0060301699031437154</v>
+        <v>-0.0027485701253922314</v>
       </c>
       <c r="Y24">
-        <v>0.0034850457589071437</v>
+        <v>0.0017127046824877848</v>
       </c>
     </row>
   </sheetData>

--- a/input/ES/reg_wages.xlsx
+++ b/input/ES/reg_wages.xlsx
@@ -384,73 +384,73 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>0.025696420185059358</v>
+        <v>0.025729023556672</v>
       </c>
       <c r="C2">
-        <v>3.2975039681769835e-06</v>
+        <v>3.2995982364234852e-06</v>
       </c>
       <c r="D2">
-        <v>-3.6529812395758479e-08</v>
+        <v>-3.6559464471196361e-08</v>
       </c>
       <c r="E2">
-        <v>3.8134397798468078e-06</v>
+        <v>3.8277589222418845e-06</v>
       </c>
       <c r="F2">
-        <v>1.1283716607503379e-07</v>
+        <v>1.7609498400654027e-07</v>
       </c>
       <c r="G2">
-        <v>-8.024408023972643e-08</v>
+        <v>-8.0653965597875513e-08</v>
       </c>
       <c r="H2">
-        <v>-6.8250074294380194e-09</v>
+        <v>-7.8762962788455679e-09</v>
       </c>
       <c r="I2">
-        <v>3.5764024527174491e-07</v>
+        <v>3.2989559988356562e-07</v>
       </c>
       <c r="J2">
-        <v>9.0310592838376997e-07</v>
+        <v>8.5930459096122898e-07</v>
       </c>
       <c r="K2">
-        <v>1.0197007572277122e-06</v>
+        <v>9.6407141763929916e-07</v>
       </c>
       <c r="L2">
-        <v>1.752819666886691e-06</v>
+        <v>1.7024774339856528e-06</v>
       </c>
       <c r="M2">
-        <v>1.3864298727483544e-07</v>
+        <v>1.241566710718255e-07</v>
       </c>
       <c r="N2">
-        <v>3.2017440313383282e-07</v>
+        <v>3.1769465646999755e-07</v>
       </c>
       <c r="O2">
-        <v>1.142212658762969e-07</v>
+        <v>1.1628935727995375e-07</v>
       </c>
       <c r="P2">
-        <v>3.341249343141725e-07</v>
+        <v>3.2817034454393521e-07</v>
       </c>
       <c r="Q2">
-        <v>1.0958239262944224e-08</v>
+        <v>1.0915884705018853e-08</v>
       </c>
       <c r="R2">
-        <v>-3.8139965223970614e-08</v>
+        <v>-2.6817344936607236e-08</v>
       </c>
       <c r="S2">
-        <v>-3.7161572841632485e-08</v>
+        <v>-5.364130532496442e-08</v>
       </c>
       <c r="T2">
-        <v>8.9567784602453331e-08</v>
+        <v>8.6372161145701118e-08</v>
       </c>
       <c r="U2">
-        <v>-4.3050807129335377e-07</v>
+        <v>-4.2290467950104068e-07</v>
       </c>
       <c r="V2">
-        <v>-4.3886414477833709e-07</v>
+        <v>-4.27002655545462e-07</v>
       </c>
       <c r="W2">
-        <v>-8.1948005135246106e-05</v>
+        <v>-8.1590817495457311e-05</v>
       </c>
       <c r="X2">
-        <v>4.0370232315436746e-06</v>
+        <v>3.9901979423824158e-06</v>
       </c>
     </row>
     <row r="3">
@@ -458,73 +458,73 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>-8.8913982016396769e-05</v>
+        <v>-8.8812115573679224e-05</v>
       </c>
       <c r="C3">
-        <v>-3.6529812395758479e-08</v>
+        <v>-3.6559464471196361e-08</v>
       </c>
       <c r="D3">
-        <v>4.1973120484063419e-10</v>
+        <v>4.2010750604200305e-10</v>
       </c>
       <c r="E3">
-        <v>1.3039625982074321e-08</v>
+        <v>1.2788975340658385e-08</v>
       </c>
       <c r="F3">
-        <v>5.5741750235237881e-08</v>
+        <v>5.4922323366422722e-08</v>
       </c>
       <c r="G3">
-        <v>-3.8173297851703347e-10</v>
+        <v>-3.7495942631153517e-10</v>
       </c>
       <c r="H3">
-        <v>-1.2333690609531079e-09</v>
+        <v>-1.2189136991434899e-09</v>
       </c>
       <c r="I3">
-        <v>-4.0520286944204514e-09</v>
+        <v>-3.7319349364623934e-09</v>
       </c>
       <c r="J3">
-        <v>-9.6805696241493437e-09</v>
+        <v>-9.1784828666292821e-09</v>
       </c>
       <c r="K3">
-        <v>-9.0386324349088642e-09</v>
+        <v>-8.4040053533193612e-09</v>
       </c>
       <c r="L3">
-        <v>-1.4122102515186193e-08</v>
+        <v>-1.3558838176621225e-08</v>
       </c>
       <c r="M3">
-        <v>-1.7582652920199261e-09</v>
+        <v>-1.5971615157790988e-09</v>
       </c>
       <c r="N3">
-        <v>-3.6751477929240483e-09</v>
+        <v>-3.6474948461027171e-09</v>
       </c>
       <c r="O3">
-        <v>-1.5255190061157289e-09</v>
+        <v>-1.5487966269317116e-09</v>
       </c>
       <c r="P3">
-        <v>-3.6367402927319189e-09</v>
+        <v>-3.5624493890489849e-09</v>
       </c>
       <c r="Q3">
-        <v>5.4656640424326504e-11</v>
+        <v>4.2898625971502261e-11</v>
       </c>
       <c r="R3">
-        <v>7.5094641308874071e-10</v>
+        <v>6.2009569886426286e-10</v>
       </c>
       <c r="S3">
-        <v>9.9371006257775301e-10</v>
+        <v>1.1804216816992043e-09</v>
       </c>
       <c r="T3">
-        <v>-1.5064205468023872e-09</v>
+        <v>-1.4697388526011166e-09</v>
       </c>
       <c r="U3">
-        <v>6.1127464348943115e-09</v>
+        <v>6.0501682233354254e-09</v>
       </c>
       <c r="V3">
-        <v>6.2173691225822712e-09</v>
+        <v>6.0875926006412541e-09</v>
       </c>
       <c r="W3">
-        <v>9.2675456231938234e-07</v>
+        <v>9.2284000205573004e-07</v>
       </c>
       <c r="X3">
-        <v>-4.4930703899308752e-08</v>
+        <v>-4.4424433027561278e-08</v>
       </c>
     </row>
     <row r="4">
@@ -532,73 +532,73 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>-0.11343046949276511</v>
+        <v>-0.10965260631032274</v>
       </c>
       <c r="C4">
-        <v>3.8134397798468078e-06</v>
+        <v>3.8277589222418845e-06</v>
       </c>
       <c r="D4">
-        <v>1.3039625982074321e-08</v>
+        <v>1.2788975340658385e-08</v>
       </c>
       <c r="E4">
-        <v>0.00070919912071874716</v>
+        <v>0.000709459601611502</v>
       </c>
       <c r="F4">
-        <v>0.00023356271206436403</v>
+        <v>0.00023312844987124907</v>
       </c>
       <c r="G4">
-        <v>-1.4948598237245384e-05</v>
+        <v>-1.4957840598252015e-05</v>
       </c>
       <c r="H4">
-        <v>-5.0013452777215388e-06</v>
+        <v>-4.9935222034041668e-06</v>
       </c>
       <c r="I4">
-        <v>8.4080989935792137e-07</v>
+        <v>9.0018252344327447e-07</v>
       </c>
       <c r="J4">
-        <v>-2.7413066161234023e-06</v>
+        <v>-2.6845742726977543e-06</v>
       </c>
       <c r="K4">
-        <v>-3.5284807172009454e-06</v>
+        <v>-3.4482773625145712e-06</v>
       </c>
       <c r="L4">
-        <v>1.045490110851464e-08</v>
+        <v>8.1439838235357847e-10</v>
       </c>
       <c r="M4">
-        <v>2.3005580802923954e-06</v>
+        <v>2.2251701420626057e-06</v>
       </c>
       <c r="N4">
-        <v>2.3265125389912814e-06</v>
+        <v>2.3501550562870658e-06</v>
       </c>
       <c r="O4">
-        <v>1.278156403751324e-06</v>
+        <v>1.1170187068807747e-06</v>
       </c>
       <c r="P4">
-        <v>7.0587358472521583e-07</v>
+        <v>7.1113453533008501e-07</v>
       </c>
       <c r="Q4">
-        <v>-7.6302690183408902e-07</v>
+        <v>-9.4072034336560488e-07</v>
       </c>
       <c r="R4">
-        <v>1.0067700657887708e-06</v>
+        <v>9.2157139453280425e-07</v>
       </c>
       <c r="S4">
-        <v>-2.0678765079626196e-06</v>
+        <v>-2.1106656553475872e-06</v>
       </c>
       <c r="T4">
-        <v>3.0613904650882423e-07</v>
+        <v>2.9426931527776577e-07</v>
       </c>
       <c r="U4">
-        <v>6.5105715053470193e-07</v>
+        <v>6.3895141129178482e-07</v>
       </c>
       <c r="V4">
-        <v>-1.2759035791928479e-06</v>
+        <v>-1.2754998993734713e-06</v>
       </c>
       <c r="W4">
-        <v>-0.00023009096026126906</v>
+        <v>-0.00022902708987753193</v>
       </c>
       <c r="X4">
-        <v>-1.1341283837345014e-05</v>
+        <v>-1.1074392183280852e-05</v>
       </c>
     </row>
     <row r="5">
@@ -606,73 +606,73 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>0.046824045938554777</v>
+        <v>0.048874151579941225</v>
       </c>
       <c r="C5">
-        <v>1.1283716607503379e-07</v>
+        <v>1.7609498400654027e-07</v>
       </c>
       <c r="D5">
-        <v>5.5741750235237881e-08</v>
+        <v>5.4922323366422722e-08</v>
       </c>
       <c r="E5">
-        <v>0.00023356271206436403</v>
+        <v>0.00023312844987124907</v>
       </c>
       <c r="F5">
-        <v>0.00073661597848024261</v>
+        <v>0.00073648391261978401</v>
       </c>
       <c r="G5">
-        <v>-5.0643292157262754e-06</v>
+        <v>-5.0545789331978326e-06</v>
       </c>
       <c r="H5">
-        <v>-1.5061695869096753e-05</v>
+        <v>-1.5062311788179668e-05</v>
       </c>
       <c r="I5">
-        <v>-2.5688894739788384e-06</v>
+        <v>-3.0390021186726046e-06</v>
       </c>
       <c r="J5">
-        <v>-1.1196877800254609e-05</v>
+        <v>-1.1609769801558883e-05</v>
       </c>
       <c r="K5">
-        <v>-1.2843871475047249e-05</v>
+        <v>-1.3228556812213985e-05</v>
       </c>
       <c r="L5">
-        <v>-6.7142440201013043e-06</v>
+        <v>-7.1621684364391638e-06</v>
       </c>
       <c r="M5">
-        <v>1.7232189954144349e-06</v>
+        <v>1.8559847380038938e-06</v>
       </c>
       <c r="N5">
-        <v>-1.686686436667657e-06</v>
+        <v>-1.6167694720781554e-06</v>
       </c>
       <c r="O5">
-        <v>-6.6342444036298734e-06</v>
+        <v>-6.480270206164239e-06</v>
       </c>
       <c r="P5">
-        <v>-4.2414349194628831e-06</v>
+        <v>-4.1291271692011328e-06</v>
       </c>
       <c r="Q5">
-        <v>-1.1369617532126823e-05</v>
+        <v>-1.1489513463520052e-05</v>
       </c>
       <c r="R5">
-        <v>-5.1746972412528082e-06</v>
+        <v>-5.1627345155512233e-06</v>
       </c>
       <c r="S5">
-        <v>1.3786576642619549e-06</v>
+        <v>1.346492301551596e-06</v>
       </c>
       <c r="T5">
-        <v>4.0984884995767465e-07</v>
+        <v>4.1709998447961879e-07</v>
       </c>
       <c r="U5">
-        <v>2.3364861998721039e-06</v>
+        <v>2.372166225105908e-06</v>
       </c>
       <c r="V5">
-        <v>1.1289433398846271e-06</v>
+        <v>1.1007433048304987e-06</v>
       </c>
       <c r="W5">
-        <v>-0.0001524006388416583</v>
+        <v>-0.00015390420348669105</v>
       </c>
       <c r="X5">
-        <v>-1.381490843236969e-05</v>
+        <v>-1.3652671718948899e-05</v>
       </c>
     </row>
     <row r="6">
@@ -680,73 +680,73 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>-0.0059623937203997068</v>
+        <v>-0.0060525907748720182</v>
       </c>
       <c r="C6">
-        <v>-8.024408023972643e-08</v>
+        <v>-8.0653965597875513e-08</v>
       </c>
       <c r="D6">
-        <v>-3.8173297851703347e-10</v>
+        <v>-3.7495942631153517e-10</v>
       </c>
       <c r="E6">
-        <v>-1.4948598237245384e-05</v>
+        <v>-1.4957840598252015e-05</v>
       </c>
       <c r="F6">
-        <v>-5.0643292157262754e-06</v>
+        <v>-5.0545789331978326e-06</v>
       </c>
       <c r="G6">
-        <v>3.3347564511095149e-07</v>
+        <v>3.337341479610004e-07</v>
       </c>
       <c r="H6">
-        <v>1.151587337617194e-07</v>
+        <v>1.149621099661209e-07</v>
       </c>
       <c r="I6">
-        <v>-2.4255309777454766e-08</v>
+        <v>-2.5456990589984611e-08</v>
       </c>
       <c r="J6">
-        <v>4.9636289838053165e-08</v>
+        <v>4.9343901793638584e-08</v>
       </c>
       <c r="K6">
-        <v>1.1711422476994188e-07</v>
+        <v>1.1612214653160678e-07</v>
       </c>
       <c r="L6">
-        <v>6.5081523902758838e-08</v>
+        <v>6.5861668680520826e-08</v>
       </c>
       <c r="M6">
-        <v>-1.9961831057816129e-08</v>
+        <v>-1.807945721190512e-08</v>
       </c>
       <c r="N6">
-        <v>-3.5275887801187731e-08</v>
+        <v>-3.5997748764080934e-08</v>
       </c>
       <c r="O6">
-        <v>-1.671182211494701e-08</v>
+        <v>-1.2762229273894052e-08</v>
       </c>
       <c r="P6">
-        <v>-2.8219795948845958e-08</v>
+        <v>-2.8336005794566414e-08</v>
       </c>
       <c r="Q6">
-        <v>2.1816823366073077e-08</v>
+        <v>2.6111115388487911e-08</v>
       </c>
       <c r="R6">
-        <v>-2.9309071900597909e-08</v>
+        <v>-2.7737055571011313e-08</v>
       </c>
       <c r="S6">
-        <v>3.1503821667351492e-08</v>
+        <v>3.3502323851939582e-08</v>
       </c>
       <c r="T6">
-        <v>2.2128527109311206e-09</v>
+        <v>2.5086487795685132e-09</v>
       </c>
       <c r="U6">
-        <v>-2.994253271236064e-08</v>
+        <v>-3.0044420403808428e-08</v>
       </c>
       <c r="V6">
-        <v>1.5776979302878209e-08</v>
+        <v>1.5728952573711131e-08</v>
       </c>
       <c r="W6">
-        <v>3.9178240106067675e-06</v>
+        <v>3.8920617314655697e-06</v>
       </c>
       <c r="X6">
-        <v>1.5280981299700067e-07</v>
+        <v>1.4711621008646803e-07</v>
       </c>
     </row>
     <row r="7">
@@ -754,73 +754,73 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>-0.012919196063505355</v>
+        <v>-0.012998994915556358</v>
       </c>
       <c r="C7">
-        <v>-6.8250074294380194e-09</v>
+        <v>-7.8762962788455679e-09</v>
       </c>
       <c r="D7">
-        <v>-1.2333690609531079e-09</v>
+        <v>-1.2189136991434899e-09</v>
       </c>
       <c r="E7">
-        <v>-5.0013452777215388e-06</v>
+        <v>-4.9935222034041668e-06</v>
       </c>
       <c r="F7">
-        <v>-1.5061695869096753e-05</v>
+        <v>-1.5062311788179668e-05</v>
       </c>
       <c r="G7">
-        <v>1.151587337617194e-07</v>
+        <v>1.149621099661209e-07</v>
       </c>
       <c r="H7">
-        <v>3.2689343983341527e-07</v>
+        <v>3.2697709572269071e-07</v>
       </c>
       <c r="I7">
-        <v>4.2490607035674828e-08</v>
+        <v>5.1935838930347099e-08</v>
       </c>
       <c r="J7">
-        <v>2.2308907829895926e-07</v>
+        <v>2.3175682159255382e-07</v>
       </c>
       <c r="K7">
-        <v>3.3631007008296663e-07</v>
+        <v>3.4434686199032316e-07</v>
       </c>
       <c r="L7">
-        <v>2.4995037235956296e-07</v>
+        <v>2.5899882456414782e-07</v>
       </c>
       <c r="M7">
-        <v>-5.4543774580176689e-09</v>
+        <v>-7.904841062613128e-09</v>
       </c>
       <c r="N7">
-        <v>7.7145377521158658e-08</v>
+        <v>7.5081583969181696e-08</v>
       </c>
       <c r="O7">
-        <v>1.0811413766204395e-07</v>
+        <v>1.0539244222855904e-07</v>
       </c>
       <c r="P7">
-        <v>7.5041780804141119e-08</v>
+        <v>7.2851890920698179e-08</v>
       </c>
       <c r="Q7">
-        <v>1.9414465994645628e-07</v>
+        <v>1.9769427107113253e-07</v>
       </c>
       <c r="R7">
-        <v>8.1597653882209219e-08</v>
+        <v>8.1062200545965806e-08</v>
       </c>
       <c r="S7">
-        <v>-5.3488352977584973e-08</v>
+        <v>-5.0744367461554634e-08</v>
       </c>
       <c r="T7">
-        <v>1.366702920055904e-08</v>
+        <v>1.3385583977406992e-08</v>
       </c>
       <c r="U7">
-        <v>-9.8542793182894399e-08</v>
+        <v>-1.0044611239573867e-07</v>
       </c>
       <c r="V7">
-        <v>-6.3493159269762477e-08</v>
+        <v>-6.2851181346921051e-08</v>
       </c>
       <c r="W7">
-        <v>1.0277331053915232e-06</v>
+        <v>1.0655424713222984e-06</v>
       </c>
       <c r="X7">
-        <v>6.4128100646700016e-08</v>
+        <v>6.2136819873766579e-08</v>
       </c>
     </row>
     <row r="8">
@@ -828,73 +828,73 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>-0.05695035937833752</v>
+        <v>-0.052681765434884668</v>
       </c>
       <c r="C8">
-        <v>3.5764024527174491e-07</v>
+        <v>3.2989559988356562e-07</v>
       </c>
       <c r="D8">
-        <v>-4.0520286944204514e-09</v>
+        <v>-3.7319349364623934e-09</v>
       </c>
       <c r="E8">
-        <v>8.4080989935792137e-07</v>
+        <v>9.0018252344327447e-07</v>
       </c>
       <c r="F8">
-        <v>-2.5688894739788384e-06</v>
+        <v>-3.0390021186726046e-06</v>
       </c>
       <c r="G8">
-        <v>-2.4255309777454766e-08</v>
+        <v>-2.5456990589984611e-08</v>
       </c>
       <c r="H8">
-        <v>4.2490607035674828e-08</v>
+        <v>5.1935838930347099e-08</v>
       </c>
       <c r="I8">
-        <v>0.0019978313649363045</v>
+        <v>0.0019968866773757746</v>
       </c>
       <c r="J8">
-        <v>0.0016980916101362862</v>
+        <v>0.0016975902365500392</v>
       </c>
       <c r="K8">
-        <v>0.0016986117127408354</v>
+        <v>0.0016981186569895266</v>
       </c>
       <c r="L8">
-        <v>0.0016985883913872351</v>
+        <v>0.0016981063530942756</v>
       </c>
       <c r="M8">
-        <v>8.1722791458565194e-07</v>
+        <v>8.4470744711710967e-07</v>
       </c>
       <c r="N8">
-        <v>1.8991381061682696e-06</v>
+        <v>1.8976059647008032e-06</v>
       </c>
       <c r="O8">
-        <v>-4.3603241183414831e-08</v>
+        <v>2.6238107221671154e-08</v>
       </c>
       <c r="P8">
-        <v>1.599250973033335e-06</v>
+        <v>1.621134941583355e-06</v>
       </c>
       <c r="Q8">
-        <v>1.3154260810286157e-07</v>
+        <v>-5.2411169944939973e-08</v>
       </c>
       <c r="R8">
-        <v>-1.3519296256240985e-06</v>
+        <v>-1.3310203822138573e-06</v>
       </c>
       <c r="S8">
-        <v>-2.6690265932160374e-07</v>
+        <v>-2.9141251213106696e-07</v>
       </c>
       <c r="T8">
-        <v>3.0884058561387618e-07</v>
+        <v>2.966851573054459e-07</v>
       </c>
       <c r="U8">
-        <v>-8.8144932168151532e-07</v>
+        <v>-8.3763211414687949e-07</v>
       </c>
       <c r="V8">
-        <v>-1.5700449837232645e-06</v>
+        <v>-1.5229115191253454e-06</v>
       </c>
       <c r="W8">
-        <v>-0.0017395412902696035</v>
+        <v>-0.0017372286078741065</v>
       </c>
       <c r="X8">
-        <v>6.0638198289440282e-06</v>
+        <v>6.0082792923725052e-06</v>
       </c>
     </row>
     <row r="9">
@@ -902,73 +902,73 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>0.0082652908405317031</v>
+        <v>0.012601878612169787</v>
       </c>
       <c r="C9">
-        <v>9.0310592838376997e-07</v>
+        <v>8.5930459096122898e-07</v>
       </c>
       <c r="D9">
-        <v>-9.6805696241493437e-09</v>
+        <v>-9.1784828666292821e-09</v>
       </c>
       <c r="E9">
-        <v>-2.7413066161234023e-06</v>
+        <v>-2.6845742726977543e-06</v>
       </c>
       <c r="F9">
-        <v>-1.1196877800254609e-05</v>
+        <v>-1.1609769801558883e-05</v>
       </c>
       <c r="G9">
-        <v>4.9636289838053165e-08</v>
+        <v>4.9343901793638584e-08</v>
       </c>
       <c r="H9">
-        <v>2.2308907829895926e-07</v>
+        <v>2.3175682159255382e-07</v>
       </c>
       <c r="I9">
-        <v>0.0016980916101362862</v>
+        <v>0.0016975902365500392</v>
       </c>
       <c r="J9">
-        <v>0.0017416834966166501</v>
+        <v>0.0017411589495235126</v>
       </c>
       <c r="K9">
-        <v>0.0017019684157258859</v>
+        <v>0.0017014312502845368</v>
       </c>
       <c r="L9">
-        <v>0.0017024816565692404</v>
+        <v>0.0017019579692115123</v>
       </c>
       <c r="M9">
-        <v>-5.0488061109787032e-07</v>
+        <v>-5.3039455539826598e-07</v>
       </c>
       <c r="N9">
-        <v>7.1123634158072459e-07</v>
+        <v>6.8688694002929633e-07</v>
       </c>
       <c r="O9">
-        <v>-9.3138013792192457e-07</v>
+        <v>-9.3523175115713503e-07</v>
       </c>
       <c r="P9">
-        <v>1.4286494242565412e-06</v>
+        <v>1.4140803562458175e-06</v>
       </c>
       <c r="Q9">
-        <v>-1.1932871211495151e-06</v>
+        <v>-1.3523932796731767e-06</v>
       </c>
       <c r="R9">
-        <v>-2.6379844205111986e-06</v>
+        <v>-2.5952813499462006e-06</v>
       </c>
       <c r="S9">
-        <v>6.1314794196074334e-08</v>
+        <v>7.5918833615956413e-08</v>
       </c>
       <c r="T9">
-        <v>2.429677446205117e-07</v>
+        <v>2.3252801701078076e-07</v>
       </c>
       <c r="U9">
-        <v>-1.4188388735541499e-06</v>
+        <v>-1.3540405158185203e-06</v>
       </c>
       <c r="V9">
-        <v>-1.2015932200612024e-06</v>
+        <v>-1.115124663923553e-06</v>
       </c>
       <c r="W9">
-        <v>-0.0017500342722169364</v>
+        <v>-0.0017474780441503945</v>
       </c>
       <c r="X9">
-        <v>1.2343919075922591e-05</v>
+        <v>1.2144176101253963e-05</v>
       </c>
     </row>
     <row r="10">
@@ -976,73 +976,73 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>0.063584343197898338</v>
+        <v>0.06851634425852525</v>
       </c>
       <c r="C10">
-        <v>1.0197007572277122e-06</v>
+        <v>9.6407141763929916e-07</v>
       </c>
       <c r="D10">
-        <v>-9.0386324349088642e-09</v>
+        <v>-8.4040053533193612e-09</v>
       </c>
       <c r="E10">
-        <v>-3.5284807172009454e-06</v>
+        <v>-3.4482773625145712e-06</v>
       </c>
       <c r="F10">
-        <v>-1.2843871475047249e-05</v>
+        <v>-1.3228556812213985e-05</v>
       </c>
       <c r="G10">
-        <v>1.1711422476994188e-07</v>
+        <v>1.1612214653160678e-07</v>
       </c>
       <c r="H10">
-        <v>3.3631007008296663e-07</v>
+        <v>3.4434686199032316e-07</v>
       </c>
       <c r="I10">
-        <v>0.0016986117127408354</v>
+        <v>0.0016981186569895266</v>
       </c>
       <c r="J10">
-        <v>0.0017019684157258859</v>
+        <v>0.0017014312502845368</v>
       </c>
       <c r="K10">
-        <v>0.0017149497043046642</v>
+        <v>0.0017143939629419699</v>
       </c>
       <c r="L10">
-        <v>0.0017073043766120031</v>
+        <v>0.0017067650231300641</v>
       </c>
       <c r="M10">
-        <v>-2.1777239171497569e-06</v>
+        <v>-2.2056210288169596e-06</v>
       </c>
       <c r="N10">
-        <v>-2.0145431667135718e-07</v>
+        <v>-2.4566982973921525e-07</v>
       </c>
       <c r="O10">
-        <v>-2.5340321938349034e-06</v>
+        <v>-2.5441566525286113e-06</v>
       </c>
       <c r="P10">
-        <v>1.2279031633990134e-07</v>
+        <v>9.2783942308730268e-08</v>
       </c>
       <c r="Q10">
-        <v>-2.8172173738938189e-06</v>
+        <v>-2.9719316698044262e-06</v>
       </c>
       <c r="R10">
-        <v>-2.2278579874561082e-06</v>
+        <v>-2.2211951992499049e-06</v>
       </c>
       <c r="S10">
-        <v>5.1178886280251581e-07</v>
+        <v>5.1790724660609186e-07</v>
       </c>
       <c r="T10">
-        <v>4.67606941863126e-07</v>
+        <v>4.5979768344282892e-07</v>
       </c>
       <c r="U10">
-        <v>-2.9274803892434655e-06</v>
+        <v>-2.8619636165220192e-06</v>
       </c>
       <c r="V10">
-        <v>-1.5440782323262466e-06</v>
+        <v>-1.5133739088166414e-06</v>
       </c>
       <c r="W10">
-        <v>-0.0017840923352891898</v>
+        <v>-0.0017815056291897776</v>
       </c>
       <c r="X10">
-        <v>1.5322817894831174e-05</v>
+        <v>1.5072125949871779e-05</v>
       </c>
     </row>
     <row r="11">
@@ -1050,73 +1050,73 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>0.1182612509606307</v>
+        <v>0.12296382117752443</v>
       </c>
       <c r="C11">
-        <v>1.752819666886691e-06</v>
+        <v>1.7024774339856528e-06</v>
       </c>
       <c r="D11">
-        <v>-1.4122102515186193e-08</v>
+        <v>-1.3558838176621225e-08</v>
       </c>
       <c r="E11">
-        <v>1.045490110851464e-08</v>
+        <v>8.1439838235357847e-10</v>
       </c>
       <c r="F11">
-        <v>-6.7142440201013043e-06</v>
+        <v>-7.1621684364391638e-06</v>
       </c>
       <c r="G11">
-        <v>6.5081523902758838e-08</v>
+        <v>6.5861668680520826e-08</v>
       </c>
       <c r="H11">
-        <v>2.4995037235956296e-07</v>
+        <v>2.5899882456414782e-07</v>
       </c>
       <c r="I11">
-        <v>0.0016985883913872351</v>
+        <v>0.0016981063530942756</v>
       </c>
       <c r="J11">
-        <v>0.0017024816565692404</v>
+        <v>0.0017019579692115123</v>
       </c>
       <c r="K11">
-        <v>0.0017073043766120031</v>
+        <v>0.0017067650231300641</v>
       </c>
       <c r="L11">
-        <v>0.0017426241417320097</v>
+        <v>0.0017420217646060346</v>
       </c>
       <c r="M11">
-        <v>-3.8399491159399608e-06</v>
+        <v>-3.8672662790935484e-06</v>
       </c>
       <c r="N11">
-        <v>-2.5026110336148554e-06</v>
+        <v>-2.5386007273936191e-06</v>
       </c>
       <c r="O11">
-        <v>-3.5458195820445875e-06</v>
+        <v>-3.5496244505492113e-06</v>
       </c>
       <c r="P11">
-        <v>-2.9509892789255098e-06</v>
+        <v>-2.9659438560866516e-06</v>
       </c>
       <c r="Q11">
-        <v>-5.5544649050715438e-06</v>
+        <v>-5.7204329420563639e-06</v>
       </c>
       <c r="R11">
-        <v>-5.1279441452728048e-06</v>
+        <v>-5.1103883499207301e-06</v>
       </c>
       <c r="S11">
-        <v>6.6774458364615741e-07</v>
+        <v>6.601019602486344e-07</v>
       </c>
       <c r="T11">
-        <v>7.3714996207856789e-07</v>
+        <v>7.2813179495945814e-07</v>
       </c>
       <c r="U11">
-        <v>-4.7864809205145175e-06</v>
+        <v>-4.7282574375888461e-06</v>
       </c>
       <c r="V11">
-        <v>-2.9978739010551306e-06</v>
+        <v>-2.954051637485095e-06</v>
       </c>
       <c r="W11">
-        <v>-0.0018341099051755057</v>
+        <v>-0.0018314917253335551</v>
       </c>
       <c r="X11">
-        <v>1.5635364415151906e-05</v>
+        <v>1.5402155260158814e-05</v>
       </c>
     </row>
     <row r="12">
@@ -1124,73 +1124,73 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>0.18659512521437158</v>
+        <v>0.18756363361655554</v>
       </c>
       <c r="C12">
-        <v>1.3864298727483544e-07</v>
+        <v>1.241566710718255e-07</v>
       </c>
       <c r="D12">
-        <v>-1.7582652920199261e-09</v>
+        <v>-1.5971615157790988e-09</v>
       </c>
       <c r="E12">
-        <v>2.3005580802923954e-06</v>
+        <v>2.2251701420626057e-06</v>
       </c>
       <c r="F12">
-        <v>1.7232189954144349e-06</v>
+        <v>1.8559847380038938e-06</v>
       </c>
       <c r="G12">
-        <v>-1.9961831057816129e-08</v>
+        <v>-1.807945721190512e-08</v>
       </c>
       <c r="H12">
-        <v>-5.4543774580176689e-09</v>
+        <v>-7.904841062613128e-09</v>
       </c>
       <c r="I12">
-        <v>8.1722791458565194e-07</v>
+        <v>8.4470744711710967e-07</v>
       </c>
       <c r="J12">
-        <v>-5.0488061109787032e-07</v>
+        <v>-5.3039455539826598e-07</v>
       </c>
       <c r="K12">
-        <v>-2.1777239171497569e-06</v>
+        <v>-2.2056210288169596e-06</v>
       </c>
       <c r="L12">
-        <v>-3.8399491159399608e-06</v>
+        <v>-3.8672662790935484e-06</v>
       </c>
       <c r="M12">
-        <v>8.2950737687791044e-05</v>
+        <v>8.2909923835444751e-05</v>
       </c>
       <c r="N12">
-        <v>4.6476418929663224e-05</v>
+        <v>4.6452197516070863e-05</v>
       </c>
       <c r="O12">
-        <v>4.627524944485173e-05</v>
+        <v>4.6250068054977736e-05</v>
       </c>
       <c r="P12">
-        <v>4.6360175714605128e-05</v>
+        <v>4.633226293688482e-05</v>
       </c>
       <c r="Q12">
-        <v>4.6193477845693241e-05</v>
+        <v>4.6168001711781971e-05</v>
       </c>
       <c r="R12">
-        <v>4.6050325393295446e-05</v>
+        <v>4.6032646543889305e-05</v>
       </c>
       <c r="S12">
-        <v>-2.0482910300169638e-06</v>
+        <v>-2.0484158394940685e-06</v>
       </c>
       <c r="T12">
-        <v>1.361144320115421e-07</v>
+        <v>1.3821677949610661e-07</v>
       </c>
       <c r="U12">
-        <v>3.1697784725870662e-08</v>
+        <v>3.5002931405936252e-08</v>
       </c>
       <c r="V12">
-        <v>-5.1941576254680557e-07</v>
+        <v>-5.1790702393725785e-07</v>
       </c>
       <c r="W12">
-        <v>-6.0857961979947391e-05</v>
+        <v>-6.0705729772257282e-05</v>
       </c>
       <c r="X12">
-        <v>1.5048789706230805e-06</v>
+        <v>1.4570914053937378e-06</v>
       </c>
     </row>
     <row r="13">
@@ -1198,73 +1198,73 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>0.17517892841517541</v>
+        <v>0.17502123970718458</v>
       </c>
       <c r="C13">
-        <v>3.2017440313383282e-07</v>
+        <v>3.1769465646999755e-07</v>
       </c>
       <c r="D13">
-        <v>-3.6751477929240483e-09</v>
+        <v>-3.6474948461027171e-09</v>
       </c>
       <c r="E13">
-        <v>2.3265125389912814e-06</v>
+        <v>2.3501550562870658e-06</v>
       </c>
       <c r="F13">
-        <v>-1.686686436667657e-06</v>
+        <v>-1.6167694720781554e-06</v>
       </c>
       <c r="G13">
-        <v>-3.5275887801187731e-08</v>
+        <v>-3.5997748764080934e-08</v>
       </c>
       <c r="H13">
-        <v>7.7145377521158658e-08</v>
+        <v>7.5081583969181696e-08</v>
       </c>
       <c r="I13">
-        <v>1.8991381061682696e-06</v>
+        <v>1.8976059647008032e-06</v>
       </c>
       <c r="J13">
-        <v>7.1123634158072459e-07</v>
+        <v>6.8688694002929633e-07</v>
       </c>
       <c r="K13">
-        <v>-2.0145431667135718e-07</v>
+        <v>-2.4566982973921525e-07</v>
       </c>
       <c r="L13">
-        <v>-2.5026110336148554e-06</v>
+        <v>-2.5386007273936191e-06</v>
       </c>
       <c r="M13">
-        <v>4.6476418929663224e-05</v>
+        <v>4.6452197516070863e-05</v>
       </c>
       <c r="N13">
-        <v>9.7782619499126334e-05</v>
+        <v>9.75963891504561e-05</v>
       </c>
       <c r="O13">
-        <v>4.6152205248872275e-05</v>
+        <v>4.6128910765609187e-05</v>
       </c>
       <c r="P13">
-        <v>4.6559022675460846e-05</v>
+        <v>4.6530320894656486e-05</v>
       </c>
       <c r="Q13">
-        <v>4.6181317642674313e-05</v>
+        <v>4.6159832694176174e-05</v>
       </c>
       <c r="R13">
-        <v>4.61636667145194e-05</v>
+        <v>4.6137738753150446e-05</v>
       </c>
       <c r="S13">
-        <v>3.0267839694968292e-07</v>
+        <v>2.5914744252164813e-07</v>
       </c>
       <c r="T13">
-        <v>-2.7636266740667387e-07</v>
+        <v>-2.7236775495689169e-07</v>
       </c>
       <c r="U13">
-        <v>1.3730319702048104e-06</v>
+        <v>1.3948218939648056e-06</v>
       </c>
       <c r="V13">
-        <v>-8.7062776029841975e-09</v>
+        <v>1.1160074936462467e-08</v>
       </c>
       <c r="W13">
-        <v>-2.5835974256953269e-05</v>
+        <v>-2.6101873759929318e-05</v>
       </c>
       <c r="X13">
-        <v>1.4721279851961132e-06</v>
+        <v>1.4799476039164049e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1272,73 +1272,73 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>0.063304241408129167</v>
+        <v>0.062201922063827235</v>
       </c>
       <c r="C14">
-        <v>1.142212658762969e-07</v>
+        <v>1.1628935727995375e-07</v>
       </c>
       <c r="D14">
-        <v>-1.5255190061157289e-09</v>
+        <v>-1.5487966269317116e-09</v>
       </c>
       <c r="E14">
-        <v>1.278156403751324e-06</v>
+        <v>1.1170187068807747e-06</v>
       </c>
       <c r="F14">
-        <v>-6.6342444036298734e-06</v>
+        <v>-6.480270206164239e-06</v>
       </c>
       <c r="G14">
-        <v>-1.671182211494701e-08</v>
+        <v>-1.2762229273894052e-08</v>
       </c>
       <c r="H14">
-        <v>1.0811413766204395e-07</v>
+        <v>1.0539244222855904e-07</v>
       </c>
       <c r="I14">
-        <v>-4.3603241183414831e-08</v>
+        <v>2.6238107221671154e-08</v>
       </c>
       <c r="J14">
-        <v>-9.3138013792192457e-07</v>
+        <v>-9.3523175115713503e-07</v>
       </c>
       <c r="K14">
-        <v>-2.5340321938349034e-06</v>
+        <v>-2.5441566525286113e-06</v>
       </c>
       <c r="L14">
-        <v>-3.5458195820445875e-06</v>
+        <v>-3.5496244505492113e-06</v>
       </c>
       <c r="M14">
-        <v>4.627524944485173e-05</v>
+        <v>4.6250068054977736e-05</v>
       </c>
       <c r="N14">
-        <v>4.6152205248872275e-05</v>
+        <v>4.6128910765609187e-05</v>
       </c>
       <c r="O14">
-        <v>8.9501910032662477e-05</v>
+        <v>8.9468687489309843e-05</v>
       </c>
       <c r="P14">
-        <v>4.6261948584373075e-05</v>
+        <v>4.6236293818853066e-05</v>
       </c>
       <c r="Q14">
-        <v>4.6713631465493459e-05</v>
+        <v>4.6688083805813537e-05</v>
       </c>
       <c r="R14">
-        <v>4.6368721523783043e-05</v>
+        <v>4.6345012762850995e-05</v>
       </c>
       <c r="S14">
-        <v>-1.4453915249546863e-06</v>
+        <v>-1.4536793504527942e-06</v>
       </c>
       <c r="T14">
-        <v>-1.119435648061316e-07</v>
+        <v>-1.1362984237927514e-07</v>
       </c>
       <c r="U14">
-        <v>-4.1910620422897877e-08</v>
+        <v>-1.1525581570987e-08</v>
       </c>
       <c r="V14">
-        <v>-4.1795223417274571e-07</v>
+        <v>-3.9882995497884263e-07</v>
       </c>
       <c r="W14">
-        <v>-3.3366815790390487e-05</v>
+        <v>-3.3213518157624563e-05</v>
       </c>
       <c r="X14">
-        <v>-9.7760128243339665e-07</v>
+        <v>-9.9972266835786739e-07</v>
       </c>
     </row>
     <row r="15">
@@ -1346,73 +1346,73 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>0.1480753680648923</v>
+        <v>0.14873863182170674</v>
       </c>
       <c r="C15">
-        <v>3.341249343141725e-07</v>
+        <v>3.2817034454393521e-07</v>
       </c>
       <c r="D15">
-        <v>-3.6367402927319189e-09</v>
+        <v>-3.5624493890489849e-09</v>
       </c>
       <c r="E15">
-        <v>7.0587358472521583e-07</v>
+        <v>7.1113453533008501e-07</v>
       </c>
       <c r="F15">
-        <v>-4.2414349194628831e-06</v>
+        <v>-4.1291271692011328e-06</v>
       </c>
       <c r="G15">
-        <v>-2.8219795948845958e-08</v>
+        <v>-2.8336005794566414e-08</v>
       </c>
       <c r="H15">
-        <v>7.5041780804141119e-08</v>
+        <v>7.2851890920698179e-08</v>
       </c>
       <c r="I15">
-        <v>1.599250973033335e-06</v>
+        <v>1.621134941583355e-06</v>
       </c>
       <c r="J15">
-        <v>1.4286494242565412e-06</v>
+        <v>1.4140803562458175e-06</v>
       </c>
       <c r="K15">
-        <v>1.2279031633990134e-07</v>
+        <v>9.2783942308730268e-08</v>
       </c>
       <c r="L15">
-        <v>-2.9509892789255098e-06</v>
+        <v>-2.9659438560866516e-06</v>
       </c>
       <c r="M15">
-        <v>4.6360175714605128e-05</v>
+        <v>4.633226293688482e-05</v>
       </c>
       <c r="N15">
-        <v>4.6559022675460846e-05</v>
+        <v>4.6530320894656486e-05</v>
       </c>
       <c r="O15">
-        <v>4.6261948584373075e-05</v>
+        <v>4.6236293818853066e-05</v>
       </c>
       <c r="P15">
-        <v>7.0238266712816343e-05</v>
+        <v>7.0168915429237347e-05</v>
       </c>
       <c r="Q15">
-        <v>4.6459496914630588e-05</v>
+        <v>4.6436289944037896e-05</v>
       </c>
       <c r="R15">
-        <v>4.638431579853753e-05</v>
+        <v>4.6359745838662621e-05</v>
       </c>
       <c r="S15">
-        <v>4.245805439207837e-07</v>
+        <v>4.0831357893568859e-07</v>
       </c>
       <c r="T15">
-        <v>-5.6624270643329493e-07</v>
+        <v>-5.6757370586780441e-07</v>
       </c>
       <c r="U15">
-        <v>4.1658103635407505e-06</v>
+        <v>4.2013417873175332e-06</v>
       </c>
       <c r="V15">
-        <v>3.586554724291756e-06</v>
+        <v>3.6023916853943343e-06</v>
       </c>
       <c r="W15">
-        <v>2.9775632100304642e-06</v>
+        <v>3.2850335311441452e-06</v>
       </c>
       <c r="X15">
-        <v>1.561261445704054e-06</v>
+        <v>1.5265679256769023e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1420,73 +1420,73 @@
         <v>37</v>
       </c>
       <c r="B16">
-        <v>0.089064392742123008</v>
+        <v>0.08951854345130858</v>
       </c>
       <c r="C16">
-        <v>1.0958239262944224e-08</v>
+        <v>1.0915884705018853e-08</v>
       </c>
       <c r="D16">
-        <v>5.4656640424326504e-11</v>
+        <v>4.2898625971502261e-11</v>
       </c>
       <c r="E16">
-        <v>-7.6302690183408902e-07</v>
+        <v>-9.4072034336560488e-07</v>
       </c>
       <c r="F16">
-        <v>-1.1369617532126823e-05</v>
+        <v>-1.1489513463520052e-05</v>
       </c>
       <c r="G16">
-        <v>2.1816823366073077e-08</v>
+        <v>2.6111115388487911e-08</v>
       </c>
       <c r="H16">
-        <v>1.9414465994645628e-07</v>
+        <v>1.9769427107113253e-07</v>
       </c>
       <c r="I16">
-        <v>1.3154260810286157e-07</v>
+        <v>-5.2411169944939973e-08</v>
       </c>
       <c r="J16">
-        <v>-1.1932871211495151e-06</v>
+        <v>-1.3523932796731767e-06</v>
       </c>
       <c r="K16">
-        <v>-2.8172173738938189e-06</v>
+        <v>-2.9719316698044262e-06</v>
       </c>
       <c r="L16">
-        <v>-5.5544649050715438e-06</v>
+        <v>-5.7204329420563639e-06</v>
       </c>
       <c r="M16">
-        <v>4.6193477845693241e-05</v>
+        <v>4.6168001711781971e-05</v>
       </c>
       <c r="N16">
-        <v>4.6181317642674313e-05</v>
+        <v>4.6159832694176174e-05</v>
       </c>
       <c r="O16">
-        <v>4.6713631465493459e-05</v>
+        <v>4.6688083805813537e-05</v>
       </c>
       <c r="P16">
-        <v>4.6459496914630588e-05</v>
+        <v>4.6436289944037896e-05</v>
       </c>
       <c r="Q16">
-        <v>8.7439698158099015e-05</v>
+        <v>8.7461769811171157e-05</v>
       </c>
       <c r="R16">
-        <v>4.6804717924462996e-05</v>
+        <v>4.6777583959678942e-05</v>
       </c>
       <c r="S16">
-        <v>-1.0988373658608962e-06</v>
+        <v>-1.06796875701763e-06</v>
       </c>
       <c r="T16">
-        <v>-3.7273091293591381e-07</v>
+        <v>-3.6452028849542224e-07</v>
       </c>
       <c r="U16">
-        <v>1.9358410586813311e-06</v>
+        <v>1.8933899252498969e-06</v>
       </c>
       <c r="V16">
-        <v>9.145010668859207e-07</v>
+        <v>8.7704957592123142e-07</v>
       </c>
       <c r="W16">
-        <v>-4.5585630841097833e-06</v>
+        <v>-5.2030548933747672e-06</v>
       </c>
       <c r="X16">
-        <v>-3.3911771963062025e-06</v>
+        <v>-3.3847883008847637e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1494,73 +1494,73 @@
         <v>38</v>
       </c>
       <c r="B17">
-        <v>0.071112566938278388</v>
+        <v>0.070862339431664922</v>
       </c>
       <c r="C17">
-        <v>-3.8139965223970614e-08</v>
+        <v>-2.6817344936607236e-08</v>
       </c>
       <c r="D17">
-        <v>7.5094641308874071e-10</v>
+        <v>6.2009569886426286e-10</v>
       </c>
       <c r="E17">
-        <v>1.0067700657887708e-06</v>
+        <v>9.2157139453280425e-07</v>
       </c>
       <c r="F17">
-        <v>-5.1746972412528082e-06</v>
+        <v>-5.1627345155512233e-06</v>
       </c>
       <c r="G17">
-        <v>-2.9309071900597909e-08</v>
+        <v>-2.7737055571011313e-08</v>
       </c>
       <c r="H17">
-        <v>8.1597653882209219e-08</v>
+        <v>8.1062200545965806e-08</v>
       </c>
       <c r="I17">
-        <v>-1.3519296256240985e-06</v>
+        <v>-1.3310203822138573e-06</v>
       </c>
       <c r="J17">
-        <v>-2.6379844205111986e-06</v>
+        <v>-2.5952813499462006e-06</v>
       </c>
       <c r="K17">
-        <v>-2.2278579874561082e-06</v>
+        <v>-2.2211951992499049e-06</v>
       </c>
       <c r="L17">
-        <v>-5.1279441452728048e-06</v>
+        <v>-5.1103883499207301e-06</v>
       </c>
       <c r="M17">
-        <v>4.6050325393295446e-05</v>
+        <v>4.6032646543889305e-05</v>
       </c>
       <c r="N17">
-        <v>4.61636667145194e-05</v>
+        <v>4.6137738753150446e-05</v>
       </c>
       <c r="O17">
-        <v>4.6368721523783043e-05</v>
+        <v>4.6345012762850995e-05</v>
       </c>
       <c r="P17">
-        <v>4.638431579853753e-05</v>
+        <v>4.6359745838662621e-05</v>
       </c>
       <c r="Q17">
-        <v>4.6804717924462996e-05</v>
+        <v>4.6777583959678942e-05</v>
       </c>
       <c r="R17">
-        <v>0.00022833070433600559</v>
+        <v>0.00022764404123583063</v>
       </c>
       <c r="S17">
-        <v>6.7887909396852992e-07</v>
+        <v>6.2649646005319296e-07</v>
       </c>
       <c r="T17">
-        <v>-7.262438765752836e-08</v>
+        <v>-6.0427110249314001e-08</v>
       </c>
       <c r="U17">
-        <v>1.316131146748266e-06</v>
+        <v>1.2803443060331379e-06</v>
       </c>
       <c r="V17">
-        <v>1.437114023221423e-06</v>
+        <v>1.4031050353264428e-06</v>
       </c>
       <c r="W17">
-        <v>-3.5239166088930301e-05</v>
+        <v>-3.6689872272613068e-05</v>
       </c>
       <c r="X17">
-        <v>-2.4678787547563495e-06</v>
+        <v>-2.382379452920277e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1568,73 +1568,73 @@
         <v>39</v>
       </c>
       <c r="B18">
-        <v>0.051372291646209538</v>
+        <v>0.050773723929798044</v>
       </c>
       <c r="C18">
-        <v>-3.7161572841632485e-08</v>
+        <v>-5.364130532496442e-08</v>
       </c>
       <c r="D18">
-        <v>9.9371006257775301e-10</v>
+        <v>1.1804216816992043e-09</v>
       </c>
       <c r="E18">
-        <v>-2.0678765079626196e-06</v>
+        <v>-2.1106656553475872e-06</v>
       </c>
       <c r="F18">
-        <v>1.3786576642619549e-06</v>
+        <v>1.346492301551596e-06</v>
       </c>
       <c r="G18">
-        <v>3.1503821667351492e-08</v>
+        <v>3.3502323851939582e-08</v>
       </c>
       <c r="H18">
-        <v>-5.3488352977584973e-08</v>
+        <v>-5.0744367461554634e-08</v>
       </c>
       <c r="I18">
-        <v>-2.6690265932160374e-07</v>
+        <v>-2.9141251213106696e-07</v>
       </c>
       <c r="J18">
-        <v>6.1314794196074334e-08</v>
+        <v>7.5918833615956413e-08</v>
       </c>
       <c r="K18">
-        <v>5.1178886280251581e-07</v>
+        <v>5.1790724660609186e-07</v>
       </c>
       <c r="L18">
-        <v>6.6774458364615741e-07</v>
+        <v>6.601019602486344e-07</v>
       </c>
       <c r="M18">
-        <v>-2.0482910300169638e-06</v>
+        <v>-2.0484158394940685e-06</v>
       </c>
       <c r="N18">
-        <v>3.0267839694968292e-07</v>
+        <v>2.5914744252164813e-07</v>
       </c>
       <c r="O18">
-        <v>-1.4453915249546863e-06</v>
+        <v>-1.4536793504527942e-06</v>
       </c>
       <c r="P18">
-        <v>4.245805439207837e-07</v>
+        <v>4.0831357893568859e-07</v>
       </c>
       <c r="Q18">
-        <v>-1.0988373658608962e-06</v>
+        <v>-1.06796875701763e-06</v>
       </c>
       <c r="R18">
-        <v>6.7887909396852992e-07</v>
+        <v>6.2649646005319296e-07</v>
       </c>
       <c r="S18">
-        <v>2.6575064765735505e-05</v>
+        <v>2.6608305823766698e-05</v>
       </c>
       <c r="T18">
-        <v>1.7060194870029367e-08</v>
+        <v>5.1928689289217135e-09</v>
       </c>
       <c r="U18">
-        <v>-4.5716282686620832e-07</v>
+        <v>-4.0954947859474373e-07</v>
       </c>
       <c r="V18">
-        <v>-8.71959017555618e-07</v>
+        <v>-8.4010178873622318e-07</v>
       </c>
       <c r="W18">
-        <v>-9.7947343193200566e-06</v>
+        <v>-8.2233332443071515e-06</v>
       </c>
       <c r="X18">
-        <v>-3.0446323904264108e-06</v>
+        <v>-3.093094995171607e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1642,73 +1642,73 @@
         <v>40</v>
       </c>
       <c r="B19">
-        <v>0.0055558810710798603</v>
+        <v>0.005575794936456966</v>
       </c>
       <c r="C19">
-        <v>8.9567784602453331e-08</v>
+        <v>8.6372161145701118e-08</v>
       </c>
       <c r="D19">
-        <v>-1.5064205468023872e-09</v>
+        <v>-1.4697388526011166e-09</v>
       </c>
       <c r="E19">
-        <v>3.0613904650882423e-07</v>
+        <v>2.9426931527776577e-07</v>
       </c>
       <c r="F19">
-        <v>4.0984884995767465e-07</v>
+        <v>4.1709998447961879e-07</v>
       </c>
       <c r="G19">
-        <v>2.2128527109311206e-09</v>
+        <v>2.5086487795685132e-09</v>
       </c>
       <c r="H19">
-        <v>1.366702920055904e-08</v>
+        <v>1.3385583977406992e-08</v>
       </c>
       <c r="I19">
-        <v>3.0884058561387618e-07</v>
+        <v>2.966851573054459e-07</v>
       </c>
       <c r="J19">
-        <v>2.429677446205117e-07</v>
+        <v>2.3252801701078076e-07</v>
       </c>
       <c r="K19">
-        <v>4.67606941863126e-07</v>
+        <v>4.5979768344282892e-07</v>
       </c>
       <c r="L19">
-        <v>7.3714996207856789e-07</v>
+        <v>7.2813179495945814e-07</v>
       </c>
       <c r="M19">
-        <v>1.361144320115421e-07</v>
+        <v>1.3821677949610661e-07</v>
       </c>
       <c r="N19">
-        <v>-2.7636266740667387e-07</v>
+        <v>-2.7236775495689169e-07</v>
       </c>
       <c r="O19">
-        <v>-1.119435648061316e-07</v>
+        <v>-1.1362984237927514e-07</v>
       </c>
       <c r="P19">
-        <v>-5.6624270643329493e-07</v>
+        <v>-5.6757370586780441e-07</v>
       </c>
       <c r="Q19">
-        <v>-3.7273091293591381e-07</v>
+        <v>-3.6452028849542224e-07</v>
       </c>
       <c r="R19">
-        <v>-7.262438765752836e-08</v>
+        <v>-6.0427110249314001e-08</v>
       </c>
       <c r="S19">
-        <v>1.7060194870029367e-08</v>
+        <v>5.1928689289217135e-09</v>
       </c>
       <c r="T19">
-        <v>2.9752906647221398e-06</v>
+        <v>2.9732397476632213e-06</v>
       </c>
       <c r="U19">
-        <v>-1.0748474512769788e-05</v>
+        <v>-1.0738190508463268e-05</v>
       </c>
       <c r="V19">
-        <v>-1.0939979412821618e-05</v>
+        <v>-1.0929818795445748e-05</v>
       </c>
       <c r="W19">
-        <v>-0.00030118844128276481</v>
+        <v>-0.00030090158347031363</v>
       </c>
       <c r="X19">
-        <v>1.7966849015138045e-07</v>
+        <v>1.5528070938230189e-07</v>
       </c>
     </row>
     <row r="20">
@@ -1716,73 +1716,73 @@
         <v>41</v>
       </c>
       <c r="B20">
-        <v>-0.097440885266903823</v>
+        <v>-0.096842805656502676</v>
       </c>
       <c r="C20">
-        <v>-4.3050807129335377e-07</v>
+        <v>-4.2290467950104068e-07</v>
       </c>
       <c r="D20">
-        <v>6.1127464348943115e-09</v>
+        <v>6.0501682233354254e-09</v>
       </c>
       <c r="E20">
-        <v>6.5105715053470193e-07</v>
+        <v>6.3895141129178482e-07</v>
       </c>
       <c r="F20">
-        <v>2.3364861998721039e-06</v>
+        <v>2.372166225105908e-06</v>
       </c>
       <c r="G20">
-        <v>-2.994253271236064e-08</v>
+        <v>-3.0044420403808428e-08</v>
       </c>
       <c r="H20">
-        <v>-9.8542793182894399e-08</v>
+        <v>-1.0044611239573867e-07</v>
       </c>
       <c r="I20">
-        <v>-8.8144932168151532e-07</v>
+        <v>-8.3763211414687949e-07</v>
       </c>
       <c r="J20">
-        <v>-1.4188388735541499e-06</v>
+        <v>-1.3540405158185203e-06</v>
       </c>
       <c r="K20">
-        <v>-2.9274803892434655e-06</v>
+        <v>-2.8619636165220192e-06</v>
       </c>
       <c r="L20">
-        <v>-4.7864809205145175e-06</v>
+        <v>-4.7282574375888461e-06</v>
       </c>
       <c r="M20">
-        <v>3.1697784725870662e-08</v>
+        <v>3.5002931405936252e-08</v>
       </c>
       <c r="N20">
-        <v>1.3730319702048104e-06</v>
+        <v>1.3948218939648056e-06</v>
       </c>
       <c r="O20">
-        <v>-4.1910620422897877e-08</v>
+        <v>-1.1525581570987e-08</v>
       </c>
       <c r="P20">
-        <v>4.1658103635407505e-06</v>
+        <v>4.2013417873175332e-06</v>
       </c>
       <c r="Q20">
-        <v>1.9358410586813311e-06</v>
+        <v>1.8933899252498969e-06</v>
       </c>
       <c r="R20">
-        <v>1.316131146748266e-06</v>
+        <v>1.2803443060331379e-06</v>
       </c>
       <c r="S20">
-        <v>-4.5716282686620832e-07</v>
+        <v>-4.0954947859474373e-07</v>
       </c>
       <c r="T20">
-        <v>-1.0748474512769788e-05</v>
+        <v>-1.0738190508463268e-05</v>
       </c>
       <c r="U20">
-        <v>0.00015653595057605512</v>
+        <v>0.00015641752457716529</v>
       </c>
       <c r="V20">
-        <v>4.6553405918093734e-05</v>
+        <v>4.6498863491718477e-05</v>
       </c>
       <c r="W20">
-        <v>0.0010850978160424894</v>
+        <v>0.0010837602829331396</v>
       </c>
       <c r="X20">
-        <v>-1.7354828856531645e-06</v>
+        <v>-1.5961234905841039e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1790,73 +1790,73 @@
         <v>42</v>
       </c>
       <c r="B21">
-        <v>-0.048147200828972406</v>
+        <v>-0.049526743329220038</v>
       </c>
       <c r="C21">
-        <v>-4.3886414477833709e-07</v>
+        <v>-4.27002655545462e-07</v>
       </c>
       <c r="D21">
-        <v>6.2173691225822712e-09</v>
+        <v>6.0875926006412541e-09</v>
       </c>
       <c r="E21">
-        <v>-1.2759035791928479e-06</v>
+        <v>-1.2754998993734713e-06</v>
       </c>
       <c r="F21">
-        <v>1.1289433398846271e-06</v>
+        <v>1.1007433048304987e-06</v>
       </c>
       <c r="G21">
-        <v>1.5776979302878209e-08</v>
+        <v>1.5728952573711131e-08</v>
       </c>
       <c r="H21">
-        <v>-6.3493159269762477e-08</v>
+        <v>-6.2851181346921051e-08</v>
       </c>
       <c r="I21">
-        <v>-1.5700449837232645e-06</v>
+        <v>-1.5229115191253454e-06</v>
       </c>
       <c r="J21">
-        <v>-1.2015932200612024e-06</v>
+        <v>-1.115124663923553e-06</v>
       </c>
       <c r="K21">
-        <v>-1.5440782323262466e-06</v>
+        <v>-1.5133739088166414e-06</v>
       </c>
       <c r="L21">
-        <v>-2.9978739010551306e-06</v>
+        <v>-2.954051637485095e-06</v>
       </c>
       <c r="M21">
-        <v>-5.1941576254680557e-07</v>
+        <v>-5.1790702393725785e-07</v>
       </c>
       <c r="N21">
-        <v>-8.7062776029841975e-09</v>
+        <v>1.1160074936462467e-08</v>
       </c>
       <c r="O21">
-        <v>-4.1795223417274571e-07</v>
+        <v>-3.9882995497884263e-07</v>
       </c>
       <c r="P21">
-        <v>3.586554724291756e-06</v>
+        <v>3.6023916853943343e-06</v>
       </c>
       <c r="Q21">
-        <v>9.145010668859207e-07</v>
+        <v>8.7704957592123142e-07</v>
       </c>
       <c r="R21">
-        <v>1.437114023221423e-06</v>
+        <v>1.4031050353264428e-06</v>
       </c>
       <c r="S21">
-        <v>-8.71959017555618e-07</v>
+        <v>-8.4010178873622318e-07</v>
       </c>
       <c r="T21">
-        <v>-1.0939979412821618e-05</v>
+        <v>-1.0929818795445748e-05</v>
       </c>
       <c r="U21">
-        <v>4.6553405918093734e-05</v>
+        <v>4.6498863491718477e-05</v>
       </c>
       <c r="V21">
-        <v>0.00015369901290262949</v>
+        <v>0.00015347916001205318</v>
       </c>
       <c r="W21">
-        <v>0.0011028502601045632</v>
+        <v>0.0011015188690491145</v>
       </c>
       <c r="X21">
-        <v>1.3479960049563198e-06</v>
+        <v>1.406487366733789e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1864,73 +1864,73 @@
         <v>43</v>
       </c>
       <c r="B22">
-        <v>0.79636229069833875</v>
+        <v>0.78857923403586505</v>
       </c>
       <c r="C22">
-        <v>-8.1948005135246106e-05</v>
+        <v>-8.1590817495457311e-05</v>
       </c>
       <c r="D22">
-        <v>9.2675456231938234e-07</v>
+        <v>9.2284000205573004e-07</v>
       </c>
       <c r="E22">
-        <v>-0.00023009096026126906</v>
+        <v>-0.00022902708987753193</v>
       </c>
       <c r="F22">
-        <v>-0.0001524006388416583</v>
+        <v>-0.00015390420348669105</v>
       </c>
       <c r="G22">
-        <v>3.9178240106067675e-06</v>
+        <v>3.8920617314655697e-06</v>
       </c>
       <c r="H22">
-        <v>1.0277331053915232e-06</v>
+        <v>1.0655424713222984e-06</v>
       </c>
       <c r="I22">
-        <v>-0.0017395412902696035</v>
+        <v>-0.0017372286078741065</v>
       </c>
       <c r="J22">
-        <v>-0.0017500342722169364</v>
+        <v>-0.0017474780441503945</v>
       </c>
       <c r="K22">
-        <v>-0.0017840923352891898</v>
+        <v>-0.0017815056291897776</v>
       </c>
       <c r="L22">
-        <v>-0.0018341099051755057</v>
+        <v>-0.0018314917253335551</v>
       </c>
       <c r="M22">
-        <v>-6.0857961979947391e-05</v>
+        <v>-6.0705729772257282e-05</v>
       </c>
       <c r="N22">
-        <v>-2.5835974256953269e-05</v>
+        <v>-2.6101873759929318e-05</v>
       </c>
       <c r="O22">
-        <v>-3.3366815790390487e-05</v>
+        <v>-3.3213518157624563e-05</v>
       </c>
       <c r="P22">
-        <v>2.9775632100304642e-06</v>
+        <v>3.2850335311441452e-06</v>
       </c>
       <c r="Q22">
-        <v>-4.5585630841097833e-06</v>
+        <v>-5.2030548933747672e-06</v>
       </c>
       <c r="R22">
-        <v>-3.5239166088930301e-05</v>
+        <v>-3.6689872272613068e-05</v>
       </c>
       <c r="S22">
-        <v>-9.7947343193200566e-06</v>
+        <v>-8.2233332443071515e-06</v>
       </c>
       <c r="T22">
-        <v>-0.00030118844128276481</v>
+        <v>-0.00030090158347031363</v>
       </c>
       <c r="U22">
-        <v>0.0010850978160424894</v>
+        <v>0.0010837602829331396</v>
       </c>
       <c r="V22">
-        <v>0.0011028502601045632</v>
+        <v>0.0011015188690491145</v>
       </c>
       <c r="W22">
-        <v>0.033937293545460844</v>
+        <v>0.033896979763544895</v>
       </c>
       <c r="X22">
-        <v>-0.00012866173175828395</v>
+        <v>-0.00012481376072628032</v>
       </c>
     </row>
     <row r="23">
@@ -1938,73 +1938,73 @@
         <v>44</v>
       </c>
       <c r="B23">
-        <v>-0.23686682811636584</v>
+        <v>-0.23916801242531022</v>
       </c>
       <c r="C23">
-        <v>4.0370232315436746e-06</v>
+        <v>3.9901979423824158e-06</v>
       </c>
       <c r="D23">
-        <v>-4.4930703899308752e-08</v>
+        <v>-4.4424433027561278e-08</v>
       </c>
       <c r="E23">
-        <v>-1.1341283837345014e-05</v>
+        <v>-1.1074392183280852e-05</v>
       </c>
       <c r="F23">
-        <v>-1.381490843236969e-05</v>
+        <v>-1.3652671718948899e-05</v>
       </c>
       <c r="G23">
-        <v>1.5280981299700067e-07</v>
+        <v>1.4711621008646803e-07</v>
       </c>
       <c r="H23">
-        <v>6.4128100646700016e-08</v>
+        <v>6.2136819873766579e-08</v>
       </c>
       <c r="I23">
-        <v>6.0638198289440282e-06</v>
+        <v>6.0082792923725052e-06</v>
       </c>
       <c r="J23">
-        <v>1.2343919075922591e-05</v>
+        <v>1.2144176101253963e-05</v>
       </c>
       <c r="K23">
-        <v>1.5322817894831174e-05</v>
+        <v>1.5072125949871779e-05</v>
       </c>
       <c r="L23">
-        <v>1.5635364415151906e-05</v>
+        <v>1.5402155260158814e-05</v>
       </c>
       <c r="M23">
-        <v>1.5048789706230805e-06</v>
+        <v>1.4570914053937378e-06</v>
       </c>
       <c r="N23">
-        <v>1.4721279851961132e-06</v>
+        <v>1.4799476039164049e-06</v>
       </c>
       <c r="O23">
-        <v>-9.7760128243339665e-07</v>
+        <v>-9.9972266835786739e-07</v>
       </c>
       <c r="P23">
-        <v>1.561261445704054e-06</v>
+        <v>1.5265679256769023e-06</v>
       </c>
       <c r="Q23">
-        <v>-3.3911771963062025e-06</v>
+        <v>-3.3847883008847637e-06</v>
       </c>
       <c r="R23">
-        <v>-2.4678787547563495e-06</v>
+        <v>-2.382379452920277e-06</v>
       </c>
       <c r="S23">
-        <v>-3.0446323904264108e-06</v>
+        <v>-3.093094995171607e-06</v>
       </c>
       <c r="T23">
-        <v>1.7966849015138045e-07</v>
+        <v>1.5528070938230189e-07</v>
       </c>
       <c r="U23">
-        <v>-1.7354828856531645e-06</v>
+        <v>-1.5961234905841039e-06</v>
       </c>
       <c r="V23">
-        <v>1.3479960049563198e-06</v>
+        <v>1.406487366733789e-06</v>
       </c>
       <c r="W23">
-        <v>-0.00012866173175828395</v>
+        <v>-0.00012481376072628032</v>
       </c>
       <c r="X23">
-        <v>4.3554566343627936e-05</v>
+        <v>4.3050897223684884e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2095,73 +2095,73 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>0.029375659118469555</v>
+        <v>0.029304468380890958</v>
       </c>
       <c r="C2">
-        <v>3.3279902099848618e-06</v>
+        <v>3.3277665819098632e-06</v>
       </c>
       <c r="D2">
-        <v>-3.6262271155531198e-08</v>
+        <v>-3.6256238193580023e-08</v>
       </c>
       <c r="E2">
-        <v>7.8876387254454837e-06</v>
+        <v>7.875786342117136e-06</v>
       </c>
       <c r="F2">
-        <v>4.8225913342166112e-06</v>
+        <v>4.8534740498705207e-06</v>
       </c>
       <c r="G2">
-        <v>-1.721906801668218e-07</v>
+        <v>-1.7180921914963914e-07</v>
       </c>
       <c r="H2">
-        <v>-1.1251897676673943e-07</v>
+        <v>-1.1299430830558791e-07</v>
       </c>
       <c r="I2">
-        <v>1.2333236412625038e-06</v>
+        <v>1.2203749245586736e-06</v>
       </c>
       <c r="J2">
-        <v>2.2665815362355675e-06</v>
+        <v>2.2620517313749093e-06</v>
       </c>
       <c r="K2">
-        <v>2.7258112901682537e-06</v>
+        <v>2.7175649982540268e-06</v>
       </c>
       <c r="L2">
-        <v>3.7322547528325326e-06</v>
+        <v>3.7270443275845188e-06</v>
       </c>
       <c r="M2">
-        <v>1.4041082979469972e-07</v>
+        <v>1.3242427099082017e-07</v>
       </c>
       <c r="N2">
-        <v>4.380868490048439e-08</v>
+        <v>3.4021699186380314e-08</v>
       </c>
       <c r="O2">
-        <v>4.4122284688709487e-08</v>
+        <v>4.1199629221796811e-08</v>
       </c>
       <c r="P2">
-        <v>2.3827625833281059e-07</v>
+        <v>2.3503751258158647e-07</v>
       </c>
       <c r="Q2">
-        <v>-2.99062881405449e-07</v>
+        <v>-3.0315349501780647e-07</v>
       </c>
       <c r="R2">
-        <v>-1.7545300850464649e-07</v>
+        <v>-1.8448597074994997e-07</v>
       </c>
       <c r="S2">
-        <v>6.3831462097915736e-07</v>
+        <v>6.1317041227937914e-07</v>
       </c>
       <c r="T2">
-        <v>9.2347866611862261e-08</v>
+        <v>9.1433302351410934e-08</v>
       </c>
       <c r="U2">
-        <v>-4.4559128900166206e-07</v>
+        <v>-4.4187157155297356e-07</v>
       </c>
       <c r="V2">
-        <v>-3.4696848245923081e-07</v>
+        <v>-3.4007625083862886e-07</v>
       </c>
       <c r="W2">
-        <v>-8.6135704860567633e-05</v>
+        <v>-8.6040988374671139e-05</v>
       </c>
       <c r="X2">
-        <v>6.7069195917287852e-06</v>
+        <v>6.6983336736830681e-06</v>
       </c>
     </row>
     <row r="3">
@@ -2169,73 +2169,73 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>-0.00012672132021444428</v>
+        <v>-0.00012600871232662779</v>
       </c>
       <c r="C3">
-        <v>-3.6262271155531198e-08</v>
+        <v>-3.6256238193580023e-08</v>
       </c>
       <c r="D3">
-        <v>4.1204813477196182e-10</v>
+        <v>4.1194770910693481e-10</v>
       </c>
       <c r="E3">
-        <v>-2.2517946028243797e-08</v>
+        <v>-2.234287455343257e-08</v>
       </c>
       <c r="F3">
-        <v>1.2678412889262683e-08</v>
+        <v>1.2358769660655425e-08</v>
       </c>
       <c r="G3">
-        <v>4.5724150215993446e-10</v>
+        <v>4.5212494381047084e-10</v>
       </c>
       <c r="H3">
-        <v>-2.2399023302630454e-10</v>
+        <v>-2.1924705357031688e-10</v>
       </c>
       <c r="I3">
-        <v>-1.4721713719761832e-08</v>
+        <v>-1.4574497861450604e-08</v>
       </c>
       <c r="J3">
-        <v>-2.5881535583296474e-08</v>
+        <v>-2.583116851997405e-08</v>
       </c>
       <c r="K3">
-        <v>-2.898552477092516e-08</v>
+        <v>-2.8891118858202746e-08</v>
       </c>
       <c r="L3">
-        <v>-3.6752763542972027e-08</v>
+        <v>-3.6687367601419436e-08</v>
       </c>
       <c r="M3">
-        <v>-1.4335994195424684e-09</v>
+        <v>-1.3532631099741185e-09</v>
       </c>
       <c r="N3">
-        <v>-1.8337673303141687e-10</v>
+        <v>-7.7216328031094901e-11</v>
       </c>
       <c r="O3">
-        <v>-2.9514634650504945e-10</v>
+        <v>-2.5703214701683863e-10</v>
       </c>
       <c r="P3">
-        <v>-2.5128847962562099e-09</v>
+        <v>-2.4720971613208312e-09</v>
       </c>
       <c r="Q3">
-        <v>3.3443603061827796e-09</v>
+        <v>3.3912251853804481e-09</v>
       </c>
       <c r="R3">
-        <v>1.7804072977194792e-09</v>
+        <v>1.8702353340994968e-09</v>
       </c>
       <c r="S3">
-        <v>-6.5396647830094919e-09</v>
+        <v>-6.3034527205006183e-09</v>
       </c>
       <c r="T3">
-        <v>-1.318850483344708e-09</v>
+        <v>-1.3088361037032431e-09</v>
       </c>
       <c r="U3">
-        <v>5.5683694421109859e-09</v>
+        <v>5.5271120990364915e-09</v>
       </c>
       <c r="V3">
-        <v>4.4451197735316568e-09</v>
+        <v>4.3634231168503242e-09</v>
       </c>
       <c r="W3">
-        <v>9.337960431079408e-07</v>
+        <v>9.32666134507562e-07</v>
       </c>
       <c r="X3">
-        <v>-7.6213490241779506e-08</v>
+        <v>-7.6102452998463248e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2243,73 +2243,73 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>0.038448889080366908</v>
+        <v>0.038660361325360354</v>
       </c>
       <c r="C4">
-        <v>7.8876387254454837e-06</v>
+        <v>7.875786342117136e-06</v>
       </c>
       <c r="D4">
-        <v>-2.2517946028243797e-08</v>
+        <v>-2.234287455343257e-08</v>
       </c>
       <c r="E4">
-        <v>0.00068956939451041556</v>
+        <v>0.00068982719809837023</v>
       </c>
       <c r="F4">
-        <v>0.00028330989048693097</v>
+        <v>0.00028344086101974816</v>
       </c>
       <c r="G4">
-        <v>-1.4536450294102679e-05</v>
+        <v>-1.4541058849345792e-05</v>
       </c>
       <c r="H4">
-        <v>-5.9623228648482768e-06</v>
+        <v>-5.9654160450793485e-06</v>
       </c>
       <c r="I4">
-        <v>2.41022682042803e-06</v>
+        <v>2.4283288153532044e-06</v>
       </c>
       <c r="J4">
-        <v>-7.6065349548365968e-07</v>
+        <v>-7.3721318382573883e-07</v>
       </c>
       <c r="K4">
-        <v>-3.218915130107781e-06</v>
+        <v>-3.1650487660597686e-06</v>
       </c>
       <c r="L4">
-        <v>-1.5005007366577838e-06</v>
+        <v>-1.4237940591402796e-06</v>
       </c>
       <c r="M4">
-        <v>1.7127143869271695e-06</v>
+        <v>1.6622575011406164e-06</v>
       </c>
       <c r="N4">
-        <v>2.4120803576117145e-06</v>
+        <v>2.4425170728605643e-06</v>
       </c>
       <c r="O4">
-        <v>7.6900538884351821e-07</v>
+        <v>7.8399950842260416e-07</v>
       </c>
       <c r="P4">
-        <v>1.3072263182490793e-06</v>
+        <v>1.3397666519991191e-06</v>
       </c>
       <c r="Q4">
-        <v>-1.0766089063389579e-06</v>
+        <v>-1.0432476651663814e-06</v>
       </c>
       <c r="R4">
-        <v>-3.8249167689963524e-06</v>
+        <v>-3.799292902340429e-06</v>
       </c>
       <c r="S4">
-        <v>-6.1745447681902818e-07</v>
+        <v>-6.9751214761713487e-07</v>
       </c>
       <c r="T4">
-        <v>5.8779696145160811e-07</v>
+        <v>5.9091881038287369e-07</v>
       </c>
       <c r="U4">
-        <v>-2.0959982591894199e-06</v>
+        <v>-2.1304495827494137e-06</v>
       </c>
       <c r="V4">
-        <v>-1.1654882370044985e-06</v>
+        <v>-1.1562106075093108e-06</v>
       </c>
       <c r="W4">
-        <v>-0.00037464939001333083</v>
+        <v>-0.00037489637493388938</v>
       </c>
       <c r="X4">
-        <v>-1.035688868389197e-05</v>
+        <v>-1.0243959403182706e-05</v>
       </c>
     </row>
     <row r="5">
@@ -2317,73 +2317,73 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>0.03356211294832457</v>
+        <v>0.033939975436265341</v>
       </c>
       <c r="C5">
-        <v>4.8225913342166112e-06</v>
+        <v>4.8534740498705207e-06</v>
       </c>
       <c r="D5">
-        <v>1.2678412889262683e-08</v>
+        <v>1.2358769660655425e-08</v>
       </c>
       <c r="E5">
-        <v>0.00028330989048693097</v>
+        <v>0.00028344086101974816</v>
       </c>
       <c r="F5">
-        <v>0.00058536503964136757</v>
+        <v>0.00058496023649203205</v>
       </c>
       <c r="G5">
-        <v>-5.9905700585669627e-06</v>
+        <v>-5.9935462054647493e-06</v>
       </c>
       <c r="H5">
-        <v>-1.2110876026805744e-05</v>
+        <v>-1.2103310159845404e-05</v>
       </c>
       <c r="I5">
-        <v>5.0664366784036076e-06</v>
+        <v>5.096622059880086e-06</v>
       </c>
       <c r="J5">
-        <v>-4.0939540307735126e-06</v>
+        <v>-4.0322910408202024e-06</v>
       </c>
       <c r="K5">
-        <v>-8.2093599110819967e-06</v>
+        <v>-8.1263037536554121e-06</v>
       </c>
       <c r="L5">
-        <v>-2.4377180695303889e-06</v>
+        <v>-2.3318770889250815e-06</v>
       </c>
       <c r="M5">
-        <v>2.5128821941412691e-06</v>
+        <v>2.4956105618682054e-06</v>
       </c>
       <c r="N5">
-        <v>3.0301203591299258e-06</v>
+        <v>3.0304882586065933e-06</v>
       </c>
       <c r="O5">
-        <v>-2.6209433696631801e-06</v>
+        <v>-2.5897387198499301e-06</v>
       </c>
       <c r="P5">
-        <v>-1.9724439576049307e-06</v>
+        <v>-1.957097597665036e-06</v>
       </c>
       <c r="Q5">
-        <v>-7.5058704414926041e-06</v>
+        <v>-7.5039176025411833e-06</v>
       </c>
       <c r="R5">
-        <v>-4.7843497757450738e-06</v>
+        <v>-4.8341476658612585e-06</v>
       </c>
       <c r="S5">
-        <v>2.6551264185437377e-06</v>
+        <v>2.4480398886233273e-06</v>
       </c>
       <c r="T5">
-        <v>8.5086434858341272e-07</v>
+        <v>8.4946513488096088e-07</v>
       </c>
       <c r="U5">
-        <v>-1.8732273009389505e-06</v>
+        <v>-1.8789024920683692e-06</v>
       </c>
       <c r="V5">
-        <v>-2.3220229144512334e-06</v>
+        <v>-2.3452097451311026e-06</v>
       </c>
       <c r="W5">
-        <v>-0.00033166157308438439</v>
+        <v>-0.00033233066122836615</v>
       </c>
       <c r="X5">
-        <v>-1.6851567021776492e-05</v>
+        <v>-1.6649078159195759e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2391,73 +2391,73 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>-0.0072963258095088803</v>
+        <v>-0.0072935981863029784</v>
       </c>
       <c r="C6">
-        <v>-1.721906801668218e-07</v>
+        <v>-1.7180921914963914e-07</v>
       </c>
       <c r="D6">
-        <v>4.5724150215993446e-10</v>
+        <v>4.5212494381047084e-10</v>
       </c>
       <c r="E6">
-        <v>-1.4536450294102679e-05</v>
+        <v>-1.4541058849345792e-05</v>
       </c>
       <c r="F6">
-        <v>-5.9905700585669627e-06</v>
+        <v>-5.9935462054647493e-06</v>
       </c>
       <c r="G6">
-        <v>3.2464608052607189e-07</v>
+        <v>3.2470821809155251e-07</v>
       </c>
       <c r="H6">
-        <v>1.333951378970521e-07</v>
+        <v>1.3345760222478075e-07</v>
       </c>
       <c r="I6">
-        <v>-7.3161196917114321e-08</v>
+        <v>-7.3316770446671278e-08</v>
       </c>
       <c r="J6">
-        <v>-1.851156588879776e-08</v>
+        <v>-1.8525171539065129e-08</v>
       </c>
       <c r="K6">
-        <v>6.8822861719614051e-08</v>
+        <v>6.8213080032162214e-08</v>
       </c>
       <c r="L6">
-        <v>4.6440395198811167e-08</v>
+        <v>4.5301713225344336e-08</v>
       </c>
       <c r="M6">
-        <v>-2.8353879337663724e-08</v>
+        <v>-2.7110784952384792e-08</v>
       </c>
       <c r="N6">
-        <v>-2.1417050174670084e-08</v>
+        <v>-2.205717658107253e-08</v>
       </c>
       <c r="O6">
-        <v>-2.8757219342061482e-08</v>
+        <v>-2.9134285916161691e-08</v>
       </c>
       <c r="P6">
-        <v>-3.2425692134887075e-08</v>
+        <v>-3.3108017086683912e-08</v>
       </c>
       <c r="Q6">
-        <v>1.2513510070548327e-08</v>
+        <v>1.1837208848915771e-08</v>
       </c>
       <c r="R6">
-        <v>7.8209858965876035e-08</v>
+        <v>7.7700586551148731e-08</v>
       </c>
       <c r="S6">
-        <v>4.9620404200772498e-08</v>
+        <v>5.1325755776148814e-08</v>
       </c>
       <c r="T6">
-        <v>-6.9565804294949885e-09</v>
+        <v>-7.0237580086676753e-09</v>
       </c>
       <c r="U6">
-        <v>1.9010334441766715e-08</v>
+        <v>1.9596915265461783e-08</v>
       </c>
       <c r="V6">
-        <v>1.6026538654936847e-08</v>
+        <v>1.5962966911549896e-08</v>
       </c>
       <c r="W6">
-        <v>7.3433440236952521e-06</v>
+        <v>7.3451955300170365e-06</v>
       </c>
       <c r="X6">
-        <v>1.8119699709677232e-07</v>
+        <v>1.8006685033436893e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2465,73 +2465,73 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>-0.010961756273961525</v>
+        <v>-0.01095751355064079</v>
       </c>
       <c r="C7">
-        <v>-1.1251897676673943e-07</v>
+        <v>-1.1299430830558791e-07</v>
       </c>
       <c r="D7">
-        <v>-2.2399023302630454e-10</v>
+        <v>-2.1924705357031688e-10</v>
       </c>
       <c r="E7">
-        <v>-5.9623228648482768e-06</v>
+        <v>-5.9654160450793485e-06</v>
       </c>
       <c r="F7">
-        <v>-1.2110876026805744e-05</v>
+        <v>-1.2103310159845404e-05</v>
       </c>
       <c r="G7">
-        <v>1.333951378970521e-07</v>
+        <v>1.3345760222478075e-07</v>
       </c>
       <c r="H7">
-        <v>2.659461947314574e-07</v>
+        <v>2.6578420359680728e-07</v>
       </c>
       <c r="I7">
-        <v>-1.3328553427478961e-07</v>
+        <v>-1.3344401242046761e-07</v>
       </c>
       <c r="J7">
-        <v>6.1434589131513894e-08</v>
+        <v>6.0807594061931456e-08</v>
       </c>
       <c r="K7">
-        <v>2.0385180899495021e-07</v>
+        <v>2.0282250668887564e-07</v>
       </c>
       <c r="L7">
-        <v>1.2010355033783214e-07</v>
+        <v>1.1848433068855169e-07</v>
       </c>
       <c r="M7">
-        <v>-2.2046817601907856e-08</v>
+        <v>-2.1522399071321141e-08</v>
       </c>
       <c r="N7">
-        <v>-5.9895431393608689e-10</v>
+        <v>-5.9105678655030301e-10</v>
       </c>
       <c r="O7">
-        <v>-7.0701380993573055e-09</v>
+        <v>-7.6899049050211708e-09</v>
       </c>
       <c r="P7">
-        <v>3.8395609796791128e-08</v>
+        <v>3.8084712323638717e-08</v>
       </c>
       <c r="Q7">
-        <v>1.0202727998399963e-07</v>
+        <v>1.0202075855837463e-07</v>
       </c>
       <c r="R7">
-        <v>9.5432132150408785e-08</v>
+        <v>9.6408748897893304e-08</v>
       </c>
       <c r="S7">
-        <v>2.166237268980406e-08</v>
+        <v>2.5866261108271413e-08</v>
       </c>
       <c r="T7">
-        <v>-3.0193255652640209e-09</v>
+        <v>-3.0063424931974649e-09</v>
       </c>
       <c r="U7">
-        <v>-7.4089991632828871e-09</v>
+        <v>-7.3738086454167161e-09</v>
       </c>
       <c r="V7">
-        <v>1.8777698169445832e-08</v>
+        <v>1.93111779765943e-08</v>
       </c>
       <c r="W7">
-        <v>5.5634150626270134e-06</v>
+        <v>5.5747967682259737e-06</v>
       </c>
       <c r="X7">
-        <v>2.0285732989710305e-07</v>
+        <v>2.0048888398869515e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2539,73 +2539,73 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>-0.10058549067353313</v>
+        <v>-0.10019180883230826</v>
       </c>
       <c r="C8">
-        <v>1.2333236412625038e-06</v>
+        <v>1.2203749245586736e-06</v>
       </c>
       <c r="D8">
-        <v>-1.4721713719761832e-08</v>
+        <v>-1.4574497861450604e-08</v>
       </c>
       <c r="E8">
-        <v>2.41022682042803e-06</v>
+        <v>2.4283288153532044e-06</v>
       </c>
       <c r="F8">
-        <v>5.0664366784036076e-06</v>
+        <v>5.096622059880086e-06</v>
       </c>
       <c r="G8">
-        <v>-7.3161196917114321e-08</v>
+        <v>-7.3316770446671278e-08</v>
       </c>
       <c r="H8">
-        <v>-1.3328553427478961e-07</v>
+        <v>-1.3344401242046761e-07</v>
       </c>
       <c r="I8">
-        <v>0.0023345892887651348</v>
+        <v>0.0023297155832861607</v>
       </c>
       <c r="J8">
-        <v>0.0019641737963285401</v>
+        <v>0.001960056336199703</v>
       </c>
       <c r="K8">
-        <v>0.0019640688149028642</v>
+        <v>0.0019599377503952721</v>
       </c>
       <c r="L8">
-        <v>0.0019634706296957219</v>
+        <v>0.0019593381035337395</v>
       </c>
       <c r="M8">
-        <v>3.2825259747920316e-06</v>
+        <v>3.2692721284208732e-06</v>
       </c>
       <c r="N8">
-        <v>2.4874756927726963e-06</v>
+        <v>2.4818213960924314e-06</v>
       </c>
       <c r="O8">
-        <v>1.1930872587068983e-06</v>
+        <v>1.1884416644066176e-06</v>
       </c>
       <c r="P8">
-        <v>2.0021600693850307e-06</v>
+        <v>1.9949937339022108e-06</v>
       </c>
       <c r="Q8">
-        <v>2.0798043023296797e-06</v>
+        <v>2.07989012295187e-06</v>
       </c>
       <c r="R8">
-        <v>2.2271271196166561e-06</v>
+        <v>2.2288861110207443e-06</v>
       </c>
       <c r="S8">
-        <v>1.1803478862580395e-06</v>
+        <v>1.1870397698440001e-06</v>
       </c>
       <c r="T8">
-        <v>2.6170602307804488e-07</v>
+        <v>2.6048587385437226e-07</v>
       </c>
       <c r="U8">
-        <v>-9.7178305191811022e-07</v>
+        <v>-9.7036558096646029e-07</v>
       </c>
       <c r="V8">
-        <v>-2.4068820777528743e-07</v>
+        <v>-2.3655314454218611e-07</v>
       </c>
       <c r="W8">
-        <v>-0.0020177277923954578</v>
+        <v>-0.0020131834897640305</v>
       </c>
       <c r="X8">
-        <v>6.8887760842260003e-06</v>
+        <v>6.7619871101391233e-06</v>
       </c>
     </row>
     <row r="9">
@@ -2613,73 +2613,73 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>-0.080096063042714508</v>
+        <v>-0.08074140497011445</v>
       </c>
       <c r="C9">
-        <v>2.2665815362355675e-06</v>
+        <v>2.2620517313749093e-06</v>
       </c>
       <c r="D9">
-        <v>-2.5881535583296474e-08</v>
+        <v>-2.583116851997405e-08</v>
       </c>
       <c r="E9">
-        <v>-7.6065349548365968e-07</v>
+        <v>-7.3721318382573883e-07</v>
       </c>
       <c r="F9">
-        <v>-4.0939540307735126e-06</v>
+        <v>-4.0322910408202024e-06</v>
       </c>
       <c r="G9">
-        <v>-1.851156588879776e-08</v>
+        <v>-1.8525171539065129e-08</v>
       </c>
       <c r="H9">
-        <v>6.1434589131513894e-08</v>
+        <v>6.0807594061931456e-08</v>
       </c>
       <c r="I9">
-        <v>0.0019641737963285401</v>
+        <v>0.001960056336199703</v>
       </c>
       <c r="J9">
-        <v>0.0020138558553832804</v>
+        <v>0.0020096877004255349</v>
       </c>
       <c r="K9">
-        <v>0.0019721317809909067</v>
+        <v>0.0019680140931073236</v>
       </c>
       <c r="L9">
-        <v>0.0019723314537297477</v>
+        <v>0.0019682108171540603</v>
       </c>
       <c r="M9">
-        <v>2.6860309871752469e-06</v>
+        <v>2.6733615820256112e-06</v>
       </c>
       <c r="N9">
-        <v>8.2129124583263951e-07</v>
+        <v>8.1265378895562124e-07</v>
       </c>
       <c r="O9">
-        <v>-9.6624730398145827e-07</v>
+        <v>-9.7308034903004958e-07</v>
       </c>
       <c r="P9">
-        <v>6.8152339478594483e-07</v>
+        <v>6.7828484908038567e-07</v>
       </c>
       <c r="Q9">
-        <v>-1.0839373045809267e-06</v>
+        <v>-1.0868131397276185e-06</v>
       </c>
       <c r="R9">
-        <v>-6.6015261868477459e-07</v>
+        <v>-6.6213701618915961e-07</v>
       </c>
       <c r="S9">
-        <v>2.1909178074049111e-07</v>
+        <v>2.1368613878028847e-07</v>
       </c>
       <c r="T9">
-        <v>2.2576538981983191e-07</v>
+        <v>2.2509655782129379e-07</v>
       </c>
       <c r="U9">
-        <v>-4.6147680511370409e-07</v>
+        <v>-4.5748136709023879e-07</v>
       </c>
       <c r="V9">
-        <v>-1.0352812569220545e-06</v>
+        <v>-1.0166493437895547e-06</v>
       </c>
       <c r="W9">
-        <v>-0.0020470076158963044</v>
+        <v>-0.0020427333724603574</v>
       </c>
       <c r="X9">
-        <v>2.2186131349639733e-05</v>
+        <v>2.210043715273794e-05</v>
       </c>
     </row>
     <row r="10">
@@ -2687,73 +2687,73 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>-0.023875208229729203</v>
+        <v>-0.024429920046577572</v>
       </c>
       <c r="C10">
-        <v>2.7258112901682537e-06</v>
+        <v>2.7175649982540268e-06</v>
       </c>
       <c r="D10">
-        <v>-2.898552477092516e-08</v>
+        <v>-2.8891118858202746e-08</v>
       </c>
       <c r="E10">
-        <v>-3.218915130107781e-06</v>
+        <v>-3.1650487660597686e-06</v>
       </c>
       <c r="F10">
-        <v>-8.2093599110819967e-06</v>
+        <v>-8.1263037536554121e-06</v>
       </c>
       <c r="G10">
-        <v>6.8822861719614051e-08</v>
+        <v>6.8213080032162214e-08</v>
       </c>
       <c r="H10">
-        <v>2.0385180899495021e-07</v>
+        <v>2.0282250668887564e-07</v>
       </c>
       <c r="I10">
-        <v>0.0019640688149028642</v>
+        <v>0.0019599377503952721</v>
       </c>
       <c r="J10">
-        <v>0.0019721317809909067</v>
+        <v>0.0019680140931073236</v>
       </c>
       <c r="K10">
-        <v>0.0019859684356466952</v>
+        <v>0.0019818228318265246</v>
       </c>
       <c r="L10">
-        <v>0.001978714297088075</v>
+        <v>0.0019745705385105592</v>
       </c>
       <c r="M10">
-        <v>2.2236406151331254e-06</v>
+        <v>2.2010263492423475e-06</v>
       </c>
       <c r="N10">
-        <v>2.2814319343545029e-07</v>
+        <v>2.2495789090421857e-07</v>
       </c>
       <c r="O10">
-        <v>-2.1056621502812261e-06</v>
+        <v>-2.1106940167920388e-06</v>
       </c>
       <c r="P10">
-        <v>3.553171303792283e-07</v>
+        <v>3.5569649405672466e-07</v>
       </c>
       <c r="Q10">
-        <v>-2.2292834289343421e-06</v>
+        <v>-2.2273139660582542e-06</v>
       </c>
       <c r="R10">
-        <v>7.9549732674391419e-07</v>
+        <v>7.9814351110590633e-07</v>
       </c>
       <c r="S10">
-        <v>2.2873187431132911e-07</v>
+        <v>2.1849314146575468e-07</v>
       </c>
       <c r="T10">
-        <v>5.24114297731499e-07</v>
+        <v>5.2168095401258857e-07</v>
       </c>
       <c r="U10">
-        <v>-2.3594303585497083e-06</v>
+        <v>-2.3423779986298857e-06</v>
       </c>
       <c r="V10">
-        <v>-1.4475734578342303e-06</v>
+        <v>-1.4176485901720909e-06</v>
       </c>
       <c r="W10">
-        <v>-0.0020984949640080559</v>
+        <v>-0.0020939486593126566</v>
       </c>
       <c r="X10">
-        <v>2.8872792830923177e-05</v>
+        <v>2.8748539147132294e-05</v>
       </c>
     </row>
     <row r="11">
@@ -2761,73 +2761,73 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>0.018179892873423975</v>
+        <v>0.01724943002914011</v>
       </c>
       <c r="C11">
-        <v>3.7322547528325326e-06</v>
+        <v>3.7270443275845188e-06</v>
       </c>
       <c r="D11">
-        <v>-3.6752763542972027e-08</v>
+        <v>-3.6687367601419436e-08</v>
       </c>
       <c r="E11">
-        <v>-1.5005007366577838e-06</v>
+        <v>-1.4237940591402796e-06</v>
       </c>
       <c r="F11">
-        <v>-2.4377180695303889e-06</v>
+        <v>-2.3318770889250815e-06</v>
       </c>
       <c r="G11">
-        <v>4.6440395198811167e-08</v>
+        <v>4.5301713225344336e-08</v>
       </c>
       <c r="H11">
-        <v>1.2010355033783214e-07</v>
+        <v>1.1848433068855169e-07</v>
       </c>
       <c r="I11">
-        <v>0.0019634706296957219</v>
+        <v>0.0019593381035337395</v>
       </c>
       <c r="J11">
-        <v>0.0019723314537297477</v>
+        <v>0.0019682108171540603</v>
       </c>
       <c r="K11">
-        <v>0.001978714297088075</v>
+        <v>0.0019745705385105592</v>
       </c>
       <c r="L11">
-        <v>0.0020118803083875492</v>
+        <v>0.0020077188952238997</v>
       </c>
       <c r="M11">
-        <v>1.0381286348901247e-06</v>
+        <v>1.0087831413556252e-06</v>
       </c>
       <c r="N11">
-        <v>-1.4740194276012787e-06</v>
+        <v>-1.4988509929777088e-06</v>
       </c>
       <c r="O11">
-        <v>-2.4543342064783845e-06</v>
+        <v>-2.458394498269031e-06</v>
       </c>
       <c r="P11">
-        <v>-2.0935206828177745e-06</v>
+        <v>-2.0954335635347651e-06</v>
       </c>
       <c r="Q11">
-        <v>-4.3514767903426905e-06</v>
+        <v>-4.3517848067245034e-06</v>
       </c>
       <c r="R11">
-        <v>-2.3173572496350908e-06</v>
+        <v>-2.3352127729077371e-06</v>
       </c>
       <c r="S11">
-        <v>-3.4224784417662871e-07</v>
+        <v>-3.6078984385276784e-07</v>
       </c>
       <c r="T11">
-        <v>6.9030153453445602e-07</v>
+        <v>6.8587446402941553e-07</v>
       </c>
       <c r="U11">
-        <v>-3.5735310416959659e-06</v>
+        <v>-3.5588441295212184e-06</v>
       </c>
       <c r="V11">
-        <v>-2.5430432574825612e-06</v>
+        <v>-2.5155064773176471e-06</v>
       </c>
       <c r="W11">
-        <v>-0.0021453854904648724</v>
+        <v>-0.002140701991227041</v>
       </c>
       <c r="X11">
-        <v>2.9927801989330906e-05</v>
+        <v>2.9801435083563976e-05</v>
       </c>
     </row>
     <row r="12">
@@ -2835,73 +2835,73 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>0.16365800758800902</v>
+        <v>0.16290315058061611</v>
       </c>
       <c r="C12">
-        <v>1.4041082979469972e-07</v>
+        <v>1.3242427099082017e-07</v>
       </c>
       <c r="D12">
-        <v>-1.4335994195424684e-09</v>
+        <v>-1.3532631099741185e-09</v>
       </c>
       <c r="E12">
-        <v>1.7127143869271695e-06</v>
+        <v>1.6622575011406164e-06</v>
       </c>
       <c r="F12">
-        <v>2.5128821941412691e-06</v>
+        <v>2.4956105618682054e-06</v>
       </c>
       <c r="G12">
-        <v>-2.8353879337663724e-08</v>
+        <v>-2.7110784952384792e-08</v>
       </c>
       <c r="H12">
-        <v>-2.2046817601907856e-08</v>
+        <v>-2.1522399071321141e-08</v>
       </c>
       <c r="I12">
-        <v>3.2825259747920316e-06</v>
+        <v>3.2692721284208732e-06</v>
       </c>
       <c r="J12">
-        <v>2.6860309871752469e-06</v>
+        <v>2.6733615820256112e-06</v>
       </c>
       <c r="K12">
-        <v>2.2236406151331254e-06</v>
+        <v>2.2010263492423475e-06</v>
       </c>
       <c r="L12">
-        <v>1.0381286348901247e-06</v>
+        <v>1.0087831413556252e-06</v>
       </c>
       <c r="M12">
-        <v>8.3204938489662921e-05</v>
+        <v>8.3124959602675369e-05</v>
       </c>
       <c r="N12">
-        <v>4.7316968276197888e-05</v>
+        <v>4.7258761605229485e-05</v>
       </c>
       <c r="O12">
-        <v>4.6884944178442028e-05</v>
+        <v>4.6826236079568155e-05</v>
       </c>
       <c r="P12">
-        <v>4.7176437306905528e-05</v>
+        <v>4.7117153017484883e-05</v>
       </c>
       <c r="Q12">
-        <v>4.6846647944421673e-05</v>
+        <v>4.6790044751384948e-05</v>
       </c>
       <c r="R12">
-        <v>4.6922506101528113e-05</v>
+        <v>4.6867071854580429e-05</v>
       </c>
       <c r="S12">
-        <v>3.7665197011923627e-07</v>
+        <v>4.0542036354900724e-07</v>
       </c>
       <c r="T12">
-        <v>1.7276710674373856e-07</v>
+        <v>1.7193558736642124e-07</v>
       </c>
       <c r="U12">
-        <v>3.139075213811659e-08</v>
+        <v>1.914741126104333e-08</v>
       </c>
       <c r="V12">
-        <v>-3.7746945115730733e-07</v>
+        <v>-3.7963872752715711e-07</v>
       </c>
       <c r="W12">
-        <v>-7.1134568991818329e-05</v>
+        <v>-7.0775073589259712e-05</v>
       </c>
       <c r="X12">
-        <v>2.0739626442682634e-06</v>
+        <v>2.0218881463061296e-06</v>
       </c>
     </row>
     <row r="13">
@@ -2909,73 +2909,73 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>0.15557706192950091</v>
+        <v>0.15484906137823834</v>
       </c>
       <c r="C13">
-        <v>4.380868490048439e-08</v>
+        <v>3.4021699186380314e-08</v>
       </c>
       <c r="D13">
-        <v>-1.8337673303141687e-10</v>
+        <v>-7.7216328031094901e-11</v>
       </c>
       <c r="E13">
-        <v>2.4120803576117145e-06</v>
+        <v>2.4425170728605643e-06</v>
       </c>
       <c r="F13">
-        <v>3.0301203591299258e-06</v>
+        <v>3.0304882586065933e-06</v>
       </c>
       <c r="G13">
-        <v>-2.1417050174670084e-08</v>
+        <v>-2.205717658107253e-08</v>
       </c>
       <c r="H13">
-        <v>-5.9895431393608689e-10</v>
+        <v>-5.9105678655030301e-10</v>
       </c>
       <c r="I13">
-        <v>2.4874756927726963e-06</v>
+        <v>2.4818213960924314e-06</v>
       </c>
       <c r="J13">
-        <v>8.2129124583263951e-07</v>
+        <v>8.1265378895562124e-07</v>
       </c>
       <c r="K13">
-        <v>2.2814319343545029e-07</v>
+        <v>2.2495789090421857e-07</v>
       </c>
       <c r="L13">
-        <v>-1.4740194276012787e-06</v>
+        <v>-1.4988509929777088e-06</v>
       </c>
       <c r="M13">
-        <v>4.7316968276197888e-05</v>
+        <v>4.7258761605229485e-05</v>
       </c>
       <c r="N13">
-        <v>0.00010108394079083829</v>
+        <v>0.00010100591844615261</v>
       </c>
       <c r="O13">
-        <v>4.6825807754023282e-05</v>
+        <v>4.6767136016781004e-05</v>
       </c>
       <c r="P13">
-        <v>4.7266918584361561e-05</v>
+        <v>4.7208847230968127e-05</v>
       </c>
       <c r="Q13">
-        <v>4.6938619103807022e-05</v>
+        <v>4.6881133585329607e-05</v>
       </c>
       <c r="R13">
-        <v>4.7084381253587998e-05</v>
+        <v>4.7027528479085853e-05</v>
       </c>
       <c r="S13">
-        <v>4.3496486255882944e-07</v>
+        <v>4.5824050726587156e-07</v>
       </c>
       <c r="T13">
-        <v>-1.7895408280841728e-07</v>
+        <v>-1.7879651922193223e-07</v>
       </c>
       <c r="U13">
-        <v>9.9631696083391135e-07</v>
+        <v>9.9331761643290248e-07</v>
       </c>
       <c r="V13">
-        <v>-3.6088785329453103e-07</v>
+        <v>-3.5156385181820259e-07</v>
       </c>
       <c r="W13">
-        <v>-3.2179817211009222e-05</v>
+        <v>-3.1913844089469088e-05</v>
       </c>
       <c r="X13">
-        <v>6.6739022485783718e-08</v>
+        <v>4.2377151779158134e-08</v>
       </c>
     </row>
     <row r="14">
@@ -2983,73 +2983,73 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>-0.040197828195555833</v>
+        <v>-0.040375423515322743</v>
       </c>
       <c r="C14">
-        <v>4.4122284688709487e-08</v>
+        <v>4.1199629221796811e-08</v>
       </c>
       <c r="D14">
-        <v>-2.9514634650504945e-10</v>
+        <v>-2.5703214701683863e-10</v>
       </c>
       <c r="E14">
-        <v>7.6900538884351821e-07</v>
+        <v>7.8399950842260416e-07</v>
       </c>
       <c r="F14">
-        <v>-2.6209433696631801e-06</v>
+        <v>-2.5897387198499301e-06</v>
       </c>
       <c r="G14">
-        <v>-2.8757219342061482e-08</v>
+        <v>-2.9134285916161691e-08</v>
       </c>
       <c r="H14">
-        <v>-7.0701380993573055e-09</v>
+        <v>-7.6899049050211708e-09</v>
       </c>
       <c r="I14">
-        <v>1.1930872587068983e-06</v>
+        <v>1.1884416644066176e-06</v>
       </c>
       <c r="J14">
-        <v>-9.6624730398145827e-07</v>
+        <v>-9.7308034903004958e-07</v>
       </c>
       <c r="K14">
-        <v>-2.1056621502812261e-06</v>
+        <v>-2.1106940167920388e-06</v>
       </c>
       <c r="L14">
-        <v>-2.4543342064783845e-06</v>
+        <v>-2.458394498269031e-06</v>
       </c>
       <c r="M14">
-        <v>4.6884944178442028e-05</v>
+        <v>4.6826236079568155e-05</v>
       </c>
       <c r="N14">
-        <v>4.6825807754023282e-05</v>
+        <v>4.6767136016781004e-05</v>
       </c>
       <c r="O14">
-        <v>8.51416296336889e-05</v>
+        <v>8.5043527142738835e-05</v>
       </c>
       <c r="P14">
-        <v>4.7089110981367829e-05</v>
+        <v>4.7029972791636713e-05</v>
       </c>
       <c r="Q14">
-        <v>4.7437548052888804e-05</v>
+        <v>4.7379476932489482e-05</v>
       </c>
       <c r="R14">
-        <v>4.7162560233743226e-05</v>
+        <v>4.7104389952101061e-05</v>
       </c>
       <c r="S14">
-        <v>-3.8558696130886547e-07</v>
+        <v>-3.8688400766176488e-07</v>
       </c>
       <c r="T14">
-        <v>-9.078536228236172e-08</v>
+        <v>-9.0976459154106532e-08</v>
       </c>
       <c r="U14">
-        <v>-1.275282769523594e-07</v>
+        <v>-1.3971537334794349e-07</v>
       </c>
       <c r="V14">
-        <v>-2.3709729775831237e-08</v>
+        <v>-2.6172274466155383e-08</v>
       </c>
       <c r="W14">
-        <v>-3.5990810904028854e-05</v>
+        <v>-3.5852411591505495e-05</v>
       </c>
       <c r="X14">
-        <v>-4.511587874639927e-07</v>
+        <v>-4.6712552284808283e-07</v>
       </c>
     </row>
     <row r="15">
@@ -3057,73 +3057,73 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>0.1007388342949881</v>
+        <v>0.10020598553399319</v>
       </c>
       <c r="C15">
-        <v>2.3827625833281059e-07</v>
+        <v>2.3503751258158647e-07</v>
       </c>
       <c r="D15">
-        <v>-2.5128847962562099e-09</v>
+        <v>-2.4720971613208312e-09</v>
       </c>
       <c r="E15">
-        <v>1.3072263182490793e-06</v>
+        <v>1.3397666519991191e-06</v>
       </c>
       <c r="F15">
-        <v>-1.9724439576049307e-06</v>
+        <v>-1.957097597665036e-06</v>
       </c>
       <c r="G15">
-        <v>-3.2425692134887075e-08</v>
+        <v>-3.3108017086683912e-08</v>
       </c>
       <c r="H15">
-        <v>3.8395609796791128e-08</v>
+        <v>3.8084712323638717e-08</v>
       </c>
       <c r="I15">
-        <v>2.0021600693850307e-06</v>
+        <v>1.9949937339022108e-06</v>
       </c>
       <c r="J15">
-        <v>6.8152339478594483e-07</v>
+        <v>6.7828484908038567e-07</v>
       </c>
       <c r="K15">
-        <v>3.553171303792283e-07</v>
+        <v>3.5569649405672466e-07</v>
       </c>
       <c r="L15">
-        <v>-2.0935206828177745e-06</v>
+        <v>-2.0954335635347651e-06</v>
       </c>
       <c r="M15">
-        <v>4.7176437306905528e-05</v>
+        <v>4.7117153017484883e-05</v>
       </c>
       <c r="N15">
-        <v>4.7266918584361561e-05</v>
+        <v>4.7208847230968127e-05</v>
       </c>
       <c r="O15">
-        <v>4.7089110981367829e-05</v>
+        <v>4.7029972791636713e-05</v>
       </c>
       <c r="P15">
-        <v>7.0976359353320517e-05</v>
+        <v>7.0895258158684877e-05</v>
       </c>
       <c r="Q15">
-        <v>4.7242990058070845e-05</v>
+        <v>4.7183947289028346e-05</v>
       </c>
       <c r="R15">
-        <v>4.7220256880313026e-05</v>
+        <v>4.7162486984871733e-05</v>
       </c>
       <c r="S15">
-        <v>2.8194387418862452e-07</v>
+        <v>2.8359655300270586e-07</v>
       </c>
       <c r="T15">
-        <v>-5.124505496224439e-07</v>
+        <v>-5.1135723925139545e-07</v>
       </c>
       <c r="U15">
-        <v>3.7968176110638784e-06</v>
+        <v>3.7791539272654555e-06</v>
       </c>
       <c r="V15">
-        <v>3.309427656934714e-06</v>
+        <v>3.3033793173223865e-06</v>
       </c>
       <c r="W15">
-        <v>-1.340213646973437e-06</v>
+        <v>-1.3320146414675573e-06</v>
       </c>
       <c r="X15">
-        <v>1.0580653316468206e-06</v>
+        <v>1.0526112198095969e-06</v>
       </c>
     </row>
     <row r="16">
@@ -3131,73 +3131,73 @@
         <v>37</v>
       </c>
       <c r="B16">
-        <v>0.0092736149766526437</v>
+        <v>0.008462760982044109</v>
       </c>
       <c r="C16">
-        <v>-2.99062881405449e-07</v>
+        <v>-3.0315349501780647e-07</v>
       </c>
       <c r="D16">
-        <v>3.3443603061827796e-09</v>
+        <v>3.3912251853804481e-09</v>
       </c>
       <c r="E16">
-        <v>-1.0766089063389579e-06</v>
+        <v>-1.0432476651663814e-06</v>
       </c>
       <c r="F16">
-        <v>-7.5058704414926041e-06</v>
+        <v>-7.5039176025411833e-06</v>
       </c>
       <c r="G16">
-        <v>1.2513510070548327e-08</v>
+        <v>1.1837208848915771e-08</v>
       </c>
       <c r="H16">
-        <v>1.0202727998399963e-07</v>
+        <v>1.0202075855837463e-07</v>
       </c>
       <c r="I16">
-        <v>2.0798043023296797e-06</v>
+        <v>2.07989012295187e-06</v>
       </c>
       <c r="J16">
-        <v>-1.0839373045809267e-06</v>
+        <v>-1.0868131397276185e-06</v>
       </c>
       <c r="K16">
-        <v>-2.2292834289343421e-06</v>
+        <v>-2.2273139660582542e-06</v>
       </c>
       <c r="L16">
-        <v>-4.3514767903426905e-06</v>
+        <v>-4.3517848067245034e-06</v>
       </c>
       <c r="M16">
-        <v>4.6846647944421673e-05</v>
+        <v>4.6790044751384948e-05</v>
       </c>
       <c r="N16">
-        <v>4.6938619103807022e-05</v>
+        <v>4.6881133585329607e-05</v>
       </c>
       <c r="O16">
-        <v>4.7437548052888804e-05</v>
+        <v>4.7379476932489482e-05</v>
       </c>
       <c r="P16">
-        <v>4.7242990058070845e-05</v>
+        <v>4.7183947289028346e-05</v>
       </c>
       <c r="Q16">
-        <v>8.2301326942635627e-05</v>
+        <v>8.2210000132421188e-05</v>
       </c>
       <c r="R16">
-        <v>4.7564827657778204e-05</v>
+        <v>4.7507186944180965e-05</v>
       </c>
       <c r="S16">
-        <v>-9.2991343076317298e-07</v>
+        <v>-9.1827990817003183e-07</v>
       </c>
       <c r="T16">
-        <v>-2.4670300268298013e-07</v>
+        <v>-2.4472671988733706e-07</v>
       </c>
       <c r="U16">
-        <v>1.0448503742937948e-06</v>
+        <v>1.0244605103029822e-06</v>
       </c>
       <c r="V16">
-        <v>7.8771671293451827e-07</v>
+        <v>7.8442128306490154e-07</v>
       </c>
       <c r="W16">
-        <v>-1.1638070097909952e-05</v>
+        <v>-1.1693876973018769e-05</v>
       </c>
       <c r="X16">
-        <v>-2.8664403560488243e-06</v>
+        <v>-2.8739416513452563e-06</v>
       </c>
     </row>
     <row r="17">
@@ -3205,73 +3205,73 @@
         <v>38</v>
       </c>
       <c r="B17">
-        <v>-0.051315773389335059</v>
+        <v>-0.051568170884711495</v>
       </c>
       <c r="C17">
-        <v>-1.7545300850464649e-07</v>
+        <v>-1.8448597074994997e-07</v>
       </c>
       <c r="D17">
-        <v>1.7804072977194792e-09</v>
+        <v>1.8702353340994968e-09</v>
       </c>
       <c r="E17">
-        <v>-3.8249167689963524e-06</v>
+        <v>-3.799292902340429e-06</v>
       </c>
       <c r="F17">
-        <v>-4.7843497757450738e-06</v>
+        <v>-4.8341476658612585e-06</v>
       </c>
       <c r="G17">
-        <v>7.8209858965876035e-08</v>
+        <v>7.7700586551148731e-08</v>
       </c>
       <c r="H17">
-        <v>9.5432132150408785e-08</v>
+        <v>9.6408748897893304e-08</v>
       </c>
       <c r="I17">
-        <v>2.2271271196166561e-06</v>
+        <v>2.2288861110207443e-06</v>
       </c>
       <c r="J17">
-        <v>-6.6015261868477459e-07</v>
+        <v>-6.6213701618915961e-07</v>
       </c>
       <c r="K17">
-        <v>7.9549732674391419e-07</v>
+        <v>7.9814351110590633e-07</v>
       </c>
       <c r="L17">
-        <v>-2.3173572496350908e-06</v>
+        <v>-2.3352127729077371e-06</v>
       </c>
       <c r="M17">
-        <v>4.6922506101528113e-05</v>
+        <v>4.6867071854580429e-05</v>
       </c>
       <c r="N17">
-        <v>4.7084381253587998e-05</v>
+        <v>4.7027528479085853e-05</v>
       </c>
       <c r="O17">
-        <v>4.7162560233743226e-05</v>
+        <v>4.7104389952101061e-05</v>
       </c>
       <c r="P17">
-        <v>4.7220256880313026e-05</v>
+        <v>4.7162486984871733e-05</v>
       </c>
       <c r="Q17">
-        <v>4.7564827657778204e-05</v>
+        <v>4.7507186944180965e-05</v>
       </c>
       <c r="R17">
-        <v>0.00023219852991016572</v>
+        <v>0.00023200266279684964</v>
       </c>
       <c r="S17">
-        <v>-6.0215449896334543e-07</v>
+        <v>-5.6931076792342789e-07</v>
       </c>
       <c r="T17">
-        <v>8.6609719655588869e-08</v>
+        <v>8.659504018323991e-08</v>
       </c>
       <c r="U17">
-        <v>1.1295128361037212e-06</v>
+        <v>1.1654848915569879e-06</v>
       </c>
       <c r="V17">
-        <v>8.3451214705338291e-07</v>
+        <v>8.3226423290220244e-07</v>
       </c>
       <c r="W17">
-        <v>-5.0555335630387713e-05</v>
+        <v>-5.0281507677801282e-05</v>
       </c>
       <c r="X17">
-        <v>-3.9298627327537028e-06</v>
+        <v>-3.931225077069045e-06</v>
       </c>
     </row>
     <row r="18">
@@ -3279,73 +3279,73 @@
         <v>39</v>
       </c>
       <c r="B18">
-        <v>0.11249909852080556</v>
+        <v>0.11249730582362745</v>
       </c>
       <c r="C18">
-        <v>6.3831462097915736e-07</v>
+        <v>6.1317041227937914e-07</v>
       </c>
       <c r="D18">
-        <v>-6.5396647830094919e-09</v>
+        <v>-6.3034527205006183e-09</v>
       </c>
       <c r="E18">
-        <v>-6.1745447681902818e-07</v>
+        <v>-6.9751214761713487e-07</v>
       </c>
       <c r="F18">
-        <v>2.6551264185437377e-06</v>
+        <v>2.4480398886233273e-06</v>
       </c>
       <c r="G18">
-        <v>4.9620404200772498e-08</v>
+        <v>5.1325755776148814e-08</v>
       </c>
       <c r="H18">
-        <v>2.166237268980406e-08</v>
+        <v>2.5866261108271413e-08</v>
       </c>
       <c r="I18">
-        <v>1.1803478862580395e-06</v>
+        <v>1.1870397698440001e-06</v>
       </c>
       <c r="J18">
-        <v>2.1909178074049111e-07</v>
+        <v>2.1368613878028847e-07</v>
       </c>
       <c r="K18">
-        <v>2.2873187431132911e-07</v>
+        <v>2.1849314146575468e-07</v>
       </c>
       <c r="L18">
-        <v>-3.4224784417662871e-07</v>
+        <v>-3.6078984385276784e-07</v>
       </c>
       <c r="M18">
-        <v>3.7665197011923627e-07</v>
+        <v>4.0542036354900724e-07</v>
       </c>
       <c r="N18">
-        <v>4.3496486255882944e-07</v>
+        <v>4.5824050726587156e-07</v>
       </c>
       <c r="O18">
-        <v>-3.8558696130886547e-07</v>
+        <v>-3.8688400766176488e-07</v>
       </c>
       <c r="P18">
-        <v>2.8194387418862452e-07</v>
+        <v>2.8359655300270586e-07</v>
       </c>
       <c r="Q18">
-        <v>-9.2991343076317298e-07</v>
+        <v>-9.1827990817003183e-07</v>
       </c>
       <c r="R18">
-        <v>-6.0215449896334543e-07</v>
+        <v>-5.6931076792342789e-07</v>
       </c>
       <c r="S18">
-        <v>5.6055650708995507e-05</v>
+        <v>5.6127519183614449e-05</v>
       </c>
       <c r="T18">
-        <v>-1.3392042174056749e-07</v>
+        <v>-1.3559268288564981e-07</v>
       </c>
       <c r="U18">
-        <v>1.1238324281131318e-07</v>
+        <v>1.0697337946205363e-07</v>
       </c>
       <c r="V18">
-        <v>-7.3402692833243432e-07</v>
+        <v>-7.3195359925038322e-07</v>
       </c>
       <c r="W18">
-        <v>-7.5158473762935867e-06</v>
+        <v>-6.678726684464545e-06</v>
       </c>
       <c r="X18">
-        <v>-6.1795548449070217e-06</v>
+        <v>-6.2478278667181685e-06</v>
       </c>
     </row>
     <row r="19">
@@ -3353,73 +3353,73 @@
         <v>40</v>
       </c>
       <c r="B19">
-        <v>0.0030025822199691017</v>
+        <v>0.0029492079007361451</v>
       </c>
       <c r="C19">
-        <v>9.2347866611862261e-08</v>
+        <v>9.1433302351410934e-08</v>
       </c>
       <c r="D19">
-        <v>-1.318850483344708e-09</v>
+        <v>-1.3088361037032431e-09</v>
       </c>
       <c r="E19">
-        <v>5.8779696145160811e-07</v>
+        <v>5.9091881038287369e-07</v>
       </c>
       <c r="F19">
-        <v>8.5086434858341272e-07</v>
+        <v>8.4946513488096088e-07</v>
       </c>
       <c r="G19">
-        <v>-6.9565804294949885e-09</v>
+        <v>-7.0237580086676753e-09</v>
       </c>
       <c r="H19">
-        <v>-3.0193255652640209e-09</v>
+        <v>-3.0063424931974649e-09</v>
       </c>
       <c r="I19">
-        <v>2.6170602307804488e-07</v>
+        <v>2.6048587385437226e-07</v>
       </c>
       <c r="J19">
-        <v>2.2576538981983191e-07</v>
+        <v>2.2509655782129379e-07</v>
       </c>
       <c r="K19">
-        <v>5.24114297731499e-07</v>
+        <v>5.2168095401258857e-07</v>
       </c>
       <c r="L19">
-        <v>6.9030153453445602e-07</v>
+        <v>6.8587446402941553e-07</v>
       </c>
       <c r="M19">
-        <v>1.7276710674373856e-07</v>
+        <v>1.7193558736642124e-07</v>
       </c>
       <c r="N19">
-        <v>-1.7895408280841728e-07</v>
+        <v>-1.7879651922193223e-07</v>
       </c>
       <c r="O19">
-        <v>-9.078536228236172e-08</v>
+        <v>-9.0976459154106532e-08</v>
       </c>
       <c r="P19">
-        <v>-5.124505496224439e-07</v>
+        <v>-5.1135723925139545e-07</v>
       </c>
       <c r="Q19">
-        <v>-2.4670300268298013e-07</v>
+        <v>-2.4472671988733706e-07</v>
       </c>
       <c r="R19">
-        <v>8.6609719655588869e-08</v>
+        <v>8.659504018323991e-08</v>
       </c>
       <c r="S19">
-        <v>-1.3392042174056749e-07</v>
+        <v>-1.3559268288564981e-07</v>
       </c>
       <c r="T19">
-        <v>2.6825903495362383e-06</v>
+        <v>2.6789831622114565e-06</v>
       </c>
       <c r="U19">
-        <v>-9.8491095138724426e-06</v>
+        <v>-9.8354292181449076e-06</v>
       </c>
       <c r="V19">
-        <v>-1.0019804652105466e-05</v>
+        <v>-1.0005552327941355e-05</v>
       </c>
       <c r="W19">
-        <v>-0.00027211715918463292</v>
+        <v>-0.00027173172787541743</v>
       </c>
       <c r="X19">
-        <v>2.2624288011360063e-07</v>
+        <v>2.2400293937615162e-07</v>
       </c>
     </row>
     <row r="20">
@@ -3427,73 +3427,73 @@
         <v>41</v>
       </c>
       <c r="B20">
-        <v>-0.074508971438190949</v>
+        <v>-0.073774301169634959</v>
       </c>
       <c r="C20">
-        <v>-4.4559128900166206e-07</v>
+        <v>-4.4187157155297356e-07</v>
       </c>
       <c r="D20">
-        <v>5.5683694421109859e-09</v>
+        <v>5.5271120990364915e-09</v>
       </c>
       <c r="E20">
-        <v>-2.0959982591894199e-06</v>
+        <v>-2.1304495827494137e-06</v>
       </c>
       <c r="F20">
-        <v>-1.8732273009389505e-06</v>
+        <v>-1.8789024920683692e-06</v>
       </c>
       <c r="G20">
-        <v>1.9010334441766715e-08</v>
+        <v>1.9596915265461783e-08</v>
       </c>
       <c r="H20">
-        <v>-7.4089991632828871e-09</v>
+        <v>-7.3738086454167161e-09</v>
       </c>
       <c r="I20">
-        <v>-9.7178305191811022e-07</v>
+        <v>-9.7036558096646029e-07</v>
       </c>
       <c r="J20">
-        <v>-4.6147680511370409e-07</v>
+        <v>-4.5748136709023879e-07</v>
       </c>
       <c r="K20">
-        <v>-2.3594303585497083e-06</v>
+        <v>-2.3423779986298857e-06</v>
       </c>
       <c r="L20">
-        <v>-3.5735310416959659e-06</v>
+        <v>-3.5588441295212184e-06</v>
       </c>
       <c r="M20">
-        <v>3.139075213811659e-08</v>
+        <v>1.914741126104333e-08</v>
       </c>
       <c r="N20">
-        <v>9.9631696083391135e-07</v>
+        <v>9.9331761643290248e-07</v>
       </c>
       <c r="O20">
-        <v>-1.275282769523594e-07</v>
+        <v>-1.3971537334794349e-07</v>
       </c>
       <c r="P20">
-        <v>3.7968176110638784e-06</v>
+        <v>3.7791539272654555e-06</v>
       </c>
       <c r="Q20">
-        <v>1.0448503742937948e-06</v>
+        <v>1.0244605103029822e-06</v>
       </c>
       <c r="R20">
-        <v>1.1295128361037212e-06</v>
+        <v>1.1654848915569879e-06</v>
       </c>
       <c r="S20">
-        <v>1.1238324281131318e-07</v>
+        <v>1.0697337946205363e-07</v>
       </c>
       <c r="T20">
-        <v>-9.8491095138724426e-06</v>
+        <v>-9.8354292181449076e-06</v>
       </c>
       <c r="U20">
-        <v>0.00014901235678002711</v>
+        <v>0.00014886853949704415</v>
       </c>
       <c r="V20">
-        <v>4.3522314412432709e-05</v>
+        <v>4.3463360599683116e-05</v>
       </c>
       <c r="W20">
-        <v>0.00099553256909250786</v>
+        <v>0.0009940786937304364</v>
       </c>
       <c r="X20">
-        <v>-8.8023992502645066e-07</v>
+        <v>-8.5955444220759953e-07</v>
       </c>
     </row>
     <row r="21">
@@ -3501,73 +3501,73 @@
         <v>42</v>
       </c>
       <c r="B21">
-        <v>-0.030273208814415358</v>
+        <v>-0.03013444172599446</v>
       </c>
       <c r="C21">
-        <v>-3.4696848245923081e-07</v>
+        <v>-3.4007625083862886e-07</v>
       </c>
       <c r="D21">
-        <v>4.4451197735316568e-09</v>
+        <v>4.3634231168503242e-09</v>
       </c>
       <c r="E21">
-        <v>-1.1654882370044985e-06</v>
+        <v>-1.1562106075093108e-06</v>
       </c>
       <c r="F21">
-        <v>-2.3220229144512334e-06</v>
+        <v>-2.3452097451311026e-06</v>
       </c>
       <c r="G21">
-        <v>1.6026538654936847e-08</v>
+        <v>1.5962966911549896e-08</v>
       </c>
       <c r="H21">
-        <v>1.8777698169445832e-08</v>
+        <v>1.93111779765943e-08</v>
       </c>
       <c r="I21">
-        <v>-2.4068820777528743e-07</v>
+        <v>-2.3655314454218611e-07</v>
       </c>
       <c r="J21">
-        <v>-1.0352812569220545e-06</v>
+        <v>-1.0166493437895547e-06</v>
       </c>
       <c r="K21">
-        <v>-1.4475734578342303e-06</v>
+        <v>-1.4176485901720909e-06</v>
       </c>
       <c r="L21">
-        <v>-2.5430432574825612e-06</v>
+        <v>-2.5155064773176471e-06</v>
       </c>
       <c r="M21">
-        <v>-3.7746945115730733e-07</v>
+        <v>-3.7963872752715711e-07</v>
       </c>
       <c r="N21">
-        <v>-3.6088785329453103e-07</v>
+        <v>-3.5156385181820259e-07</v>
       </c>
       <c r="O21">
-        <v>-2.3709729775831237e-08</v>
+        <v>-2.6172274466155383e-08</v>
       </c>
       <c r="P21">
-        <v>3.309427656934714e-06</v>
+        <v>3.3033793173223865e-06</v>
       </c>
       <c r="Q21">
-        <v>7.8771671293451827e-07</v>
+        <v>7.8442128306490154e-07</v>
       </c>
       <c r="R21">
-        <v>8.3451214705338291e-07</v>
+        <v>8.3226423290220244e-07</v>
       </c>
       <c r="S21">
-        <v>-7.3402692833243432e-07</v>
+        <v>-7.3195359925038322e-07</v>
       </c>
       <c r="T21">
-        <v>-1.0019804652105466e-05</v>
+        <v>-1.0005552327941355e-05</v>
       </c>
       <c r="U21">
-        <v>4.3522314412432709e-05</v>
+        <v>4.3463360599683116e-05</v>
       </c>
       <c r="V21">
-        <v>0.00014960385826336608</v>
+        <v>0.00014944561423280224</v>
       </c>
       <c r="W21">
-        <v>0.0010091054864431934</v>
+        <v>0.0010074962506007987</v>
       </c>
       <c r="X21">
-        <v>1.9602230418419477e-06</v>
+        <v>2.016817476566481e-06</v>
       </c>
     </row>
     <row r="22">
@@ -3575,73 +3575,73 @@
         <v>43</v>
       </c>
       <c r="B22">
-        <v>1.2202177544122985</v>
+        <v>1.2282354059708973</v>
       </c>
       <c r="C22">
-        <v>-8.6135704860567633e-05</v>
+        <v>-8.6040988374671139e-05</v>
       </c>
       <c r="D22">
-        <v>9.337960431079408e-07</v>
+        <v>9.32666134507562e-07</v>
       </c>
       <c r="E22">
-        <v>-0.00037464939001333083</v>
+        <v>-0.00037489637493388938</v>
       </c>
       <c r="F22">
-        <v>-0.00033166157308438439</v>
+        <v>-0.00033233066122836615</v>
       </c>
       <c r="G22">
-        <v>7.3433440236952521e-06</v>
+        <v>7.3451955300170365e-06</v>
       </c>
       <c r="H22">
-        <v>5.5634150626270134e-06</v>
+        <v>5.5747967682259737e-06</v>
       </c>
       <c r="I22">
-        <v>-0.0020177277923954578</v>
+        <v>-0.0020131834897640305</v>
       </c>
       <c r="J22">
-        <v>-0.0020470076158963044</v>
+        <v>-0.0020427333724603574</v>
       </c>
       <c r="K22">
-        <v>-0.0020984949640080559</v>
+        <v>-0.0020939486593126566</v>
       </c>
       <c r="L22">
-        <v>-0.0021453854904648724</v>
+        <v>-0.002140701991227041</v>
       </c>
       <c r="M22">
-        <v>-7.1134568991818329e-05</v>
+        <v>-7.0775073589259712e-05</v>
       </c>
       <c r="N22">
-        <v>-3.2179817211009222e-05</v>
+        <v>-3.1913844089469088e-05</v>
       </c>
       <c r="O22">
-        <v>-3.5990810904028854e-05</v>
+        <v>-3.5852411591505495e-05</v>
       </c>
       <c r="P22">
-        <v>-1.340213646973437e-06</v>
+        <v>-1.3320146414675573e-06</v>
       </c>
       <c r="Q22">
-        <v>-1.1638070097909952e-05</v>
+        <v>-1.1693876973018769e-05</v>
       </c>
       <c r="R22">
-        <v>-5.0555335630387713e-05</v>
+        <v>-5.0281507677801282e-05</v>
       </c>
       <c r="S22">
-        <v>-7.5158473762935867e-06</v>
+        <v>-6.678726684464545e-06</v>
       </c>
       <c r="T22">
-        <v>-0.00027211715918463292</v>
+        <v>-0.00027173172787541743</v>
       </c>
       <c r="U22">
-        <v>0.00099553256909250786</v>
+        <v>0.0009940786937304364</v>
       </c>
       <c r="V22">
-        <v>0.0010091054864431934</v>
+        <v>0.0010074962506007987</v>
       </c>
       <c r="W22">
-        <v>0.03149410169124052</v>
+        <v>0.031448920111851374</v>
       </c>
       <c r="X22">
-        <v>-0.00020369333500919038</v>
+        <v>-0.00020321321750107655</v>
       </c>
     </row>
     <row r="23">
@@ -3649,73 +3649,73 @@
         <v>44</v>
       </c>
       <c r="B23">
-        <v>-0.35513461619989861</v>
+        <v>-0.35608164477567161</v>
       </c>
       <c r="C23">
-        <v>6.7069195917287852e-06</v>
+        <v>6.6983336736830681e-06</v>
       </c>
       <c r="D23">
-        <v>-7.6213490241779506e-08</v>
+        <v>-7.6102452998463248e-08</v>
       </c>
       <c r="E23">
-        <v>-1.035688868389197e-05</v>
+        <v>-1.0243959403182706e-05</v>
       </c>
       <c r="F23">
-        <v>-1.6851567021776492e-05</v>
+        <v>-1.6649078159195759e-05</v>
       </c>
       <c r="G23">
-        <v>1.8119699709677232e-07</v>
+        <v>1.8006685033436893e-07</v>
       </c>
       <c r="H23">
-        <v>2.0285732989710305e-07</v>
+        <v>2.0048888398869515e-07</v>
       </c>
       <c r="I23">
-        <v>6.8887760842260003e-06</v>
+        <v>6.7619871101391233e-06</v>
       </c>
       <c r="J23">
-        <v>2.2186131349639733e-05</v>
+        <v>2.210043715273794e-05</v>
       </c>
       <c r="K23">
-        <v>2.8872792830923177e-05</v>
+        <v>2.8748539147132294e-05</v>
       </c>
       <c r="L23">
-        <v>2.9927801989330906e-05</v>
+        <v>2.9801435083563976e-05</v>
       </c>
       <c r="M23">
-        <v>2.0739626442682634e-06</v>
+        <v>2.0218881463061296e-06</v>
       </c>
       <c r="N23">
-        <v>6.6739022485783718e-08</v>
+        <v>4.2377151779158134e-08</v>
       </c>
       <c r="O23">
-        <v>-4.511587874639927e-07</v>
+        <v>-4.6712552284808283e-07</v>
       </c>
       <c r="P23">
-        <v>1.0580653316468206e-06</v>
+        <v>1.0526112198095969e-06</v>
       </c>
       <c r="Q23">
-        <v>-2.8664403560488243e-06</v>
+        <v>-2.8739416513452563e-06</v>
       </c>
       <c r="R23">
-        <v>-3.9298627327537028e-06</v>
+        <v>-3.931225077069045e-06</v>
       </c>
       <c r="S23">
-        <v>-6.1795548449070217e-06</v>
+        <v>-6.2478278667181685e-06</v>
       </c>
       <c r="T23">
-        <v>2.2624288011360063e-07</v>
+        <v>2.2400293937615162e-07</v>
       </c>
       <c r="U23">
-        <v>-8.8023992502645066e-07</v>
+        <v>-8.5955444220759953e-07</v>
       </c>
       <c r="V23">
-        <v>1.9602230418419477e-06</v>
+        <v>2.016817476566481e-06</v>
       </c>
       <c r="W23">
-        <v>-0.00020369333500919038</v>
+        <v>-0.00020321321750107655</v>
       </c>
       <c r="X23">
-        <v>6.3399253414147367e-05</v>
+        <v>6.3163220734755118e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3809,76 +3809,76 @@
         <v>46</v>
       </c>
       <c r="B2">
-        <v>0.83490606256408417</v>
+        <v>0.83596893272361272</v>
       </c>
       <c r="C2">
-        <v>5.4149444841903821e-06</v>
+        <v>5.3733834497379924e-06</v>
       </c>
       <c r="D2">
-        <v>-1.9170400435041665e-07</v>
+        <v>-1.8523088764908586e-07</v>
       </c>
       <c r="E2">
-        <v>1.1102350662795997e-09</v>
+        <v>1.0451818117665417e-09</v>
       </c>
       <c r="F2">
-        <v>9.3179337954984099e-07</v>
+        <v>8.9160667790745651e-07</v>
       </c>
       <c r="G2">
-        <v>2.089789604934276e-07</v>
+        <v>1.8952123942299434e-07</v>
       </c>
       <c r="H2">
-        <v>2.7941512939287481e-08</v>
+        <v>2.8482986135698152e-08</v>
       </c>
       <c r="I2">
-        <v>6.4904040226913373e-08</v>
+        <v>6.4741003335853085e-08</v>
       </c>
       <c r="J2">
-        <v>-6.9382535870024479e-08</v>
+        <v>-5.5416920629332894e-08</v>
       </c>
       <c r="K2">
-        <v>-4.389170197566782e-07</v>
+        <v>-4.1435326814029137e-07</v>
       </c>
       <c r="L2">
-        <v>-8.2474746917796295e-07</v>
+        <v>-7.9539555705563971e-07</v>
       </c>
       <c r="M2">
-        <v>-1.1548416059109898e-06</v>
+        <v>-1.1201912345917517e-06</v>
       </c>
       <c r="N2">
-        <v>-1.0802015969646813e-06</v>
+        <v>-1.0812895239641038e-06</v>
       </c>
       <c r="O2">
-        <v>-9.968017005840478e-07</v>
+        <v>-9.8702004422987384e-07</v>
       </c>
       <c r="P2">
-        <v>-4.1098103065741263e-07</v>
+        <v>-4.0751056955999707e-07</v>
       </c>
       <c r="Q2">
-        <v>-8.503463491871904e-07</v>
+        <v>-8.5025892793197639e-07</v>
       </c>
       <c r="R2">
-        <v>-4.9303470864363799e-07</v>
+        <v>-4.9730227545150158e-07</v>
       </c>
       <c r="S2">
-        <v>-4.0457110883420921e-07</v>
+        <v>-4.1243217955804353e-07</v>
       </c>
       <c r="T2">
-        <v>1.5961393929950517e-07</v>
+        <v>1.6121997229266642e-07</v>
       </c>
       <c r="U2">
-        <v>3.7565263323006585e-08</v>
+        <v>3.952257033518018e-08</v>
       </c>
       <c r="V2">
-        <v>1.2109519962481994e-07</v>
+        <v>1.1196006088809518e-07</v>
       </c>
       <c r="W2">
-        <v>3.0392419529036894e-07</v>
+        <v>2.9855936410170464e-07</v>
       </c>
       <c r="X2">
-        <v>-9.5958740143851906e-06</v>
+        <v>-9.8882464922141834e-06</v>
       </c>
       <c r="Y2">
-        <v>4.2058815475524122e-07</v>
+        <v>5.2653314240877144e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3886,76 +3886,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>0.0090653067350520387</v>
+        <v>0.0077557290159983834</v>
       </c>
       <c r="C3">
-        <v>-1.9170400435041665e-07</v>
+        <v>-1.8523088764908586e-07</v>
       </c>
       <c r="D3">
-        <v>1.1192572000669344e-05</v>
+        <v>1.078820108103064e-05</v>
       </c>
       <c r="E3">
-        <v>-1.2185083522255474e-07</v>
+        <v>-1.1758235362736952e-07</v>
       </c>
       <c r="F3">
-        <v>-2.0201999328672566e-05</v>
+        <v>-1.9099917878957656e-05</v>
       </c>
       <c r="G3">
-        <v>-2.5637694875882812e-05</v>
+        <v>-2.5028632506768124e-05</v>
       </c>
       <c r="H3">
-        <v>2.5659718394078791e-07</v>
+        <v>2.3543775607227238e-07</v>
       </c>
       <c r="I3">
-        <v>5.0806724060246176e-08</v>
+        <v>5.6750008453215386e-08</v>
       </c>
       <c r="J3">
-        <v>1.4284797802598443e-05</v>
+        <v>1.4119691601741593e-05</v>
       </c>
       <c r="K3">
-        <v>2.9842502337778091e-05</v>
+        <v>2.8980988067088397e-05</v>
       </c>
       <c r="L3">
-        <v>3.8579333329106759e-05</v>
+        <v>3.7381280979789322e-05</v>
       </c>
       <c r="M3">
-        <v>3.9779566615345429e-05</v>
+        <v>3.8462424625086868e-05</v>
       </c>
       <c r="N3">
-        <v>2.1705180812626739e-06</v>
+        <v>1.9477502786327976e-06</v>
       </c>
       <c r="O3">
-        <v>3.2565846257639228e-06</v>
+        <v>3.2285442031433375e-06</v>
       </c>
       <c r="P3">
-        <v>-3.9172667434620598e-06</v>
+        <v>-3.7775807599166381e-06</v>
       </c>
       <c r="Q3">
-        <v>2.5616244434764704e-06</v>
+        <v>2.316967375360055e-06</v>
       </c>
       <c r="R3">
-        <v>-8.5413095471995388e-06</v>
+        <v>-8.3379587628583321e-06</v>
       </c>
       <c r="S3">
-        <v>-6.9175867121210128e-06</v>
+        <v>-6.6346476000919986e-06</v>
       </c>
       <c r="T3">
-        <v>-2.3795956639701235e-07</v>
+        <v>-2.5552464680696466e-07</v>
       </c>
       <c r="U3">
-        <v>-2.0017585538444142e-08</v>
+        <v>-2.0978758287499497e-08</v>
       </c>
       <c r="V3">
-        <v>-7.8215473990291999e-06</v>
+        <v>-7.5337859728192343e-06</v>
       </c>
       <c r="W3">
-        <v>1.0355701785805711e-06</v>
+        <v>9.7857096735174554e-07</v>
       </c>
       <c r="X3">
-        <v>-0.00030442236026177933</v>
+        <v>-0.00029308869745130639</v>
       </c>
       <c r="Y3">
-        <v>0.00018589599351392399</v>
+        <v>0.00017935393671850524</v>
       </c>
     </row>
     <row r="4">
@@ -3963,76 +3963,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>-7.8075964907221805e-05</v>
+        <v>-6.4111435057464863e-05</v>
       </c>
       <c r="C4">
-        <v>1.1102350662795997e-09</v>
+        <v>1.0451818117665417e-09</v>
       </c>
       <c r="D4">
-        <v>-1.2185083522255474e-07</v>
+        <v>-1.1758235362736952e-07</v>
       </c>
       <c r="E4">
-        <v>1.3311051287264849e-09</v>
+        <v>1.286019641498694e-09</v>
       </c>
       <c r="F4">
-        <v>2.3644388862352365e-07</v>
+        <v>2.2443425661289164e-07</v>
       </c>
       <c r="G4">
-        <v>2.9615059554108301e-07</v>
+        <v>2.8955901497537319e-07</v>
       </c>
       <c r="H4">
-        <v>-3.1761372525692363e-09</v>
+        <v>-2.9428201615580653e-09</v>
       </c>
       <c r="I4">
-        <v>-9.524871316569343e-10</v>
+        <v>-1.0111411649665294e-09</v>
       </c>
       <c r="J4">
-        <v>-1.5547477286129524e-07</v>
+        <v>-1.5385954837085906e-07</v>
       </c>
       <c r="K4">
-        <v>-3.2464896080022149e-07</v>
+        <v>-3.156597235798091e-07</v>
       </c>
       <c r="L4">
-        <v>-4.1911197519529342e-07</v>
+        <v>-4.0658116168416758e-07</v>
       </c>
       <c r="M4">
-        <v>-4.3126530003810835e-07</v>
+        <v>-4.1746830865503773e-07</v>
       </c>
       <c r="N4">
-        <v>-2.3470515219144589e-08</v>
+        <v>-2.10740934401793e-08</v>
       </c>
       <c r="O4">
-        <v>-3.5262592434547071e-08</v>
+        <v>-3.5002286211156039e-08</v>
       </c>
       <c r="P4">
-        <v>4.2617600863876326e-08</v>
+        <v>4.1147944587535564e-08</v>
       </c>
       <c r="Q4">
-        <v>-2.7675765860521686e-08</v>
+        <v>-2.5043553001252754e-08</v>
       </c>
       <c r="R4">
-        <v>9.3064981657292449e-08</v>
+        <v>9.0958803228087087e-08</v>
       </c>
       <c r="S4">
-        <v>7.5431400360237955e-08</v>
+        <v>7.2437661636943674e-08</v>
       </c>
       <c r="T4">
-        <v>2.6852729225980295e-09</v>
+        <v>2.87963846506743e-09</v>
       </c>
       <c r="U4">
-        <v>5.8951553396905426e-11</v>
+        <v>7.152844568044469e-11</v>
       </c>
       <c r="V4">
-        <v>8.5508111950068873e-08</v>
+        <v>8.2482743687639325e-08</v>
       </c>
       <c r="W4">
-        <v>-1.0859427514709191e-08</v>
+        <v>-1.0255640136179812e-08</v>
       </c>
       <c r="X4">
-        <v>3.3220812413424139e-06</v>
+        <v>3.202364903835218e-06</v>
       </c>
       <c r="Y4">
-        <v>-2.0234058564472576e-06</v>
+        <v>-1.9546168496313033e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4040,76 +4040,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.054485874728289946</v>
+        <v>-0.051915573579878513</v>
       </c>
       <c r="C5">
-        <v>9.3179337954984099e-07</v>
+        <v>8.9160667790745651e-07</v>
       </c>
       <c r="D5">
-        <v>-2.0201999328672566e-05</v>
+        <v>-1.9099917878957656e-05</v>
       </c>
       <c r="E5">
-        <v>2.3644388862352365e-07</v>
+        <v>2.2443425661289164e-07</v>
       </c>
       <c r="F5">
-        <v>0.00027779364057496528</v>
+        <v>0.00027110659969969107</v>
       </c>
       <c r="G5">
-        <v>0.00012487442748567899</v>
+        <v>0.00012167664639471345</v>
       </c>
       <c r="H5">
-        <v>-5.4405572857225522e-06</v>
+        <v>-5.3119059886715972e-06</v>
       </c>
       <c r="I5">
-        <v>-1.6276468052586796e-06</v>
+        <v>-1.6130326058510098e-06</v>
       </c>
       <c r="J5">
-        <v>-2.7803838990665341e-05</v>
+        <v>-2.7081745090967454e-05</v>
       </c>
       <c r="K5">
-        <v>-6.0651932358632397e-05</v>
+        <v>-5.8109998805798102e-05</v>
       </c>
       <c r="L5">
-        <v>-7.9122141456063096e-05</v>
+        <v>-7.5605800143977678e-05</v>
       </c>
       <c r="M5">
-        <v>-8.0208772531911111e-05</v>
+        <v>-7.6443911466357183e-05</v>
       </c>
       <c r="N5">
-        <v>-3.631601993855779e-06</v>
+        <v>-3.1714344885453338e-06</v>
       </c>
       <c r="O5">
-        <v>-5.5695825012548857e-06</v>
+        <v>-5.4638227884470947e-06</v>
       </c>
       <c r="P5">
-        <v>8.6809161868353704e-06</v>
+        <v>8.2253492070051281e-06</v>
       </c>
       <c r="Q5">
-        <v>-4.4801773536565245e-06</v>
+        <v>-3.924883974633872e-06</v>
       </c>
       <c r="R5">
-        <v>1.7482499834264954e-05</v>
+        <v>1.6763990322568507e-05</v>
       </c>
       <c r="S5">
-        <v>1.4769458480835752e-05</v>
+        <v>1.3971897420916514e-05</v>
       </c>
       <c r="T5">
-        <v>6.8208045815348623e-08</v>
+        <v>3.8043203317419708e-08</v>
       </c>
       <c r="U5">
-        <v>2.5991658397765661e-07</v>
+        <v>2.5496848134892517e-07</v>
       </c>
       <c r="V5">
-        <v>1.6058854667617644e-05</v>
+        <v>1.5240299716567509e-05</v>
       </c>
       <c r="W5">
-        <v>-2.9351116732279857e-06</v>
+        <v>-2.7837869228119566e-06</v>
       </c>
       <c r="X5">
-        <v>0.00050325609427480053</v>
+        <v>0.00047377480336275251</v>
       </c>
       <c r="Y5">
-        <v>-0.00038651503738428863</v>
+        <v>-0.00036764531166609413</v>
       </c>
     </row>
     <row r="6">
@@ -4117,76 +4117,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.016203745025241273</v>
+        <v>-0.010993474724085652</v>
       </c>
       <c r="C6">
-        <v>2.089789604934276e-07</v>
+        <v>1.8952123942299434e-07</v>
       </c>
       <c r="D6">
-        <v>-2.5637694875882812e-05</v>
+        <v>-2.5028632506768124e-05</v>
       </c>
       <c r="E6">
-        <v>2.9615059554108301e-07</v>
+        <v>2.8955901497537319e-07</v>
       </c>
       <c r="F6">
-        <v>0.00012487442748567899</v>
+        <v>0.00012167664639471345</v>
       </c>
       <c r="G6">
-        <v>0.00030855178787808667</v>
+        <v>0.0003044901246147851</v>
       </c>
       <c r="H6">
-        <v>-2.2365232511937591e-06</v>
+        <v>-2.1669579024087423e-06</v>
       </c>
       <c r="I6">
-        <v>-5.0740932757516796e-06</v>
+        <v>-5.0203156928627054e-06</v>
       </c>
       <c r="J6">
-        <v>-3.6004482042494818e-05</v>
+        <v>-3.6188562055855735e-05</v>
       </c>
       <c r="K6">
-        <v>-7.7316075197451662e-05</v>
+        <v>-7.6372126962495998e-05</v>
       </c>
       <c r="L6">
-        <v>-9.9778824410068552e-05</v>
+        <v>-9.8334877831784067e-05</v>
       </c>
       <c r="M6">
-        <v>-0.00010057819284417825</v>
+        <v>-9.892361128971511e-05</v>
       </c>
       <c r="N6">
-        <v>-4.7367393060452349e-06</v>
+        <v>-4.2325819683246116e-06</v>
       </c>
       <c r="O6">
-        <v>-8.4143917276524361e-06</v>
+        <v>-8.4637324959544136e-06</v>
       </c>
       <c r="P6">
-        <v>8.0561838559952498e-06</v>
+        <v>7.9418933953488437e-06</v>
       </c>
       <c r="Q6">
-        <v>-7.4135845518161722e-06</v>
+        <v>-6.861200562728997e-06</v>
       </c>
       <c r="R6">
-        <v>1.8303644756337456e-05</v>
+        <v>1.8131052493671668e-05</v>
       </c>
       <c r="S6">
-        <v>1.5620405915373223e-05</v>
+        <v>1.5231585823013674e-05</v>
       </c>
       <c r="T6">
-        <v>7.9144542865582013e-07</v>
+        <v>8.1748740439333399e-07</v>
       </c>
       <c r="U6">
-        <v>2.8655030166801858e-07</v>
+        <v>2.8606804417565665e-07</v>
       </c>
       <c r="V6">
-        <v>1.9715418306668763e-05</v>
+        <v>1.9328832556404838e-05</v>
       </c>
       <c r="W6">
-        <v>-2.7128615164868928e-06</v>
+        <v>-2.6161138441762384e-06</v>
       </c>
       <c r="X6">
-        <v>0.00065246730075265011</v>
+        <v>0.00063633512521571629</v>
       </c>
       <c r="Y6">
-        <v>-0.00047065749231569389</v>
+        <v>-0.00046151776770814542</v>
       </c>
     </row>
     <row r="7">
@@ -4194,76 +4194,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.00030273868509955477</v>
+        <v>-0.00032020669879346034</v>
       </c>
       <c r="C7">
-        <v>2.7941512939287481e-08</v>
+        <v>2.8482986135698152e-08</v>
       </c>
       <c r="D7">
-        <v>2.5659718394078791e-07</v>
+        <v>2.3543775607227238e-07</v>
       </c>
       <c r="E7">
-        <v>-3.1761372525692363e-09</v>
+        <v>-2.9428201615580653e-09</v>
       </c>
       <c r="F7">
-        <v>-5.4405572857225522e-06</v>
+        <v>-5.3119059886715972e-06</v>
       </c>
       <c r="G7">
-        <v>-2.2365232511937591e-06</v>
+        <v>-2.1669579024087423e-06</v>
       </c>
       <c r="H7">
-        <v>1.1424902088387156e-07</v>
+        <v>1.1175213953464179e-07</v>
       </c>
       <c r="I7">
-        <v>3.6501694422914346e-08</v>
+        <v>3.6015730599872475e-08</v>
       </c>
       <c r="J7">
-        <v>3.4881645867390443e-07</v>
+        <v>3.2868895174443007e-07</v>
       </c>
       <c r="K7">
-        <v>7.801407385316338e-07</v>
+        <v>7.2684843827298276e-07</v>
       </c>
       <c r="L7">
-        <v>1.0354016048426646e-06</v>
+        <v>9.6300092239522609e-07</v>
       </c>
       <c r="M7">
-        <v>1.0452873540547052e-06</v>
+        <v>9.6911610073336062e-07</v>
       </c>
       <c r="N7">
-        <v>4.0508315537168323e-08</v>
+        <v>3.35793701616647e-08</v>
       </c>
       <c r="O7">
-        <v>6.1047307161279447e-08</v>
+        <v>5.7751309403487276e-08</v>
       </c>
       <c r="P7">
-        <v>-1.1618928720924609e-07</v>
+        <v>-1.0683085581326183e-07</v>
       </c>
       <c r="Q7">
-        <v>4.4025686323584624e-08</v>
+        <v>3.5408911147849777e-08</v>
       </c>
       <c r="R7">
-        <v>-2.2671440292976046e-07</v>
+        <v>-2.1087533031331836e-07</v>
       </c>
       <c r="S7">
-        <v>-2.0094002984831379e-07</v>
+        <v>-1.8573907866308477e-07</v>
       </c>
       <c r="T7">
-        <v>1.5725185508595396e-10</v>
+        <v>1.5285789314621634e-09</v>
       </c>
       <c r="U7">
-        <v>-1.8115508004098128e-09</v>
+        <v>-1.6913945037192328e-09</v>
       </c>
       <c r="V7">
-        <v>-2.1324803933218143e-07</v>
+        <v>-1.9737459784505626e-07</v>
       </c>
       <c r="W7">
-        <v>4.1082399052457023e-08</v>
+        <v>3.8271111370818125e-08</v>
       </c>
       <c r="X7">
-        <v>-6.3622847002115338e-06</v>
+        <v>-5.7986118354851107e-06</v>
       </c>
       <c r="Y7">
-        <v>5.0368660252443435e-06</v>
+        <v>4.6668168801555951e-06</v>
       </c>
     </row>
     <row r="8">
@@ -4271,76 +4271,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>-0.0019611283378634164</v>
+        <v>-0.0019589666641436866</v>
       </c>
       <c r="C8">
-        <v>6.4904040226913373e-08</v>
+        <v>6.4741003335853085e-08</v>
       </c>
       <c r="D8">
-        <v>5.0806724060246176e-08</v>
+        <v>5.6750008453215386e-08</v>
       </c>
       <c r="E8">
-        <v>-9.524871316569343e-10</v>
+        <v>-1.0111411649665294e-09</v>
       </c>
       <c r="F8">
-        <v>-1.6276468052586796e-06</v>
+        <v>-1.6130326058510098e-06</v>
       </c>
       <c r="G8">
-        <v>-5.0740932757516796e-06</v>
+        <v>-5.0203156928627054e-06</v>
       </c>
       <c r="H8">
-        <v>3.6501694422914346e-08</v>
+        <v>3.6015730599872475e-08</v>
       </c>
       <c r="I8">
-        <v>1.0683910696755915e-07</v>
+        <v>1.0539418555111052e-07</v>
       </c>
       <c r="J8">
-        <v>6.7729220510425642e-08</v>
+        <v>7.9483940318504154e-08</v>
       </c>
       <c r="K8">
-        <v>1.8982351553323668e-07</v>
+        <v>2.1123067186189236e-07</v>
       </c>
       <c r="L8">
-        <v>2.6014435230324474e-07</v>
+        <v>2.8653866565306642e-07</v>
       </c>
       <c r="M8">
-        <v>2.3725852053151399e-07</v>
+        <v>2.6459655466789445e-07</v>
       </c>
       <c r="N8">
-        <v>-6.2970214572685166e-09</v>
+        <v>-6.4510485540121733e-09</v>
       </c>
       <c r="O8">
-        <v>2.5035108160045569e-08</v>
+        <v>2.6983237896345839e-08</v>
       </c>
       <c r="P8">
-        <v>1.0618101419584612e-08</v>
+        <v>6.7625147823716487e-09</v>
       </c>
       <c r="Q8">
-        <v>2.4915806087741695e-08</v>
+        <v>2.5105860996466806e-08</v>
       </c>
       <c r="R8">
-        <v>1.3112688904982292e-08</v>
+        <v>7.4998762011283649e-09</v>
       </c>
       <c r="S8">
-        <v>-4.8491981354917893e-09</v>
+        <v>-1.0115428229654229e-08</v>
       </c>
       <c r="T8">
-        <v>-1.2438801471828536e-08</v>
+        <v>-1.1629063311467248e-08</v>
       </c>
       <c r="U8">
-        <v>2.9433769826306958e-09</v>
+        <v>2.8609432706315583e-09</v>
       </c>
       <c r="V8">
-        <v>-5.444744392702974e-08</v>
+        <v>-6.0440935877825779e-08</v>
       </c>
       <c r="W8">
-        <v>-7.255588097708684e-09</v>
+        <v>-6.6345886968933701e-09</v>
       </c>
       <c r="X8">
-        <v>-1.1209254959576135e-06</v>
+        <v>-1.2956862747183844e-06</v>
       </c>
       <c r="Y8">
-        <v>9.087217792319713e-07</v>
+        <v>1.0298579055546431e-06</v>
       </c>
     </row>
     <row r="9">
@@ -4348,76 +4348,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>-0.016262208043115935</v>
+        <v>-0.016465943703390225</v>
       </c>
       <c r="C9">
-        <v>-6.9382535870024479e-08</v>
+        <v>-5.5416920629332894e-08</v>
       </c>
       <c r="D9">
-        <v>1.4284797802598443e-05</v>
+        <v>1.4119691601741593e-05</v>
       </c>
       <c r="E9">
-        <v>-1.5547477286129524e-07</v>
+        <v>-1.5385954837085906e-07</v>
       </c>
       <c r="F9">
-        <v>-2.7803838990665341e-05</v>
+        <v>-2.7081745090967454e-05</v>
       </c>
       <c r="G9">
-        <v>-3.6004482042494818e-05</v>
+        <v>-3.6188562055855735e-05</v>
       </c>
       <c r="H9">
-        <v>3.4881645867390443e-07</v>
+        <v>3.2868895174443007e-07</v>
       </c>
       <c r="I9">
-        <v>6.7729220510425642e-08</v>
+        <v>7.9483940318504154e-08</v>
       </c>
       <c r="J9">
-        <v>0.00061487167017753946</v>
+        <v>0.0006069854079226027</v>
       </c>
       <c r="K9">
-        <v>0.00054852890550611676</v>
+        <v>0.00054166969668980225</v>
       </c>
       <c r="L9">
-        <v>0.00056091255366612163</v>
+        <v>0.00055392354543796108</v>
       </c>
       <c r="M9">
-        <v>0.00056226386330454972</v>
+        <v>0.00055514872790326164</v>
       </c>
       <c r="N9">
-        <v>3.0933796796486743e-06</v>
+        <v>2.7818032847449628e-06</v>
       </c>
       <c r="O9">
-        <v>5.1390006481087921e-06</v>
+        <v>5.1990676847342861e-06</v>
       </c>
       <c r="P9">
-        <v>-5.4387840462035279e-06</v>
+        <v>-5.3984857763778649e-06</v>
       </c>
       <c r="Q9">
-        <v>3.9659579421946913e-06</v>
+        <v>3.6927183244349148e-06</v>
       </c>
       <c r="R9">
-        <v>-1.1777350205071405e-05</v>
+        <v>-1.1852842128071647e-05</v>
       </c>
       <c r="S9">
-        <v>-1.014924195108342e-05</v>
+        <v>-1.0049408340543792e-05</v>
       </c>
       <c r="T9">
-        <v>-3.4204518793654737e-07</v>
+        <v>-3.788496091340483e-07</v>
       </c>
       <c r="U9">
-        <v>5.955013657228466e-08</v>
+        <v>6.3786928896046897e-08</v>
       </c>
       <c r="V9">
-        <v>-1.1436448180573681e-05</v>
+        <v>-1.1344945597678733e-05</v>
       </c>
       <c r="W9">
-        <v>1.1452816325383639e-06</v>
+        <v>1.0829567384257129e-06</v>
       </c>
       <c r="X9">
-        <v>-0.00091262790470936434</v>
+        <v>-0.00090166215190190166</v>
       </c>
       <c r="Y9">
-        <v>0.00026249820986849612</v>
+        <v>0.00026048345453684294</v>
       </c>
     </row>
     <row r="10">
@@ -4425,76 +4425,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>0.020895713598523543</v>
+        <v>0.017118416739888342</v>
       </c>
       <c r="C10">
-        <v>-4.389170197566782e-07</v>
+        <v>-4.1435326814029137e-07</v>
       </c>
       <c r="D10">
-        <v>2.9842502337778091e-05</v>
+        <v>2.8980988067088397e-05</v>
       </c>
       <c r="E10">
-        <v>-3.2464896080022149e-07</v>
+        <v>-3.156597235798091e-07</v>
       </c>
       <c r="F10">
-        <v>-6.0651932358632397e-05</v>
+        <v>-5.8109998805798102e-05</v>
       </c>
       <c r="G10">
-        <v>-7.7316075197451662e-05</v>
+        <v>-7.6372126962495998e-05</v>
       </c>
       <c r="H10">
-        <v>7.801407385316338e-07</v>
+        <v>7.2684843827298276e-07</v>
       </c>
       <c r="I10">
-        <v>1.8982351553323668e-07</v>
+        <v>2.1123067186189236e-07</v>
       </c>
       <c r="J10">
-        <v>0.00054852890550611676</v>
+        <v>0.00054166969668980225</v>
       </c>
       <c r="K10">
-        <v>0.00060623479366765155</v>
+        <v>0.00059761373576641588</v>
       </c>
       <c r="L10">
-        <v>0.00062034672638229874</v>
+        <v>0.00061117750056256998</v>
       </c>
       <c r="M10">
-        <v>0.0006233552829110374</v>
+        <v>0.00061387092563975438</v>
       </c>
       <c r="N10">
-        <v>5.8690581764370234e-06</v>
+        <v>5.2191862982817486e-06</v>
       </c>
       <c r="O10">
-        <v>9.5366841757540435e-06</v>
+        <v>9.5417422234827724e-06</v>
       </c>
       <c r="P10">
-        <v>-1.1859304983706229e-05</v>
+        <v>-1.1569690649293653e-05</v>
       </c>
       <c r="Q10">
-        <v>7.6195116392870917e-06</v>
+        <v>6.9637360858907681e-06</v>
       </c>
       <c r="R10">
-        <v>-2.5422248068628436e-05</v>
+        <v>-2.5071138989268565e-05</v>
       </c>
       <c r="S10">
-        <v>-2.1053711903401142e-05</v>
+        <v>-2.0438344068910519e-05</v>
       </c>
       <c r="T10">
-        <v>-5.254650045859939e-07</v>
+        <v>-5.7008395136857153e-07</v>
       </c>
       <c r="U10">
-        <v>-2.6138651677631299e-08</v>
+        <v>-1.8966972811293684e-08</v>
       </c>
       <c r="V10">
-        <v>-2.3315385097676407e-05</v>
+        <v>-2.2707300335499415e-05</v>
       </c>
       <c r="W10">
-        <v>3.1463906391498534e-06</v>
+        <v>2.9808144207689845e-06</v>
       </c>
       <c r="X10">
-        <v>-0.0013388504605177575</v>
+        <v>-0.0013087381304975731</v>
       </c>
       <c r="Y10">
-        <v>0.00054686572298210767</v>
+        <v>0.00053309040145493457</v>
       </c>
     </row>
     <row r="11">
@@ -4502,76 +4502,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>0.038042078126474789</v>
+        <v>0.032989516672799549</v>
       </c>
       <c r="C11">
-        <v>-8.2474746917796295e-07</v>
+        <v>-7.9539555705563971e-07</v>
       </c>
       <c r="D11">
-        <v>3.8579333329106759e-05</v>
+        <v>3.7381280979789322e-05</v>
       </c>
       <c r="E11">
-        <v>-4.1911197519529342e-07</v>
+        <v>-4.0658116168416758e-07</v>
       </c>
       <c r="F11">
-        <v>-7.9122141456063096e-05</v>
+        <v>-7.5605800143977678e-05</v>
       </c>
       <c r="G11">
-        <v>-9.9778824410068552e-05</v>
+        <v>-9.8334877831784067e-05</v>
       </c>
       <c r="H11">
-        <v>1.0354016048426646e-06</v>
+        <v>9.6300092239522609e-07</v>
       </c>
       <c r="I11">
-        <v>2.6014435230324474e-07</v>
+        <v>2.8653866565306642e-07</v>
       </c>
       <c r="J11">
-        <v>0.00056091255366612163</v>
+        <v>0.00055392354543796108</v>
       </c>
       <c r="K11">
-        <v>0.00062034672638229874</v>
+        <v>0.00061117750056256998</v>
       </c>
       <c r="L11">
-        <v>0.00065710757180092191</v>
+        <v>0.00064686508360065986</v>
       </c>
       <c r="M11">
-        <v>0.00065865758530372204</v>
+        <v>0.0006480378586677186</v>
       </c>
       <c r="N11">
-        <v>7.2373262994493086e-06</v>
+        <v>6.4069214171233633e-06</v>
       </c>
       <c r="O11">
-        <v>1.2032443787187547e-05</v>
+        <v>1.2016340580359791e-05</v>
       </c>
       <c r="P11">
-        <v>-1.5739382032367234e-05</v>
+        <v>-1.5323769395112382e-05</v>
       </c>
       <c r="Q11">
-        <v>9.3367505924156006e-06</v>
+        <v>8.472800339568593e-06</v>
       </c>
       <c r="R11">
-        <v>-3.3271063146459877e-05</v>
+        <v>-3.2736930049167515e-05</v>
       </c>
       <c r="S11">
-        <v>-2.7009261030942069e-05</v>
+        <v>-2.6160988390879633e-05</v>
       </c>
       <c r="T11">
-        <v>-5.8427042448626439e-07</v>
+        <v>-6.4642832625541814e-07</v>
       </c>
       <c r="U11">
-        <v>2.4579581091591098e-09</v>
+        <v>1.0683012752814403e-08</v>
       </c>
       <c r="V11">
-        <v>-3.0437422389276659e-05</v>
+        <v>-2.9588216406378364e-05</v>
       </c>
       <c r="W11">
-        <v>4.0077784754383725e-06</v>
+        <v>3.7825042944085633e-06</v>
       </c>
       <c r="X11">
-        <v>-0.0015876835256496032</v>
+        <v>-0.0015482347822010833</v>
       </c>
       <c r="Y11">
-        <v>0.00070736538284481331</v>
+        <v>0.00068796758865905753</v>
       </c>
     </row>
     <row r="12">
@@ -4579,76 +4579,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.047613654257599614</v>
+        <v>0.04212883766875803</v>
       </c>
       <c r="C12">
-        <v>-1.1548416059109898e-06</v>
+        <v>-1.1201912345917517e-06</v>
       </c>
       <c r="D12">
-        <v>3.9779566615345429e-05</v>
+        <v>3.8462424625086868e-05</v>
       </c>
       <c r="E12">
-        <v>-4.3126530003810835e-07</v>
+        <v>-4.1746830865503773e-07</v>
       </c>
       <c r="F12">
-        <v>-8.0208772531911111e-05</v>
+        <v>-7.6443911466357183e-05</v>
       </c>
       <c r="G12">
-        <v>-0.00010057819284417825</v>
+        <v>-9.892361128971511e-05</v>
       </c>
       <c r="H12">
-        <v>1.0452873540547052e-06</v>
+        <v>9.6911610073336062e-07</v>
       </c>
       <c r="I12">
-        <v>2.3725852053151399e-07</v>
+        <v>2.6459655466789445e-07</v>
       </c>
       <c r="J12">
-        <v>0.00056226386330454972</v>
+        <v>0.00055514872790326164</v>
       </c>
       <c r="K12">
-        <v>0.0006233552829110374</v>
+        <v>0.00061387092563975438</v>
       </c>
       <c r="L12">
-        <v>0.00065865758530372204</v>
+        <v>0.0006480378586677186</v>
       </c>
       <c r="M12">
-        <v>0.00067266830267302268</v>
+        <v>0.00066142373902961513</v>
       </c>
       <c r="N12">
-        <v>7.0810126765002326e-06</v>
+        <v>6.2155595883116511e-06</v>
       </c>
       <c r="O12">
-        <v>1.1762218290051498e-05</v>
+        <v>1.1728226567563437e-05</v>
       </c>
       <c r="P12">
-        <v>-1.6343020623086341e-05</v>
+        <v>-1.5881268877140092e-05</v>
       </c>
       <c r="Q12">
-        <v>8.8054843259354408e-06</v>
+        <v>7.9116302669957144e-06</v>
       </c>
       <c r="R12">
-        <v>-3.4854538055549133e-05</v>
+        <v>-3.4226425767333398e-05</v>
       </c>
       <c r="S12">
-        <v>-2.8444940106264236e-05</v>
+        <v>-2.7504256448001208e-05</v>
       </c>
       <c r="T12">
-        <v>-5.6805946546510858e-07</v>
+        <v>-6.3429918422868578e-07</v>
       </c>
       <c r="U12">
-        <v>6.5456480167735415e-08</v>
+        <v>7.1899868797108613e-08</v>
       </c>
       <c r="V12">
-        <v>-3.1663908300751647e-05</v>
+        <v>-3.0708581302851942e-05</v>
       </c>
       <c r="W12">
-        <v>3.6688987721083748e-06</v>
+        <v>3.4395930788355279e-06</v>
       </c>
       <c r="X12">
-        <v>-0.0016276743318835922</v>
+        <v>-0.001584694468340643</v>
       </c>
       <c r="Y12">
-        <v>0.00072541972682367735</v>
+        <v>0.00070394648932827343</v>
       </c>
     </row>
     <row r="13">
@@ -4656,76 +4656,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.023430647992605573</v>
+        <v>0.022348989480954772</v>
       </c>
       <c r="C13">
-        <v>-1.0802015969646813e-06</v>
+        <v>-1.0812895239641038e-06</v>
       </c>
       <c r="D13">
-        <v>2.1705180812626739e-06</v>
+        <v>1.9477502786327976e-06</v>
       </c>
       <c r="E13">
-        <v>-2.3470515219144589e-08</v>
+        <v>-2.10740934401793e-08</v>
       </c>
       <c r="F13">
-        <v>-3.631601993855779e-06</v>
+        <v>-3.1714344885453338e-06</v>
       </c>
       <c r="G13">
-        <v>-4.7367393060452349e-06</v>
+        <v>-4.2325819683246116e-06</v>
       </c>
       <c r="H13">
-        <v>4.0508315537168323e-08</v>
+        <v>3.35793701616647e-08</v>
       </c>
       <c r="I13">
-        <v>-6.2970214572685166e-09</v>
+        <v>-6.4510485540121733e-09</v>
       </c>
       <c r="J13">
-        <v>3.0933796796486743e-06</v>
+        <v>2.7818032847449628e-06</v>
       </c>
       <c r="K13">
-        <v>5.8690581764370234e-06</v>
+        <v>5.2191862982817486e-06</v>
       </c>
       <c r="L13">
-        <v>7.2373262994493086e-06</v>
+        <v>6.4069214171233633e-06</v>
       </c>
       <c r="M13">
-        <v>7.0810126765002326e-06</v>
+        <v>6.2155595883116511e-06</v>
       </c>
       <c r="N13">
-        <v>2.4070780431922979e-05</v>
+        <v>2.3593435506784572e-05</v>
       </c>
       <c r="O13">
-        <v>1.4041960768521622e-05</v>
+        <v>1.3760713829482724e-05</v>
       </c>
       <c r="P13">
-        <v>1.2406018112468796e-05</v>
+        <v>1.22595166608463e-05</v>
       </c>
       <c r="Q13">
-        <v>1.3836042222886755e-05</v>
+        <v>1.3524594715238235e-05</v>
       </c>
       <c r="R13">
-        <v>1.1447607551893188e-05</v>
+        <v>1.1381109135054202e-05</v>
       </c>
       <c r="S13">
-        <v>1.1719203612126038e-05</v>
+        <v>1.1646786222322096e-05</v>
       </c>
       <c r="T13">
-        <v>-6.9071152178091714e-07</v>
+        <v>-6.8159688656404654e-07</v>
       </c>
       <c r="U13">
-        <v>3.2238112507922701e-08</v>
+        <v>3.0316067672793052e-08</v>
       </c>
       <c r="V13">
-        <v>-1.6245071757062736e-06</v>
+        <v>-1.4516428289582201e-06</v>
       </c>
       <c r="W13">
-        <v>2.4133608828007539e-08</v>
+        <v>-6.9341915582743417e-10</v>
       </c>
       <c r="X13">
-        <v>-7.3831641599804269e-05</v>
+        <v>-6.7125664838746385e-05</v>
       </c>
       <c r="Y13">
-        <v>3.8876075961376768e-05</v>
+        <v>3.49400894387941e-05</v>
       </c>
     </row>
     <row r="14">
@@ -4733,76 +4733,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.029087704644993957</v>
+        <v>0.028210706677526599</v>
       </c>
       <c r="C14">
-        <v>-9.968017005840478e-07</v>
+        <v>-9.8702004422987384e-07</v>
       </c>
       <c r="D14">
-        <v>3.2565846257639228e-06</v>
+        <v>3.2285442031433375e-06</v>
       </c>
       <c r="E14">
-        <v>-3.5262592434547071e-08</v>
+        <v>-3.5002286211156039e-08</v>
       </c>
       <c r="F14">
-        <v>-5.5695825012548857e-06</v>
+        <v>-5.4638227884470947e-06</v>
       </c>
       <c r="G14">
-        <v>-8.4143917276524361e-06</v>
+        <v>-8.4637324959544136e-06</v>
       </c>
       <c r="H14">
-        <v>6.1047307161279447e-08</v>
+        <v>5.7751309403487276e-08</v>
       </c>
       <c r="I14">
-        <v>2.5035108160045569e-08</v>
+        <v>2.6983237896345839e-08</v>
       </c>
       <c r="J14">
-        <v>5.1390006481087921e-06</v>
+        <v>5.1990676847342861e-06</v>
       </c>
       <c r="K14">
-        <v>9.5366841757540435e-06</v>
+        <v>9.5417422234827724e-06</v>
       </c>
       <c r="L14">
-        <v>1.2032443787187547e-05</v>
+        <v>1.2016340580359791e-05</v>
       </c>
       <c r="M14">
-        <v>1.1762218290051498e-05</v>
+        <v>1.1728226567563437e-05</v>
       </c>
       <c r="N14">
-        <v>1.4041960768521622e-05</v>
+        <v>1.3760713829482724e-05</v>
       </c>
       <c r="O14">
-        <v>2.8591668680719527e-05</v>
+        <v>2.8098071429372689e-05</v>
       </c>
       <c r="P14">
-        <v>1.1959034007195313e-05</v>
+        <v>1.1734644961474874e-05</v>
       </c>
       <c r="Q14">
-        <v>1.4125136921928142e-05</v>
+        <v>1.3839386905056588e-05</v>
       </c>
       <c r="R14">
-        <v>1.0563432772918668e-05</v>
+        <v>1.0316423878656624e-05</v>
       </c>
       <c r="S14">
-        <v>1.1052612379658422e-05</v>
+        <v>1.0844419867748279e-05</v>
       </c>
       <c r="T14">
-        <v>-8.6062159873588874e-09</v>
+        <v>-2.8420099716199465e-08</v>
       </c>
       <c r="U14">
-        <v>-8.3219969458834459e-08</v>
+        <v>-8.4269467920941017e-08</v>
       </c>
       <c r="V14">
-        <v>-2.0270905054865779e-06</v>
+        <v>-2.0068602661917605e-06</v>
       </c>
       <c r="W14">
-        <v>3.0901366540381607e-07</v>
+        <v>3.1549384007364928e-07</v>
       </c>
       <c r="X14">
-        <v>-9.3483960018726379e-05</v>
+        <v>-9.2367342708290557e-05</v>
       </c>
       <c r="Y14">
-        <v>5.7559167331081122e-05</v>
+        <v>5.7268536675292722e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4810,76 +4810,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.0035294315085298328</v>
+        <v>0.0041529260004039108</v>
       </c>
       <c r="C15">
-        <v>-4.1098103065741263e-07</v>
+        <v>-4.0751056955999707e-07</v>
       </c>
       <c r="D15">
-        <v>-3.9172667434620598e-06</v>
+        <v>-3.7775807599166381e-06</v>
       </c>
       <c r="E15">
-        <v>4.2617600863876326e-08</v>
+        <v>4.1147944587535564e-08</v>
       </c>
       <c r="F15">
-        <v>8.6809161868353704e-06</v>
+        <v>8.2253492070051281e-06</v>
       </c>
       <c r="G15">
-        <v>8.0561838559952498e-06</v>
+        <v>7.9418933953488437e-06</v>
       </c>
       <c r="H15">
-        <v>-1.1618928720924609e-07</v>
+        <v>-1.0683085581326183e-07</v>
       </c>
       <c r="I15">
-        <v>1.0618101419584612e-08</v>
+        <v>6.7625147823716487e-09</v>
       </c>
       <c r="J15">
-        <v>-5.4387840462035279e-06</v>
+        <v>-5.3984857763778649e-06</v>
       </c>
       <c r="K15">
-        <v>-1.1859304983706229e-05</v>
+        <v>-1.1569690649293653e-05</v>
       </c>
       <c r="L15">
-        <v>-1.5739382032367234e-05</v>
+        <v>-1.5323769395112382e-05</v>
       </c>
       <c r="M15">
-        <v>-1.6343020623086341e-05</v>
+        <v>-1.5881268877140092e-05</v>
       </c>
       <c r="N15">
-        <v>1.2406018112468796e-05</v>
+        <v>1.22595166608463e-05</v>
       </c>
       <c r="O15">
-        <v>1.1959034007195313e-05</v>
+        <v>1.1734644961474874e-05</v>
       </c>
       <c r="P15">
-        <v>2.732104178588196e-05</v>
+        <v>2.6846762942057136e-05</v>
       </c>
       <c r="Q15">
-        <v>1.224946588347958e-05</v>
+        <v>1.2111622133327185e-05</v>
       </c>
       <c r="R15">
-        <v>1.6691385068045789e-05</v>
+        <v>1.6390707266135053e-05</v>
       </c>
       <c r="S15">
-        <v>1.5936372934331804e-05</v>
+        <v>1.5605600328285622e-05</v>
       </c>
       <c r="T15">
-        <v>-4.0108086500794395e-07</v>
+        <v>-3.9040138738492253e-07</v>
       </c>
       <c r="U15">
-        <v>-1.8725193260008439e-08</v>
+        <v>-2.002325330800641e-08</v>
       </c>
       <c r="V15">
-        <v>3.1095308112344178e-06</v>
+        <v>3.0190943041081984e-06</v>
       </c>
       <c r="W15">
-        <v>-5.2243891837971979e-07</v>
+        <v>-4.9168289708035081e-07</v>
       </c>
       <c r="X15">
-        <v>0.00010058405661502449</v>
+        <v>9.7018976219735405e-05</v>
       </c>
       <c r="Y15">
-        <v>-7.3381672070635059e-05</v>
+        <v>-7.1081519411094965e-05</v>
       </c>
     </row>
     <row r="16">
@@ -4887,76 +4887,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.025603504673016118</v>
+        <v>0.024574099861228469</v>
       </c>
       <c r="C16">
-        <v>-8.503463491871904e-07</v>
+        <v>-8.5025892793197639e-07</v>
       </c>
       <c r="D16">
-        <v>2.5616244434764704e-06</v>
+        <v>2.316967375360055e-06</v>
       </c>
       <c r="E16">
-        <v>-2.7675765860521686e-08</v>
+        <v>-2.5043553001252754e-08</v>
       </c>
       <c r="F16">
-        <v>-4.4801773536565245e-06</v>
+        <v>-3.924883974633872e-06</v>
       </c>
       <c r="G16">
-        <v>-7.4135845518161722e-06</v>
+        <v>-6.861200562728997e-06</v>
       </c>
       <c r="H16">
-        <v>4.4025686323584624e-08</v>
+        <v>3.5408911147849777e-08</v>
       </c>
       <c r="I16">
-        <v>2.4915806087741695e-08</v>
+        <v>2.5105860996466806e-08</v>
       </c>
       <c r="J16">
-        <v>3.9659579421946913e-06</v>
+        <v>3.6927183244349148e-06</v>
       </c>
       <c r="K16">
-        <v>7.6195116392870917e-06</v>
+        <v>6.9637360858907681e-06</v>
       </c>
       <c r="L16">
-        <v>9.3367505924156006e-06</v>
+        <v>8.472800339568593e-06</v>
       </c>
       <c r="M16">
-        <v>8.8054843259354408e-06</v>
+        <v>7.9116302669957144e-06</v>
       </c>
       <c r="N16">
-        <v>1.3836042222886755e-05</v>
+        <v>1.3524594715238235e-05</v>
       </c>
       <c r="O16">
-        <v>1.4125136921928142e-05</v>
+        <v>1.3839386905056588e-05</v>
       </c>
       <c r="P16">
-        <v>1.224946588347958e-05</v>
+        <v>1.2111622133327185e-05</v>
       </c>
       <c r="Q16">
-        <v>2.0615781575586699e-05</v>
+        <v>2.0173638303776986e-05</v>
       </c>
       <c r="R16">
-        <v>1.1212209065329734e-05</v>
+        <v>1.1161112879941461e-05</v>
       </c>
       <c r="S16">
-        <v>1.1576443897960304e-05</v>
+        <v>1.1516557311702751e-05</v>
       </c>
       <c r="T16">
-        <v>4.7019590636019592e-08</v>
+        <v>4.2760050429708797e-08</v>
       </c>
       <c r="U16">
-        <v>-1.7360743829891166e-07</v>
+        <v>-1.7265816824017144e-07</v>
       </c>
       <c r="V16">
-        <v>-6.6573803187886861e-07</v>
+        <v>-4.8952380548002722e-07</v>
       </c>
       <c r="W16">
-        <v>1.2746315986340119e-06</v>
+        <v>1.2328018889834958e-06</v>
       </c>
       <c r="X16">
-        <v>-6.5125806844308051e-05</v>
+        <v>-5.8142806718111204e-05</v>
       </c>
       <c r="Y16">
-        <v>4.479010644990466e-05</v>
+        <v>4.0463187050596504e-05</v>
       </c>
     </row>
     <row r="17">
@@ -4964,76 +4964,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>0.01521001120519266</v>
+        <v>0.015935377627654804</v>
       </c>
       <c r="C17">
-        <v>-4.9303470864363799e-07</v>
+        <v>-4.9730227545150158e-07</v>
       </c>
       <c r="D17">
-        <v>-8.5413095471995388e-06</v>
+        <v>-8.3379587628583321e-06</v>
       </c>
       <c r="E17">
-        <v>9.3064981657292449e-08</v>
+        <v>9.0958803228087087e-08</v>
       </c>
       <c r="F17">
-        <v>1.7482499834264954e-05</v>
+        <v>1.6763990322568507e-05</v>
       </c>
       <c r="G17">
-        <v>1.8303644756337456e-05</v>
+        <v>1.8131052493671668e-05</v>
       </c>
       <c r="H17">
-        <v>-2.2671440292976046e-07</v>
+        <v>-2.1087533031331836e-07</v>
       </c>
       <c r="I17">
-        <v>1.3112688904982292e-08</v>
+        <v>7.4998762011283649e-09</v>
       </c>
       <c r="J17">
-        <v>-1.1777350205071405e-05</v>
+        <v>-1.1852842128071647e-05</v>
       </c>
       <c r="K17">
-        <v>-2.5422248068628436e-05</v>
+        <v>-2.5071138989268565e-05</v>
       </c>
       <c r="L17">
-        <v>-3.3271063146459877e-05</v>
+        <v>-3.2736930049167515e-05</v>
       </c>
       <c r="M17">
-        <v>-3.4854538055549133e-05</v>
+        <v>-3.4226425767333398e-05</v>
       </c>
       <c r="N17">
-        <v>1.1447607551893188e-05</v>
+        <v>1.1381109135054202e-05</v>
       </c>
       <c r="O17">
-        <v>1.0563432772918668e-05</v>
+        <v>1.0316423878656624e-05</v>
       </c>
       <c r="P17">
-        <v>1.6691385068045789e-05</v>
+        <v>1.6390707266135053e-05</v>
       </c>
       <c r="Q17">
-        <v>1.1212209065329734e-05</v>
+        <v>1.1161112879941461e-05</v>
       </c>
       <c r="R17">
-        <v>3.2840825552024607e-05</v>
+        <v>3.2370250725976686e-05</v>
       </c>
       <c r="S17">
-        <v>1.9237983852947061e-05</v>
+        <v>1.8855048124291703e-05</v>
       </c>
       <c r="T17">
-        <v>-2.33898727898607e-07</v>
+        <v>-2.058796888674574e-07</v>
       </c>
       <c r="U17">
-        <v>-5.9652446247993817e-08</v>
+        <v>-5.7730369474870973e-08</v>
       </c>
       <c r="V17">
-        <v>7.0605225212848227e-06</v>
+        <v>6.9040248125664161e-06</v>
       </c>
       <c r="W17">
-        <v>-7.952644641934495e-07</v>
+        <v>-7.7215759256513901e-07</v>
       </c>
       <c r="X17">
-        <v>0.00023419712648719068</v>
+        <v>0.00022852611217229489</v>
       </c>
       <c r="Y17">
-        <v>-0.00015884221803105428</v>
+        <v>-0.00015561471402370121</v>
       </c>
     </row>
     <row r="18">
@@ -5041,76 +5041,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>0.0096526882218952188</v>
+        <v>0.0098469644202704779</v>
       </c>
       <c r="C18">
-        <v>-4.0457110883420921e-07</v>
+        <v>-4.1243217955804353e-07</v>
       </c>
       <c r="D18">
-        <v>-6.9175867121210128e-06</v>
+        <v>-6.6346476000919986e-06</v>
       </c>
       <c r="E18">
-        <v>7.5431400360237955e-08</v>
+        <v>7.2437661636943674e-08</v>
       </c>
       <c r="F18">
-        <v>1.4769458480835752e-05</v>
+        <v>1.3971897420916514e-05</v>
       </c>
       <c r="G18">
-        <v>1.5620405915373223e-05</v>
+        <v>1.5231585823013674e-05</v>
       </c>
       <c r="H18">
-        <v>-2.0094002984831379e-07</v>
+        <v>-1.8573907866308477e-07</v>
       </c>
       <c r="I18">
-        <v>-4.8491981354917893e-09</v>
+        <v>-1.0115428229654229e-08</v>
       </c>
       <c r="J18">
-        <v>-1.014924195108342e-05</v>
+        <v>-1.0049408340543792e-05</v>
       </c>
       <c r="K18">
-        <v>-2.1053711903401142e-05</v>
+        <v>-2.0438344068910519e-05</v>
       </c>
       <c r="L18">
-        <v>-2.7009261030942069e-05</v>
+        <v>-2.6160988390879633e-05</v>
       </c>
       <c r="M18">
-        <v>-2.8444940106264236e-05</v>
+        <v>-2.7504256448001208e-05</v>
       </c>
       <c r="N18">
-        <v>1.1719203612126038e-05</v>
+        <v>1.1646786222322096e-05</v>
       </c>
       <c r="O18">
-        <v>1.1052612379658422e-05</v>
+        <v>1.0844419867748279e-05</v>
       </c>
       <c r="P18">
-        <v>1.5936372934331804e-05</v>
+        <v>1.5605600328285622e-05</v>
       </c>
       <c r="Q18">
-        <v>1.1576443897960304e-05</v>
+        <v>1.1516557311702751e-05</v>
       </c>
       <c r="R18">
-        <v>1.9237983852947061e-05</v>
+        <v>1.8855048124291703e-05</v>
       </c>
       <c r="S18">
-        <v>7.2219381336933298e-05</v>
+        <v>7.0694897866597082e-05</v>
       </c>
       <c r="T18">
-        <v>3.3710838328491461e-07</v>
+        <v>3.274964918795045e-07</v>
       </c>
       <c r="U18">
-        <v>2.2121955252224153e-09</v>
+        <v>3.6352277773525647e-09</v>
       </c>
       <c r="V18">
-        <v>5.6480744361936988e-06</v>
+        <v>5.4308513801767099e-06</v>
       </c>
       <c r="W18">
-        <v>-4.2287593562071534e-07</v>
+        <v>-3.9433186956089406e-07</v>
       </c>
       <c r="X18">
-        <v>0.00018191453983690197</v>
+        <v>0.00017413441745246897</v>
       </c>
       <c r="Y18">
-        <v>-0.00012818933719486122</v>
+        <v>-0.00012344804578653132</v>
       </c>
     </row>
     <row r="19">
@@ -5118,76 +5118,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.055160178004331983</v>
+        <v>0.055879592638901202</v>
       </c>
       <c r="C19">
-        <v>1.5961393929950517e-07</v>
+        <v>1.6121997229266642e-07</v>
       </c>
       <c r="D19">
-        <v>-2.3795956639701235e-07</v>
+        <v>-2.5552464680696466e-07</v>
       </c>
       <c r="E19">
-        <v>2.6852729225980295e-09</v>
+        <v>2.87963846506743e-09</v>
       </c>
       <c r="F19">
-        <v>6.8208045815348623e-08</v>
+        <v>3.8043203317419708e-08</v>
       </c>
       <c r="G19">
-        <v>7.9144542865582013e-07</v>
+        <v>8.1748740439333399e-07</v>
       </c>
       <c r="H19">
-        <v>1.5725185508595396e-10</v>
+        <v>1.5285789314621634e-09</v>
       </c>
       <c r="I19">
-        <v>-1.2438801471828536e-08</v>
+        <v>-1.1629063311467248e-08</v>
       </c>
       <c r="J19">
-        <v>-3.4204518793654737e-07</v>
+        <v>-3.788496091340483e-07</v>
       </c>
       <c r="K19">
-        <v>-5.254650045859939e-07</v>
+        <v>-5.7008395136857153e-07</v>
       </c>
       <c r="L19">
-        <v>-5.8427042448626439e-07</v>
+        <v>-6.4642832625541814e-07</v>
       </c>
       <c r="M19">
-        <v>-5.6805946546510858e-07</v>
+        <v>-6.3429918422868578e-07</v>
       </c>
       <c r="N19">
-        <v>-6.9071152178091714e-07</v>
+        <v>-6.8159688656404654e-07</v>
       </c>
       <c r="O19">
-        <v>-8.6062159873588874e-09</v>
+        <v>-2.8420099716199465e-08</v>
       </c>
       <c r="P19">
-        <v>-4.0108086500794395e-07</v>
+        <v>-3.9040138738492253e-07</v>
       </c>
       <c r="Q19">
-        <v>4.7019590636019592e-08</v>
+        <v>4.2760050429708797e-08</v>
       </c>
       <c r="R19">
-        <v>-2.33898727898607e-07</v>
+        <v>-2.058796888674574e-07</v>
       </c>
       <c r="S19">
-        <v>3.3710838328491461e-07</v>
+        <v>3.274964918795045e-07</v>
       </c>
       <c r="T19">
-        <v>7.8955631438471635e-06</v>
+        <v>7.8224933444394302e-06</v>
       </c>
       <c r="U19">
-        <v>1.435195099747199e-09</v>
+        <v>-4.894737302264703e-10</v>
       </c>
       <c r="V19">
-        <v>5.0927482704789162e-09</v>
+        <v>2.9364185751310978e-08</v>
       </c>
       <c r="W19">
-        <v>-2.5912249614332344e-07</v>
+        <v>-2.5006095718608825e-07</v>
       </c>
       <c r="X19">
-        <v>3.4444129915008987e-06</v>
+        <v>4.1336223997390042e-06</v>
       </c>
       <c r="Y19">
-        <v>-4.7239067074631937e-06</v>
+        <v>-4.9837274017593888e-06</v>
       </c>
     </row>
     <row r="20">
@@ -5195,76 +5195,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>0.010206939491254789</v>
+        <v>0.010115357623111981</v>
       </c>
       <c r="C20">
-        <v>3.7565263323006585e-08</v>
+        <v>3.952257033518018e-08</v>
       </c>
       <c r="D20">
-        <v>-2.0017585538444142e-08</v>
+        <v>-2.0978758287499497e-08</v>
       </c>
       <c r="E20">
-        <v>5.8951553396905426e-11</v>
+        <v>7.152844568044469e-11</v>
       </c>
       <c r="F20">
-        <v>2.5991658397765661e-07</v>
+        <v>2.5496848134892517e-07</v>
       </c>
       <c r="G20">
-        <v>2.8655030166801858e-07</v>
+        <v>2.8606804417565665e-07</v>
       </c>
       <c r="H20">
-        <v>-1.8115508004098128e-09</v>
+        <v>-1.6913945037192328e-09</v>
       </c>
       <c r="I20">
-        <v>2.9433769826306958e-09</v>
+        <v>2.8609432706315583e-09</v>
       </c>
       <c r="J20">
-        <v>5.955013657228466e-08</v>
+        <v>6.3786928896046897e-08</v>
       </c>
       <c r="K20">
-        <v>-2.6138651677631299e-08</v>
+        <v>-1.8966972811293684e-08</v>
       </c>
       <c r="L20">
-        <v>2.4579581091591098e-09</v>
+        <v>1.0683012752814403e-08</v>
       </c>
       <c r="M20">
-        <v>6.5456480167735415e-08</v>
+        <v>7.1899868797108613e-08</v>
       </c>
       <c r="N20">
-        <v>3.2238112507922701e-08</v>
+        <v>3.0316067672793052e-08</v>
       </c>
       <c r="O20">
-        <v>-8.3219969458834459e-08</v>
+        <v>-8.4269467920941017e-08</v>
       </c>
       <c r="P20">
-        <v>-1.8725193260008439e-08</v>
+        <v>-2.002325330800641e-08</v>
       </c>
       <c r="Q20">
-        <v>-1.7360743829891166e-07</v>
+        <v>-1.7265816824017144e-07</v>
       </c>
       <c r="R20">
-        <v>-5.9652446247993817e-08</v>
+        <v>-5.7730369474870973e-08</v>
       </c>
       <c r="S20">
-        <v>2.2121955252224153e-09</v>
+        <v>3.6352277773525647e-09</v>
       </c>
       <c r="T20">
-        <v>1.435195099747199e-09</v>
+        <v>-4.894737302264703e-10</v>
       </c>
       <c r="U20">
-        <v>8.8239399589656674e-07</v>
+        <v>8.7169073639593096e-07</v>
       </c>
       <c r="V20">
-        <v>-3.1366985950991495e-06</v>
+        <v>-3.0985251951022797e-06</v>
       </c>
       <c r="W20">
-        <v>-3.234970501477392e-06</v>
+        <v>-3.1956918658958637e-06</v>
       </c>
       <c r="X20">
-        <v>-8.8165096026272539e-05</v>
+        <v>-8.7079827477529095e-05</v>
       </c>
       <c r="Y20">
-        <v>-7.0768431516283677e-07</v>
+        <v>-7.1447459469946505e-07</v>
       </c>
     </row>
     <row r="21">
@@ -5272,76 +5272,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.08438464923298282</v>
+        <v>-0.082089446962218621</v>
       </c>
       <c r="C21">
-        <v>1.2109519962481994e-07</v>
+        <v>1.1196006088809518e-07</v>
       </c>
       <c r="D21">
-        <v>-7.8215473990291999e-06</v>
+        <v>-7.5337859728192343e-06</v>
       </c>
       <c r="E21">
-        <v>8.5508111950068873e-08</v>
+        <v>8.2482743687639325e-08</v>
       </c>
       <c r="F21">
-        <v>1.6058854667617644e-05</v>
+        <v>1.5240299716567509e-05</v>
       </c>
       <c r="G21">
-        <v>1.9715418306668763e-05</v>
+        <v>1.9328832556404838e-05</v>
       </c>
       <c r="H21">
-        <v>-2.1324803933218143e-07</v>
+        <v>-1.9737459784505626e-07</v>
       </c>
       <c r="I21">
-        <v>-5.444744392702974e-08</v>
+        <v>-6.0440935877825779e-08</v>
       </c>
       <c r="J21">
-        <v>-1.1436448180573681e-05</v>
+        <v>-1.1344945597678733e-05</v>
       </c>
       <c r="K21">
-        <v>-2.3315385097676407e-05</v>
+        <v>-2.2707300335499415e-05</v>
       </c>
       <c r="L21">
-        <v>-3.0437422389276659e-05</v>
+        <v>-2.9588216406378364e-05</v>
       </c>
       <c r="M21">
-        <v>-3.1663908300751647e-05</v>
+        <v>-3.0708581302851942e-05</v>
       </c>
       <c r="N21">
-        <v>-1.6245071757062736e-06</v>
+        <v>-1.4516428289582201e-06</v>
       </c>
       <c r="O21">
-        <v>-2.0270905054865779e-06</v>
+        <v>-2.0068602661917605e-06</v>
       </c>
       <c r="P21">
-        <v>3.1095308112344178e-06</v>
+        <v>3.0190943041081984e-06</v>
       </c>
       <c r="Q21">
-        <v>-6.6573803187886861e-07</v>
+        <v>-4.8952380548002722e-07</v>
       </c>
       <c r="R21">
-        <v>7.0605225212848227e-06</v>
+        <v>6.9040248125664161e-06</v>
       </c>
       <c r="S21">
-        <v>5.6480744361936988e-06</v>
+        <v>5.4308513801767099e-06</v>
       </c>
       <c r="T21">
-        <v>5.0927482704789162e-09</v>
+        <v>2.9364185751310978e-08</v>
       </c>
       <c r="U21">
-        <v>-3.1366985950991495e-06</v>
+        <v>-3.0985251951022797e-06</v>
       </c>
       <c r="V21">
-        <v>5.0678680019036081e-05</v>
+        <v>4.9771861544856508e-05</v>
       </c>
       <c r="W21">
-        <v>1.2716786352939688e-05</v>
+        <v>1.2585990332363481e-05</v>
       </c>
       <c r="X21">
-        <v>0.0005321876985731255</v>
+        <v>0.00052033261415242844</v>
       </c>
       <c r="Y21">
-        <v>-0.00014192090778209941</v>
+        <v>-0.00013708649300372681</v>
       </c>
     </row>
     <row r="22">
@@ -5349,76 +5349,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>0.0059931099562607563</v>
+        <v>0.0065866794375065733</v>
       </c>
       <c r="C22">
-        <v>3.0392419529036894e-07</v>
+        <v>2.9855936410170464e-07</v>
       </c>
       <c r="D22">
-        <v>1.0355701785805711e-06</v>
+        <v>9.7857096735174554e-07</v>
       </c>
       <c r="E22">
-        <v>-1.0859427514709191e-08</v>
+        <v>-1.0255640136179812e-08</v>
       </c>
       <c r="F22">
-        <v>-2.9351116732279857e-06</v>
+        <v>-2.7837869228119566e-06</v>
       </c>
       <c r="G22">
-        <v>-2.7128615164868928e-06</v>
+        <v>-2.6161138441762384e-06</v>
       </c>
       <c r="H22">
-        <v>4.1082399052457023e-08</v>
+        <v>3.8271111370818125e-08</v>
       </c>
       <c r="I22">
-        <v>-7.255588097708684e-09</v>
+        <v>-6.6345886968933701e-09</v>
       </c>
       <c r="J22">
-        <v>1.1452816325383639e-06</v>
+        <v>1.0829567384257129e-06</v>
       </c>
       <c r="K22">
-        <v>3.1463906391498534e-06</v>
+        <v>2.9808144207689845e-06</v>
       </c>
       <c r="L22">
-        <v>4.0077784754383725e-06</v>
+        <v>3.7825042944085633e-06</v>
       </c>
       <c r="M22">
-        <v>3.6688987721083748e-06</v>
+        <v>3.4395930788355279e-06</v>
       </c>
       <c r="N22">
-        <v>2.4133608828007539e-08</v>
+        <v>-6.9341915582743417e-10</v>
       </c>
       <c r="O22">
-        <v>3.0901366540381607e-07</v>
+        <v>3.1549384007364928e-07</v>
       </c>
       <c r="P22">
-        <v>-5.2243891837971979e-07</v>
+        <v>-4.9168289708035081e-07</v>
       </c>
       <c r="Q22">
-        <v>1.2746315986340119e-06</v>
+        <v>1.2328018889834958e-06</v>
       </c>
       <c r="R22">
-        <v>-7.952644641934495e-07</v>
+        <v>-7.7215759256513901e-07</v>
       </c>
       <c r="S22">
-        <v>-4.2287593562071534e-07</v>
+        <v>-3.9433186956089406e-07</v>
       </c>
       <c r="T22">
-        <v>-2.5912249614332344e-07</v>
+        <v>-2.5006095718608825e-07</v>
       </c>
       <c r="U22">
-        <v>-3.234970501477392e-06</v>
+        <v>-3.1956918658958637e-06</v>
       </c>
       <c r="V22">
-        <v>1.2716786352939688e-05</v>
+        <v>1.2585990332363481e-05</v>
       </c>
       <c r="W22">
-        <v>4.3228741629367646e-05</v>
+        <v>4.2548054561253356e-05</v>
       </c>
       <c r="X22">
-        <v>0.00029288390551605078</v>
+        <v>0.00029061843507478314</v>
       </c>
       <c r="Y22">
-        <v>2.2161272781502884e-05</v>
+        <v>2.1148253325507254e-05</v>
       </c>
     </row>
     <row r="23">
@@ -5426,76 +5426,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>-0.92950523258235174</v>
+        <v>-0.8850349803990808</v>
       </c>
       <c r="C23">
-        <v>-9.5958740143851906e-06</v>
+        <v>-9.8882464922141834e-06</v>
       </c>
       <c r="D23">
-        <v>-0.00030442236026177933</v>
+        <v>-0.00029308869745130639</v>
       </c>
       <c r="E23">
-        <v>3.3220812413424139e-06</v>
+        <v>3.202364903835218e-06</v>
       </c>
       <c r="F23">
-        <v>0.00050325609427480053</v>
+        <v>0.00047377480336275251</v>
       </c>
       <c r="G23">
-        <v>0.00065246730075265011</v>
+        <v>0.00063633512521571629</v>
       </c>
       <c r="H23">
-        <v>-6.3622847002115338e-06</v>
+        <v>-5.7986118354851107e-06</v>
       </c>
       <c r="I23">
-        <v>-1.1209254959576135e-06</v>
+        <v>-1.2956862747183844e-06</v>
       </c>
       <c r="J23">
-        <v>-0.00091262790470936434</v>
+        <v>-0.00090166215190190166</v>
       </c>
       <c r="K23">
-        <v>-0.0013388504605177575</v>
+        <v>-0.0013087381304975731</v>
       </c>
       <c r="L23">
-        <v>-0.0015876835256496032</v>
+        <v>-0.0015482347822010833</v>
       </c>
       <c r="M23">
-        <v>-0.0016276743318835922</v>
+        <v>-0.001584694468340643</v>
       </c>
       <c r="N23">
-        <v>-7.3831641599804269e-05</v>
+        <v>-6.7125664838746385e-05</v>
       </c>
       <c r="O23">
-        <v>-9.3483960018726379e-05</v>
+        <v>-9.2367342708290557e-05</v>
       </c>
       <c r="P23">
-        <v>0.00010058405661502449</v>
+        <v>9.7018976219735405e-05</v>
       </c>
       <c r="Q23">
-        <v>-6.5125806844308051e-05</v>
+        <v>-5.8142806718111204e-05</v>
       </c>
       <c r="R23">
-        <v>0.00023419712648719068</v>
+        <v>0.00022852611217229489</v>
       </c>
       <c r="S23">
-        <v>0.00018191453983690197</v>
+        <v>0.00017413441745246897</v>
       </c>
       <c r="T23">
-        <v>3.4444129915008987e-06</v>
+        <v>4.1336223997390042e-06</v>
       </c>
       <c r="U23">
-        <v>-8.8165096026272539e-05</v>
+        <v>-8.7079827477529095e-05</v>
       </c>
       <c r="V23">
-        <v>0.0005321876985731255</v>
+        <v>0.00052033261415242844</v>
       </c>
       <c r="W23">
-        <v>0.00029288390551605078</v>
+        <v>0.00029061843507478314</v>
       </c>
       <c r="X23">
-        <v>0.017800131515057632</v>
+        <v>0.01736986875190057</v>
       </c>
       <c r="Y23">
-        <v>-0.0051312155197763493</v>
+        <v>-0.0049476127376636399</v>
       </c>
     </row>
     <row r="24">
@@ -5503,76 +5503,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>0.054908965052377357</v>
+        <v>0.028486134118750298</v>
       </c>
       <c r="C24">
-        <v>4.2058815475524122e-07</v>
+        <v>5.2653314240877144e-07</v>
       </c>
       <c r="D24">
-        <v>0.00018589599351392399</v>
+        <v>0.00017935393671850524</v>
       </c>
       <c r="E24">
-        <v>-2.0234058564472576e-06</v>
+        <v>-1.9546168496313033e-06</v>
       </c>
       <c r="F24">
-        <v>-0.00038651503738428863</v>
+        <v>-0.00036764531166609413</v>
       </c>
       <c r="G24">
-        <v>-0.00047065749231569389</v>
+        <v>-0.00046151776770814542</v>
       </c>
       <c r="H24">
-        <v>5.0368660252443435e-06</v>
+        <v>4.6668168801555951e-06</v>
       </c>
       <c r="I24">
-        <v>9.087217792319713e-07</v>
+        <v>1.0298579055546431e-06</v>
       </c>
       <c r="J24">
-        <v>0.00026249820986849612</v>
+        <v>0.00026048345453684294</v>
       </c>
       <c r="K24">
-        <v>0.00054686572298210767</v>
+        <v>0.00053309040145493457</v>
       </c>
       <c r="L24">
-        <v>0.00070736538284481331</v>
+        <v>0.00068796758865905753</v>
       </c>
       <c r="M24">
-        <v>0.00072541972682367735</v>
+        <v>0.00070394648932827343</v>
       </c>
       <c r="N24">
-        <v>3.8876075961376768e-05</v>
+        <v>3.49400894387941e-05</v>
       </c>
       <c r="O24">
-        <v>5.7559167331081122e-05</v>
+        <v>5.7268536675292722e-05</v>
       </c>
       <c r="P24">
-        <v>-7.3381672070635059e-05</v>
+        <v>-7.1081519411094965e-05</v>
       </c>
       <c r="Q24">
-        <v>4.479010644990466e-05</v>
+        <v>4.0463187050596504e-05</v>
       </c>
       <c r="R24">
-        <v>-0.00015884221803105428</v>
+        <v>-0.00015561471402370121</v>
       </c>
       <c r="S24">
-        <v>-0.00012818933719486122</v>
+        <v>-0.00012344804578653132</v>
       </c>
       <c r="T24">
-        <v>-4.7239067074631937e-06</v>
+        <v>-4.9837274017593888e-06</v>
       </c>
       <c r="U24">
-        <v>-7.0768431516283677e-07</v>
+        <v>-7.1447459469946505e-07</v>
       </c>
       <c r="V24">
-        <v>-0.00014192090778209941</v>
+        <v>-0.00013708649300372681</v>
       </c>
       <c r="W24">
-        <v>2.2161272781502884e-05</v>
+        <v>2.1148253325507254e-05</v>
       </c>
       <c r="X24">
-        <v>-0.0051312155197763493</v>
+        <v>-0.0049476127376636399</v>
       </c>
       <c r="Y24">
-        <v>0.0034041640890603319</v>
+        <v>0.003295738331562948</v>
       </c>
     </row>
   </sheetData>
@@ -5666,76 +5666,76 @@
         <v>46</v>
       </c>
       <c r="B2">
-        <v>0.86975088072294982</v>
+        <v>0.87017358620909802</v>
       </c>
       <c r="C2">
-        <v>3.7493092483746337e-06</v>
+        <v>3.7455901031321337e-06</v>
       </c>
       <c r="D2">
-        <v>-2.6020684252774799e-08</v>
+        <v>-2.5463292484954859e-08</v>
       </c>
       <c r="E2">
-        <v>-4.0356222855670436e-10</v>
+        <v>-4.0951449339564105e-10</v>
       </c>
       <c r="F2">
-        <v>-5.6546087702198896e-08</v>
+        <v>-6.153843641284571e-08</v>
       </c>
       <c r="G2">
-        <v>-1.5564906990507795e-07</v>
+        <v>-1.4658504722214993e-07</v>
       </c>
       <c r="H2">
-        <v>2.3649609794356989e-08</v>
+        <v>2.3666873668032104e-08</v>
       </c>
       <c r="I2">
-        <v>3.8848045755767354e-08</v>
+        <v>3.8570960307743966e-08</v>
       </c>
       <c r="J2">
-        <v>4.7915313652132934e-07</v>
+        <v>4.8925797649863998e-07</v>
       </c>
       <c r="K2">
-        <v>8.3409089714013324e-07</v>
+        <v>8.3888762870922126e-07</v>
       </c>
       <c r="L2">
-        <v>6.8138721747397799e-07</v>
+        <v>6.8538715174851297e-07</v>
       </c>
       <c r="M2">
-        <v>5.4874956897907983e-07</v>
+        <v>5.5294709581041855e-07</v>
       </c>
       <c r="N2">
-        <v>-5.8330687499419406e-07</v>
+        <v>-5.8003277200696815e-07</v>
       </c>
       <c r="O2">
-        <v>-5.9153659494403362e-07</v>
+        <v>-5.8881656735429783e-07</v>
       </c>
       <c r="P2">
-        <v>6.1276383870881833e-08</v>
+        <v>6.1025194298369335e-08</v>
       </c>
       <c r="Q2">
-        <v>-3.9080372082962989e-07</v>
+        <v>-3.8608326960992045e-07</v>
       </c>
       <c r="R2">
-        <v>-1.422498135683048e-07</v>
+        <v>-1.3943567657905874e-07</v>
       </c>
       <c r="S2">
-        <v>3.831574188680449e-08</v>
+        <v>3.8573716394313458e-08</v>
       </c>
       <c r="T2">
-        <v>-1.3980890365962598e-07</v>
+        <v>-1.3616001575206501e-07</v>
       </c>
       <c r="U2">
-        <v>1.7995809731197625e-08</v>
+        <v>1.7756957830991322e-08</v>
       </c>
       <c r="V2">
-        <v>3.4055850287699676e-09</v>
+        <v>5.1035991310827435e-09</v>
       </c>
       <c r="W2">
-        <v>2.873535427769429e-07</v>
+        <v>2.8507987742309056e-07</v>
       </c>
       <c r="X2">
-        <v>-1.0213282233439339e-05</v>
+        <v>-1.0197283313057048e-05</v>
       </c>
       <c r="Y2">
-        <v>3.305903920989959e-06</v>
+        <v>3.3161199978792739e-06</v>
       </c>
     </row>
     <row r="3">
@@ -5743,76 +5743,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-0.0049820258574171236</v>
+        <v>-0.0048665801789393491</v>
       </c>
       <c r="C3">
-        <v>-2.6020684252774799e-08</v>
+        <v>-2.5463292484954859e-08</v>
       </c>
       <c r="D3">
-        <v>6.4920014096326296e-06</v>
+        <v>6.5073716825911249e-06</v>
       </c>
       <c r="E3">
-        <v>-7.2217789537414341e-08</v>
+        <v>-7.2416707469989917e-08</v>
       </c>
       <c r="F3">
-        <v>-4.4837722738557759e-06</v>
+        <v>-4.480861275071764e-06</v>
       </c>
       <c r="G3">
-        <v>-8.4319290491743917e-06</v>
+        <v>-8.3356795039817963e-06</v>
       </c>
       <c r="H3">
-        <v>4.9617903803808591e-08</v>
+        <v>4.9740142691177389e-08</v>
       </c>
       <c r="I3">
-        <v>3.6304586080088117e-08</v>
+        <v>3.4849343180374809e-08</v>
       </c>
       <c r="J3">
-        <v>8.2975147555771073e-06</v>
+        <v>8.2368135458373971e-06</v>
       </c>
       <c r="K3">
-        <v>2.6866290794447383e-05</v>
+        <v>2.6953325434801304e-05</v>
       </c>
       <c r="L3">
-        <v>3.2519824450121845e-05</v>
+        <v>3.2559579366196956e-05</v>
       </c>
       <c r="M3">
-        <v>3.3966365713674791e-05</v>
+        <v>3.3971187998804516e-05</v>
       </c>
       <c r="N3">
-        <v>1.5008711439621603e-06</v>
+        <v>1.5036292876598443e-06</v>
       </c>
       <c r="O3">
-        <v>6.2949577764948125e-07</v>
+        <v>6.5816325992677467e-07</v>
       </c>
       <c r="P3">
-        <v>-1.6847509287975427e-06</v>
+        <v>-1.7229465559257723e-06</v>
       </c>
       <c r="Q3">
-        <v>6.4996117400315975e-07</v>
+        <v>7.2656055996105918e-07</v>
       </c>
       <c r="R3">
-        <v>-2.9823135974582155e-06</v>
+        <v>-2.9946641593910616e-06</v>
       </c>
       <c r="S3">
-        <v>-4.0738935503178311e-06</v>
+        <v>-3.982745131600678e-06</v>
       </c>
       <c r="T3">
-        <v>-1.4884043431229844e-07</v>
+        <v>-1.4916558131902089e-07</v>
       </c>
       <c r="U3">
-        <v>-5.9045169121804041e-08</v>
+        <v>-5.9322263142227653e-08</v>
       </c>
       <c r="V3">
-        <v>-1.452944066437684e-06</v>
+        <v>-1.4179535737706194e-06</v>
       </c>
       <c r="W3">
-        <v>2.1899198775295396e-06</v>
+        <v>2.2710943231992687e-06</v>
       </c>
       <c r="X3">
-        <v>-0.00017668152883912151</v>
+        <v>-0.00017703334712202291</v>
       </c>
       <c r="Y3">
-        <v>9.8922400228267234e-05</v>
+        <v>9.9138062489961595e-05</v>
       </c>
     </row>
     <row r="4">
@@ -5820,76 +5820,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>6.8657210371679092e-05</v>
+        <v>6.7041355936394044e-05</v>
       </c>
       <c r="C4">
-        <v>-4.0356222855670436e-10</v>
+        <v>-4.0951449339564105e-10</v>
       </c>
       <c r="D4">
-        <v>-7.2217789537414341e-08</v>
+        <v>-7.2416707469989917e-08</v>
       </c>
       <c r="E4">
-        <v>8.0783068173369531e-10</v>
+        <v>8.1033704916334342e-10</v>
       </c>
       <c r="F4">
-        <v>6.7352991174450275e-08</v>
+        <v>6.7267003722120364e-08</v>
       </c>
       <c r="G4">
-        <v>1.115918906753979e-07</v>
+        <v>1.1047217740933634e-07</v>
       </c>
       <c r="H4">
-        <v>-9.381530559641011e-10</v>
+        <v>-9.3810170809264214e-10</v>
       </c>
       <c r="I4">
-        <v>-7.9209737482479619e-10</v>
+        <v>-7.7421132900690928e-10</v>
       </c>
       <c r="J4">
-        <v>-9.3060084178158029e-08</v>
+        <v>-9.2429786711935274e-08</v>
       </c>
       <c r="K4">
-        <v>-3.006834914001377e-07</v>
+        <v>-3.0177878272469431e-07</v>
       </c>
       <c r="L4">
-        <v>-3.6338290619828779e-07</v>
+        <v>-3.6397429834765903e-07</v>
       </c>
       <c r="M4">
-        <v>-3.7868040509728426e-07</v>
+        <v>-3.7888996188288361e-07</v>
       </c>
       <c r="N4">
-        <v>-1.6599433517581187e-08</v>
+        <v>-1.6641427075731853e-08</v>
       </c>
       <c r="O4">
-        <v>-6.7970503252989376e-09</v>
+        <v>-7.1259114761369133e-09</v>
       </c>
       <c r="P4">
-        <v>1.8897972135137436e-08</v>
+        <v>1.9333394750823933e-08</v>
       </c>
       <c r="Q4">
-        <v>-7.118513568822003e-09</v>
+        <v>-7.9789545272392282e-09</v>
       </c>
       <c r="R4">
-        <v>3.3364712290748938e-08</v>
+        <v>3.351655658874889e-08</v>
       </c>
       <c r="S4">
-        <v>4.5498903101837152e-08</v>
+        <v>4.4495924518943013e-08</v>
       </c>
       <c r="T4">
-        <v>1.7297438270260241e-09</v>
+        <v>1.7209266169577375e-09</v>
       </c>
       <c r="U4">
-        <v>5.8630657187560685e-10</v>
+        <v>5.8964105650822177e-10</v>
       </c>
       <c r="V4">
-        <v>1.6429437300475129e-08</v>
+        <v>1.604853022048258e-08</v>
       </c>
       <c r="W4">
-        <v>-2.4375005538066314e-08</v>
+        <v>-2.5291826489466105e-08</v>
       </c>
       <c r="X4">
-        <v>1.9668894929256238e-06</v>
+        <v>1.9716172634088894e-06</v>
       </c>
       <c r="Y4">
-        <v>-1.1072361420490673e-06</v>
+        <v>-1.1100836137402527e-06</v>
       </c>
     </row>
     <row r="5">
@@ -5897,76 +5897,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>0.00057550558606304036</v>
+        <v>0.00024173886216620106</v>
       </c>
       <c r="C5">
-        <v>-5.6546087702198896e-08</v>
+        <v>-6.153843641284571e-08</v>
       </c>
       <c r="D5">
-        <v>-4.4837722738557759e-06</v>
+        <v>-4.480861275071764e-06</v>
       </c>
       <c r="E5">
-        <v>6.7352991174450275e-08</v>
+        <v>6.7267003722120364e-08</v>
       </c>
       <c r="F5">
-        <v>0.00019444848296790355</v>
+        <v>0.00019341263693941263</v>
       </c>
       <c r="G5">
-        <v>8.4814638127603186e-05</v>
+        <v>8.4248092696034642e-05</v>
       </c>
       <c r="H5">
-        <v>-4.0125967802973832e-06</v>
+        <v>-3.9914814545206835e-06</v>
       </c>
       <c r="I5">
-        <v>-1.6139445221402664e-06</v>
+        <v>-1.6039339703295172e-06</v>
       </c>
       <c r="J5">
-        <v>-9.0649502230944772e-06</v>
+        <v>-8.9553040723459494e-06</v>
       </c>
       <c r="K5">
-        <v>-3.1167343615661486e-05</v>
+        <v>-3.1086386551006157e-05</v>
       </c>
       <c r="L5">
-        <v>-3.8148457151824427e-05</v>
+        <v>-3.795370018976658e-05</v>
       </c>
       <c r="M5">
-        <v>-3.9089452174247567e-05</v>
+        <v>-3.8854351100365799e-05</v>
       </c>
       <c r="N5">
-        <v>-1.1531209037193306e-06</v>
+        <v>-1.1600766546879222e-06</v>
       </c>
       <c r="O5">
-        <v>3.1617444695255206e-07</v>
+        <v>2.6392529109500689e-07</v>
       </c>
       <c r="P5">
-        <v>2.2974523175395136e-06</v>
+        <v>2.3286671552412344e-06</v>
       </c>
       <c r="Q5">
-        <v>-9.3083412858741814e-09</v>
+        <v>-8.9670787633987661e-08</v>
       </c>
       <c r="R5">
-        <v>3.1103810922205245e-06</v>
+        <v>3.1152569640727955e-06</v>
       </c>
       <c r="S5">
-        <v>3.7063988518787839e-06</v>
+        <v>3.5982889772311151e-06</v>
       </c>
       <c r="T5">
-        <v>4.0098069644085504e-07</v>
+        <v>3.5299432809711229e-07</v>
       </c>
       <c r="U5">
-        <v>2.4936636386985689e-07</v>
+        <v>2.4931418402225249e-07</v>
       </c>
       <c r="V5">
-        <v>1.0631059525672129e-06</v>
+        <v>1.034060772953959e-06</v>
       </c>
       <c r="W5">
-        <v>-2.8934685905956172e-06</v>
+        <v>-2.9696244576241511e-06</v>
       </c>
       <c r="X5">
-        <v>8.0744572336243663e-05</v>
+        <v>8.0645816439924495e-05</v>
       </c>
       <c r="Y5">
-        <v>-0.00011561373723827647</v>
+        <v>-0.00011514442612879788</v>
       </c>
     </row>
     <row r="6">
@@ -5974,76 +5974,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.021546442268283984</v>
+        <v>-0.020111811919564539</v>
       </c>
       <c r="C6">
-        <v>-1.5564906990507795e-07</v>
+        <v>-1.4658504722214993e-07</v>
       </c>
       <c r="D6">
-        <v>-8.4319290491743917e-06</v>
+        <v>-8.3356795039817963e-06</v>
       </c>
       <c r="E6">
-        <v>1.115918906753979e-07</v>
+        <v>1.1047217740933634e-07</v>
       </c>
       <c r="F6">
-        <v>8.4814638127603186e-05</v>
+        <v>8.4248092696034642e-05</v>
       </c>
       <c r="G6">
-        <v>0.00017525938764336856</v>
+        <v>0.00017403856557860958</v>
       </c>
       <c r="H6">
-        <v>-1.7071555804151653e-06</v>
+        <v>-1.6966345331117696e-06</v>
       </c>
       <c r="I6">
-        <v>-3.3705387204697344e-06</v>
+        <v>-3.3497169152026212e-06</v>
       </c>
       <c r="J6">
-        <v>-1.2704703787767528e-05</v>
+        <v>-1.2443517541754958e-05</v>
       </c>
       <c r="K6">
-        <v>-4.7004137331979826e-05</v>
+        <v>-4.6492343909083125e-05</v>
       </c>
       <c r="L6">
-        <v>-5.7622802465991116e-05</v>
+        <v>-5.6872610648825668e-05</v>
       </c>
       <c r="M6">
-        <v>-5.8372642374019188e-05</v>
+        <v>-5.7540628449669062e-05</v>
       </c>
       <c r="N6">
-        <v>-1.7211455778821662e-06</v>
+        <v>-1.718195227079201e-06</v>
       </c>
       <c r="O6">
-        <v>-3.3538541482072645e-08</v>
+        <v>-1.0186513479947145e-07</v>
       </c>
       <c r="P6">
-        <v>2.3179724315835008e-06</v>
+        <v>2.3353047554062051e-06</v>
       </c>
       <c r="Q6">
-        <v>-1.330157009369033e-06</v>
+        <v>-1.455739284230507e-06</v>
       </c>
       <c r="R6">
-        <v>3.1106497498038197e-06</v>
+        <v>3.0649153366343928e-06</v>
       </c>
       <c r="S6">
-        <v>5.6190447616348639e-06</v>
+        <v>5.3510251537816151e-06</v>
       </c>
       <c r="T6">
-        <v>1.3148158607457092e-06</v>
+        <v>1.2574795862726638e-06</v>
       </c>
       <c r="U6">
-        <v>2.9566211107643744e-07</v>
+        <v>2.932464162576188e-07</v>
       </c>
       <c r="V6">
-        <v>2.12955715060847e-06</v>
+        <v>2.0490153751788601e-06</v>
       </c>
       <c r="W6">
-        <v>-4.1967795708656656e-06</v>
+        <v>-4.2763502427032355e-06</v>
       </c>
       <c r="X6">
-        <v>0.00018616673067599869</v>
+        <v>0.0001835639333458929</v>
       </c>
       <c r="Y6">
-        <v>-0.00017212153293463017</v>
+        <v>-0.00017005070667945835</v>
       </c>
     </row>
     <row r="7">
@@ -6051,76 +6051,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.00084380521135939493</v>
+        <v>-0.00083520240690028663</v>
       </c>
       <c r="C7">
-        <v>2.3649609794356989e-08</v>
+        <v>2.3666873668032104e-08</v>
       </c>
       <c r="D7">
-        <v>4.9617903803808591e-08</v>
+        <v>4.9740142691177389e-08</v>
       </c>
       <c r="E7">
-        <v>-9.381530559641011e-10</v>
+        <v>-9.3810170809264214e-10</v>
       </c>
       <c r="F7">
-        <v>-4.0125967802973832e-06</v>
+        <v>-3.9914814545206835e-06</v>
       </c>
       <c r="G7">
-        <v>-1.7071555804151653e-06</v>
+        <v>-1.6966345331117696e-06</v>
       </c>
       <c r="H7">
-        <v>8.7435946642852617e-08</v>
+        <v>8.6972559181136112e-08</v>
       </c>
       <c r="I7">
-        <v>3.5288465635049357e-08</v>
+        <v>3.5083290526457424e-08</v>
       </c>
       <c r="J7">
-        <v>1.2668275442650656e-07</v>
+        <v>1.2541440639258442e-07</v>
       </c>
       <c r="K7">
-        <v>4.4789464588845343e-07</v>
+        <v>4.4705360808838321e-07</v>
       </c>
       <c r="L7">
-        <v>5.5831176476437219e-07</v>
+        <v>5.5569958767979785e-07</v>
       </c>
       <c r="M7">
-        <v>5.7120364065679443e-07</v>
+        <v>5.6801944588276739e-07</v>
       </c>
       <c r="N7">
-        <v>1.0845928954749191e-08</v>
+        <v>1.1120579529753495e-08</v>
       </c>
       <c r="O7">
-        <v>-7.8863308380046609e-09</v>
+        <v>-6.9999057907504329e-09</v>
       </c>
       <c r="P7">
-        <v>-3.7810072888058567e-08</v>
+        <v>-3.8247518384853388e-08</v>
       </c>
       <c r="Q7">
-        <v>-7.5861303317833193e-09</v>
+        <v>-6.3952851757562133e-09</v>
       </c>
       <c r="R7">
-        <v>-4.5723386324652696e-08</v>
+        <v>-4.5839516851015402e-08</v>
       </c>
       <c r="S7">
-        <v>-4.6432332062957618e-08</v>
+        <v>-4.5019511668339298e-08</v>
       </c>
       <c r="T7">
-        <v>3.6740225890595579e-09</v>
+        <v>4.6211833496374502e-09</v>
       </c>
       <c r="U7">
-        <v>-3.2473049249459306e-09</v>
+        <v>-3.2577914551374159e-09</v>
       </c>
       <c r="V7">
-        <v>-1.7905531805868269e-08</v>
+        <v>-1.7619596333339717e-08</v>
       </c>
       <c r="W7">
-        <v>4.2667883946027046e-08</v>
+        <v>4.3787616223116093e-08</v>
       </c>
       <c r="X7">
-        <v>-7.0436012023153355e-07</v>
+        <v>-7.0655734668493626e-07</v>
       </c>
       <c r="Y7">
-        <v>1.6868593373019716e-06</v>
+        <v>1.6808773836413849e-06</v>
       </c>
     </row>
     <row r="8">
@@ -6128,76 +6128,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>-0.00070010586150180882</v>
+        <v>-0.00072814448933075963</v>
       </c>
       <c r="C8">
-        <v>3.8848045755767354e-08</v>
+        <v>3.8570960307743966e-08</v>
       </c>
       <c r="D8">
-        <v>3.6304586080088117e-08</v>
+        <v>3.4849343180374809e-08</v>
       </c>
       <c r="E8">
-        <v>-7.9209737482479619e-10</v>
+        <v>-7.7421132900690928e-10</v>
       </c>
       <c r="F8">
-        <v>-1.6139445221402664e-06</v>
+        <v>-1.6039339703295172e-06</v>
       </c>
       <c r="G8">
-        <v>-3.3705387204697344e-06</v>
+        <v>-3.3497169152026212e-06</v>
       </c>
       <c r="H8">
-        <v>3.5288465635049357e-08</v>
+        <v>3.5083290526457424e-08</v>
       </c>
       <c r="I8">
-        <v>7.1668537277623062e-08</v>
+        <v>7.1268068892854593e-08</v>
       </c>
       <c r="J8">
-        <v>6.8052189089356633e-08</v>
+        <v>6.5440398918909037e-08</v>
       </c>
       <c r="K8">
-        <v>3.351880387446948e-07</v>
+        <v>3.2708854311942424e-07</v>
       </c>
       <c r="L8">
-        <v>4.3107311852507323e-07</v>
+        <v>4.2003867497536045e-07</v>
       </c>
       <c r="M8">
-        <v>4.2446323942422309e-07</v>
+        <v>4.1268133804249056e-07</v>
       </c>
       <c r="N8">
-        <v>1.3306708774711502e-09</v>
+        <v>1.4466355660548216e-09</v>
       </c>
       <c r="O8">
-        <v>-5.4217143545375601e-09</v>
+        <v>-4.6893273287719084e-09</v>
       </c>
       <c r="P8">
-        <v>-2.010986336759991e-08</v>
+        <v>-1.9756728060537573e-08</v>
       </c>
       <c r="Q8">
-        <v>9.1743366550895453e-09</v>
+        <v>1.0074088770675369e-08</v>
       </c>
       <c r="R8">
-        <v>-6.8766190139455755e-09</v>
+        <v>-6.0002379425467037e-09</v>
       </c>
       <c r="S8">
-        <v>-1.7199568806099296e-08</v>
+        <v>-1.4550934089842533e-08</v>
       </c>
       <c r="T8">
-        <v>-1.0865355455699018e-09</v>
+        <v>-9.5673130677360808e-11</v>
       </c>
       <c r="U8">
-        <v>-8.8413202586812228e-10</v>
+        <v>-8.6722433636599614e-10</v>
       </c>
       <c r="V8">
-        <v>-2.1145732159066031e-08</v>
+        <v>-2.0522554097975296e-08</v>
       </c>
       <c r="W8">
-        <v>2.7448085571362176e-08</v>
+        <v>2.7595347401232782e-08</v>
       </c>
       <c r="X8">
-        <v>-5.1289073447274079e-07</v>
+        <v>-4.727051714262155e-07</v>
       </c>
       <c r="Y8">
-        <v>1.192513436268208e-06</v>
+        <v>1.1616178523498549e-06</v>
       </c>
     </row>
     <row r="9">
@@ -6205,76 +6205,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>-0.018317645453312267</v>
+        <v>-0.014531997590364847</v>
       </c>
       <c r="C9">
-        <v>4.7915313652132934e-07</v>
+        <v>4.8925797649863998e-07</v>
       </c>
       <c r="D9">
-        <v>8.2975147555771073e-06</v>
+        <v>8.2368135458373971e-06</v>
       </c>
       <c r="E9">
-        <v>-9.3060084178158029e-08</v>
+        <v>-9.2429786711935274e-08</v>
       </c>
       <c r="F9">
-        <v>-9.0649502230944772e-06</v>
+        <v>-8.9553040723459494e-06</v>
       </c>
       <c r="G9">
-        <v>-1.2704703787767528e-05</v>
+        <v>-1.2443517541754958e-05</v>
       </c>
       <c r="H9">
-        <v>1.2668275442650656e-07</v>
+        <v>1.2541440639258442e-07</v>
       </c>
       <c r="I9">
-        <v>6.8052189089356633e-08</v>
+        <v>6.5440398918909037e-08</v>
       </c>
       <c r="J9">
-        <v>0.0006089531188407328</v>
+        <v>0.00060598829116597286</v>
       </c>
       <c r="K9">
-        <v>0.00054469028556392691</v>
+        <v>0.00054196441322601399</v>
       </c>
       <c r="L9">
-        <v>0.00055267386829419116</v>
+        <v>0.00054979407451874744</v>
       </c>
       <c r="M9">
-        <v>0.00055427776517151268</v>
+        <v>0.00055132595463684903</v>
       </c>
       <c r="N9">
-        <v>2.7449286249292225e-06</v>
+        <v>2.7346483213481995e-06</v>
       </c>
       <c r="O9">
-        <v>1.5205527580832647e-06</v>
+        <v>1.5527966575267211e-06</v>
       </c>
       <c r="P9">
-        <v>-2.4602292046622618e-06</v>
+        <v>-2.4853306939663024e-06</v>
       </c>
       <c r="Q9">
-        <v>1.159232439146969e-06</v>
+        <v>1.2664181213836998e-06</v>
       </c>
       <c r="R9">
-        <v>-3.9142690101402254e-06</v>
+        <v>-3.8886348389328e-06</v>
       </c>
       <c r="S9">
-        <v>-4.9740430826625885e-06</v>
+        <v>-4.7875920425684822e-06</v>
       </c>
       <c r="T9">
-        <v>-5.4990974310952464e-07</v>
+        <v>-5.2449917965968779e-07</v>
       </c>
       <c r="U9">
-        <v>-8.7998620831458841e-09</v>
+        <v>-7.1393510156707709e-09</v>
       </c>
       <c r="V9">
-        <v>-2.1678559648716723e-06</v>
+        <v>-2.0758039924247681e-06</v>
       </c>
       <c r="W9">
-        <v>3.010978595897957e-06</v>
+        <v>3.0880766929247896e-06</v>
       </c>
       <c r="X9">
-        <v>-0.00074523114350746617</v>
+        <v>-0.00074109057269741187</v>
       </c>
       <c r="Y9">
-        <v>0.000141595968505922</v>
+        <v>0.00014047524971138209</v>
       </c>
     </row>
     <row r="10">
@@ -6282,76 +6282,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>-0.026376237821834969</v>
+        <v>-0.02487462373328999</v>
       </c>
       <c r="C10">
-        <v>8.3409089714013324e-07</v>
+        <v>8.3888762870922126e-07</v>
       </c>
       <c r="D10">
-        <v>2.6866290794447383e-05</v>
+        <v>2.6953325434801304e-05</v>
       </c>
       <c r="E10">
-        <v>-3.006834914001377e-07</v>
+        <v>-3.0177878272469431e-07</v>
       </c>
       <c r="F10">
-        <v>-3.1167343615661486e-05</v>
+        <v>-3.1086386551006157e-05</v>
       </c>
       <c r="G10">
-        <v>-4.7004137331979826e-05</v>
+        <v>-4.6492343909083125e-05</v>
       </c>
       <c r="H10">
-        <v>4.4789464588845343e-07</v>
+        <v>4.4705360808838321e-07</v>
       </c>
       <c r="I10">
-        <v>3.351880387446948e-07</v>
+        <v>3.2708854311942424e-07</v>
       </c>
       <c r="J10">
-        <v>0.00054469028556392691</v>
+        <v>0.00054196441322601399</v>
       </c>
       <c r="K10">
-        <v>0.00064350435838150214</v>
+        <v>0.00064138700202582514</v>
       </c>
       <c r="L10">
-        <v>0.00065986188304341766</v>
+        <v>0.00065758719751453343</v>
       </c>
       <c r="M10">
-        <v>0.00066559637746996551</v>
+        <v>0.00066315717131365916</v>
       </c>
       <c r="N10">
-        <v>7.4164454368304886e-06</v>
+        <v>7.4326802505971126e-06</v>
       </c>
       <c r="O10">
-        <v>3.0157035244512283e-06</v>
+        <v>3.1597114751417542e-06</v>
       </c>
       <c r="P10">
-        <v>-8.5038717859722384e-06</v>
+        <v>-8.6803020372593287e-06</v>
       </c>
       <c r="Q10">
-        <v>2.8040376653474367e-06</v>
+        <v>3.1666317932371666e-06</v>
       </c>
       <c r="R10">
-        <v>-1.4226247799795768e-05</v>
+        <v>-1.4285871858542221e-05</v>
       </c>
       <c r="S10">
-        <v>-1.8938739548977797e-05</v>
+        <v>-1.850849768843195e-05</v>
       </c>
       <c r="T10">
-        <v>-1.7434364261560208e-06</v>
+        <v>-1.7110847861158479e-06</v>
       </c>
       <c r="U10">
-        <v>-2.584254374300843e-07</v>
+        <v>-2.5820740980031268e-07</v>
       </c>
       <c r="V10">
-        <v>-6.5833724288756769e-06</v>
+        <v>-6.4241339447724978e-06</v>
       </c>
       <c r="W10">
-        <v>1.0329262700234433e-05</v>
+        <v>1.0701347380193287e-05</v>
       </c>
       <c r="X10">
-        <v>-0.0012597000370176302</v>
+        <v>-0.0012593773847295185</v>
       </c>
       <c r="Y10">
-        <v>0.00046583080152770096</v>
+        <v>0.00046685688466352557</v>
       </c>
     </row>
     <row r="11">
@@ -6359,76 +6359,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.022803440788909155</v>
+        <v>-0.021021141132617598</v>
       </c>
       <c r="C11">
-        <v>6.8138721747397799e-07</v>
+        <v>6.8538715174851297e-07</v>
       </c>
       <c r="D11">
-        <v>3.2519824450121845e-05</v>
+        <v>3.2559579366196956e-05</v>
       </c>
       <c r="E11">
-        <v>-3.6338290619828779e-07</v>
+        <v>-3.6397429834765903e-07</v>
       </c>
       <c r="F11">
-        <v>-3.8148457151824427e-05</v>
+        <v>-3.795370018976658e-05</v>
       </c>
       <c r="G11">
-        <v>-5.7622802465991116e-05</v>
+        <v>-5.6872610648825668e-05</v>
       </c>
       <c r="H11">
-        <v>5.5831176476437219e-07</v>
+        <v>5.5569958767979785e-07</v>
       </c>
       <c r="I11">
-        <v>4.3107311852507323e-07</v>
+        <v>4.2003867497536045e-07</v>
       </c>
       <c r="J11">
-        <v>0.00055267386829419116</v>
+        <v>0.00054979407451874744</v>
       </c>
       <c r="K11">
-        <v>0.00065986188304341766</v>
+        <v>0.00065758719751453343</v>
       </c>
       <c r="L11">
-        <v>0.00069500881340959911</v>
+        <v>0.00069237850847714527</v>
       </c>
       <c r="M11">
-        <v>0.00070016236595029085</v>
+        <v>0.00069733177691196969</v>
       </c>
       <c r="N11">
-        <v>8.7874293070027796e-06</v>
+        <v>8.7896769042137928e-06</v>
       </c>
       <c r="O11">
-        <v>3.5077856709944612e-06</v>
+        <v>3.6739617881226561e-06</v>
       </c>
       <c r="P11">
-        <v>-1.0484730405781603e-05</v>
+        <v>-1.0679105414866754e-05</v>
       </c>
       <c r="Q11">
-        <v>3.3239401602094616e-06</v>
+        <v>3.7543648000603331e-06</v>
       </c>
       <c r="R11">
-        <v>-1.7420948205828125e-05</v>
+        <v>-1.7459201745622419e-05</v>
       </c>
       <c r="S11">
-        <v>-2.2579347144171473e-05</v>
+        <v>-2.2014309702910317e-05</v>
       </c>
       <c r="T11">
-        <v>-2.031040103899715e-06</v>
+        <v>-1.9905403501951961e-06</v>
       </c>
       <c r="U11">
-        <v>-2.6388657331497087e-07</v>
+        <v>-2.6312521255255998e-07</v>
       </c>
       <c r="V11">
-        <v>-8.4177487108553692e-06</v>
+        <v>-8.2059366754182249e-06</v>
       </c>
       <c r="W11">
-        <v>1.2496710816861038e-05</v>
+        <v>1.2921121850759924e-05</v>
       </c>
       <c r="X11">
-        <v>-0.0014246005271922877</v>
+        <v>-0.0014228667256926284</v>
       </c>
       <c r="Y11">
-        <v>0.00056448322647335619</v>
+        <v>0.0005645798539305638</v>
       </c>
     </row>
     <row r="12">
@@ -6436,76 +6436,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>-0.015940442378472451</v>
+        <v>-0.014622398185052857</v>
       </c>
       <c r="C12">
-        <v>5.4874956897907983e-07</v>
+        <v>5.5294709581041855e-07</v>
       </c>
       <c r="D12">
-        <v>3.3966365713674791e-05</v>
+        <v>3.3971187998804516e-05</v>
       </c>
       <c r="E12">
-        <v>-3.7868040509728426e-07</v>
+        <v>-3.7888996188288361e-07</v>
       </c>
       <c r="F12">
-        <v>-3.9089452174247567e-05</v>
+        <v>-3.8854351100365799e-05</v>
       </c>
       <c r="G12">
-        <v>-5.8372642374019188e-05</v>
+        <v>-5.7540628449669062e-05</v>
       </c>
       <c r="H12">
-        <v>5.7120364065679443e-07</v>
+        <v>5.6801944588276739e-07</v>
       </c>
       <c r="I12">
-        <v>4.2446323942422309e-07</v>
+        <v>4.1268133804249056e-07</v>
       </c>
       <c r="J12">
-        <v>0.00055427776517151268</v>
+        <v>0.00055132595463684903</v>
       </c>
       <c r="K12">
-        <v>0.00066559637746996551</v>
+        <v>0.00066315717131365916</v>
       </c>
       <c r="L12">
-        <v>0.00070016236595029085</v>
+        <v>0.00069733177691196969</v>
       </c>
       <c r="M12">
-        <v>0.00071533295645487824</v>
+        <v>0.000712224200245616</v>
       </c>
       <c r="N12">
-        <v>8.8381051002626628e-06</v>
+        <v>8.8296282929386885e-06</v>
       </c>
       <c r="O12">
-        <v>3.2529216484541024e-06</v>
+        <v>3.4221150019848024e-06</v>
       </c>
       <c r="P12">
-        <v>-1.0936252240624855e-05</v>
+        <v>-1.1124134926433122e-05</v>
       </c>
       <c r="Q12">
-        <v>2.8834708102124759e-06</v>
+        <v>3.3285040425201515e-06</v>
       </c>
       <c r="R12">
-        <v>-1.8552351795101257e-05</v>
+        <v>-1.8570030123922372e-05</v>
       </c>
       <c r="S12">
-        <v>-2.4202830423442321e-05</v>
+        <v>-2.358920133953951e-05</v>
       </c>
       <c r="T12">
-        <v>-2.236052886520916e-06</v>
+        <v>-2.1960887191663948e-06</v>
       </c>
       <c r="U12">
-        <v>-2.3967346192380434e-07</v>
+        <v>-2.3925477211716713e-07</v>
       </c>
       <c r="V12">
-        <v>-8.988114897224455e-06</v>
+        <v>-8.7545917942057211e-06</v>
       </c>
       <c r="W12">
-        <v>1.2692324832023408e-05</v>
+        <v>1.3121135840477063e-05</v>
       </c>
       <c r="X12">
-        <v>-0.0014689048567187229</v>
+        <v>-0.0014660988908250169</v>
       </c>
       <c r="Y12">
-        <v>0.00058550601628740693</v>
+        <v>0.00058498233402656883</v>
       </c>
     </row>
     <row r="13">
@@ -6513,76 +6513,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.022874529471946091</v>
+        <v>0.022964240666390159</v>
       </c>
       <c r="C13">
-        <v>-5.8330687499419406e-07</v>
+        <v>-5.8003277200696815e-07</v>
       </c>
       <c r="D13">
-        <v>1.5008711439621603e-06</v>
+        <v>1.5036292876598443e-06</v>
       </c>
       <c r="E13">
-        <v>-1.6599433517581187e-08</v>
+        <v>-1.6641427075731853e-08</v>
       </c>
       <c r="F13">
-        <v>-1.1531209037193306e-06</v>
+        <v>-1.1600766546879222e-06</v>
       </c>
       <c r="G13">
-        <v>-1.7211455778821662e-06</v>
+        <v>-1.718195227079201e-06</v>
       </c>
       <c r="H13">
-        <v>1.0845928954749191e-08</v>
+        <v>1.1120579529753495e-08</v>
       </c>
       <c r="I13">
-        <v>1.3306708774711502e-09</v>
+        <v>1.4466355660548216e-09</v>
       </c>
       <c r="J13">
-        <v>2.7449286249292225e-06</v>
+        <v>2.7346483213481995e-06</v>
       </c>
       <c r="K13">
-        <v>7.4164454368304886e-06</v>
+        <v>7.4326802505971126e-06</v>
       </c>
       <c r="L13">
-        <v>8.7874293070027796e-06</v>
+        <v>8.7896769042137928e-06</v>
       </c>
       <c r="M13">
-        <v>8.8381051002626628e-06</v>
+        <v>8.8296282929386885e-06</v>
       </c>
       <c r="N13">
-        <v>2.0050047062684238e-05</v>
+        <v>1.992162358159755e-05</v>
       </c>
       <c r="O13">
-        <v>1.1467319450577922e-05</v>
+        <v>1.1399991988973245e-05</v>
       </c>
       <c r="P13">
-        <v>1.0665525592105547e-05</v>
+        <v>1.0582060935247457e-05</v>
       </c>
       <c r="Q13">
-        <v>1.1400605672398986e-05</v>
+        <v>1.1345437508517581e-05</v>
       </c>
       <c r="R13">
-        <v>1.0374560138716969e-05</v>
+        <v>1.0297901050509592e-05</v>
       </c>
       <c r="S13">
-        <v>1.0071096869765839e-05</v>
+        <v>1.0022396901481907e-05</v>
       </c>
       <c r="T13">
-        <v>5.1364467425380882e-08</v>
+        <v>5.8563787207205364e-08</v>
       </c>
       <c r="U13">
-        <v>2.6668127355950781e-08</v>
+        <v>2.6604309960064068e-08</v>
       </c>
       <c r="V13">
-        <v>-4.1325835706299723e-07</v>
+        <v>-4.0764343993739495e-07</v>
       </c>
       <c r="W13">
-        <v>4.014699990072e-07</v>
+        <v>4.1828663820254353e-07</v>
       </c>
       <c r="X13">
-        <v>-5.6539326209574275e-05</v>
+        <v>-5.6518821285302194e-05</v>
       </c>
       <c r="Y13">
-        <v>2.5469938952961809e-05</v>
+        <v>2.5502264548919633e-05</v>
       </c>
     </row>
     <row r="14">
@@ -6590,76 +6590,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.023668422532654585</v>
+        <v>0.023264366460753069</v>
       </c>
       <c r="C14">
-        <v>-5.9153659494403362e-07</v>
+        <v>-5.8881656735429783e-07</v>
       </c>
       <c r="D14">
-        <v>6.2949577764948125e-07</v>
+        <v>6.5816325992677467e-07</v>
       </c>
       <c r="E14">
-        <v>-6.7970503252989376e-09</v>
+        <v>-7.1259114761369133e-09</v>
       </c>
       <c r="F14">
-        <v>3.1617444695255206e-07</v>
+        <v>2.6392529109500689e-07</v>
       </c>
       <c r="G14">
-        <v>-3.3538541482072645e-08</v>
+        <v>-1.0186513479947145e-07</v>
       </c>
       <c r="H14">
-        <v>-7.8863308380046609e-09</v>
+        <v>-6.9999057907504329e-09</v>
       </c>
       <c r="I14">
-        <v>-5.4217143545375601e-09</v>
+        <v>-4.6893273287719084e-09</v>
       </c>
       <c r="J14">
-        <v>1.5205527580832647e-06</v>
+        <v>1.5527966575267211e-06</v>
       </c>
       <c r="K14">
-        <v>3.0157035244512283e-06</v>
+        <v>3.1597114751417542e-06</v>
       </c>
       <c r="L14">
-        <v>3.5077856709944612e-06</v>
+        <v>3.6739617881226561e-06</v>
       </c>
       <c r="M14">
-        <v>3.2529216484541024e-06</v>
+        <v>3.4221150019848024e-06</v>
       </c>
       <c r="N14">
-        <v>1.1467319450577922e-05</v>
+        <v>1.1399991988973245e-05</v>
       </c>
       <c r="O14">
-        <v>2.4121605495951048e-05</v>
+        <v>2.3970345558452938e-05</v>
       </c>
       <c r="P14">
-        <v>1.0924164319234877e-05</v>
+        <v>1.083787138639576e-05</v>
       </c>
       <c r="Q14">
-        <v>1.1334882696038892e-05</v>
+        <v>1.1271001813080713e-05</v>
       </c>
       <c r="R14">
-        <v>1.084945650129914e-05</v>
+        <v>1.0759482293158281e-05</v>
       </c>
       <c r="S14">
-        <v>1.0734141503816105e-05</v>
+        <v>1.0649993287799263e-05</v>
       </c>
       <c r="T14">
-        <v>1.3025283331446349e-07</v>
+        <v>1.2987999733062132e-07</v>
       </c>
       <c r="U14">
-        <v>-5.2716883873425985e-08</v>
+        <v>-5.2601212373663103e-08</v>
       </c>
       <c r="V14">
-        <v>6.0541068925221891e-08</v>
+        <v>5.6160652472939705e-08</v>
       </c>
       <c r="W14">
-        <v>7.7016920278972321e-08</v>
+        <v>9.4829411417871598e-08</v>
       </c>
       <c r="X14">
-        <v>-2.3191385662431578e-05</v>
+        <v>-2.3954351510575792e-05</v>
       </c>
       <c r="Y14">
-        <v>9.7566046105163711e-06</v>
+        <v>1.0266538175491447e-05</v>
       </c>
     </row>
     <row r="15">
@@ -6667,76 +6667,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>-0.0048969764469375433</v>
+        <v>-0.0053858236153253233</v>
       </c>
       <c r="C15">
-        <v>6.1276383870881833e-08</v>
+        <v>6.1025194298369335e-08</v>
       </c>
       <c r="D15">
-        <v>-1.6847509287975427e-06</v>
+        <v>-1.7229465559257723e-06</v>
       </c>
       <c r="E15">
-        <v>1.8897972135137436e-08</v>
+        <v>1.9333394750823933e-08</v>
       </c>
       <c r="F15">
-        <v>2.2974523175395136e-06</v>
+        <v>2.3286671552412344e-06</v>
       </c>
       <c r="G15">
-        <v>2.3179724315835008e-06</v>
+        <v>2.3353047554062051e-06</v>
       </c>
       <c r="H15">
-        <v>-3.7810072888058567e-08</v>
+        <v>-3.8247518384853388e-08</v>
       </c>
       <c r="I15">
-        <v>-2.010986336759991e-08</v>
+        <v>-1.9756728060537573e-08</v>
       </c>
       <c r="J15">
-        <v>-2.4602292046622618e-06</v>
+        <v>-2.4853306939663024e-06</v>
       </c>
       <c r="K15">
-        <v>-8.5038717859722384e-06</v>
+        <v>-8.6803020372593287e-06</v>
       </c>
       <c r="L15">
-        <v>-1.0484730405781603e-05</v>
+        <v>-1.0679105414866754e-05</v>
       </c>
       <c r="M15">
-        <v>-1.0936252240624855e-05</v>
+        <v>-1.1124134926433122e-05</v>
       </c>
       <c r="N15">
-        <v>1.0665525592105547e-05</v>
+        <v>1.0582060935247457e-05</v>
       </c>
       <c r="O15">
-        <v>1.0924164319234877e-05</v>
+        <v>1.083787138639576e-05</v>
       </c>
       <c r="P15">
-        <v>2.0772728256596493e-05</v>
+        <v>2.0659282704076149e-05</v>
       </c>
       <c r="Q15">
-        <v>1.098415706448276e-05</v>
+        <v>1.0883632786198736e-05</v>
       </c>
       <c r="R15">
-        <v>1.2142068628927472e-05</v>
+        <v>1.208934214369541e-05</v>
       </c>
       <c r="S15">
-        <v>1.2423515307059621e-05</v>
+        <v>1.2345416810482609e-05</v>
       </c>
       <c r="T15">
-        <v>-1.0546193135909428e-08</v>
+        <v>-1.2542888066234922e-08</v>
       </c>
       <c r="U15">
-        <v>-4.489354974277207e-10</v>
+        <v>-2.5226644901516321e-10</v>
       </c>
       <c r="V15">
-        <v>3.9596818227467573e-07</v>
+        <v>3.9304273748900155e-07</v>
       </c>
       <c r="W15">
-        <v>-7.2102564324556662e-07</v>
+        <v>-7.6029263166931739e-07</v>
       </c>
       <c r="X15">
-        <v>3.8540245118071877e-05</v>
+        <v>3.9668550861533729e-05</v>
       </c>
       <c r="Y15">
-        <v>-2.9713623869275202e-05</v>
+        <v>-3.0351675639999245e-05</v>
       </c>
     </row>
     <row r="16">
@@ -6744,76 +6744,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.014519476654106456</v>
+        <v>0.014185084558156863</v>
       </c>
       <c r="C16">
-        <v>-3.9080372082962989e-07</v>
+        <v>-3.8608326960992045e-07</v>
       </c>
       <c r="D16">
-        <v>6.4996117400315975e-07</v>
+        <v>7.2656055996105918e-07</v>
       </c>
       <c r="E16">
-        <v>-7.118513568822003e-09</v>
+        <v>-7.9789545272392282e-09</v>
       </c>
       <c r="F16">
-        <v>-9.3083412858741814e-09</v>
+        <v>-8.9670787633987661e-08</v>
       </c>
       <c r="G16">
-        <v>-1.330157009369033e-06</v>
+        <v>-1.455739284230507e-06</v>
       </c>
       <c r="H16">
-        <v>-7.5861303317833193e-09</v>
+        <v>-6.3952851757562133e-09</v>
       </c>
       <c r="I16">
-        <v>9.1743366550895453e-09</v>
+        <v>1.0074088770675369e-08</v>
       </c>
       <c r="J16">
-        <v>1.159232439146969e-06</v>
+        <v>1.2664181213836998e-06</v>
       </c>
       <c r="K16">
-        <v>2.8040376653474367e-06</v>
+        <v>3.1666317932371666e-06</v>
       </c>
       <c r="L16">
-        <v>3.3239401602094616e-06</v>
+        <v>3.7543648000603331e-06</v>
       </c>
       <c r="M16">
-        <v>2.8834708102124759e-06</v>
+        <v>3.3285040425201515e-06</v>
       </c>
       <c r="N16">
-        <v>1.1400605672398986e-05</v>
+        <v>1.1345437508517581e-05</v>
       </c>
       <c r="O16">
-        <v>1.1334882696038892e-05</v>
+        <v>1.1271001813080713e-05</v>
       </c>
       <c r="P16">
-        <v>1.098415706448276e-05</v>
+        <v>1.0883632786198736e-05</v>
       </c>
       <c r="Q16">
-        <v>1.6951521861526585e-05</v>
+        <v>1.6856150343571417e-05</v>
       </c>
       <c r="R16">
-        <v>1.091219010831858e-05</v>
+        <v>1.0797891716623801e-05</v>
       </c>
       <c r="S16">
-        <v>1.0770948807376037e-05</v>
+        <v>1.0654463907218917e-05</v>
       </c>
       <c r="T16">
-        <v>1.1055444961409331e-07</v>
+        <v>1.0548654806824383e-07</v>
       </c>
       <c r="U16">
-        <v>-1.2195734979326113e-07</v>
+        <v>-1.227259308664003e-07</v>
       </c>
       <c r="V16">
-        <v>6.8186842487580836e-07</v>
+        <v>6.6582473839723897e-07</v>
       </c>
       <c r="W16">
-        <v>9.2344366717895829e-07</v>
+        <v>9.5793600015807192e-07</v>
       </c>
       <c r="X16">
-        <v>-1.6506508620669098e-05</v>
+        <v>-1.8571770418101834e-05</v>
       </c>
       <c r="Y16">
-        <v>1.0072949624571831e-05</v>
+        <v>1.1379452088892319e-05</v>
       </c>
     </row>
     <row r="17">
@@ -6821,76 +6821,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>0.0077534181918946362</v>
+        <v>0.0070955289907382591</v>
       </c>
       <c r="C17">
-        <v>-1.422498135683048e-07</v>
+        <v>-1.3943567657905874e-07</v>
       </c>
       <c r="D17">
-        <v>-2.9823135974582155e-06</v>
+        <v>-2.9946641593910616e-06</v>
       </c>
       <c r="E17">
-        <v>3.3364712290748938e-08</v>
+        <v>3.351655658874889e-08</v>
       </c>
       <c r="F17">
-        <v>3.1103810922205245e-06</v>
+        <v>3.1152569640727955e-06</v>
       </c>
       <c r="G17">
-        <v>3.1106497498038197e-06</v>
+        <v>3.0649153366343928e-06</v>
       </c>
       <c r="H17">
-        <v>-4.5723386324652696e-08</v>
+        <v>-4.5839516851015402e-08</v>
       </c>
       <c r="I17">
-        <v>-6.8766190139455755e-09</v>
+        <v>-6.0002379425467037e-09</v>
       </c>
       <c r="J17">
-        <v>-3.9142690101402254e-06</v>
+        <v>-3.8886348389328e-06</v>
       </c>
       <c r="K17">
-        <v>-1.4226247799795768e-05</v>
+        <v>-1.4285871858542221e-05</v>
       </c>
       <c r="L17">
-        <v>-1.7420948205828125e-05</v>
+        <v>-1.7459201745622419e-05</v>
       </c>
       <c r="M17">
-        <v>-1.8552351795101257e-05</v>
+        <v>-1.8570030123922372e-05</v>
       </c>
       <c r="N17">
-        <v>1.0374560138716969e-05</v>
+        <v>1.0297901050509592e-05</v>
       </c>
       <c r="O17">
-        <v>1.084945650129914e-05</v>
+        <v>1.0759482293158281e-05</v>
       </c>
       <c r="P17">
-        <v>1.2142068628927472e-05</v>
+        <v>1.208934214369541e-05</v>
       </c>
       <c r="Q17">
-        <v>1.091219010831858e-05</v>
+        <v>1.0797891716623801e-05</v>
       </c>
       <c r="R17">
-        <v>2.131181826112905e-05</v>
+        <v>2.119081904265316e-05</v>
       </c>
       <c r="S17">
-        <v>1.3398387265432405e-05</v>
+        <v>1.3278670817572928e-05</v>
       </c>
       <c r="T17">
-        <v>-9.4865716912762452e-08</v>
+        <v>-9.6299923420024177e-08</v>
       </c>
       <c r="U17">
-        <v>-1.6808675362616801e-08</v>
+        <v>-1.6868012331158241e-08</v>
       </c>
       <c r="V17">
-        <v>9.4007228602262187e-07</v>
+        <v>9.2098486038787447e-07</v>
       </c>
       <c r="W17">
-        <v>-1.0738758910207293e-06</v>
+        <v>-1.118887840227617e-06</v>
       </c>
       <c r="X17">
-        <v>7.7907037649363172e-05</v>
+        <v>7.8291025191910515e-05</v>
       </c>
       <c r="Y17">
-        <v>-5.1863180440202406e-05</v>
+        <v>-5.2031793683561721e-05</v>
       </c>
     </row>
     <row r="18">
@@ -6898,76 +6898,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.0039516675357244412</v>
+        <v>-0.0046513919171504645</v>
       </c>
       <c r="C18">
-        <v>3.831574188680449e-08</v>
+        <v>3.8573716394313458e-08</v>
       </c>
       <c r="D18">
-        <v>-4.0738935503178311e-06</v>
+        <v>-3.982745131600678e-06</v>
       </c>
       <c r="E18">
-        <v>4.5498903101837152e-08</v>
+        <v>4.4495924518943013e-08</v>
       </c>
       <c r="F18">
-        <v>3.7063988518787839e-06</v>
+        <v>3.5982889772311151e-06</v>
       </c>
       <c r="G18">
-        <v>5.6190447616348639e-06</v>
+        <v>5.3510251537816151e-06</v>
       </c>
       <c r="H18">
-        <v>-4.6432332062957618e-08</v>
+        <v>-4.5019511668339298e-08</v>
       </c>
       <c r="I18">
-        <v>-1.7199568806099296e-08</v>
+        <v>-1.4550934089842533e-08</v>
       </c>
       <c r="J18">
-        <v>-4.9740430826625885e-06</v>
+        <v>-4.7875920425684822e-06</v>
       </c>
       <c r="K18">
-        <v>-1.8938739548977797e-05</v>
+        <v>-1.850849768843195e-05</v>
       </c>
       <c r="L18">
-        <v>-2.2579347144171473e-05</v>
+        <v>-2.2014309702910317e-05</v>
       </c>
       <c r="M18">
-        <v>-2.4202830423442321e-05</v>
+        <v>-2.358920133953951e-05</v>
       </c>
       <c r="N18">
-        <v>1.0071096869765839e-05</v>
+        <v>1.0022396901481907e-05</v>
       </c>
       <c r="O18">
-        <v>1.0734141503816105e-05</v>
+        <v>1.0649993287799263e-05</v>
       </c>
       <c r="P18">
-        <v>1.2423515307059621e-05</v>
+        <v>1.2345416810482609e-05</v>
       </c>
       <c r="Q18">
-        <v>1.0770948807376037e-05</v>
+        <v>1.0654463907218917e-05</v>
       </c>
       <c r="R18">
-        <v>1.3398387265432405e-05</v>
+        <v>1.3278670817572928e-05</v>
       </c>
       <c r="S18">
-        <v>6.0292996480164563e-05</v>
+        <v>5.9776723830122364e-05</v>
       </c>
       <c r="T18">
-        <v>6.3942500874135346e-08</v>
+        <v>5.4360245686735291e-08</v>
       </c>
       <c r="U18">
-        <v>8.1448764664496548e-08</v>
+        <v>7.9687758374587749e-08</v>
       </c>
       <c r="V18">
-        <v>1.2386295702407575e-06</v>
+        <v>1.1864362339082116e-06</v>
       </c>
       <c r="W18">
-        <v>-1.4835219700372946e-06</v>
+        <v>-1.4968737632837275e-06</v>
       </c>
       <c r="X18">
-        <v>9.8258050731745892e-05</v>
+        <v>9.5810941297787118e-05</v>
       </c>
       <c r="Y18">
-        <v>-7.1671545818464792e-05</v>
+        <v>-7.0008776947201763e-05</v>
       </c>
     </row>
     <row r="19">
@@ -6975,76 +6975,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.069043616531642746</v>
+        <v>0.070321543756838356</v>
       </c>
       <c r="C19">
-        <v>-1.3980890365962598e-07</v>
+        <v>-1.3616001575206501e-07</v>
       </c>
       <c r="D19">
-        <v>-1.4884043431229844e-07</v>
+        <v>-1.4916558131902089e-07</v>
       </c>
       <c r="E19">
-        <v>1.7297438270260241e-09</v>
+        <v>1.7209266169577375e-09</v>
       </c>
       <c r="F19">
-        <v>4.0098069644085504e-07</v>
+        <v>3.5299432809711229e-07</v>
       </c>
       <c r="G19">
-        <v>1.3148158607457092e-06</v>
+        <v>1.2574795862726638e-06</v>
       </c>
       <c r="H19">
-        <v>3.6740225890595579e-09</v>
+        <v>4.6211833496374502e-09</v>
       </c>
       <c r="I19">
-        <v>-1.0865355455699018e-09</v>
+        <v>-9.5673130677360808e-11</v>
       </c>
       <c r="J19">
-        <v>-5.4990974310952464e-07</v>
+        <v>-5.2449917965968779e-07</v>
       </c>
       <c r="K19">
-        <v>-1.7434364261560208e-06</v>
+        <v>-1.7110847861158479e-06</v>
       </c>
       <c r="L19">
-        <v>-2.031040103899715e-06</v>
+        <v>-1.9905403501951961e-06</v>
       </c>
       <c r="M19">
-        <v>-2.236052886520916e-06</v>
+        <v>-2.1960887191663948e-06</v>
       </c>
       <c r="N19">
-        <v>5.1364467425380882e-08</v>
+        <v>5.8563787207205364e-08</v>
       </c>
       <c r="O19">
-        <v>1.3025283331446349e-07</v>
+        <v>1.2987999733062132e-07</v>
       </c>
       <c r="P19">
-        <v>-1.0546193135909428e-08</v>
+        <v>-1.2542888066234922e-08</v>
       </c>
       <c r="Q19">
-        <v>1.1055444961409331e-07</v>
+        <v>1.0548654806824383e-07</v>
       </c>
       <c r="R19">
-        <v>-9.4865716912762452e-08</v>
+        <v>-9.6299923420024177e-08</v>
       </c>
       <c r="S19">
-        <v>6.3942500874135346e-08</v>
+        <v>5.4360245686735291e-08</v>
       </c>
       <c r="T19">
-        <v>1.4483927529275792e-05</v>
+        <v>1.4488390624966214e-05</v>
       </c>
       <c r="U19">
-        <v>-2.2549808028429151e-08</v>
+        <v>-2.2769090191931259e-08</v>
       </c>
       <c r="V19">
-        <v>6.2763225757431089e-08</v>
+        <v>5.1080413321941071e-08</v>
       </c>
       <c r="W19">
-        <v>-3.2253755552994855e-07</v>
+        <v>-3.2998471550627043e-07</v>
       </c>
       <c r="X19">
-        <v>6.641151462444159e-06</v>
+        <v>6.6447269065823674e-06</v>
       </c>
       <c r="Y19">
-        <v>-6.6510148861428491e-06</v>
+        <v>-6.5429005069827848e-06</v>
       </c>
     </row>
     <row r="20">
@@ -7052,76 +7052,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>0.0070264445659336721</v>
+        <v>0.0070507810367886718</v>
       </c>
       <c r="C20">
-        <v>1.7995809731197625e-08</v>
+        <v>1.7756957830991322e-08</v>
       </c>
       <c r="D20">
-        <v>-5.9045169121804041e-08</v>
+        <v>-5.9322263142227653e-08</v>
       </c>
       <c r="E20">
-        <v>5.8630657187560685e-10</v>
+        <v>5.8964105650822177e-10</v>
       </c>
       <c r="F20">
-        <v>2.4936636386985689e-07</v>
+        <v>2.4931418402225249e-07</v>
       </c>
       <c r="G20">
-        <v>2.9566211107643744e-07</v>
+        <v>2.932464162576188e-07</v>
       </c>
       <c r="H20">
-        <v>-3.2473049249459306e-09</v>
+        <v>-3.2577914551374159e-09</v>
       </c>
       <c r="I20">
-        <v>-8.8413202586812228e-10</v>
+        <v>-8.6722433636599614e-10</v>
       </c>
       <c r="J20">
-        <v>-8.7998620831458841e-09</v>
+        <v>-7.1393510156707709e-09</v>
       </c>
       <c r="K20">
-        <v>-2.584254374300843e-07</v>
+        <v>-2.5820740980031268e-07</v>
       </c>
       <c r="L20">
-        <v>-2.6388657331497087e-07</v>
+        <v>-2.6312521255255998e-07</v>
       </c>
       <c r="M20">
-        <v>-2.3967346192380434e-07</v>
+        <v>-2.3925477211716713e-07</v>
       </c>
       <c r="N20">
-        <v>2.6668127355950781e-08</v>
+        <v>2.6604309960064068e-08</v>
       </c>
       <c r="O20">
-        <v>-5.2716883873425985e-08</v>
+        <v>-5.2601212373663103e-08</v>
       </c>
       <c r="P20">
-        <v>-4.489354974277207e-10</v>
+        <v>-2.5226644901516321e-10</v>
       </c>
       <c r="Q20">
-        <v>-1.2195734979326113e-07</v>
+        <v>-1.227259308664003e-07</v>
       </c>
       <c r="R20">
-        <v>-1.6808675362616801e-08</v>
+        <v>-1.6868012331158241e-08</v>
       </c>
       <c r="S20">
-        <v>8.1448764664496548e-08</v>
+        <v>7.9687758374587749e-08</v>
       </c>
       <c r="T20">
-        <v>-2.2549808028429151e-08</v>
+        <v>-2.2769090191931259e-08</v>
       </c>
       <c r="U20">
-        <v>6.3872727161321803e-07</v>
+        <v>6.366751717518795e-07</v>
       </c>
       <c r="V20">
-        <v>-2.3138535826157306e-06</v>
+        <v>-2.3070015218310622e-06</v>
       </c>
       <c r="W20">
-        <v>-2.4014350255821309e-06</v>
+        <v>-2.3946495289300862e-06</v>
       </c>
       <c r="X20">
-        <v>-6.2576360770925157e-05</v>
+        <v>-6.2363785817037457e-05</v>
       </c>
       <c r="Y20">
-        <v>-1.1909410549241248e-06</v>
+        <v>-1.1884746138285158e-06</v>
       </c>
     </row>
     <row r="21">
@@ -7129,76 +7129,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.07499136753439678</v>
+        <v>-0.074423829967239355</v>
       </c>
       <c r="C21">
-        <v>3.4055850287699676e-09</v>
+        <v>5.1035991310827435e-09</v>
       </c>
       <c r="D21">
-        <v>-1.452944066437684e-06</v>
+        <v>-1.4179535737706194e-06</v>
       </c>
       <c r="E21">
-        <v>1.6429437300475129e-08</v>
+        <v>1.604853022048258e-08</v>
       </c>
       <c r="F21">
-        <v>1.0631059525672129e-06</v>
+        <v>1.034060772953959e-06</v>
       </c>
       <c r="G21">
-        <v>2.12955715060847e-06</v>
+        <v>2.0490153751788601e-06</v>
       </c>
       <c r="H21">
-        <v>-1.7905531805868269e-08</v>
+        <v>-1.7619596333339717e-08</v>
       </c>
       <c r="I21">
-        <v>-2.1145732159066031e-08</v>
+        <v>-2.0522554097975296e-08</v>
       </c>
       <c r="J21">
-        <v>-2.1678559648716723e-06</v>
+        <v>-2.0758039924247681e-06</v>
       </c>
       <c r="K21">
-        <v>-6.5833724288756769e-06</v>
+        <v>-6.4241339447724978e-06</v>
       </c>
       <c r="L21">
-        <v>-8.4177487108553692e-06</v>
+        <v>-8.2059366754182249e-06</v>
       </c>
       <c r="M21">
-        <v>-8.988114897224455e-06</v>
+        <v>-8.7545917942057211e-06</v>
       </c>
       <c r="N21">
-        <v>-4.1325835706299723e-07</v>
+        <v>-4.0764343993739495e-07</v>
       </c>
       <c r="O21">
-        <v>6.0541068925221891e-08</v>
+        <v>5.6160652472939705e-08</v>
       </c>
       <c r="P21">
-        <v>3.9596818227467573e-07</v>
+        <v>3.9304273748900155e-07</v>
       </c>
       <c r="Q21">
-        <v>6.8186842487580836e-07</v>
+        <v>6.6582473839723897e-07</v>
       </c>
       <c r="R21">
-        <v>9.4007228602262187e-07</v>
+        <v>9.2098486038787447e-07</v>
       </c>
       <c r="S21">
-        <v>1.2386295702407575e-06</v>
+        <v>1.1864362339082116e-06</v>
       </c>
       <c r="T21">
-        <v>6.2763225757431089e-08</v>
+        <v>5.1080413321941071e-08</v>
       </c>
       <c r="U21">
-        <v>-2.3138535826157306e-06</v>
+        <v>-2.3070015218310622e-06</v>
       </c>
       <c r="V21">
-        <v>3.5185495089717083e-05</v>
+        <v>3.4978780575581734e-05</v>
       </c>
       <c r="W21">
-        <v>9.7125149795642154e-06</v>
+        <v>9.6716028422096549e-06</v>
       </c>
       <c r="X21">
-        <v>0.00027308343086591443</v>
+        <v>0.00027136363104951911</v>
       </c>
       <c r="Y21">
-        <v>-2.4332457282517719e-05</v>
+        <v>-2.3721423204220327e-05</v>
       </c>
     </row>
     <row r="22">
@@ -7206,76 +7206,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>0.02559804532032502</v>
+        <v>0.025049621975596997</v>
       </c>
       <c r="C22">
-        <v>2.873535427769429e-07</v>
+        <v>2.8507987742309056e-07</v>
       </c>
       <c r="D22">
-        <v>2.1899198775295396e-06</v>
+        <v>2.2710943231992687e-06</v>
       </c>
       <c r="E22">
-        <v>-2.4375005538066314e-08</v>
+        <v>-2.5291826489466105e-08</v>
       </c>
       <c r="F22">
-        <v>-2.8934685905956172e-06</v>
+        <v>-2.9696244576241511e-06</v>
       </c>
       <c r="G22">
-        <v>-4.1967795708656656e-06</v>
+        <v>-4.2763502427032355e-06</v>
       </c>
       <c r="H22">
-        <v>4.2667883946027046e-08</v>
+        <v>4.3787616223116093e-08</v>
       </c>
       <c r="I22">
-        <v>2.7448085571362176e-08</v>
+        <v>2.7595347401232782e-08</v>
       </c>
       <c r="J22">
-        <v>3.010978595897957e-06</v>
+        <v>3.0880766929247896e-06</v>
       </c>
       <c r="K22">
-        <v>1.0329262700234433e-05</v>
+        <v>1.0701347380193287e-05</v>
       </c>
       <c r="L22">
-        <v>1.2496710816861038e-05</v>
+        <v>1.2921121850759924e-05</v>
       </c>
       <c r="M22">
-        <v>1.2692324832023408e-05</v>
+        <v>1.3121135840477063e-05</v>
       </c>
       <c r="N22">
-        <v>4.014699990072e-07</v>
+        <v>4.1828663820254353e-07</v>
       </c>
       <c r="O22">
-        <v>7.7016920278972321e-08</v>
+        <v>9.4829411417871598e-08</v>
       </c>
       <c r="P22">
-        <v>-7.2102564324556662e-07</v>
+        <v>-7.6029263166931739e-07</v>
       </c>
       <c r="Q22">
-        <v>9.2344366717895829e-07</v>
+        <v>9.5793600015807192e-07</v>
       </c>
       <c r="R22">
-        <v>-1.0738758910207293e-06</v>
+        <v>-1.118887840227617e-06</v>
       </c>
       <c r="S22">
-        <v>-1.4835219700372946e-06</v>
+        <v>-1.4968737632837275e-06</v>
       </c>
       <c r="T22">
-        <v>-3.2253755552994855e-07</v>
+        <v>-3.2998471550627043e-07</v>
       </c>
       <c r="U22">
-        <v>-2.4014350255821309e-06</v>
+        <v>-2.3946495289300862e-06</v>
       </c>
       <c r="V22">
-        <v>9.7125149795642154e-06</v>
+        <v>9.6716028422096549e-06</v>
       </c>
       <c r="W22">
-        <v>3.59430484649174e-05</v>
+        <v>3.5785424758318928e-05</v>
       </c>
       <c r="X22">
-        <v>0.00017561015272217327</v>
+        <v>0.00017264643445611484</v>
       </c>
       <c r="Y22">
-        <v>4.0335248818838959e-05</v>
+        <v>4.1651615983933347e-05</v>
       </c>
     </row>
     <row r="23">
@@ -7283,76 +7283,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>-0.25715976351179865</v>
+        <v>-0.26452451931773391</v>
       </c>
       <c r="C23">
-        <v>-1.0213282233439339e-05</v>
+        <v>-1.0197283313057048e-05</v>
       </c>
       <c r="D23">
-        <v>-0.00017668152883912151</v>
+        <v>-0.00017703334712202291</v>
       </c>
       <c r="E23">
-        <v>1.9668894929256238e-06</v>
+        <v>1.9716172634088894e-06</v>
       </c>
       <c r="F23">
-        <v>8.0744572336243663e-05</v>
+        <v>8.0645816439924495e-05</v>
       </c>
       <c r="G23">
-        <v>0.00018616673067599869</v>
+        <v>0.0001835639333458929</v>
       </c>
       <c r="H23">
-        <v>-7.0436012023153355e-07</v>
+        <v>-7.0655734668493626e-07</v>
       </c>
       <c r="I23">
-        <v>-5.1289073447274079e-07</v>
+        <v>-4.727051714262155e-07</v>
       </c>
       <c r="J23">
-        <v>-0.00074523114350746617</v>
+        <v>-0.00074109057269741187</v>
       </c>
       <c r="K23">
-        <v>-0.0012597000370176302</v>
+        <v>-0.0012593773847295185</v>
       </c>
       <c r="L23">
-        <v>-0.0014246005271922877</v>
+        <v>-0.0014228667256926284</v>
       </c>
       <c r="M23">
-        <v>-0.0014689048567187229</v>
+        <v>-0.0014660988908250169</v>
       </c>
       <c r="N23">
-        <v>-5.6539326209574275e-05</v>
+        <v>-5.6518821285302194e-05</v>
       </c>
       <c r="O23">
-        <v>-2.3191385662431578e-05</v>
+        <v>-2.3954351510575792e-05</v>
       </c>
       <c r="P23">
-        <v>3.8540245118071877e-05</v>
+        <v>3.9668550861533729e-05</v>
       </c>
       <c r="Q23">
-        <v>-1.6506508620669098e-05</v>
+        <v>-1.8571770418101834e-05</v>
       </c>
       <c r="R23">
-        <v>7.7907037649363172e-05</v>
+        <v>7.8291025191910515e-05</v>
       </c>
       <c r="S23">
-        <v>9.8258050731745892e-05</v>
+        <v>9.5810941297787118e-05</v>
       </c>
       <c r="T23">
-        <v>6.641151462444159e-06</v>
+        <v>6.6447269065823674e-06</v>
       </c>
       <c r="U23">
-        <v>-6.2576360770925157e-05</v>
+        <v>-6.2363785817037457e-05</v>
       </c>
       <c r="V23">
-        <v>0.00027308343086591443</v>
+        <v>0.00027136363104951911</v>
       </c>
       <c r="W23">
-        <v>0.00017561015272217327</v>
+        <v>0.00017264643445611484</v>
       </c>
       <c r="X23">
-        <v>0.011856810853525031</v>
+        <v>0.011841098322798808</v>
       </c>
       <c r="Y23">
-        <v>-0.0027485701253922314</v>
+        <v>-0.0027535894636796336</v>
       </c>
     </row>
     <row r="24">
@@ -7360,76 +7360,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-0.17798602943342903</v>
+        <v>-0.17293257027377587</v>
       </c>
       <c r="C24">
-        <v>3.305903920989959e-06</v>
+        <v>3.3161199978792739e-06</v>
       </c>
       <c r="D24">
-        <v>9.8922400228267234e-05</v>
+        <v>9.9138062489961595e-05</v>
       </c>
       <c r="E24">
-        <v>-1.1072361420490673e-06</v>
+        <v>-1.1100836137402527e-06</v>
       </c>
       <c r="F24">
-        <v>-0.00011561373723827647</v>
+        <v>-0.00011514442612879788</v>
       </c>
       <c r="G24">
-        <v>-0.00017212153293463017</v>
+        <v>-0.00017005070667945835</v>
       </c>
       <c r="H24">
-        <v>1.6868593373019716e-06</v>
+        <v>1.6808773836413849e-06</v>
       </c>
       <c r="I24">
-        <v>1.192513436268208e-06</v>
+        <v>1.1616178523498549e-06</v>
       </c>
       <c r="J24">
-        <v>0.000141595968505922</v>
+        <v>0.00014047524971138209</v>
       </c>
       <c r="K24">
-        <v>0.00046583080152770096</v>
+        <v>0.00046685688466352557</v>
       </c>
       <c r="L24">
-        <v>0.00056448322647335619</v>
+        <v>0.0005645798539305638</v>
       </c>
       <c r="M24">
-        <v>0.00058550601628740693</v>
+        <v>0.00058498233402656883</v>
       </c>
       <c r="N24">
-        <v>2.5469938952961809e-05</v>
+        <v>2.5502264548919633e-05</v>
       </c>
       <c r="O24">
-        <v>9.7566046105163711e-06</v>
+        <v>1.0266538175491447e-05</v>
       </c>
       <c r="P24">
-        <v>-2.9713623869275202e-05</v>
+        <v>-3.0351675639999245e-05</v>
       </c>
       <c r="Q24">
-        <v>1.0072949624571831e-05</v>
+        <v>1.1379452088892319e-05</v>
       </c>
       <c r="R24">
-        <v>-5.1863180440202406e-05</v>
+        <v>-5.2031793683561721e-05</v>
       </c>
       <c r="S24">
-        <v>-7.1671545818464792e-05</v>
+        <v>-7.0008776947201763e-05</v>
       </c>
       <c r="T24">
-        <v>-6.6510148861428491e-06</v>
+        <v>-6.5429005069827848e-06</v>
       </c>
       <c r="U24">
-        <v>-1.1909410549241248e-06</v>
+        <v>-1.1884746138285158e-06</v>
       </c>
       <c r="V24">
-        <v>-2.4332457282517719e-05</v>
+        <v>-2.3721423204220327e-05</v>
       </c>
       <c r="W24">
-        <v>4.0335248818838959e-05</v>
+        <v>4.1651615983933347e-05</v>
       </c>
       <c r="X24">
-        <v>-0.0027485701253922314</v>
+        <v>-0.0027535894636796336</v>
       </c>
       <c r="Y24">
-        <v>0.0017127046824877848</v>
+        <v>0.0017146511604589345</v>
       </c>
     </row>
   </sheetData>
